--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="283">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -861,6 +861,9 @@
   <si>
     <t>['22', '59']</t>
   </si>
+  <si>
+    <t>['5', '56']</t>
+  </si>
 </sst>
 </file>
 
@@ -1221,7 +1224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP172"/>
+  <dimension ref="A1:BP173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4851,7 +4854,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AQ18">
         <v>2.44</v>
@@ -5060,7 +5063,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ19">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -7735,7 +7738,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -8562,7 +8565,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ36">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR36">
         <v>1.59</v>
@@ -11652,7 +11655,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ51">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR51">
         <v>1.08</v>
@@ -12473,7 +12476,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AQ55">
         <v>1.56</v>
@@ -14536,7 +14539,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ65">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -16799,7 +16802,7 @@
         <v>0.75</v>
       </c>
       <c r="AP76">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AQ76">
         <v>0.7</v>
@@ -18862,7 +18865,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ86">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR86">
         <v>1.12</v>
@@ -20713,7 +20716,7 @@
         <v>0</v>
       </c>
       <c r="AP95">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AQ95">
         <v>0.7</v>
@@ -22570,7 +22573,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ104">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR104">
         <v>1</v>
@@ -24833,7 +24836,7 @@
         <v>0.33</v>
       </c>
       <c r="AP115">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AQ115">
         <v>0.8</v>
@@ -26690,7 +26693,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ124">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR124">
         <v>1.55</v>
@@ -27923,7 +27926,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AQ130">
         <v>0.5600000000000001</v>
@@ -31837,7 +31840,7 @@
         <v>0.5</v>
       </c>
       <c r="AP149">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AQ149">
         <v>0.8</v>
@@ -32252,7 +32255,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ151">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR151">
         <v>1.25</v>
@@ -33076,7 +33079,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ155">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR155">
         <v>2.01</v>
@@ -34721,7 +34724,7 @@
         <v>1.38</v>
       </c>
       <c r="AP163">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AQ163">
         <v>1.56</v>
@@ -36654,6 +36657,212 @@
       </c>
       <c r="BP172">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7574735</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45688.71875</v>
+      </c>
+      <c r="F173">
+        <v>20</v>
+      </c>
+      <c r="G173" t="s">
+        <v>86</v>
+      </c>
+      <c r="H173" t="s">
+        <v>75</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>1</v>
+      </c>
+      <c r="K173">
+        <v>1</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+      <c r="M173">
+        <v>2</v>
+      </c>
+      <c r="N173">
+        <v>2</v>
+      </c>
+      <c r="O173" t="s">
+        <v>90</v>
+      </c>
+      <c r="P173" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q173">
+        <v>4.2</v>
+      </c>
+      <c r="R173">
+        <v>1.96</v>
+      </c>
+      <c r="S173">
+        <v>2.9</v>
+      </c>
+      <c r="T173">
+        <v>1.5</v>
+      </c>
+      <c r="U173">
+        <v>2.41</v>
+      </c>
+      <c r="V173">
+        <v>3.4</v>
+      </c>
+      <c r="W173">
+        <v>1.27</v>
+      </c>
+      <c r="X173">
+        <v>9.5</v>
+      </c>
+      <c r="Y173">
+        <v>1.02</v>
+      </c>
+      <c r="Z173">
+        <v>3.42</v>
+      </c>
+      <c r="AA173">
+        <v>3.14</v>
+      </c>
+      <c r="AB173">
+        <v>2.26</v>
+      </c>
+      <c r="AC173">
+        <v>1.04</v>
+      </c>
+      <c r="AD173">
+        <v>7.1</v>
+      </c>
+      <c r="AE173">
+        <v>1.42</v>
+      </c>
+      <c r="AF173">
+        <v>2.56</v>
+      </c>
+      <c r="AG173">
+        <v>2.4</v>
+      </c>
+      <c r="AH173">
+        <v>1.55</v>
+      </c>
+      <c r="AI173">
+        <v>2.02</v>
+      </c>
+      <c r="AJ173">
+        <v>1.71</v>
+      </c>
+      <c r="AK173">
+        <v>1.66</v>
+      </c>
+      <c r="AL173">
+        <v>1.35</v>
+      </c>
+      <c r="AM173">
+        <v>1.32</v>
+      </c>
+      <c r="AN173">
+        <v>0.33</v>
+      </c>
+      <c r="AO173">
+        <v>1.11</v>
+      </c>
+      <c r="AP173">
+        <v>0.3</v>
+      </c>
+      <c r="AQ173">
+        <v>1.3</v>
+      </c>
+      <c r="AR173">
+        <v>1.33</v>
+      </c>
+      <c r="AS173">
+        <v>1.21</v>
+      </c>
+      <c r="AT173">
+        <v>2.54</v>
+      </c>
+      <c r="AU173">
+        <v>2</v>
+      </c>
+      <c r="AV173">
+        <v>6</v>
+      </c>
+      <c r="AW173">
+        <v>4</v>
+      </c>
+      <c r="AX173">
+        <v>15</v>
+      </c>
+      <c r="AY173">
+        <v>7</v>
+      </c>
+      <c r="AZ173">
+        <v>28</v>
+      </c>
+      <c r="BA173">
+        <v>2</v>
+      </c>
+      <c r="BB173">
+        <v>7</v>
+      </c>
+      <c r="BC173">
+        <v>9</v>
+      </c>
+      <c r="BD173">
+        <v>2.05</v>
+      </c>
+      <c r="BE173">
+        <v>8</v>
+      </c>
+      <c r="BF173">
+        <v>2.05</v>
+      </c>
+      <c r="BG173">
+        <v>1.29</v>
+      </c>
+      <c r="BH173">
+        <v>3.35</v>
+      </c>
+      <c r="BI173">
+        <v>1.53</v>
+      </c>
+      <c r="BJ173">
+        <v>2.41</v>
+      </c>
+      <c r="BK173">
+        <v>1.91</v>
+      </c>
+      <c r="BL173">
+        <v>1.8</v>
+      </c>
+      <c r="BM173">
+        <v>2.38</v>
+      </c>
+      <c r="BN173">
+        <v>1.54</v>
+      </c>
+      <c r="BO173">
+        <v>3.2</v>
+      </c>
+      <c r="BP173">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="287">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -619,6 +619,15 @@
     <t>['14', '33', '69']</t>
   </si>
   <si>
+    <t>['48', '57']</t>
+  </si>
+  <si>
+    <t>['45+1']</t>
+  </si>
+  <si>
+    <t>['55', '78']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -692,9 +701,6 @@
   </si>
   <si>
     <t>['85']</t>
-  </si>
-  <si>
-    <t>['45+1']</t>
   </si>
   <si>
     <t>['11', '31', '90+1']</t>
@@ -863,6 +869,12 @@
   </si>
   <si>
     <t>['5', '56']</t>
+  </si>
+  <si>
+    <t>['5', '26']</t>
+  </si>
+  <si>
+    <t>['45+4', '84']</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP173"/>
+  <dimension ref="A1:BP177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1686,7 +1698,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2304,7 +2316,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2716,7 +2728,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -3334,7 +3346,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3412,7 +3424,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
         <v>1.44</v>
@@ -3540,7 +3552,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3618,10 +3630,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ12">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3952,7 +3964,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4030,7 +4042,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ14">
         <v>2.3</v>
@@ -4239,7 +4251,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ15">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4364,7 +4376,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4445,7 +4457,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ16">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4648,10 +4660,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4776,7 +4788,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4982,7 +4994,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5188,7 +5200,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5394,7 +5406,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -7042,7 +7054,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7248,7 +7260,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7326,10 +7338,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR30">
         <v>0.55</v>
@@ -7454,7 +7466,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -7535,7 +7547,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ31">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR31">
         <v>1</v>
@@ -7741,7 +7753,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR32">
         <v>0.64</v>
@@ -8150,7 +8162,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ34">
         <v>0.8</v>
@@ -8359,7 +8371,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ35">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR35">
         <v>1.11</v>
@@ -8484,7 +8496,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q36">
         <v>2.55</v>
@@ -8562,7 +8574,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ36">
         <v>1.3</v>
@@ -8768,7 +8780,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ37">
         <v>2.44</v>
@@ -8896,7 +8908,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9102,7 +9114,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9514,7 +9526,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9720,7 +9732,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -9926,7 +9938,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10338,7 +10350,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10544,7 +10556,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10750,7 +10762,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10828,7 +10840,7 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ47">
         <v>2.44</v>
@@ -10956,7 +10968,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11037,7 +11049,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR48">
         <v>1.23</v>
@@ -11240,7 +11252,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ49">
         <v>0.33</v>
@@ -11368,7 +11380,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11446,7 +11458,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ50">
         <v>1.44</v>
@@ -11780,7 +11792,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -11858,10 +11870,10 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ52">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR52">
         <v>1.51</v>
@@ -11986,7 +11998,7 @@
         <v>90</v>
       </c>
       <c r="P53" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12067,7 +12079,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ53">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR53">
         <v>1</v>
@@ -12273,7 +12285,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ54">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR54">
         <v>1.92</v>
@@ -12398,7 +12410,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12604,7 +12616,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -13016,7 +13028,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13222,7 +13234,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -13715,7 +13727,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ61">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR61">
         <v>2.38</v>
@@ -14124,7 +14136,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ63">
         <v>0.9</v>
@@ -14742,7 +14754,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ66">
         <v>0.33</v>
@@ -15157,7 +15169,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ68">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR68">
         <v>0.83</v>
@@ -15363,7 +15375,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ69">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR69">
         <v>2.1</v>
@@ -15569,7 +15581,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR70">
         <v>1.2</v>
@@ -15694,7 +15706,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -15772,7 +15784,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ71">
         <v>0.9</v>
@@ -15900,7 +15912,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16312,7 +16324,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16390,7 +16402,7 @@
         <v>0.5</v>
       </c>
       <c r="AP74">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ74">
         <v>0.6</v>
@@ -16518,7 +16530,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16599,7 +16611,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ75">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR75">
         <v>0.89</v>
@@ -16724,7 +16736,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16930,7 +16942,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17548,7 +17560,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17754,7 +17766,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -17960,7 +17972,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18166,7 +18178,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18247,7 +18259,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ83">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR83">
         <v>1.47</v>
@@ -18372,7 +18384,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18578,7 +18590,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18656,7 +18668,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ85">
         <v>0.9</v>
@@ -18784,7 +18796,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19068,7 +19080,7 @@
         <v>1.2</v>
       </c>
       <c r="AP87">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ87">
         <v>0.7</v>
@@ -19196,7 +19208,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19483,7 +19495,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ89">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR89">
         <v>2.03</v>
@@ -19686,7 +19698,7 @@
         <v>1.5</v>
       </c>
       <c r="AP90">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ90">
         <v>1.44</v>
@@ -19814,7 +19826,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -20020,7 +20032,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20307,7 +20319,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ93">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR93">
         <v>0.99</v>
@@ -20513,7 +20525,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ94">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR94">
         <v>1.13</v>
@@ -20638,7 +20650,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -21128,7 +21140,7 @@
         <v>1.6</v>
       </c>
       <c r="AP97">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ97">
         <v>1</v>
@@ -21256,7 +21268,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21874,7 +21886,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22158,7 +22170,7 @@
         <v>1.33</v>
       </c>
       <c r="AP102">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ102">
         <v>0.9</v>
@@ -22286,7 +22298,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22492,7 +22504,7 @@
         <v>154</v>
       </c>
       <c r="P104" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22698,7 +22710,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -22904,7 +22916,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q106">
         <v>5.5</v>
@@ -23188,7 +23200,7 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ107">
         <v>0.6</v>
@@ -23397,7 +23409,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ108">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR108">
         <v>2.03</v>
@@ -23728,7 +23740,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -23809,7 +23821,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ110">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR110">
         <v>1.54</v>
@@ -23934,7 +23946,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q111">
         <v>2.75</v>
@@ -24012,7 +24024,7 @@
         <v>0.33</v>
       </c>
       <c r="AP111">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ111">
         <v>0.3</v>
@@ -24424,7 +24436,7 @@
         <v>0.5</v>
       </c>
       <c r="AP113">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ113">
         <v>0.7</v>
@@ -25045,7 +25057,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ116">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR116">
         <v>1.23</v>
@@ -25170,7 +25182,7 @@
         <v>163</v>
       </c>
       <c r="P117" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q117">
         <v>3.25</v>
@@ -25251,7 +25263,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ117">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR117">
         <v>1.23</v>
@@ -25660,7 +25672,7 @@
         <v>0.86</v>
       </c>
       <c r="AP119">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ119">
         <v>0.7</v>
@@ -25788,7 +25800,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26200,7 +26212,7 @@
         <v>167</v>
       </c>
       <c r="P122" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q122">
         <v>11</v>
@@ -26406,7 +26418,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26487,7 +26499,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ123">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR123">
         <v>1.04</v>
@@ -26612,7 +26624,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -27024,7 +27036,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27230,7 +27242,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27308,7 +27320,7 @@
         <v>1.83</v>
       </c>
       <c r="AP127">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ127">
         <v>1.56</v>
@@ -27436,7 +27448,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27517,7 +27529,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ128">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR128">
         <v>1.24</v>
@@ -27642,7 +27654,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27929,7 +27941,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ130">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR130">
         <v>1.33</v>
@@ -28054,7 +28066,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28260,7 +28272,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28338,7 +28350,7 @@
         <v>2.17</v>
       </c>
       <c r="AP132">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ132">
         <v>2.44</v>
@@ -28544,7 +28556,7 @@
         <v>2.57</v>
       </c>
       <c r="AP133">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ133">
         <v>2.3</v>
@@ -28672,7 +28684,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -28750,7 +28762,7 @@
         <v>0.29</v>
       </c>
       <c r="AP134">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ134">
         <v>0.3</v>
@@ -28959,7 +28971,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ135">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR135">
         <v>2.03</v>
@@ -29496,7 +29508,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29702,7 +29714,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -30114,7 +30126,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30320,7 +30332,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30526,7 +30538,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -30607,7 +30619,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ143">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR143">
         <v>1.64</v>
@@ -30938,7 +30950,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31144,7 +31156,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31222,7 +31234,7 @@
         <v>2.38</v>
       </c>
       <c r="AP146">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ146">
         <v>2.3</v>
@@ -31350,7 +31362,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q147">
         <v>2.55</v>
@@ -31431,7 +31443,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ147">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR147">
         <v>1.11</v>
@@ -31556,7 +31568,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31762,7 +31774,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -31843,7 +31855,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ149">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR149">
         <v>1.35</v>
@@ -32046,7 +32058,7 @@
         <v>0.75</v>
       </c>
       <c r="AP150">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ150">
         <v>0.8</v>
@@ -32174,7 +32186,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32380,7 +32392,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32461,7 +32473,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ152">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR152">
         <v>1.17</v>
@@ -32586,7 +32598,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -32664,7 +32676,7 @@
         <v>0.38</v>
       </c>
       <c r="AP153">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ153">
         <v>0.7</v>
@@ -32870,7 +32882,7 @@
         <v>1.86</v>
       </c>
       <c r="AP154">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ154">
         <v>1.44</v>
@@ -33204,7 +33216,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33282,10 +33294,10 @@
         <v>0.75</v>
       </c>
       <c r="AP156">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ156">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR156">
         <v>1.41</v>
@@ -33410,7 +33422,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33616,7 +33628,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33694,10 +33706,10 @@
         <v>0.78</v>
       </c>
       <c r="AP158">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ158">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR158">
         <v>1.33</v>
@@ -33822,7 +33834,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -33900,10 +33912,10 @@
         <v>0.63</v>
       </c>
       <c r="AP159">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ159">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR159">
         <v>1.19</v>
@@ -34234,7 +34246,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34440,7 +34452,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34518,7 +34530,7 @@
         <v>1.63</v>
       </c>
       <c r="AP162">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ162">
         <v>1.44</v>
@@ -34646,7 +34658,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -34727,7 +34739,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ163">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR163">
         <v>1.32</v>
@@ -35058,7 +35070,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -36088,7 +36100,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36706,7 +36718,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -36863,6 +36875,830 @@
       </c>
       <c r="BP173">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7574736</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45689.52083333334</v>
+      </c>
+      <c r="F174">
+        <v>20</v>
+      </c>
+      <c r="G174" t="s">
+        <v>79</v>
+      </c>
+      <c r="H174" t="s">
+        <v>72</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
+        <v>1</v>
+      </c>
+      <c r="K174">
+        <v>1</v>
+      </c>
+      <c r="L174">
+        <v>2</v>
+      </c>
+      <c r="M174">
+        <v>1</v>
+      </c>
+      <c r="N174">
+        <v>3</v>
+      </c>
+      <c r="O174" t="s">
+        <v>201</v>
+      </c>
+      <c r="P174" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q174">
+        <v>2.75</v>
+      </c>
+      <c r="R174">
+        <v>1.93</v>
+      </c>
+      <c r="S174">
+        <v>4.2</v>
+      </c>
+      <c r="T174">
+        <v>1.52</v>
+      </c>
+      <c r="U174">
+        <v>2.35</v>
+      </c>
+      <c r="V174">
+        <v>3.5</v>
+      </c>
+      <c r="W174">
+        <v>1.26</v>
+      </c>
+      <c r="X174">
+        <v>10</v>
+      </c>
+      <c r="Y174">
+        <v>1.04</v>
+      </c>
+      <c r="Z174">
+        <v>2.1</v>
+      </c>
+      <c r="AA174">
+        <v>2.9</v>
+      </c>
+      <c r="AB174">
+        <v>3.8</v>
+      </c>
+      <c r="AC174">
+        <v>1.1</v>
+      </c>
+      <c r="AD174">
+        <v>6.5</v>
+      </c>
+      <c r="AE174">
+        <v>1.55</v>
+      </c>
+      <c r="AF174">
+        <v>2.3</v>
+      </c>
+      <c r="AG174">
+        <v>2.45</v>
+      </c>
+      <c r="AH174">
+        <v>1.5</v>
+      </c>
+      <c r="AI174">
+        <v>2.15</v>
+      </c>
+      <c r="AJ174">
+        <v>1.61</v>
+      </c>
+      <c r="AK174">
+        <v>1.27</v>
+      </c>
+      <c r="AL174">
+        <v>1.33</v>
+      </c>
+      <c r="AM174">
+        <v>1.71</v>
+      </c>
+      <c r="AN174">
+        <v>1.9</v>
+      </c>
+      <c r="AO174">
+        <v>1.56</v>
+      </c>
+      <c r="AP174">
+        <v>2</v>
+      </c>
+      <c r="AQ174">
+        <v>1.4</v>
+      </c>
+      <c r="AR174">
+        <v>1.43</v>
+      </c>
+      <c r="AS174">
+        <v>1.09</v>
+      </c>
+      <c r="AT174">
+        <v>2.52</v>
+      </c>
+      <c r="AU174">
+        <v>6</v>
+      </c>
+      <c r="AV174">
+        <v>2</v>
+      </c>
+      <c r="AW174">
+        <v>11</v>
+      </c>
+      <c r="AX174">
+        <v>4</v>
+      </c>
+      <c r="AY174">
+        <v>21</v>
+      </c>
+      <c r="AZ174">
+        <v>8</v>
+      </c>
+      <c r="BA174">
+        <v>5</v>
+      </c>
+      <c r="BB174">
+        <v>2</v>
+      </c>
+      <c r="BC174">
+        <v>7</v>
+      </c>
+      <c r="BD174">
+        <v>1.58</v>
+      </c>
+      <c r="BE174">
+        <v>6.75</v>
+      </c>
+      <c r="BF174">
+        <v>2.65</v>
+      </c>
+      <c r="BG174">
+        <v>1.42</v>
+      </c>
+      <c r="BH174">
+        <v>2.55</v>
+      </c>
+      <c r="BI174">
+        <v>1.71</v>
+      </c>
+      <c r="BJ174">
+        <v>1.97</v>
+      </c>
+      <c r="BK174">
+        <v>1.95</v>
+      </c>
+      <c r="BL174">
+        <v>1.77</v>
+      </c>
+      <c r="BM174">
+        <v>2.75</v>
+      </c>
+      <c r="BN174">
+        <v>1.37</v>
+      </c>
+      <c r="BO174">
+        <v>3.65</v>
+      </c>
+      <c r="BP174">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7574742</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45689.52083333334</v>
+      </c>
+      <c r="F175">
+        <v>20</v>
+      </c>
+      <c r="G175" t="s">
+        <v>82</v>
+      </c>
+      <c r="H175" t="s">
+        <v>78</v>
+      </c>
+      <c r="I175">
+        <v>1</v>
+      </c>
+      <c r="J175">
+        <v>2</v>
+      </c>
+      <c r="K175">
+        <v>3</v>
+      </c>
+      <c r="L175">
+        <v>1</v>
+      </c>
+      <c r="M175">
+        <v>2</v>
+      </c>
+      <c r="N175">
+        <v>3</v>
+      </c>
+      <c r="O175" t="s">
+        <v>202</v>
+      </c>
+      <c r="P175" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q175">
+        <v>3.1</v>
+      </c>
+      <c r="R175">
+        <v>2</v>
+      </c>
+      <c r="S175">
+        <v>3.4</v>
+      </c>
+      <c r="T175">
+        <v>1.44</v>
+      </c>
+      <c r="U175">
+        <v>2.55</v>
+      </c>
+      <c r="V175">
+        <v>3</v>
+      </c>
+      <c r="W175">
+        <v>1.33</v>
+      </c>
+      <c r="X175">
+        <v>8</v>
+      </c>
+      <c r="Y175">
+        <v>1.06</v>
+      </c>
+      <c r="Z175">
+        <v>2.5</v>
+      </c>
+      <c r="AA175">
+        <v>3.1</v>
+      </c>
+      <c r="AB175">
+        <v>2.8</v>
+      </c>
+      <c r="AC175">
+        <v>1.07</v>
+      </c>
+      <c r="AD175">
+        <v>8</v>
+      </c>
+      <c r="AE175">
+        <v>1.38</v>
+      </c>
+      <c r="AF175">
+        <v>3</v>
+      </c>
+      <c r="AG175">
+        <v>1.02</v>
+      </c>
+      <c r="AH175">
+        <v>1.67</v>
+      </c>
+      <c r="AI175">
+        <v>1.85</v>
+      </c>
+      <c r="AJ175">
+        <v>1.82</v>
+      </c>
+      <c r="AK175">
+        <v>1.41</v>
+      </c>
+      <c r="AL175">
+        <v>1.33</v>
+      </c>
+      <c r="AM175">
+        <v>1.51</v>
+      </c>
+      <c r="AN175">
+        <v>1.78</v>
+      </c>
+      <c r="AO175">
+        <v>0.8</v>
+      </c>
+      <c r="AP175">
+        <v>1.6</v>
+      </c>
+      <c r="AQ175">
+        <v>1</v>
+      </c>
+      <c r="AR175">
+        <v>1.25</v>
+      </c>
+      <c r="AS175">
+        <v>1.19</v>
+      </c>
+      <c r="AT175">
+        <v>2.44</v>
+      </c>
+      <c r="AU175">
+        <v>7</v>
+      </c>
+      <c r="AV175">
+        <v>7</v>
+      </c>
+      <c r="AW175">
+        <v>14</v>
+      </c>
+      <c r="AX175">
+        <v>4</v>
+      </c>
+      <c r="AY175">
+        <v>23</v>
+      </c>
+      <c r="AZ175">
+        <v>14</v>
+      </c>
+      <c r="BA175">
+        <v>3</v>
+      </c>
+      <c r="BB175">
+        <v>3</v>
+      </c>
+      <c r="BC175">
+        <v>6</v>
+      </c>
+      <c r="BD175">
+        <v>1.97</v>
+      </c>
+      <c r="BE175">
+        <v>6.5</v>
+      </c>
+      <c r="BF175">
+        <v>2</v>
+      </c>
+      <c r="BG175">
+        <v>1.27</v>
+      </c>
+      <c r="BH175">
+        <v>3.3</v>
+      </c>
+      <c r="BI175">
+        <v>1.45</v>
+      </c>
+      <c r="BJ175">
+        <v>2.45</v>
+      </c>
+      <c r="BK175">
+        <v>1.7</v>
+      </c>
+      <c r="BL175">
+        <v>2.05</v>
+      </c>
+      <c r="BM175">
+        <v>2.15</v>
+      </c>
+      <c r="BN175">
+        <v>1.58</v>
+      </c>
+      <c r="BO175">
+        <v>2.75</v>
+      </c>
+      <c r="BP175">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7574738</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45689.625</v>
+      </c>
+      <c r="F176">
+        <v>20</v>
+      </c>
+      <c r="G176" t="s">
+        <v>80</v>
+      </c>
+      <c r="H176" t="s">
+        <v>74</v>
+      </c>
+      <c r="I176">
+        <v>1</v>
+      </c>
+      <c r="J176">
+        <v>1</v>
+      </c>
+      <c r="K176">
+        <v>2</v>
+      </c>
+      <c r="L176">
+        <v>1</v>
+      </c>
+      <c r="M176">
+        <v>2</v>
+      </c>
+      <c r="N176">
+        <v>3</v>
+      </c>
+      <c r="O176" t="s">
+        <v>141</v>
+      </c>
+      <c r="P176" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q176">
+        <v>2.88</v>
+      </c>
+      <c r="R176">
+        <v>2.05</v>
+      </c>
+      <c r="S176">
+        <v>4</v>
+      </c>
+      <c r="T176">
+        <v>1.5</v>
+      </c>
+      <c r="U176">
+        <v>2.5</v>
+      </c>
+      <c r="V176">
+        <v>3.4</v>
+      </c>
+      <c r="W176">
+        <v>1.3</v>
+      </c>
+      <c r="X176">
+        <v>10</v>
+      </c>
+      <c r="Y176">
+        <v>1.06</v>
+      </c>
+      <c r="Z176">
+        <v>2.15</v>
+      </c>
+      <c r="AA176">
+        <v>3</v>
+      </c>
+      <c r="AB176">
+        <v>3.6</v>
+      </c>
+      <c r="AC176">
+        <v>1.08</v>
+      </c>
+      <c r="AD176">
+        <v>8.5</v>
+      </c>
+      <c r="AE176">
+        <v>1.38</v>
+      </c>
+      <c r="AF176">
+        <v>3</v>
+      </c>
+      <c r="AG176">
+        <v>2</v>
+      </c>
+      <c r="AH176">
+        <v>1.75</v>
+      </c>
+      <c r="AI176">
+        <v>1.95</v>
+      </c>
+      <c r="AJ176">
+        <v>1.8</v>
+      </c>
+      <c r="AK176">
+        <v>1.28</v>
+      </c>
+      <c r="AL176">
+        <v>1.33</v>
+      </c>
+      <c r="AM176">
+        <v>1.68</v>
+      </c>
+      <c r="AN176">
+        <v>1.78</v>
+      </c>
+      <c r="AO176">
+        <v>1</v>
+      </c>
+      <c r="AP176">
+        <v>1.6</v>
+      </c>
+      <c r="AQ176">
+        <v>1.2</v>
+      </c>
+      <c r="AR176">
+        <v>1.21</v>
+      </c>
+      <c r="AS176">
+        <v>1.11</v>
+      </c>
+      <c r="AT176">
+        <v>2.32</v>
+      </c>
+      <c r="AU176">
+        <v>9</v>
+      </c>
+      <c r="AV176">
+        <v>6</v>
+      </c>
+      <c r="AW176">
+        <v>4</v>
+      </c>
+      <c r="AX176">
+        <v>13</v>
+      </c>
+      <c r="AY176">
+        <v>14</v>
+      </c>
+      <c r="AZ176">
+        <v>24</v>
+      </c>
+      <c r="BA176">
+        <v>3</v>
+      </c>
+      <c r="BB176">
+        <v>3</v>
+      </c>
+      <c r="BC176">
+        <v>6</v>
+      </c>
+      <c r="BD176">
+        <v>1.58</v>
+      </c>
+      <c r="BE176">
+        <v>6.75</v>
+      </c>
+      <c r="BF176">
+        <v>2.6</v>
+      </c>
+      <c r="BG176">
+        <v>1.28</v>
+      </c>
+      <c r="BH176">
+        <v>3.2</v>
+      </c>
+      <c r="BI176">
+        <v>1.48</v>
+      </c>
+      <c r="BJ176">
+        <v>2.38</v>
+      </c>
+      <c r="BK176">
+        <v>1.8</v>
+      </c>
+      <c r="BL176">
+        <v>1.85</v>
+      </c>
+      <c r="BM176">
+        <v>2.23</v>
+      </c>
+      <c r="BN176">
+        <v>1.56</v>
+      </c>
+      <c r="BO176">
+        <v>2.85</v>
+      </c>
+      <c r="BP176">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="177" spans="1:68">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>7574734</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45689.72916666666</v>
+      </c>
+      <c r="F177">
+        <v>20</v>
+      </c>
+      <c r="G177" t="s">
+        <v>85</v>
+      </c>
+      <c r="H177" t="s">
+        <v>71</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>0</v>
+      </c>
+      <c r="L177">
+        <v>2</v>
+      </c>
+      <c r="M177">
+        <v>0</v>
+      </c>
+      <c r="N177">
+        <v>2</v>
+      </c>
+      <c r="O177" t="s">
+        <v>203</v>
+      </c>
+      <c r="P177" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q177">
+        <v>2.05</v>
+      </c>
+      <c r="R177">
+        <v>2.25</v>
+      </c>
+      <c r="S177">
+        <v>7</v>
+      </c>
+      <c r="T177">
+        <v>1.4</v>
+      </c>
+      <c r="U177">
+        <v>2.75</v>
+      </c>
+      <c r="V177">
+        <v>2.75</v>
+      </c>
+      <c r="W177">
+        <v>1.4</v>
+      </c>
+      <c r="X177">
+        <v>8</v>
+      </c>
+      <c r="Y177">
+        <v>1.08</v>
+      </c>
+      <c r="Z177">
+        <v>1.44</v>
+      </c>
+      <c r="AA177">
+        <v>4.2</v>
+      </c>
+      <c r="AB177">
+        <v>6.5</v>
+      </c>
+      <c r="AC177">
+        <v>1.04</v>
+      </c>
+      <c r="AD177">
+        <v>11</v>
+      </c>
+      <c r="AE177">
+        <v>1.3</v>
+      </c>
+      <c r="AF177">
+        <v>3.4</v>
+      </c>
+      <c r="AG177">
+        <v>2.05</v>
+      </c>
+      <c r="AH177">
+        <v>1.73</v>
+      </c>
+      <c r="AI177">
+        <v>2.1</v>
+      </c>
+      <c r="AJ177">
+        <v>1.67</v>
+      </c>
+      <c r="AK177">
+        <v>1.1</v>
+      </c>
+      <c r="AL177">
+        <v>1.22</v>
+      </c>
+      <c r="AM177">
+        <v>2.6</v>
+      </c>
+      <c r="AN177">
+        <v>1.78</v>
+      </c>
+      <c r="AO177">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP177">
+        <v>1.9</v>
+      </c>
+      <c r="AQ177">
+        <v>0.5</v>
+      </c>
+      <c r="AR177">
+        <v>1.39</v>
+      </c>
+      <c r="AS177">
+        <v>1.09</v>
+      </c>
+      <c r="AT177">
+        <v>2.48</v>
+      </c>
+      <c r="AU177">
+        <v>10</v>
+      </c>
+      <c r="AV177">
+        <v>0</v>
+      </c>
+      <c r="AW177">
+        <v>6</v>
+      </c>
+      <c r="AX177">
+        <v>3</v>
+      </c>
+      <c r="AY177">
+        <v>19</v>
+      </c>
+      <c r="AZ177">
+        <v>4</v>
+      </c>
+      <c r="BA177">
+        <v>8</v>
+      </c>
+      <c r="BB177">
+        <v>2</v>
+      </c>
+      <c r="BC177">
+        <v>10</v>
+      </c>
+      <c r="BD177">
+        <v>1.3</v>
+      </c>
+      <c r="BE177">
+        <v>8</v>
+      </c>
+      <c r="BF177">
+        <v>3.8</v>
+      </c>
+      <c r="BG177">
+        <v>1.23</v>
+      </c>
+      <c r="BH177">
+        <v>3.55</v>
+      </c>
+      <c r="BI177">
+        <v>1.42</v>
+      </c>
+      <c r="BJ177">
+        <v>2.55</v>
+      </c>
+      <c r="BK177">
+        <v>1.68</v>
+      </c>
+      <c r="BL177">
+        <v>2</v>
+      </c>
+      <c r="BM177">
+        <v>2.05</v>
+      </c>
+      <c r="BN177">
+        <v>1.7</v>
+      </c>
+      <c r="BO177">
+        <v>2.63</v>
+      </c>
+      <c r="BP177">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="293">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -628,6 +628,18 @@
     <t>['55', '78']</t>
   </si>
   <si>
+    <t>['11', '26', '88']</t>
+  </si>
+  <si>
+    <t>['28', '49']</t>
+  </si>
+  <si>
+    <t>['4']</t>
+  </si>
+  <si>
+    <t>['37', '73']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -781,9 +793,6 @@
     <t>['50']</t>
   </si>
   <si>
-    <t>['4']</t>
-  </si>
-  <si>
     <t>['43', '58']</t>
   </si>
   <si>
@@ -875,6 +884,15 @@
   </si>
   <si>
     <t>['45+4', '84']</t>
+  </si>
+  <si>
+    <t>['6', '10', '34']</t>
+  </si>
+  <si>
+    <t>['66', '90+4']</t>
+  </si>
+  <si>
+    <t>['51', '76']</t>
   </si>
 </sst>
 </file>
@@ -1236,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP177"/>
+  <dimension ref="A1:BP181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1570,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ2">
         <v>0.7</v>
@@ -1698,7 +1716,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2316,7 +2334,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2603,7 +2621,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ7">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2728,7 +2746,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -3346,7 +3364,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3427,7 +3445,7 @@
         <v>2</v>
       </c>
       <c r="AQ11">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3552,7 +3570,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3836,10 +3854,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ13">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3964,7 +3982,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4376,7 +4394,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4454,7 +4472,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ16">
         <v>1</v>
@@ -4788,7 +4806,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4869,7 +4887,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ18">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4994,7 +5012,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5072,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ19">
         <v>1.3</v>
@@ -5200,7 +5218,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5406,7 +5424,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -7054,7 +7072,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7132,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ29">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR29">
         <v>1.3</v>
@@ -7260,7 +7278,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7466,7 +7484,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -7544,7 +7562,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ31">
         <v>1.4</v>
@@ -7956,10 +7974,10 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ33">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR33">
         <v>2.25</v>
@@ -8165,7 +8183,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ34">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR34">
         <v>1.18</v>
@@ -8368,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -8496,7 +8514,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q36">
         <v>2.55</v>
@@ -8783,7 +8801,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ37">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR37">
         <v>1.77</v>
@@ -8908,7 +8926,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9114,7 +9132,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9526,7 +9544,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9732,7 +9750,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -9938,7 +9956,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10019,7 +10037,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ43">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR43">
         <v>2.13</v>
@@ -10350,7 +10368,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10556,7 +10574,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10634,7 +10652,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ46">
         <v>0.9</v>
@@ -10762,7 +10780,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10843,7 +10861,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ47">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR47">
         <v>1.27</v>
@@ -10968,7 +10986,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11046,7 +11064,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ48">
         <v>1.2</v>
@@ -11380,7 +11398,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11461,7 +11479,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ50">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR50">
         <v>1.4</v>
@@ -11664,7 +11682,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ51">
         <v>1.3</v>
@@ -11792,7 +11810,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -12282,7 +12300,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ54">
         <v>0.5</v>
@@ -12410,7 +12428,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12491,7 +12509,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ55">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR55">
         <v>1.28</v>
@@ -12616,7 +12634,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -12900,7 +12918,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ57">
         <v>0.7</v>
@@ -13028,7 +13046,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13234,7 +13252,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -14345,7 +14363,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ64">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR64">
         <v>1.27</v>
@@ -14548,7 +14566,7 @@
         <v>1.33</v>
       </c>
       <c r="AP65">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ65">
         <v>1.3</v>
@@ -14960,7 +14978,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ67">
         <v>1.44</v>
@@ -15372,7 +15390,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ69">
         <v>1.4</v>
@@ -15706,7 +15724,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -15912,7 +15930,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -15993,7 +16011,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ72">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR72">
         <v>2.36</v>
@@ -16324,7 +16342,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16530,7 +16548,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16736,7 +16754,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16942,7 +16960,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17229,7 +17247,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ78">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR78">
         <v>1.68</v>
@@ -17560,7 +17578,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17638,7 +17656,7 @@
         <v>1.75</v>
       </c>
       <c r="AP80">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ80">
         <v>1</v>
@@ -17766,7 +17784,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -17847,7 +17865,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ81">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR81">
         <v>1.3</v>
@@ -17972,7 +17990,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18050,7 +18068,7 @@
         <v>0.25</v>
       </c>
       <c r="AP82">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ82">
         <v>0.33</v>
@@ -18178,7 +18196,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18256,7 +18274,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ83">
         <v>1.4</v>
@@ -18384,7 +18402,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18465,7 +18483,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ84">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR84">
         <v>1.17</v>
@@ -18590,7 +18608,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18796,7 +18814,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19208,7 +19226,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19289,7 +19307,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ88">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR88">
         <v>0.89</v>
@@ -19826,7 +19844,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -19904,7 +19922,7 @@
         <v>0.4</v>
       </c>
       <c r="AP91">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ91">
         <v>0.6</v>
@@ -20032,7 +20050,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20113,7 +20131,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ92">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR92">
         <v>1.25</v>
@@ -20650,7 +20668,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -20934,7 +20952,7 @@
         <v>0.4</v>
       </c>
       <c r="AP96">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ96">
         <v>0.3</v>
@@ -21268,7 +21286,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21555,7 +21573,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ99">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR99">
         <v>2.36</v>
@@ -21886,7 +21904,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -21964,7 +21982,7 @@
         <v>1</v>
       </c>
       <c r="AP101">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ101">
         <v>0.7</v>
@@ -22298,7 +22316,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22376,7 +22394,7 @@
         <v>1.2</v>
       </c>
       <c r="AP103">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ103">
         <v>1.44</v>
@@ -22710,7 +22728,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -22791,7 +22809,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ105">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR105">
         <v>0.97</v>
@@ -22916,7 +22934,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q106">
         <v>5.5</v>
@@ -22997,7 +23015,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ106">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR106">
         <v>1.19</v>
@@ -23612,7 +23630,7 @@
         <v>3</v>
       </c>
       <c r="AP109">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ109">
         <v>2.3</v>
@@ -23740,7 +23758,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -23946,7 +23964,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q111">
         <v>2.75</v>
@@ -24645,7 +24663,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ114">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR114">
         <v>1.09</v>
@@ -24851,7 +24869,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ115">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR115">
         <v>1.28</v>
@@ -25182,7 +25200,7 @@
         <v>163</v>
       </c>
       <c r="P117" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="Q117">
         <v>3.25</v>
@@ -25260,7 +25278,7 @@
         <v>0.67</v>
       </c>
       <c r="AP117">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ117">
         <v>1</v>
@@ -25800,7 +25818,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -25878,7 +25896,7 @@
         <v>1.29</v>
       </c>
       <c r="AP120">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ120">
         <v>0.9</v>
@@ -26212,7 +26230,7 @@
         <v>167</v>
       </c>
       <c r="P122" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q122">
         <v>11</v>
@@ -26293,7 +26311,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ122">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR122">
         <v>1.11</v>
@@ -26418,7 +26436,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26624,7 +26642,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -27036,7 +27054,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27114,7 +27132,7 @@
         <v>1.14</v>
       </c>
       <c r="AP126">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ126">
         <v>1</v>
@@ -27242,7 +27260,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27323,7 +27341,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ127">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR127">
         <v>1.37</v>
@@ -27448,7 +27466,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27654,7 +27672,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27735,7 +27753,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ129">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR129">
         <v>1.02</v>
@@ -28066,7 +28084,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28144,10 +28162,10 @@
         <v>1.67</v>
       </c>
       <c r="AP131">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ131">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR131">
         <v>1.14</v>
@@ -28272,7 +28290,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28353,7 +28371,7 @@
         <v>2</v>
       </c>
       <c r="AQ132">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR132">
         <v>1.35</v>
@@ -28684,7 +28702,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -29174,7 +29192,7 @@
         <v>0.43</v>
       </c>
       <c r="AP136">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ136">
         <v>0.7</v>
@@ -29508,7 +29526,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29714,7 +29732,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -30126,7 +30144,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30332,7 +30350,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30410,7 +30428,7 @@
         <v>0.38</v>
       </c>
       <c r="AP142">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ142">
         <v>0.3</v>
@@ -30538,7 +30556,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -30822,10 +30840,10 @@
         <v>2</v>
       </c>
       <c r="AP144">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ144">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR144">
         <v>2.11</v>
@@ -30950,7 +30968,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31156,7 +31174,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31362,7 +31380,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q147">
         <v>2.55</v>
@@ -31440,7 +31458,7 @@
         <v>0.57</v>
       </c>
       <c r="AP147">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ147">
         <v>0.5</v>
@@ -31568,7 +31586,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31649,7 +31667,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ148">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR148">
         <v>2.01</v>
@@ -31774,7 +31792,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32061,7 +32079,7 @@
         <v>2</v>
       </c>
       <c r="AQ150">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR150">
         <v>1.34</v>
@@ -32186,7 +32204,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32392,7 +32410,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32470,7 +32488,7 @@
         <v>0.43</v>
       </c>
       <c r="AP152">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ152">
         <v>1.2</v>
@@ -32598,7 +32616,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -32885,7 +32903,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ154">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR154">
         <v>1.23</v>
@@ -33216,7 +33234,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33422,7 +33440,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33500,7 +33518,7 @@
         <v>2.22</v>
       </c>
       <c r="AP157">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ157">
         <v>2.3</v>
@@ -33628,7 +33646,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33834,7 +33852,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34118,10 +34136,10 @@
         <v>0.78</v>
       </c>
       <c r="AP160">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ160">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR160">
         <v>1.14</v>
@@ -34246,7 +34264,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34324,10 +34342,10 @@
         <v>2.38</v>
       </c>
       <c r="AP161">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ161">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR161">
         <v>1.17</v>
@@ -34452,7 +34470,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34533,7 +34551,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ162">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR162">
         <v>1.23</v>
@@ -34658,7 +34676,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -35070,7 +35088,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35563,7 +35581,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ167">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR167">
         <v>1.21</v>
@@ -35766,7 +35784,7 @@
         <v>0.33</v>
       </c>
       <c r="AP168">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ168">
         <v>0.3</v>
@@ -36100,7 +36118,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36718,7 +36736,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -37130,7 +37148,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37336,7 +37354,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -37698,6 +37716,830 @@
         <v>2.63</v>
       </c>
       <c r="BP177">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="178" spans="1:68">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>7574737</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45690.625</v>
+      </c>
+      <c r="F178">
+        <v>20</v>
+      </c>
+      <c r="G178" t="s">
+        <v>70</v>
+      </c>
+      <c r="H178" t="s">
+        <v>76</v>
+      </c>
+      <c r="I178">
+        <v>2</v>
+      </c>
+      <c r="J178">
+        <v>1</v>
+      </c>
+      <c r="K178">
+        <v>3</v>
+      </c>
+      <c r="L178">
+        <v>3</v>
+      </c>
+      <c r="M178">
+        <v>1</v>
+      </c>
+      <c r="N178">
+        <v>4</v>
+      </c>
+      <c r="O178" t="s">
+        <v>204</v>
+      </c>
+      <c r="P178" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q178">
+        <v>1.5</v>
+      </c>
+      <c r="R178">
+        <v>3</v>
+      </c>
+      <c r="S178">
+        <v>13</v>
+      </c>
+      <c r="T178">
+        <v>1.22</v>
+      </c>
+      <c r="U178">
+        <v>4</v>
+      </c>
+      <c r="V178">
+        <v>2.1</v>
+      </c>
+      <c r="W178">
+        <v>1.67</v>
+      </c>
+      <c r="X178">
+        <v>4.5</v>
+      </c>
+      <c r="Y178">
+        <v>1.18</v>
+      </c>
+      <c r="Z178">
+        <v>1.12</v>
+      </c>
+      <c r="AA178">
+        <v>9</v>
+      </c>
+      <c r="AB178">
+        <v>14</v>
+      </c>
+      <c r="AC178">
+        <v>1.03</v>
+      </c>
+      <c r="AD178">
+        <v>21</v>
+      </c>
+      <c r="AE178">
+        <v>1.13</v>
+      </c>
+      <c r="AF178">
+        <v>5.75</v>
+      </c>
+      <c r="AG178">
+        <v>1.4</v>
+      </c>
+      <c r="AH178">
+        <v>2.82</v>
+      </c>
+      <c r="AI178">
+        <v>2.25</v>
+      </c>
+      <c r="AJ178">
+        <v>1.57</v>
+      </c>
+      <c r="AK178">
+        <v>1.02</v>
+      </c>
+      <c r="AL178">
+        <v>1.07</v>
+      </c>
+      <c r="AM178">
+        <v>5.25</v>
+      </c>
+      <c r="AN178">
+        <v>2.67</v>
+      </c>
+      <c r="AO178">
+        <v>0.8</v>
+      </c>
+      <c r="AP178">
+        <v>2.7</v>
+      </c>
+      <c r="AQ178">
+        <v>0.73</v>
+      </c>
+      <c r="AR178">
+        <v>2.03</v>
+      </c>
+      <c r="AS178">
+        <v>0.99</v>
+      </c>
+      <c r="AT178">
+        <v>3.02</v>
+      </c>
+      <c r="AU178">
+        <v>8</v>
+      </c>
+      <c r="AV178">
+        <v>3</v>
+      </c>
+      <c r="AW178">
+        <v>13</v>
+      </c>
+      <c r="AX178">
+        <v>5</v>
+      </c>
+      <c r="AY178">
+        <v>25</v>
+      </c>
+      <c r="AZ178">
+        <v>10</v>
+      </c>
+      <c r="BA178">
+        <v>9</v>
+      </c>
+      <c r="BB178">
+        <v>1</v>
+      </c>
+      <c r="BC178">
+        <v>10</v>
+      </c>
+      <c r="BD178">
+        <v>1.05</v>
+      </c>
+      <c r="BE178">
+        <v>14</v>
+      </c>
+      <c r="BF178">
+        <v>10</v>
+      </c>
+      <c r="BG178">
+        <v>1.2</v>
+      </c>
+      <c r="BH178">
+        <v>3.8</v>
+      </c>
+      <c r="BI178">
+        <v>1.36</v>
+      </c>
+      <c r="BJ178">
+        <v>2.8</v>
+      </c>
+      <c r="BK178">
+        <v>1.58</v>
+      </c>
+      <c r="BL178">
+        <v>2.16</v>
+      </c>
+      <c r="BM178">
+        <v>1.95</v>
+      </c>
+      <c r="BN178">
+        <v>1.7</v>
+      </c>
+      <c r="BO178">
+        <v>2.35</v>
+      </c>
+      <c r="BP178">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:68">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>7574739</v>
+      </c>
+      <c r="C179" t="s">
+        <v>68</v>
+      </c>
+      <c r="D179" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45690.72916666666</v>
+      </c>
+      <c r="F179">
+        <v>20</v>
+      </c>
+      <c r="G179" t="s">
+        <v>87</v>
+      </c>
+      <c r="H179" t="s">
+        <v>83</v>
+      </c>
+      <c r="I179">
+        <v>1</v>
+      </c>
+      <c r="J179">
+        <v>3</v>
+      </c>
+      <c r="K179">
+        <v>4</v>
+      </c>
+      <c r="L179">
+        <v>2</v>
+      </c>
+      <c r="M179">
+        <v>3</v>
+      </c>
+      <c r="N179">
+        <v>5</v>
+      </c>
+      <c r="O179" t="s">
+        <v>205</v>
+      </c>
+      <c r="P179" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q179">
+        <v>8.5</v>
+      </c>
+      <c r="R179">
+        <v>2.6</v>
+      </c>
+      <c r="S179">
+        <v>1.73</v>
+      </c>
+      <c r="T179">
+        <v>1.3</v>
+      </c>
+      <c r="U179">
+        <v>3.4</v>
+      </c>
+      <c r="V179">
+        <v>2.38</v>
+      </c>
+      <c r="W179">
+        <v>1.53</v>
+      </c>
+      <c r="X179">
+        <v>6</v>
+      </c>
+      <c r="Y179">
+        <v>1.13</v>
+      </c>
+      <c r="Z179">
+        <v>8.5</v>
+      </c>
+      <c r="AA179">
+        <v>5.8</v>
+      </c>
+      <c r="AB179">
+        <v>1.25</v>
+      </c>
+      <c r="AC179">
+        <v>1.03</v>
+      </c>
+      <c r="AD179">
+        <v>11</v>
+      </c>
+      <c r="AE179">
+        <v>1.18</v>
+      </c>
+      <c r="AF179">
+        <v>4.75</v>
+      </c>
+      <c r="AG179">
+        <v>1.61</v>
+      </c>
+      <c r="AH179">
+        <v>2.2</v>
+      </c>
+      <c r="AI179">
+        <v>2.05</v>
+      </c>
+      <c r="AJ179">
+        <v>1.7</v>
+      </c>
+      <c r="AK179">
+        <v>3.4</v>
+      </c>
+      <c r="AL179">
+        <v>1.13</v>
+      </c>
+      <c r="AM179">
+        <v>1.05</v>
+      </c>
+      <c r="AN179">
+        <v>1.4</v>
+      </c>
+      <c r="AO179">
+        <v>1.56</v>
+      </c>
+      <c r="AP179">
+        <v>1.27</v>
+      </c>
+      <c r="AQ179">
+        <v>1.7</v>
+      </c>
+      <c r="AR179">
+        <v>1.18</v>
+      </c>
+      <c r="AS179">
+        <v>1.7</v>
+      </c>
+      <c r="AT179">
+        <v>2.88</v>
+      </c>
+      <c r="AU179">
+        <v>4</v>
+      </c>
+      <c r="AV179">
+        <v>11</v>
+      </c>
+      <c r="AW179">
+        <v>4</v>
+      </c>
+      <c r="AX179">
+        <v>6</v>
+      </c>
+      <c r="AY179">
+        <v>8</v>
+      </c>
+      <c r="AZ179">
+        <v>19</v>
+      </c>
+      <c r="BA179">
+        <v>0</v>
+      </c>
+      <c r="BB179">
+        <v>7</v>
+      </c>
+      <c r="BC179">
+        <v>7</v>
+      </c>
+      <c r="BD179">
+        <v>4.1</v>
+      </c>
+      <c r="BE179">
+        <v>8</v>
+      </c>
+      <c r="BF179">
+        <v>1.25</v>
+      </c>
+      <c r="BG179">
+        <v>1.25</v>
+      </c>
+      <c r="BH179">
+        <v>3.45</v>
+      </c>
+      <c r="BI179">
+        <v>1.42</v>
+      </c>
+      <c r="BJ179">
+        <v>2.55</v>
+      </c>
+      <c r="BK179">
+        <v>1.7</v>
+      </c>
+      <c r="BL179">
+        <v>2.05</v>
+      </c>
+      <c r="BM179">
+        <v>2.08</v>
+      </c>
+      <c r="BN179">
+        <v>1.64</v>
+      </c>
+      <c r="BO179">
+        <v>2.63</v>
+      </c>
+      <c r="BP179">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:68">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>7574740</v>
+      </c>
+      <c r="C180" t="s">
+        <v>68</v>
+      </c>
+      <c r="D180" t="s">
+        <v>69</v>
+      </c>
+      <c r="E180" s="2">
+        <v>45691.65625</v>
+      </c>
+      <c r="F180">
+        <v>20</v>
+      </c>
+      <c r="G180" t="s">
+        <v>84</v>
+      </c>
+      <c r="H180" t="s">
+        <v>77</v>
+      </c>
+      <c r="I180">
+        <v>1</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>1</v>
+      </c>
+      <c r="L180">
+        <v>1</v>
+      </c>
+      <c r="M180">
+        <v>2</v>
+      </c>
+      <c r="N180">
+        <v>3</v>
+      </c>
+      <c r="O180" t="s">
+        <v>206</v>
+      </c>
+      <c r="P180" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q180">
+        <v>4.75</v>
+      </c>
+      <c r="R180">
+        <v>2.1</v>
+      </c>
+      <c r="S180">
+        <v>2.5</v>
+      </c>
+      <c r="T180">
+        <v>1.44</v>
+      </c>
+      <c r="U180">
+        <v>2.63</v>
+      </c>
+      <c r="V180">
+        <v>3</v>
+      </c>
+      <c r="W180">
+        <v>1.36</v>
+      </c>
+      <c r="X180">
+        <v>9</v>
+      </c>
+      <c r="Y180">
+        <v>1.07</v>
+      </c>
+      <c r="Z180">
+        <v>4</v>
+      </c>
+      <c r="AA180">
+        <v>3.5</v>
+      </c>
+      <c r="AB180">
+        <v>1.85</v>
+      </c>
+      <c r="AC180">
+        <v>1.06</v>
+      </c>
+      <c r="AD180">
+        <v>10</v>
+      </c>
+      <c r="AE180">
+        <v>1.36</v>
+      </c>
+      <c r="AF180">
+        <v>3.2</v>
+      </c>
+      <c r="AG180">
+        <v>1.95</v>
+      </c>
+      <c r="AH180">
+        <v>1.75</v>
+      </c>
+      <c r="AI180">
+        <v>1.91</v>
+      </c>
+      <c r="AJ180">
+        <v>1.91</v>
+      </c>
+      <c r="AK180">
+        <v>1.9</v>
+      </c>
+      <c r="AL180">
+        <v>1.29</v>
+      </c>
+      <c r="AM180">
+        <v>1.22</v>
+      </c>
+      <c r="AN180">
+        <v>1.78</v>
+      </c>
+      <c r="AO180">
+        <v>2.44</v>
+      </c>
+      <c r="AP180">
+        <v>1.6</v>
+      </c>
+      <c r="AQ180">
+        <v>2.5</v>
+      </c>
+      <c r="AR180">
+        <v>1.19</v>
+      </c>
+      <c r="AS180">
+        <v>1.47</v>
+      </c>
+      <c r="AT180">
+        <v>2.66</v>
+      </c>
+      <c r="AU180">
+        <v>8</v>
+      </c>
+      <c r="AV180">
+        <v>7</v>
+      </c>
+      <c r="AW180">
+        <v>4</v>
+      </c>
+      <c r="AX180">
+        <v>7</v>
+      </c>
+      <c r="AY180">
+        <v>13</v>
+      </c>
+      <c r="AZ180">
+        <v>17</v>
+      </c>
+      <c r="BA180">
+        <v>1</v>
+      </c>
+      <c r="BB180">
+        <v>9</v>
+      </c>
+      <c r="BC180">
+        <v>10</v>
+      </c>
+      <c r="BD180">
+        <v>2.8</v>
+      </c>
+      <c r="BE180">
+        <v>6.75</v>
+      </c>
+      <c r="BF180">
+        <v>1.52</v>
+      </c>
+      <c r="BG180">
+        <v>1.33</v>
+      </c>
+      <c r="BH180">
+        <v>2.95</v>
+      </c>
+      <c r="BI180">
+        <v>1.56</v>
+      </c>
+      <c r="BJ180">
+        <v>2.23</v>
+      </c>
+      <c r="BK180">
+        <v>1.85</v>
+      </c>
+      <c r="BL180">
+        <v>1.85</v>
+      </c>
+      <c r="BM180">
+        <v>2.4</v>
+      </c>
+      <c r="BN180">
+        <v>1.48</v>
+      </c>
+      <c r="BO180">
+        <v>3.15</v>
+      </c>
+      <c r="BP180">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="181" spans="1:68">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>7574741</v>
+      </c>
+      <c r="C181" t="s">
+        <v>68</v>
+      </c>
+      <c r="D181" t="s">
+        <v>69</v>
+      </c>
+      <c r="E181" s="2">
+        <v>45691.73958333334</v>
+      </c>
+      <c r="F181">
+        <v>20</v>
+      </c>
+      <c r="G181" t="s">
+        <v>81</v>
+      </c>
+      <c r="H181" t="s">
+        <v>73</v>
+      </c>
+      <c r="I181">
+        <v>1</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>1</v>
+      </c>
+      <c r="L181">
+        <v>2</v>
+      </c>
+      <c r="M181">
+        <v>2</v>
+      </c>
+      <c r="N181">
+        <v>4</v>
+      </c>
+      <c r="O181" t="s">
+        <v>207</v>
+      </c>
+      <c r="P181" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q181">
+        <v>6.5</v>
+      </c>
+      <c r="R181">
+        <v>2.38</v>
+      </c>
+      <c r="S181">
+        <v>2</v>
+      </c>
+      <c r="T181">
+        <v>1.33</v>
+      </c>
+      <c r="U181">
+        <v>3.25</v>
+      </c>
+      <c r="V181">
+        <v>2.63</v>
+      </c>
+      <c r="W181">
+        <v>1.44</v>
+      </c>
+      <c r="X181">
+        <v>6.5</v>
+      </c>
+      <c r="Y181">
+        <v>1.11</v>
+      </c>
+      <c r="Z181">
+        <v>6.5</v>
+      </c>
+      <c r="AA181">
+        <v>4.4</v>
+      </c>
+      <c r="AB181">
+        <v>1.44</v>
+      </c>
+      <c r="AC181">
+        <v>1.02</v>
+      </c>
+      <c r="AD181">
+        <v>15</v>
+      </c>
+      <c r="AE181">
+        <v>1.22</v>
+      </c>
+      <c r="AF181">
+        <v>4.2</v>
+      </c>
+      <c r="AG181">
+        <v>1.73</v>
+      </c>
+      <c r="AH181">
+        <v>2</v>
+      </c>
+      <c r="AI181">
+        <v>1.95</v>
+      </c>
+      <c r="AJ181">
+        <v>1.8</v>
+      </c>
+      <c r="AK181">
+        <v>2.65</v>
+      </c>
+      <c r="AL181">
+        <v>1.2</v>
+      </c>
+      <c r="AM181">
+        <v>1.11</v>
+      </c>
+      <c r="AN181">
+        <v>1.78</v>
+      </c>
+      <c r="AO181">
+        <v>1.44</v>
+      </c>
+      <c r="AP181">
+        <v>1.7</v>
+      </c>
+      <c r="AQ181">
+        <v>1.4</v>
+      </c>
+      <c r="AR181">
+        <v>1.3</v>
+      </c>
+      <c r="AS181">
+        <v>1.33</v>
+      </c>
+      <c r="AT181">
+        <v>2.63</v>
+      </c>
+      <c r="AU181">
+        <v>4</v>
+      </c>
+      <c r="AV181">
+        <v>11</v>
+      </c>
+      <c r="AW181">
+        <v>7</v>
+      </c>
+      <c r="AX181">
+        <v>14</v>
+      </c>
+      <c r="AY181">
+        <v>12</v>
+      </c>
+      <c r="AZ181">
+        <v>32</v>
+      </c>
+      <c r="BA181">
+        <v>3</v>
+      </c>
+      <c r="BB181">
+        <v>5</v>
+      </c>
+      <c r="BC181">
+        <v>8</v>
+      </c>
+      <c r="BD181">
+        <v>3.9</v>
+      </c>
+      <c r="BE181">
+        <v>8</v>
+      </c>
+      <c r="BF181">
+        <v>1.29</v>
+      </c>
+      <c r="BG181">
+        <v>1.25</v>
+      </c>
+      <c r="BH181">
+        <v>3.45</v>
+      </c>
+      <c r="BI181">
+        <v>1.42</v>
+      </c>
+      <c r="BJ181">
+        <v>2.55</v>
+      </c>
+      <c r="BK181">
+        <v>1.7</v>
+      </c>
+      <c r="BL181">
+        <v>1.95</v>
+      </c>
+      <c r="BM181">
+        <v>2.05</v>
+      </c>
+      <c r="BN181">
+        <v>1.65</v>
+      </c>
+      <c r="BO181">
+        <v>2.6</v>
+      </c>
+      <c r="BP181">
         <v>1.41</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="294">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -894,6 +894,9 @@
   <si>
     <t>['51', '76']</t>
   </si>
+  <si>
+    <t>['42']</t>
+  </si>
 </sst>
 </file>
 
@@ -1254,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP181"/>
+  <dimension ref="A1:BP182"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2206,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ5">
         <v>0.6</v>
@@ -4063,7 +4066,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ14">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -5299,7 +5302,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ20">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR20">
         <v>1.56</v>
@@ -5708,7 +5711,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ22">
         <v>0.7</v>
@@ -9007,7 +9010,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ38">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR38">
         <v>0.93</v>
@@ -10034,7 +10037,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ43">
         <v>0.73</v>
@@ -12715,7 +12718,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ56">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR56">
         <v>0.98</v>
@@ -13742,7 +13745,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ61">
         <v>1</v>
@@ -16008,7 +16011,7 @@
         <v>2.33</v>
       </c>
       <c r="AP72">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ72">
         <v>2.5</v>
@@ -17041,7 +17044,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ77">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR77">
         <v>1.24</v>
@@ -19510,7 +19513,7 @@
         <v>0.5</v>
       </c>
       <c r="AP89">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ89">
         <v>1.2</v>
@@ -21367,7 +21370,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ98">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR98">
         <v>1.75</v>
@@ -23424,7 +23427,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ108">
         <v>1.4</v>
@@ -23633,7 +23636,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ109">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR109">
         <v>1.17</v>
@@ -26926,7 +26929,7 @@
         <v>0.17</v>
       </c>
       <c r="AP125">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ125">
         <v>0.33</v>
@@ -28577,7 +28580,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ133">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR133">
         <v>1.29</v>
@@ -30016,7 +30019,7 @@
         <v>1.13</v>
       </c>
       <c r="AP140">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ140">
         <v>0.9</v>
@@ -31255,7 +31258,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ146">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR146">
         <v>1.3</v>
@@ -33521,7 +33524,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ157">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR157">
         <v>1.39</v>
@@ -36196,7 +36199,7 @@
         <v>1.5</v>
       </c>
       <c r="AP170">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ170">
         <v>1.44</v>
@@ -38541,6 +38544,212 @@
       </c>
       <c r="BP181">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="182" spans="1:68">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>7574751</v>
+      </c>
+      <c r="C182" t="s">
+        <v>68</v>
+      </c>
+      <c r="D182" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="2">
+        <v>45695.71875</v>
+      </c>
+      <c r="F182">
+        <v>21</v>
+      </c>
+      <c r="G182" t="s">
+        <v>73</v>
+      </c>
+      <c r="H182" t="s">
+        <v>70</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>1</v>
+      </c>
+      <c r="K182">
+        <v>1</v>
+      </c>
+      <c r="L182">
+        <v>1</v>
+      </c>
+      <c r="M182">
+        <v>1</v>
+      </c>
+      <c r="N182">
+        <v>2</v>
+      </c>
+      <c r="O182" t="s">
+        <v>167</v>
+      </c>
+      <c r="P182" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q182">
+        <v>3.25</v>
+      </c>
+      <c r="R182">
+        <v>2.2</v>
+      </c>
+      <c r="S182">
+        <v>3.25</v>
+      </c>
+      <c r="T182">
+        <v>1.4</v>
+      </c>
+      <c r="U182">
+        <v>2.75</v>
+      </c>
+      <c r="V182">
+        <v>2.75</v>
+      </c>
+      <c r="W182">
+        <v>1.4</v>
+      </c>
+      <c r="X182">
+        <v>8</v>
+      </c>
+      <c r="Y182">
+        <v>1.08</v>
+      </c>
+      <c r="Z182">
+        <v>2.6</v>
+      </c>
+      <c r="AA182">
+        <v>3.1</v>
+      </c>
+      <c r="AB182">
+        <v>2.7</v>
+      </c>
+      <c r="AC182">
+        <v>0</v>
+      </c>
+      <c r="AD182">
+        <v>0</v>
+      </c>
+      <c r="AE182">
+        <v>1.86</v>
+      </c>
+      <c r="AF182">
+        <v>2.02</v>
+      </c>
+      <c r="AG182">
+        <v>1.8</v>
+      </c>
+      <c r="AH182">
+        <v>1.91</v>
+      </c>
+      <c r="AI182">
+        <v>1.7</v>
+      </c>
+      <c r="AJ182">
+        <v>2.05</v>
+      </c>
+      <c r="AK182">
+        <v>0</v>
+      </c>
+      <c r="AL182">
+        <v>0</v>
+      </c>
+      <c r="AM182">
+        <v>0</v>
+      </c>
+      <c r="AN182">
+        <v>2.8</v>
+      </c>
+      <c r="AO182">
+        <v>2.3</v>
+      </c>
+      <c r="AP182">
+        <v>2.64</v>
+      </c>
+      <c r="AQ182">
+        <v>2.18</v>
+      </c>
+      <c r="AR182">
+        <v>2.01</v>
+      </c>
+      <c r="AS182">
+        <v>2.04</v>
+      </c>
+      <c r="AT182">
+        <v>4.05</v>
+      </c>
+      <c r="AU182">
+        <v>4</v>
+      </c>
+      <c r="AV182">
+        <v>4</v>
+      </c>
+      <c r="AW182">
+        <v>17</v>
+      </c>
+      <c r="AX182">
+        <v>9</v>
+      </c>
+      <c r="AY182">
+        <v>29</v>
+      </c>
+      <c r="AZ182">
+        <v>16</v>
+      </c>
+      <c r="BA182">
+        <v>6</v>
+      </c>
+      <c r="BB182">
+        <v>3</v>
+      </c>
+      <c r="BC182">
+        <v>9</v>
+      </c>
+      <c r="BD182">
+        <v>0</v>
+      </c>
+      <c r="BE182">
+        <v>0</v>
+      </c>
+      <c r="BF182">
+        <v>0</v>
+      </c>
+      <c r="BG182">
+        <v>0</v>
+      </c>
+      <c r="BH182">
+        <v>0</v>
+      </c>
+      <c r="BI182">
+        <v>0</v>
+      </c>
+      <c r="BJ182">
+        <v>0</v>
+      </c>
+      <c r="BK182">
+        <v>0</v>
+      </c>
+      <c r="BL182">
+        <v>0</v>
+      </c>
+      <c r="BM182">
+        <v>0</v>
+      </c>
+      <c r="BN182">
+        <v>0</v>
+      </c>
+      <c r="BO182">
+        <v>0</v>
+      </c>
+      <c r="BP182">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="296">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -640,6 +640,9 @@
     <t>['37', '73']</t>
   </si>
   <si>
+    <t>['7', '15', '42']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -896,6 +899,9 @@
   </si>
   <si>
     <t>['42']</t>
+  </si>
+  <si>
+    <t>['19', '85']</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP182"/>
+  <dimension ref="A1:BP185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1719,7 +1725,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -1797,7 +1803,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ3">
         <v>0.3</v>
@@ -2337,7 +2343,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2418,7 +2424,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ6">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2621,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ7">
         <v>1.7</v>
@@ -2749,7 +2755,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -2830,7 +2836,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ8">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3367,7 +3373,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3573,7 +3579,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3985,7 +3991,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4269,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ15">
         <v>1.4</v>
@@ -4397,7 +4403,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4809,7 +4815,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -5015,7 +5021,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5221,7 +5227,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5427,7 +5433,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -5508,7 +5514,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ21">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR21">
         <v>1.57</v>
@@ -5917,7 +5923,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ23">
         <v>0.9</v>
@@ -6123,7 +6129,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ24">
         <v>0.33</v>
@@ -6741,7 +6747,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -6950,7 +6956,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ28">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR28">
         <v>1.72</v>
@@ -7075,7 +7081,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7281,7 +7287,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7487,7 +7493,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -8517,7 +8523,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q36">
         <v>2.55</v>
@@ -8929,7 +8935,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9135,7 +9141,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9216,7 +9222,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ39">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR39">
         <v>1.27</v>
@@ -9419,7 +9425,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ40">
         <v>0.7</v>
@@ -9547,7 +9553,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9625,7 +9631,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ41">
         <v>0.6</v>
@@ -9753,7 +9759,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -9831,10 +9837,10 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ42">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR42">
         <v>2.4</v>
@@ -9959,7 +9965,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10371,7 +10377,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10577,7 +10583,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10783,7 +10789,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10989,7 +10995,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11401,7 +11407,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11813,7 +11819,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -12431,7 +12437,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12637,7 +12643,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -12924,7 +12930,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ57">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR57">
         <v>1.33</v>
@@ -13049,7 +13055,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13255,7 +13261,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -13333,7 +13339,7 @@
         <v>0.67</v>
       </c>
       <c r="AP59">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ59">
         <v>0.6</v>
@@ -13539,7 +13545,7 @@
         <v>0.33</v>
       </c>
       <c r="AP60">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ60">
         <v>0.3</v>
@@ -14363,7 +14369,7 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ64">
         <v>0.73</v>
@@ -14984,7 +14990,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ67">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR67">
         <v>1.08</v>
@@ -15727,7 +15733,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -15933,7 +15939,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16345,7 +16351,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16551,7 +16557,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16757,7 +16763,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16838,7 +16844,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ76">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR76">
         <v>1.15</v>
@@ -16963,7 +16969,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17041,7 +17047,7 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ77">
         <v>2.18</v>
@@ -17453,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="AP79">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ79">
         <v>0.7</v>
@@ -17581,7 +17587,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17787,7 +17793,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -17865,7 +17871,7 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ81">
         <v>1.4</v>
@@ -17993,7 +17999,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18199,7 +18205,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18405,7 +18411,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18611,7 +18617,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18817,7 +18823,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -18895,7 +18901,7 @@
         <v>1.25</v>
       </c>
       <c r="AP86">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ86">
         <v>1.3</v>
@@ -19104,7 +19110,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ87">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR87">
         <v>1.16</v>
@@ -19229,7 +19235,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19722,7 +19728,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ90">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR90">
         <v>1.22</v>
@@ -19847,7 +19853,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -20053,7 +20059,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20543,7 +20549,7 @@
         <v>0.6</v>
       </c>
       <c r="AP94">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -20671,7 +20677,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -21289,7 +21295,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21573,7 +21579,7 @@
         <v>2.25</v>
       </c>
       <c r="AP99">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ99">
         <v>1.4</v>
@@ -21907,7 +21913,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -21988,7 +21994,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ101">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR101">
         <v>1.42</v>
@@ -22319,7 +22325,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22400,7 +22406,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ103">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR103">
         <v>2.02</v>
@@ -22731,7 +22737,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -22937,7 +22943,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q106">
         <v>5.5</v>
@@ -23015,7 +23021,7 @@
         <v>2</v>
       </c>
       <c r="AP106">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ106">
         <v>2.5</v>
@@ -23761,7 +23767,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -23967,7 +23973,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q111">
         <v>2.75</v>
@@ -24251,7 +24257,7 @@
         <v>1.33</v>
       </c>
       <c r="AP112">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ112">
         <v>1</v>
@@ -24663,7 +24669,7 @@
         <v>1.8</v>
       </c>
       <c r="AP114">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ114">
         <v>1.4</v>
@@ -25696,7 +25702,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ119">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR119">
         <v>1.33</v>
@@ -25821,7 +25827,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26108,7 +26114,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ121">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR121">
         <v>1.05</v>
@@ -26233,7 +26239,7 @@
         <v>167</v>
       </c>
       <c r="P122" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q122">
         <v>11</v>
@@ -26311,7 +26317,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ122">
         <v>1.7</v>
@@ -26439,7 +26445,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26645,7 +26651,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -27057,7 +27063,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27263,7 +27269,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27469,7 +27475,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27675,7 +27681,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27753,7 +27759,7 @@
         <v>0.43</v>
       </c>
       <c r="AP129">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ129">
         <v>0.73</v>
@@ -28087,7 +28093,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28293,7 +28299,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28705,7 +28711,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -28989,7 +28995,7 @@
         <v>0.5</v>
       </c>
       <c r="AP135">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ135">
         <v>1.2</v>
@@ -29529,7 +29535,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29607,7 +29613,7 @@
         <v>0.14</v>
       </c>
       <c r="AP138">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ138">
         <v>0.33</v>
@@ -29735,7 +29741,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -29816,7 +29822,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ139">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR139">
         <v>1.09</v>
@@ -30147,7 +30153,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30353,7 +30359,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30559,7 +30565,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -30971,7 +30977,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31049,10 +31055,10 @@
         <v>1.29</v>
       </c>
       <c r="AP145">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ145">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR145">
         <v>1.04</v>
@@ -31177,7 +31183,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31383,7 +31389,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q147">
         <v>2.55</v>
@@ -31589,7 +31595,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31667,7 +31673,7 @@
         <v>2.29</v>
       </c>
       <c r="AP148">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ148">
         <v>2.5</v>
@@ -31795,7 +31801,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32207,7 +32213,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32413,7 +32419,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32619,7 +32625,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -33109,7 +33115,7 @@
         <v>1.25</v>
       </c>
       <c r="AP155">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ155">
         <v>1.3</v>
@@ -33237,7 +33243,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33443,7 +33449,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33649,7 +33655,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33855,7 +33861,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34267,7 +34273,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34473,7 +34479,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34679,7 +34685,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -34966,7 +34972,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ164">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR164">
         <v>1.09</v>
@@ -35091,7 +35097,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35375,7 +35381,7 @@
         <v>0.25</v>
       </c>
       <c r="AP166">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ166">
         <v>0.33</v>
@@ -36121,7 +36127,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36202,7 +36208,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ170">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR170">
         <v>1.95</v>
@@ -36611,7 +36617,7 @@
         <v>0.67</v>
       </c>
       <c r="AP172">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ172">
         <v>0.6</v>
@@ -36739,7 +36745,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -37151,7 +37157,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37357,7 +37363,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -37975,7 +37981,7 @@
         <v>205</v>
       </c>
       <c r="P179" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q179">
         <v>8.5</v>
@@ -38181,7 +38187,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q180">
         <v>4.75</v>
@@ -38387,7 +38393,7 @@
         <v>207</v>
       </c>
       <c r="P181" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q181">
         <v>6.5</v>
@@ -38593,7 +38599,7 @@
         <v>167</v>
       </c>
       <c r="P182" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -38749,6 +38755,624 @@
         <v>0</v>
       </c>
       <c r="BP182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:68">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>7574747</v>
+      </c>
+      <c r="C183" t="s">
+        <v>68</v>
+      </c>
+      <c r="D183" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" s="2">
+        <v>45696.52083333334</v>
+      </c>
+      <c r="F183">
+        <v>21</v>
+      </c>
+      <c r="G183" t="s">
+        <v>71</v>
+      </c>
+      <c r="H183" t="s">
+        <v>79</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+      <c r="J183">
+        <v>0</v>
+      </c>
+      <c r="K183">
+        <v>0</v>
+      </c>
+      <c r="L183">
+        <v>1</v>
+      </c>
+      <c r="M183">
+        <v>2</v>
+      </c>
+      <c r="N183">
+        <v>3</v>
+      </c>
+      <c r="O183" t="s">
+        <v>167</v>
+      </c>
+      <c r="P183" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q183">
+        <v>4.2</v>
+      </c>
+      <c r="R183">
+        <v>1.9</v>
+      </c>
+      <c r="S183">
+        <v>2.8</v>
+      </c>
+      <c r="T183">
+        <v>1.55</v>
+      </c>
+      <c r="U183">
+        <v>2.3</v>
+      </c>
+      <c r="V183">
+        <v>3.6</v>
+      </c>
+      <c r="W183">
+        <v>1.25</v>
+      </c>
+      <c r="X183">
+        <v>10.5</v>
+      </c>
+      <c r="Y183">
+        <v>1.04</v>
+      </c>
+      <c r="Z183">
+        <v>3.7</v>
+      </c>
+      <c r="AA183">
+        <v>3</v>
+      </c>
+      <c r="AB183">
+        <v>2.1</v>
+      </c>
+      <c r="AC183">
+        <v>1.1</v>
+      </c>
+      <c r="AD183">
+        <v>7</v>
+      </c>
+      <c r="AE183">
+        <v>1.53</v>
+      </c>
+      <c r="AF183">
+        <v>2.37</v>
+      </c>
+      <c r="AG183">
+        <v>2.63</v>
+      </c>
+      <c r="AH183">
+        <v>1.45</v>
+      </c>
+      <c r="AI183">
+        <v>2.2</v>
+      </c>
+      <c r="AJ183">
+        <v>1.58</v>
+      </c>
+      <c r="AK183">
+        <v>1.68</v>
+      </c>
+      <c r="AL183">
+        <v>1.34</v>
+      </c>
+      <c r="AM183">
+        <v>1.27</v>
+      </c>
+      <c r="AN183">
+        <v>1.3</v>
+      </c>
+      <c r="AO183">
+        <v>1.44</v>
+      </c>
+      <c r="AP183">
+        <v>1.18</v>
+      </c>
+      <c r="AQ183">
+        <v>1.6</v>
+      </c>
+      <c r="AR183">
+        <v>1.2</v>
+      </c>
+      <c r="AS183">
+        <v>0.98</v>
+      </c>
+      <c r="AT183">
+        <v>2.18</v>
+      </c>
+      <c r="AU183">
+        <v>4</v>
+      </c>
+      <c r="AV183">
+        <v>5</v>
+      </c>
+      <c r="AW183">
+        <v>6</v>
+      </c>
+      <c r="AX183">
+        <v>3</v>
+      </c>
+      <c r="AY183">
+        <v>11</v>
+      </c>
+      <c r="AZ183">
+        <v>9</v>
+      </c>
+      <c r="BA183">
+        <v>2</v>
+      </c>
+      <c r="BB183">
+        <v>3</v>
+      </c>
+      <c r="BC183">
+        <v>5</v>
+      </c>
+      <c r="BD183">
+        <v>2.07</v>
+      </c>
+      <c r="BE183">
+        <v>6.25</v>
+      </c>
+      <c r="BF183">
+        <v>1.94</v>
+      </c>
+      <c r="BG183">
+        <v>1.41</v>
+      </c>
+      <c r="BH183">
+        <v>2.6</v>
+      </c>
+      <c r="BI183">
+        <v>1.7</v>
+      </c>
+      <c r="BJ183">
+        <v>1.98</v>
+      </c>
+      <c r="BK183">
+        <v>2.12</v>
+      </c>
+      <c r="BL183">
+        <v>1.6</v>
+      </c>
+      <c r="BM183">
+        <v>2.75</v>
+      </c>
+      <c r="BN183">
+        <v>1.37</v>
+      </c>
+      <c r="BO183">
+        <v>3.65</v>
+      </c>
+      <c r="BP183">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="184" spans="1:68">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>7574749</v>
+      </c>
+      <c r="C184" t="s">
+        <v>68</v>
+      </c>
+      <c r="D184" t="s">
+        <v>69</v>
+      </c>
+      <c r="E184" s="2">
+        <v>45696.625</v>
+      </c>
+      <c r="F184">
+        <v>21</v>
+      </c>
+      <c r="G184" t="s">
+        <v>83</v>
+      </c>
+      <c r="H184" t="s">
+        <v>84</v>
+      </c>
+      <c r="I184">
+        <v>3</v>
+      </c>
+      <c r="J184">
+        <v>1</v>
+      </c>
+      <c r="K184">
+        <v>4</v>
+      </c>
+      <c r="L184">
+        <v>3</v>
+      </c>
+      <c r="M184">
+        <v>2</v>
+      </c>
+      <c r="N184">
+        <v>5</v>
+      </c>
+      <c r="O184" t="s">
+        <v>208</v>
+      </c>
+      <c r="P184" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q184">
+        <v>1.57</v>
+      </c>
+      <c r="R184">
+        <v>2.75</v>
+      </c>
+      <c r="S184">
+        <v>12</v>
+      </c>
+      <c r="T184">
+        <v>1.29</v>
+      </c>
+      <c r="U184">
+        <v>3.5</v>
+      </c>
+      <c r="V184">
+        <v>2.38</v>
+      </c>
+      <c r="W184">
+        <v>1.53</v>
+      </c>
+      <c r="X184">
+        <v>5.5</v>
+      </c>
+      <c r="Y184">
+        <v>1.14</v>
+      </c>
+      <c r="Z184">
+        <v>1.17</v>
+      </c>
+      <c r="AA184">
+        <v>6.5</v>
+      </c>
+      <c r="AB184">
+        <v>13</v>
+      </c>
+      <c r="AC184">
+        <v>0</v>
+      </c>
+      <c r="AD184">
+        <v>0</v>
+      </c>
+      <c r="AE184">
+        <v>0</v>
+      </c>
+      <c r="AF184">
+        <v>0</v>
+      </c>
+      <c r="AG184">
+        <v>1.65</v>
+      </c>
+      <c r="AH184">
+        <v>2.15</v>
+      </c>
+      <c r="AI184">
+        <v>2.38</v>
+      </c>
+      <c r="AJ184">
+        <v>1.53</v>
+      </c>
+      <c r="AK184">
+        <v>0</v>
+      </c>
+      <c r="AL184">
+        <v>0</v>
+      </c>
+      <c r="AM184">
+        <v>0</v>
+      </c>
+      <c r="AN184">
+        <v>2.7</v>
+      </c>
+      <c r="AO184">
+        <v>0.7</v>
+      </c>
+      <c r="AP184">
+        <v>2.73</v>
+      </c>
+      <c r="AQ184">
+        <v>0.64</v>
+      </c>
+      <c r="AR184">
+        <v>2.05</v>
+      </c>
+      <c r="AS184">
+        <v>1.17</v>
+      </c>
+      <c r="AT184">
+        <v>3.22</v>
+      </c>
+      <c r="AU184">
+        <v>7</v>
+      </c>
+      <c r="AV184">
+        <v>6</v>
+      </c>
+      <c r="AW184">
+        <v>4</v>
+      </c>
+      <c r="AX184">
+        <v>4</v>
+      </c>
+      <c r="AY184">
+        <v>11</v>
+      </c>
+      <c r="AZ184">
+        <v>10</v>
+      </c>
+      <c r="BA184">
+        <v>6</v>
+      </c>
+      <c r="BB184">
+        <v>6</v>
+      </c>
+      <c r="BC184">
+        <v>12</v>
+      </c>
+      <c r="BD184">
+        <v>0</v>
+      </c>
+      <c r="BE184">
+        <v>0</v>
+      </c>
+      <c r="BF184">
+        <v>0</v>
+      </c>
+      <c r="BG184">
+        <v>0</v>
+      </c>
+      <c r="BH184">
+        <v>0</v>
+      </c>
+      <c r="BI184">
+        <v>0</v>
+      </c>
+      <c r="BJ184">
+        <v>0</v>
+      </c>
+      <c r="BK184">
+        <v>0</v>
+      </c>
+      <c r="BL184">
+        <v>0</v>
+      </c>
+      <c r="BM184">
+        <v>0</v>
+      </c>
+      <c r="BN184">
+        <v>0</v>
+      </c>
+      <c r="BO184">
+        <v>0</v>
+      </c>
+      <c r="BP184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:68">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>7574745</v>
+      </c>
+      <c r="C185" t="s">
+        <v>68</v>
+      </c>
+      <c r="D185" t="s">
+        <v>69</v>
+      </c>
+      <c r="E185" s="2">
+        <v>45696.72916666666</v>
+      </c>
+      <c r="F185">
+        <v>21</v>
+      </c>
+      <c r="G185" t="s">
+        <v>75</v>
+      </c>
+      <c r="H185" t="s">
+        <v>85</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="L185">
+        <v>0</v>
+      </c>
+      <c r="M185">
+        <v>0</v>
+      </c>
+      <c r="N185">
+        <v>0</v>
+      </c>
+      <c r="O185" t="s">
+        <v>90</v>
+      </c>
+      <c r="P185" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q185">
+        <v>3.75</v>
+      </c>
+      <c r="R185">
+        <v>1.95</v>
+      </c>
+      <c r="S185">
+        <v>2.9</v>
+      </c>
+      <c r="T185">
+        <v>1.49</v>
+      </c>
+      <c r="U185">
+        <v>2.4</v>
+      </c>
+      <c r="V185">
+        <v>3.3</v>
+      </c>
+      <c r="W185">
+        <v>1.29</v>
+      </c>
+      <c r="X185">
+        <v>9.25</v>
+      </c>
+      <c r="Y185">
+        <v>1.05</v>
+      </c>
+      <c r="Z185">
+        <v>3.3</v>
+      </c>
+      <c r="AA185">
+        <v>3</v>
+      </c>
+      <c r="AB185">
+        <v>2.25</v>
+      </c>
+      <c r="AC185">
+        <v>1.09</v>
+      </c>
+      <c r="AD185">
+        <v>8</v>
+      </c>
+      <c r="AE185">
+        <v>1.44</v>
+      </c>
+      <c r="AF185">
+        <v>2.75</v>
+      </c>
+      <c r="AG185">
+        <v>2.3</v>
+      </c>
+      <c r="AH185">
+        <v>1.55</v>
+      </c>
+      <c r="AI185">
+        <v>2</v>
+      </c>
+      <c r="AJ185">
+        <v>1.71</v>
+      </c>
+      <c r="AK185">
+        <v>1.61</v>
+      </c>
+      <c r="AL185">
+        <v>1.33</v>
+      </c>
+      <c r="AM185">
+        <v>1.33</v>
+      </c>
+      <c r="AN185">
+        <v>1.1</v>
+      </c>
+      <c r="AO185">
+        <v>1</v>
+      </c>
+      <c r="AP185">
+        <v>1.09</v>
+      </c>
+      <c r="AQ185">
+        <v>1</v>
+      </c>
+      <c r="AR185">
+        <v>1.11</v>
+      </c>
+      <c r="AS185">
+        <v>1.45</v>
+      </c>
+      <c r="AT185">
+        <v>2.56</v>
+      </c>
+      <c r="AU185">
+        <v>4</v>
+      </c>
+      <c r="AV185">
+        <v>5</v>
+      </c>
+      <c r="AW185">
+        <v>6</v>
+      </c>
+      <c r="AX185">
+        <v>6</v>
+      </c>
+      <c r="AY185">
+        <v>13</v>
+      </c>
+      <c r="AZ185">
+        <v>15</v>
+      </c>
+      <c r="BA185">
+        <v>4</v>
+      </c>
+      <c r="BB185">
+        <v>11</v>
+      </c>
+      <c r="BC185">
+        <v>15</v>
+      </c>
+      <c r="BD185">
+        <v>0</v>
+      </c>
+      <c r="BE185">
+        <v>0</v>
+      </c>
+      <c r="BF185">
+        <v>0</v>
+      </c>
+      <c r="BG185">
+        <v>0</v>
+      </c>
+      <c r="BH185">
+        <v>0</v>
+      </c>
+      <c r="BI185">
+        <v>0</v>
+      </c>
+      <c r="BJ185">
+        <v>0</v>
+      </c>
+      <c r="BK185">
+        <v>0</v>
+      </c>
+      <c r="BL185">
+        <v>0</v>
+      </c>
+      <c r="BM185">
+        <v>0</v>
+      </c>
+      <c r="BN185">
+        <v>0</v>
+      </c>
+      <c r="BO185">
+        <v>0</v>
+      </c>
+      <c r="BP185">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="299">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -643,6 +643,15 @@
     <t>['7', '15', '42']</t>
   </si>
   <si>
+    <t>['27', '46']</t>
+  </si>
+  <si>
+    <t>['10', '81']</t>
+  </si>
+  <si>
+    <t>['37']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -1263,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP185"/>
+  <dimension ref="A1:BP189"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1725,7 +1734,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -1806,7 +1815,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ3">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2009,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ4">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2218,7 +2227,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ5">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2343,7 +2352,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2421,7 +2430,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ6">
         <v>1.6</v>
@@ -2755,7 +2764,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -2833,7 +2842,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ8">
         <v>0.64</v>
@@ -3039,10 +3048,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ9">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3373,7 +3382,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3579,7 +3588,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3991,7 +4000,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4403,7 +4412,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4815,7 +4824,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -5021,7 +5030,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5227,7 +5236,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5305,7 +5314,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ20">
         <v>2.18</v>
@@ -5433,7 +5442,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -5511,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ21">
         <v>1.6</v>
@@ -5926,7 +5935,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ23">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR23">
         <v>1.27</v>
@@ -6132,7 +6141,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ24">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR24">
         <v>2.62</v>
@@ -6338,7 +6347,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ25">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR25">
         <v>0.7</v>
@@ -6541,10 +6550,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ26">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR26">
         <v>0.6</v>
@@ -6953,7 +6962,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ28">
         <v>0.64</v>
@@ -7081,7 +7090,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7287,7 +7296,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7493,7 +7502,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -8523,7 +8532,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q36">
         <v>2.55</v>
@@ -8935,7 +8944,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9141,7 +9150,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9219,7 +9228,7 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ39">
         <v>0.64</v>
@@ -9553,7 +9562,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9634,7 +9643,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ41">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR41">
         <v>1.05</v>
@@ -9759,7 +9768,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -9965,7 +9974,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10249,10 +10258,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ44">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR44">
         <v>0.8100000000000001</v>
@@ -10377,7 +10386,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10455,7 +10464,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -10583,7 +10592,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10664,7 +10673,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ46">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR46">
         <v>1.1</v>
@@ -10789,7 +10798,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10995,7 +11004,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11282,7 +11291,7 @@
         <v>2</v>
       </c>
       <c r="AQ49">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR49">
         <v>1.09</v>
@@ -11407,7 +11416,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11819,7 +11828,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -12103,7 +12112,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ53">
         <v>1</v>
@@ -12437,7 +12446,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12643,7 +12652,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -12721,7 +12730,7 @@
         <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ56">
         <v>2.18</v>
@@ -13055,7 +13064,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13133,7 +13142,7 @@
         <v>2</v>
       </c>
       <c r="AP58">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ58">
         <v>1</v>
@@ -13261,7 +13270,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -13342,7 +13351,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ59">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR59">
         <v>2.26</v>
@@ -13548,7 +13557,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ60">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR60">
         <v>1.14</v>
@@ -13957,7 +13966,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ62">
         <v>0.7</v>
@@ -14166,7 +14175,7 @@
         <v>2</v>
       </c>
       <c r="AQ63">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR63">
         <v>1.11</v>
@@ -14784,7 +14793,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ66">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR66">
         <v>1.45</v>
@@ -15605,7 +15614,7 @@
         <v>0.67</v>
       </c>
       <c r="AP70">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ70">
         <v>1.2</v>
@@ -15733,7 +15742,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -15814,7 +15823,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ71">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR71">
         <v>1.19</v>
@@ -15939,7 +15948,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16223,10 +16232,10 @@
         <v>0.5</v>
       </c>
       <c r="AP73">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ73">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR73">
         <v>1.21</v>
@@ -16351,7 +16360,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16432,7 +16441,7 @@
         <v>2</v>
       </c>
       <c r="AQ74">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR74">
         <v>1.21</v>
@@ -16557,7 +16566,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16635,7 +16644,7 @@
         <v>0.75</v>
       </c>
       <c r="AP75">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -16763,7 +16772,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16969,7 +16978,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17253,7 +17262,7 @@
         <v>0.25</v>
       </c>
       <c r="AP78">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ78">
         <v>0.73</v>
@@ -17587,7 +17596,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17793,7 +17802,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -17999,7 +18008,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18080,7 +18089,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ82">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR82">
         <v>2.06</v>
@@ -18205,7 +18214,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18411,7 +18420,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18489,7 +18498,7 @@
         <v>1.33</v>
       </c>
       <c r="AP84">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ84">
         <v>1.7</v>
@@ -18617,7 +18626,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18698,7 +18707,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ85">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR85">
         <v>1.21</v>
@@ -18823,7 +18832,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19235,7 +19244,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19853,7 +19862,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -19934,7 +19943,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ91">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR91">
         <v>1.03</v>
@@ -20059,7 +20068,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20137,7 +20146,7 @@
         <v>0.2</v>
       </c>
       <c r="AP92">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ92">
         <v>0.73</v>
@@ -20343,7 +20352,7 @@
         <v>0.25</v>
       </c>
       <c r="AP93">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ93">
         <v>0.5</v>
@@ -20677,7 +20686,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -20964,7 +20973,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ96">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR96">
         <v>1.15</v>
@@ -21295,7 +21304,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21373,7 +21382,7 @@
         <v>3</v>
       </c>
       <c r="AP98">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ98">
         <v>2.18</v>
@@ -21785,10 +21794,10 @@
         <v>0.2</v>
       </c>
       <c r="AP100">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ100">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR100">
         <v>1.15</v>
@@ -21913,7 +21922,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22200,7 +22209,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ102">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR102">
         <v>1.15</v>
@@ -22325,7 +22334,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22609,7 +22618,7 @@
         <v>1.6</v>
       </c>
       <c r="AP104">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ104">
         <v>1.3</v>
@@ -22737,7 +22746,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -22943,7 +22952,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q106">
         <v>5.5</v>
@@ -23230,7 +23239,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ107">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR107">
         <v>1.2</v>
@@ -23767,7 +23776,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -23845,7 +23854,7 @@
         <v>0.4</v>
       </c>
       <c r="AP110">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ110">
         <v>1.2</v>
@@ -23973,7 +23982,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q111">
         <v>2.75</v>
@@ -24054,7 +24063,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ111">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR111">
         <v>1.27</v>
@@ -25081,7 +25090,7 @@
         <v>0.4</v>
       </c>
       <c r="AP116">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ116">
         <v>0.5</v>
@@ -25493,10 +25502,10 @@
         <v>0.29</v>
       </c>
       <c r="AP118">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ118">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR118">
         <v>1.14</v>
@@ -25827,7 +25836,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -25908,7 +25917,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ120">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR120">
         <v>2.02</v>
@@ -26239,7 +26248,7 @@
         <v>167</v>
       </c>
       <c r="P122" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q122">
         <v>11</v>
@@ -26445,7 +26454,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26523,7 +26532,7 @@
         <v>0.83</v>
       </c>
       <c r="AP123">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ123">
         <v>1.4</v>
@@ -26651,7 +26660,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -26729,7 +26738,7 @@
         <v>1.33</v>
       </c>
       <c r="AP124">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ124">
         <v>1.3</v>
@@ -26938,7 +26947,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ125">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR125">
         <v>2.03</v>
@@ -27063,7 +27072,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27269,7 +27278,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27475,7 +27484,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27553,7 +27562,7 @@
         <v>0.57</v>
       </c>
       <c r="AP128">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ128">
         <v>1</v>
@@ -27681,7 +27690,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -28093,7 +28102,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28299,7 +28308,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28711,7 +28720,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -28792,7 +28801,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ134">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR134">
         <v>1.28</v>
@@ -29410,7 +29419,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ137">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR137">
         <v>1.07</v>
@@ -29535,7 +29544,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29616,7 +29625,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ138">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR138">
         <v>1.22</v>
@@ -29741,7 +29750,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -29819,7 +29828,7 @@
         <v>0.75</v>
       </c>
       <c r="AP139">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ139">
         <v>0.64</v>
@@ -30028,7 +30037,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ140">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR140">
         <v>1.98</v>
@@ -30153,7 +30162,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30231,7 +30240,7 @@
         <v>1.13</v>
       </c>
       <c r="AP141">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ141">
         <v>1</v>
@@ -30359,7 +30368,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30440,7 +30449,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ142">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR142">
         <v>1.33</v>
@@ -30565,7 +30574,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -30643,7 +30652,7 @@
         <v>1.14</v>
       </c>
       <c r="AP143">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ143">
         <v>1.4</v>
@@ -30977,7 +30986,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31183,7 +31192,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31389,7 +31398,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q147">
         <v>2.55</v>
@@ -31595,7 +31604,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31801,7 +31810,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32213,7 +32222,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32291,7 +32300,7 @@
         <v>1.29</v>
       </c>
       <c r="AP151">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ151">
         <v>1.3</v>
@@ -32419,7 +32428,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32625,7 +32634,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -33243,7 +33252,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33449,7 +33458,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33655,7 +33664,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33861,7 +33870,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34273,7 +34282,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34479,7 +34488,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34685,7 +34694,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -35097,7 +35106,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35175,7 +35184,7 @@
         <v>0.44</v>
       </c>
       <c r="AP165">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ165">
         <v>0.7</v>
@@ -35384,7 +35393,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ166">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR166">
         <v>1.12</v>
@@ -35587,7 +35596,7 @@
         <v>1.75</v>
       </c>
       <c r="AP167">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ167">
         <v>1.7</v>
@@ -35796,7 +35805,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ168">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR168">
         <v>2.03</v>
@@ -35999,7 +36008,7 @@
         <v>1.11</v>
       </c>
       <c r="AP169">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ169">
         <v>1</v>
@@ -36127,7 +36136,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36411,10 +36420,10 @@
         <v>1</v>
       </c>
       <c r="AP171">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ171">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR171">
         <v>1.66</v>
@@ -36620,7 +36629,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ172">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR172">
         <v>1.24</v>
@@ -36745,7 +36754,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -37157,7 +37166,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37363,7 +37372,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -37981,7 +37990,7 @@
         <v>205</v>
       </c>
       <c r="P179" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q179">
         <v>8.5</v>
@@ -38187,7 +38196,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q180">
         <v>4.75</v>
@@ -38393,7 +38402,7 @@
         <v>207</v>
       </c>
       <c r="P181" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q181">
         <v>6.5</v>
@@ -38599,7 +38608,7 @@
         <v>167</v>
       </c>
       <c r="P182" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -39011,7 +39020,7 @@
         <v>208</v>
       </c>
       <c r="P184" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q184">
         <v>1.57</v>
@@ -39107,19 +39116,19 @@
         <v>7</v>
       </c>
       <c r="AV184">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW184">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX184">
         <v>4</v>
       </c>
       <c r="AY184">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ184">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA184">
         <v>6</v>
@@ -39374,6 +39383,830 @@
       </c>
       <c r="BP185">
         <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7574750</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45697.52083333334</v>
+      </c>
+      <c r="F186">
+        <v>21</v>
+      </c>
+      <c r="G186" t="s">
+        <v>74</v>
+      </c>
+      <c r="H186" t="s">
+        <v>86</v>
+      </c>
+      <c r="I186">
+        <v>1</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>1</v>
+      </c>
+      <c r="L186">
+        <v>2</v>
+      </c>
+      <c r="M186">
+        <v>1</v>
+      </c>
+      <c r="N186">
+        <v>3</v>
+      </c>
+      <c r="O186" t="s">
+        <v>209</v>
+      </c>
+      <c r="P186" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q186">
+        <v>2.2</v>
+      </c>
+      <c r="R186">
+        <v>2.2</v>
+      </c>
+      <c r="S186">
+        <v>6.5</v>
+      </c>
+      <c r="T186">
+        <v>1.44</v>
+      </c>
+      <c r="U186">
+        <v>2.63</v>
+      </c>
+      <c r="V186">
+        <v>3.25</v>
+      </c>
+      <c r="W186">
+        <v>1.33</v>
+      </c>
+      <c r="X186">
+        <v>9</v>
+      </c>
+      <c r="Y186">
+        <v>1.07</v>
+      </c>
+      <c r="Z186">
+        <v>1.7</v>
+      </c>
+      <c r="AA186">
+        <v>3.7</v>
+      </c>
+      <c r="AB186">
+        <v>4.6</v>
+      </c>
+      <c r="AC186">
+        <v>1.06</v>
+      </c>
+      <c r="AD186">
+        <v>10</v>
+      </c>
+      <c r="AE186">
+        <v>1.36</v>
+      </c>
+      <c r="AF186">
+        <v>3.1</v>
+      </c>
+      <c r="AG186">
+        <v>2.05</v>
+      </c>
+      <c r="AH186">
+        <v>1.7</v>
+      </c>
+      <c r="AI186">
+        <v>2.05</v>
+      </c>
+      <c r="AJ186">
+        <v>1.7</v>
+      </c>
+      <c r="AK186">
+        <v>1.12</v>
+      </c>
+      <c r="AL186">
+        <v>1.24</v>
+      </c>
+      <c r="AM186">
+        <v>2.37</v>
+      </c>
+      <c r="AN186">
+        <v>1.5</v>
+      </c>
+      <c r="AO186">
+        <v>0.9</v>
+      </c>
+      <c r="AP186">
+        <v>1.64</v>
+      </c>
+      <c r="AQ186">
+        <v>0.82</v>
+      </c>
+      <c r="AR186">
+        <v>1.19</v>
+      </c>
+      <c r="AS186">
+        <v>0.92</v>
+      </c>
+      <c r="AT186">
+        <v>2.11</v>
+      </c>
+      <c r="AU186">
+        <v>6</v>
+      </c>
+      <c r="AV186">
+        <v>7</v>
+      </c>
+      <c r="AW186">
+        <v>8</v>
+      </c>
+      <c r="AX186">
+        <v>6</v>
+      </c>
+      <c r="AY186">
+        <v>16</v>
+      </c>
+      <c r="AZ186">
+        <v>14</v>
+      </c>
+      <c r="BA186">
+        <v>5</v>
+      </c>
+      <c r="BB186">
+        <v>3</v>
+      </c>
+      <c r="BC186">
+        <v>8</v>
+      </c>
+      <c r="BD186">
+        <v>1.26</v>
+      </c>
+      <c r="BE186">
+        <v>8.4</v>
+      </c>
+      <c r="BF186">
+        <v>4.7</v>
+      </c>
+      <c r="BG186">
+        <v>1.33</v>
+      </c>
+      <c r="BH186">
+        <v>2.95</v>
+      </c>
+      <c r="BI186">
+        <v>1.61</v>
+      </c>
+      <c r="BJ186">
+        <v>2.1</v>
+      </c>
+      <c r="BK186">
+        <v>2.05</v>
+      </c>
+      <c r="BL186">
+        <v>1.63</v>
+      </c>
+      <c r="BM186">
+        <v>2.8</v>
+      </c>
+      <c r="BN186">
+        <v>1.35</v>
+      </c>
+      <c r="BO186">
+        <v>4</v>
+      </c>
+      <c r="BP186">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7574744</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45697.52083333334</v>
+      </c>
+      <c r="F187">
+        <v>21</v>
+      </c>
+      <c r="G187" t="s">
+        <v>76</v>
+      </c>
+      <c r="H187" t="s">
+        <v>82</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="L187">
+        <v>0</v>
+      </c>
+      <c r="M187">
+        <v>2</v>
+      </c>
+      <c r="N187">
+        <v>2</v>
+      </c>
+      <c r="O187" t="s">
+        <v>90</v>
+      </c>
+      <c r="P187" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q187">
+        <v>3.1</v>
+      </c>
+      <c r="R187">
+        <v>2.05</v>
+      </c>
+      <c r="S187">
+        <v>3.75</v>
+      </c>
+      <c r="T187">
+        <v>1.5</v>
+      </c>
+      <c r="U187">
+        <v>2.5</v>
+      </c>
+      <c r="V187">
+        <v>3.4</v>
+      </c>
+      <c r="W187">
+        <v>1.3</v>
+      </c>
+      <c r="X187">
+        <v>10</v>
+      </c>
+      <c r="Y187">
+        <v>1.06</v>
+      </c>
+      <c r="Z187">
+        <v>2.25</v>
+      </c>
+      <c r="AA187">
+        <v>3.1</v>
+      </c>
+      <c r="AB187">
+        <v>3.1</v>
+      </c>
+      <c r="AC187">
+        <v>1.08</v>
+      </c>
+      <c r="AD187">
+        <v>8</v>
+      </c>
+      <c r="AE187">
+        <v>1.42</v>
+      </c>
+      <c r="AF187">
+        <v>2.9</v>
+      </c>
+      <c r="AG187">
+        <v>2.15</v>
+      </c>
+      <c r="AH187">
+        <v>1.65</v>
+      </c>
+      <c r="AI187">
+        <v>1.95</v>
+      </c>
+      <c r="AJ187">
+        <v>1.8</v>
+      </c>
+      <c r="AK187">
+        <v>1.35</v>
+      </c>
+      <c r="AL187">
+        <v>1.34</v>
+      </c>
+      <c r="AM187">
+        <v>1.57</v>
+      </c>
+      <c r="AN187">
+        <v>0.78</v>
+      </c>
+      <c r="AO187">
+        <v>0.3</v>
+      </c>
+      <c r="AP187">
+        <v>0.7</v>
+      </c>
+      <c r="AQ187">
+        <v>0.55</v>
+      </c>
+      <c r="AR187">
+        <v>1.2</v>
+      </c>
+      <c r="AS187">
+        <v>1.26</v>
+      </c>
+      <c r="AT187">
+        <v>2.46</v>
+      </c>
+      <c r="AU187">
+        <v>6</v>
+      </c>
+      <c r="AV187">
+        <v>5</v>
+      </c>
+      <c r="AW187">
+        <v>17</v>
+      </c>
+      <c r="AX187">
+        <v>6</v>
+      </c>
+      <c r="AY187">
+        <v>27</v>
+      </c>
+      <c r="AZ187">
+        <v>14</v>
+      </c>
+      <c r="BA187">
+        <v>12</v>
+      </c>
+      <c r="BB187">
+        <v>3</v>
+      </c>
+      <c r="BC187">
+        <v>15</v>
+      </c>
+      <c r="BD187">
+        <v>1.75</v>
+      </c>
+      <c r="BE187">
+        <v>6.1</v>
+      </c>
+      <c r="BF187">
+        <v>2.52</v>
+      </c>
+      <c r="BG187">
+        <v>1.14</v>
+      </c>
+      <c r="BH187">
+        <v>4.45</v>
+      </c>
+      <c r="BI187">
+        <v>1.26</v>
+      </c>
+      <c r="BJ187">
+        <v>3.3</v>
+      </c>
+      <c r="BK187">
+        <v>1.49</v>
+      </c>
+      <c r="BL187">
+        <v>2.35</v>
+      </c>
+      <c r="BM187">
+        <v>1.83</v>
+      </c>
+      <c r="BN187">
+        <v>1.8</v>
+      </c>
+      <c r="BO187">
+        <v>2.37</v>
+      </c>
+      <c r="BP187">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7574748</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45697.625</v>
+      </c>
+      <c r="F188">
+        <v>21</v>
+      </c>
+      <c r="G188" t="s">
+        <v>77</v>
+      </c>
+      <c r="H188" t="s">
+        <v>80</v>
+      </c>
+      <c r="I188">
+        <v>1</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>1</v>
+      </c>
+      <c r="L188">
+        <v>2</v>
+      </c>
+      <c r="M188">
+        <v>0</v>
+      </c>
+      <c r="N188">
+        <v>2</v>
+      </c>
+      <c r="O188" t="s">
+        <v>210</v>
+      </c>
+      <c r="P188" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q188">
+        <v>2.1</v>
+      </c>
+      <c r="R188">
+        <v>2.3</v>
+      </c>
+      <c r="S188">
+        <v>6</v>
+      </c>
+      <c r="T188">
+        <v>1.36</v>
+      </c>
+      <c r="U188">
+        <v>3</v>
+      </c>
+      <c r="V188">
+        <v>2.75</v>
+      </c>
+      <c r="W188">
+        <v>1.4</v>
+      </c>
+      <c r="X188">
+        <v>7</v>
+      </c>
+      <c r="Y188">
+        <v>1.1</v>
+      </c>
+      <c r="Z188">
+        <v>1.47</v>
+      </c>
+      <c r="AA188">
+        <v>4.2</v>
+      </c>
+      <c r="AB188">
+        <v>6</v>
+      </c>
+      <c r="AC188">
+        <v>1.04</v>
+      </c>
+      <c r="AD188">
+        <v>12</v>
+      </c>
+      <c r="AE188">
+        <v>1.28</v>
+      </c>
+      <c r="AF188">
+        <v>3.6</v>
+      </c>
+      <c r="AG188">
+        <v>1.7</v>
+      </c>
+      <c r="AH188">
+        <v>2.05</v>
+      </c>
+      <c r="AI188">
+        <v>1.95</v>
+      </c>
+      <c r="AJ188">
+        <v>1.8</v>
+      </c>
+      <c r="AK188">
+        <v>1.13</v>
+      </c>
+      <c r="AL188">
+        <v>1.22</v>
+      </c>
+      <c r="AM188">
+        <v>2.45</v>
+      </c>
+      <c r="AN188">
+        <v>1.5</v>
+      </c>
+      <c r="AO188">
+        <v>0.6</v>
+      </c>
+      <c r="AP188">
+        <v>1.64</v>
+      </c>
+      <c r="AQ188">
+        <v>0.55</v>
+      </c>
+      <c r="AR188">
+        <v>1.68</v>
+      </c>
+      <c r="AS188">
+        <v>0.91</v>
+      </c>
+      <c r="AT188">
+        <v>2.59</v>
+      </c>
+      <c r="AU188">
+        <v>6</v>
+      </c>
+      <c r="AV188">
+        <v>5</v>
+      </c>
+      <c r="AW188">
+        <v>8</v>
+      </c>
+      <c r="AX188">
+        <v>3</v>
+      </c>
+      <c r="AY188">
+        <v>16</v>
+      </c>
+      <c r="AZ188">
+        <v>9</v>
+      </c>
+      <c r="BA188">
+        <v>4</v>
+      </c>
+      <c r="BB188">
+        <v>2</v>
+      </c>
+      <c r="BC188">
+        <v>6</v>
+      </c>
+      <c r="BD188">
+        <v>1.12</v>
+      </c>
+      <c r="BE188">
+        <v>10.5</v>
+      </c>
+      <c r="BF188">
+        <v>6.9</v>
+      </c>
+      <c r="BG188">
+        <v>1.24</v>
+      </c>
+      <c r="BH188">
+        <v>3.5</v>
+      </c>
+      <c r="BI188">
+        <v>1.44</v>
+      </c>
+      <c r="BJ188">
+        <v>2.45</v>
+      </c>
+      <c r="BK188">
+        <v>1.8</v>
+      </c>
+      <c r="BL188">
+        <v>1.85</v>
+      </c>
+      <c r="BM188">
+        <v>2.35</v>
+      </c>
+      <c r="BN188">
+        <v>1.49</v>
+      </c>
+      <c r="BO188">
+        <v>3.25</v>
+      </c>
+      <c r="BP188">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7574743</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45697.72916666666</v>
+      </c>
+      <c r="F189">
+        <v>21</v>
+      </c>
+      <c r="G189" t="s">
+        <v>72</v>
+      </c>
+      <c r="H189" t="s">
+        <v>87</v>
+      </c>
+      <c r="I189">
+        <v>1</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>1</v>
+      </c>
+      <c r="L189">
+        <v>1</v>
+      </c>
+      <c r="M189">
+        <v>0</v>
+      </c>
+      <c r="N189">
+        <v>1</v>
+      </c>
+      <c r="O189" t="s">
+        <v>211</v>
+      </c>
+      <c r="P189" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q189">
+        <v>2.5</v>
+      </c>
+      <c r="R189">
+        <v>2.05</v>
+      </c>
+      <c r="S189">
+        <v>5</v>
+      </c>
+      <c r="T189">
+        <v>1.5</v>
+      </c>
+      <c r="U189">
+        <v>2.5</v>
+      </c>
+      <c r="V189">
+        <v>3.4</v>
+      </c>
+      <c r="W189">
+        <v>1.3</v>
+      </c>
+      <c r="X189">
+        <v>10</v>
+      </c>
+      <c r="Y189">
+        <v>1.06</v>
+      </c>
+      <c r="Z189">
+        <v>1.8</v>
+      </c>
+      <c r="AA189">
+        <v>3.3</v>
+      </c>
+      <c r="AB189">
+        <v>4.5</v>
+      </c>
+      <c r="AC189">
+        <v>1.08</v>
+      </c>
+      <c r="AD189">
+        <v>8.5</v>
+      </c>
+      <c r="AE189">
+        <v>1.45</v>
+      </c>
+      <c r="AF189">
+        <v>2.75</v>
+      </c>
+      <c r="AG189">
+        <v>2.2</v>
+      </c>
+      <c r="AH189">
+        <v>1.61</v>
+      </c>
+      <c r="AI189">
+        <v>2.05</v>
+      </c>
+      <c r="AJ189">
+        <v>1.7</v>
+      </c>
+      <c r="AK189">
+        <v>1.2</v>
+      </c>
+      <c r="AL189">
+        <v>1.3</v>
+      </c>
+      <c r="AM189">
+        <v>1.93</v>
+      </c>
+      <c r="AN189">
+        <v>1.6</v>
+      </c>
+      <c r="AO189">
+        <v>0.33</v>
+      </c>
+      <c r="AP189">
+        <v>1.73</v>
+      </c>
+      <c r="AQ189">
+        <v>0.3</v>
+      </c>
+      <c r="AR189">
+        <v>1.19</v>
+      </c>
+      <c r="AS189">
+        <v>1.03</v>
+      </c>
+      <c r="AT189">
+        <v>2.22</v>
+      </c>
+      <c r="AU189">
+        <v>5</v>
+      </c>
+      <c r="AV189">
+        <v>5</v>
+      </c>
+      <c r="AW189">
+        <v>12</v>
+      </c>
+      <c r="AX189">
+        <v>8</v>
+      </c>
+      <c r="AY189">
+        <v>18</v>
+      </c>
+      <c r="AZ189">
+        <v>15</v>
+      </c>
+      <c r="BA189">
+        <v>5</v>
+      </c>
+      <c r="BB189">
+        <v>2</v>
+      </c>
+      <c r="BC189">
+        <v>7</v>
+      </c>
+      <c r="BD189">
+        <v>1.6</v>
+      </c>
+      <c r="BE189">
+        <v>6.75</v>
+      </c>
+      <c r="BF189">
+        <v>2.55</v>
+      </c>
+      <c r="BG189">
+        <v>1.28</v>
+      </c>
+      <c r="BH189">
+        <v>3.2</v>
+      </c>
+      <c r="BI189">
+        <v>1.49</v>
+      </c>
+      <c r="BJ189">
+        <v>2.38</v>
+      </c>
+      <c r="BK189">
+        <v>1.7</v>
+      </c>
+      <c r="BL189">
+        <v>2.05</v>
+      </c>
+      <c r="BM189">
+        <v>2.23</v>
+      </c>
+      <c r="BN189">
+        <v>1.56</v>
+      </c>
+      <c r="BO189">
+        <v>2.8</v>
+      </c>
+      <c r="BP189">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="300">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -912,6 +912,9 @@
   <si>
     <t>['19', '85']</t>
   </si>
+  <si>
+    <t>['90+6']</t>
+  </si>
 </sst>
 </file>
 
@@ -1272,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP189"/>
+  <dimension ref="A1:BP190"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1609,7 +1612,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ2">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -3254,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -5729,7 +5732,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ22">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR22">
         <v>1.3</v>
@@ -6344,7 +6347,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ25">
         <v>0.55</v>
@@ -9022,7 +9025,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ38">
         <v>2.18</v>
@@ -9437,7 +9440,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ40">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR40">
         <v>1.32</v>
@@ -13969,7 +13972,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ62">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR62">
         <v>1.53</v>
@@ -15202,7 +15205,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ68">
         <v>0.5</v>
@@ -17471,7 +17474,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ79">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR79">
         <v>2.16</v>
@@ -19322,7 +19325,7 @@
         <v>1.75</v>
       </c>
       <c r="AP88">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ88">
         <v>2.5</v>
@@ -20767,7 +20770,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ95">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR95">
         <v>1.16</v>
@@ -22824,7 +22827,7 @@
         <v>1.75</v>
       </c>
       <c r="AP105">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ105">
         <v>1.7</v>
@@ -24475,7 +24478,7 @@
         <v>2</v>
       </c>
       <c r="AQ113">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR113">
         <v>1.38</v>
@@ -26120,7 +26123,7 @@
         <v>1.5</v>
       </c>
       <c r="AP121">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ121">
         <v>1.6</v>
@@ -29213,7 +29216,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ136">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR136">
         <v>1.19</v>
@@ -29416,7 +29419,7 @@
         <v>0.63</v>
       </c>
       <c r="AP137">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ137">
         <v>0.55</v>
@@ -32715,7 +32718,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ153">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR153">
         <v>1.2</v>
@@ -34978,7 +34981,7 @@
         <v>0.78</v>
       </c>
       <c r="AP164">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ164">
         <v>0.64</v>
@@ -35187,7 +35190,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ165">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR165">
         <v>1.12</v>
@@ -40207,6 +40210,212 @@
       </c>
       <c r="BP189">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="190" spans="1:68">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7574746</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" t="s">
+        <v>69</v>
+      </c>
+      <c r="E190" s="2">
+        <v>45698.71875</v>
+      </c>
+      <c r="F190">
+        <v>21</v>
+      </c>
+      <c r="G190" t="s">
+        <v>78</v>
+      </c>
+      <c r="H190" t="s">
+        <v>81</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+      <c r="K190">
+        <v>0</v>
+      </c>
+      <c r="L190">
+        <v>1</v>
+      </c>
+      <c r="M190">
+        <v>1</v>
+      </c>
+      <c r="N190">
+        <v>2</v>
+      </c>
+      <c r="O190" t="s">
+        <v>184</v>
+      </c>
+      <c r="P190" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q190">
+        <v>2.63</v>
+      </c>
+      <c r="R190">
+        <v>2.05</v>
+      </c>
+      <c r="S190">
+        <v>4.5</v>
+      </c>
+      <c r="T190">
+        <v>1.44</v>
+      </c>
+      <c r="U190">
+        <v>2.63</v>
+      </c>
+      <c r="V190">
+        <v>3.25</v>
+      </c>
+      <c r="W190">
+        <v>1.33</v>
+      </c>
+      <c r="X190">
+        <v>10</v>
+      </c>
+      <c r="Y190">
+        <v>1.06</v>
+      </c>
+      <c r="Z190">
+        <v>1.95</v>
+      </c>
+      <c r="AA190">
+        <v>3.25</v>
+      </c>
+      <c r="AB190">
+        <v>3.9</v>
+      </c>
+      <c r="AC190">
+        <v>1.07</v>
+      </c>
+      <c r="AD190">
+        <v>9</v>
+      </c>
+      <c r="AE190">
+        <v>1.38</v>
+      </c>
+      <c r="AF190">
+        <v>3</v>
+      </c>
+      <c r="AG190">
+        <v>2.1</v>
+      </c>
+      <c r="AH190">
+        <v>1.67</v>
+      </c>
+      <c r="AI190">
+        <v>1.95</v>
+      </c>
+      <c r="AJ190">
+        <v>1.8</v>
+      </c>
+      <c r="AK190">
+        <v>1.25</v>
+      </c>
+      <c r="AL190">
+        <v>1.28</v>
+      </c>
+      <c r="AM190">
+        <v>1.83</v>
+      </c>
+      <c r="AN190">
+        <v>1.22</v>
+      </c>
+      <c r="AO190">
+        <v>0.7</v>
+      </c>
+      <c r="AP190">
+        <v>1.2</v>
+      </c>
+      <c r="AQ190">
+        <v>0.73</v>
+      </c>
+      <c r="AR190">
+        <v>1.16</v>
+      </c>
+      <c r="AS190">
+        <v>0.92</v>
+      </c>
+      <c r="AT190">
+        <v>2.08</v>
+      </c>
+      <c r="AU190">
+        <v>5</v>
+      </c>
+      <c r="AV190">
+        <v>5</v>
+      </c>
+      <c r="AW190">
+        <v>13</v>
+      </c>
+      <c r="AX190">
+        <v>7</v>
+      </c>
+      <c r="AY190">
+        <v>24</v>
+      </c>
+      <c r="AZ190">
+        <v>16</v>
+      </c>
+      <c r="BA190">
+        <v>6</v>
+      </c>
+      <c r="BB190">
+        <v>3</v>
+      </c>
+      <c r="BC190">
+        <v>9</v>
+      </c>
+      <c r="BD190">
+        <v>1.44</v>
+      </c>
+      <c r="BE190">
+        <v>6.75</v>
+      </c>
+      <c r="BF190">
+        <v>3.05</v>
+      </c>
+      <c r="BG190">
+        <v>1.29</v>
+      </c>
+      <c r="BH190">
+        <v>3.15</v>
+      </c>
+      <c r="BI190">
+        <v>1.49</v>
+      </c>
+      <c r="BJ190">
+        <v>2.38</v>
+      </c>
+      <c r="BK190">
+        <v>1.8</v>
+      </c>
+      <c r="BL190">
+        <v>1.86</v>
+      </c>
+      <c r="BM190">
+        <v>2.2</v>
+      </c>
+      <c r="BN190">
+        <v>1.56</v>
+      </c>
+      <c r="BO190">
+        <v>2.88</v>
+      </c>
+      <c r="BP190">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="300">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1275,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3054,7 +3054,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ9">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -4905,7 +4905,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ18">
         <v>2.5</v>
@@ -6144,7 +6144,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ24">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR24">
         <v>2.62</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ32">
         <v>1.2</v>
@@ -11294,7 +11294,7 @@
         <v>2</v>
       </c>
       <c r="AQ49">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR49">
         <v>1.09</v>
@@ -12527,7 +12527,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ55">
         <v>1.7</v>
@@ -14796,7 +14796,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ66">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR66">
         <v>1.45</v>
@@ -16853,7 +16853,7 @@
         <v>0.75</v>
       </c>
       <c r="AP76">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ76">
         <v>0.64</v>
@@ -18092,7 +18092,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ82">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR82">
         <v>2.06</v>
@@ -20767,7 +20767,7 @@
         <v>0</v>
       </c>
       <c r="AP95">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ95">
         <v>0.73</v>
@@ -21800,7 +21800,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ100">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR100">
         <v>1.15</v>
@@ -24887,7 +24887,7 @@
         <v>0.33</v>
       </c>
       <c r="AP115">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ115">
         <v>0.73</v>
@@ -26950,7 +26950,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ125">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR125">
         <v>2.03</v>
@@ -27977,7 +27977,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ130">
         <v>0.5</v>
@@ -29628,7 +29628,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ138">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR138">
         <v>1.22</v>
@@ -31891,7 +31891,7 @@
         <v>0.5</v>
       </c>
       <c r="AP149">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ149">
         <v>1</v>
@@ -34775,7 +34775,7 @@
         <v>1.38</v>
       </c>
       <c r="AP163">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ163">
         <v>1.4</v>
@@ -35396,7 +35396,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ166">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR166">
         <v>1.12</v>
@@ -36835,7 +36835,7 @@
         <v>1.11</v>
       </c>
       <c r="AP173">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ173">
         <v>1.3</v>
@@ -40134,7 +40134,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ189">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR189">
         <v>1.19</v>
@@ -40416,6 +40416,212 @@
       </c>
       <c r="BP190">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7574753</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45702.71875</v>
+      </c>
+      <c r="F191">
+        <v>22</v>
+      </c>
+      <c r="G191" t="s">
+        <v>86</v>
+      </c>
+      <c r="H191" t="s">
+        <v>87</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>1</v>
+      </c>
+      <c r="K191">
+        <v>1</v>
+      </c>
+      <c r="L191">
+        <v>0</v>
+      </c>
+      <c r="M191">
+        <v>1</v>
+      </c>
+      <c r="N191">
+        <v>1</v>
+      </c>
+      <c r="O191" t="s">
+        <v>90</v>
+      </c>
+      <c r="P191" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q191">
+        <v>3.5</v>
+      </c>
+      <c r="R191">
+        <v>1.95</v>
+      </c>
+      <c r="S191">
+        <v>3.1</v>
+      </c>
+      <c r="T191">
+        <v>1.49</v>
+      </c>
+      <c r="U191">
+        <v>2.4</v>
+      </c>
+      <c r="V191">
+        <v>3.25</v>
+      </c>
+      <c r="W191">
+        <v>1.29</v>
+      </c>
+      <c r="X191">
+        <v>9.25</v>
+      </c>
+      <c r="Y191">
+        <v>1.05</v>
+      </c>
+      <c r="Z191">
+        <v>3.1</v>
+      </c>
+      <c r="AA191">
+        <v>2.9</v>
+      </c>
+      <c r="AB191">
+        <v>2.4</v>
+      </c>
+      <c r="AC191">
+        <v>1.09</v>
+      </c>
+      <c r="AD191">
+        <v>7</v>
+      </c>
+      <c r="AE191">
+        <v>1.44</v>
+      </c>
+      <c r="AF191">
+        <v>2.7</v>
+      </c>
+      <c r="AG191">
+        <v>2.3</v>
+      </c>
+      <c r="AH191">
+        <v>1.57</v>
+      </c>
+      <c r="AI191">
+        <v>1.98</v>
+      </c>
+      <c r="AJ191">
+        <v>1.73</v>
+      </c>
+      <c r="AK191">
+        <v>1.53</v>
+      </c>
+      <c r="AL191">
+        <v>1.34</v>
+      </c>
+      <c r="AM191">
+        <v>1.38</v>
+      </c>
+      <c r="AN191">
+        <v>0.3</v>
+      </c>
+      <c r="AO191">
+        <v>0.3</v>
+      </c>
+      <c r="AP191">
+        <v>0.27</v>
+      </c>
+      <c r="AQ191">
+        <v>0.55</v>
+      </c>
+      <c r="AR191">
+        <v>1.28</v>
+      </c>
+      <c r="AS191">
+        <v>1.07</v>
+      </c>
+      <c r="AT191">
+        <v>2.35</v>
+      </c>
+      <c r="AU191">
+        <v>2</v>
+      </c>
+      <c r="AV191">
+        <v>6</v>
+      </c>
+      <c r="AW191">
+        <v>13</v>
+      </c>
+      <c r="AX191">
+        <v>3</v>
+      </c>
+      <c r="AY191">
+        <v>16</v>
+      </c>
+      <c r="AZ191">
+        <v>9</v>
+      </c>
+      <c r="BA191">
+        <v>7</v>
+      </c>
+      <c r="BB191">
+        <v>4</v>
+      </c>
+      <c r="BC191">
+        <v>11</v>
+      </c>
+      <c r="BD191">
+        <v>1.93</v>
+      </c>
+      <c r="BE191">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF191">
+        <v>2.2</v>
+      </c>
+      <c r="BG191">
+        <v>1.26</v>
+      </c>
+      <c r="BH191">
+        <v>3.22</v>
+      </c>
+      <c r="BI191">
+        <v>1.51</v>
+      </c>
+      <c r="BJ191">
+        <v>2.32</v>
+      </c>
+      <c r="BK191">
+        <v>1.95</v>
+      </c>
+      <c r="BL191">
+        <v>1.85</v>
+      </c>
+      <c r="BM191">
+        <v>2.45</v>
+      </c>
+      <c r="BN191">
+        <v>1.46</v>
+      </c>
+      <c r="BO191">
+        <v>3.28</v>
+      </c>
+      <c r="BP191">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="306">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -652,6 +652,15 @@
     <t>['37']</t>
   </si>
   <si>
+    <t>['12', '26', '32']</t>
+  </si>
+  <si>
+    <t>['45+4', '52']</t>
+  </si>
+  <si>
+    <t>['17', '74']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -914,6 +923,15 @@
   </si>
   <si>
     <t>['90+6']</t>
+  </si>
+  <si>
+    <t>['50', '90+6']</t>
+  </si>
+  <si>
+    <t>['4', '90+3']</t>
+  </si>
+  <si>
+    <t>['8', '45+5']</t>
   </si>
 </sst>
 </file>
@@ -1275,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP191"/>
+  <dimension ref="A1:BP195"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1609,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ2">
         <v>0.73</v>
@@ -1737,7 +1755,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2355,7 +2373,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2642,7 +2660,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ7">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2767,7 +2785,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -3385,7 +3403,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3463,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ11">
         <v>1.4</v>
@@ -3591,7 +3609,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4003,7 +4021,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4081,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ14">
         <v>2.18</v>
@@ -4290,7 +4308,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ15">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4415,7 +4433,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4493,7 +4511,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ16">
         <v>1</v>
@@ -4702,7 +4720,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ17">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4827,7 +4845,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -5033,7 +5051,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5239,7 +5257,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5445,7 +5463,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -7093,7 +7111,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7171,10 +7189,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ29">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR29">
         <v>1.3</v>
@@ -7299,7 +7317,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7377,7 +7395,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ30">
         <v>0.5</v>
@@ -7505,7 +7523,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -7586,7 +7604,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ31">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR31">
         <v>1</v>
@@ -7792,7 +7810,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ32">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR32">
         <v>0.64</v>
@@ -7995,7 +8013,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ33">
         <v>1.4</v>
@@ -8201,7 +8219,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ34">
         <v>0.73</v>
@@ -8535,7 +8553,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q36">
         <v>2.55</v>
@@ -8947,7 +8965,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9153,7 +9171,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9565,7 +9583,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9771,7 +9789,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -9977,7 +9995,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10389,7 +10407,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10595,7 +10613,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10801,7 +10819,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10879,7 +10897,7 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ47">
         <v>2.5</v>
@@ -11007,7 +11025,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11088,7 +11106,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ48">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR48">
         <v>1.23</v>
@@ -11291,7 +11309,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ49">
         <v>0.55</v>
@@ -11419,7 +11437,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11703,7 +11721,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ51">
         <v>1.3</v>
@@ -11831,7 +11849,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -11912,7 +11930,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ52">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR52">
         <v>1.51</v>
@@ -12321,7 +12339,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ54">
         <v>0.5</v>
@@ -12449,7 +12467,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12530,7 +12548,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ55">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR55">
         <v>1.28</v>
@@ -12655,7 +12673,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -13067,7 +13085,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13273,7 +13291,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -14175,7 +14193,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ63">
         <v>0.82</v>
@@ -14999,7 +15017,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ67">
         <v>1.6</v>
@@ -15411,10 +15429,10 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ69">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR69">
         <v>2.1</v>
@@ -15620,7 +15638,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ70">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR70">
         <v>1.2</v>
@@ -15745,7 +15763,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -15951,7 +15969,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16363,7 +16381,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16441,7 +16459,7 @@
         <v>0.5</v>
       </c>
       <c r="AP74">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ74">
         <v>0.55</v>
@@ -16569,7 +16587,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16775,7 +16793,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16981,7 +16999,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17599,7 +17617,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17805,7 +17823,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -18011,7 +18029,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18089,7 +18107,7 @@
         <v>0.25</v>
       </c>
       <c r="AP82">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ82">
         <v>0.55</v>
@@ -18217,7 +18235,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18298,7 +18316,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ83">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR83">
         <v>1.47</v>
@@ -18423,7 +18441,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18504,7 +18522,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ84">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR84">
         <v>1.17</v>
@@ -18629,7 +18647,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18835,7 +18853,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19247,7 +19265,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19534,7 +19552,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ89">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR89">
         <v>2.03</v>
@@ -19737,7 +19755,7 @@
         <v>1.5</v>
       </c>
       <c r="AP90">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ90">
         <v>1.6</v>
@@ -19865,7 +19883,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -19943,7 +19961,7 @@
         <v>0.4</v>
       </c>
       <c r="AP91">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ91">
         <v>0.55</v>
@@ -20071,7 +20089,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20689,7 +20707,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -21179,7 +21197,7 @@
         <v>1.6</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ97">
         <v>1</v>
@@ -21307,7 +21325,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21925,7 +21943,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22209,7 +22227,7 @@
         <v>1.33</v>
       </c>
       <c r="AP102">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ102">
         <v>0.82</v>
@@ -22337,7 +22355,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22415,7 +22433,7 @@
         <v>1.2</v>
       </c>
       <c r="AP103">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ103">
         <v>1.6</v>
@@ -22749,7 +22767,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -22830,7 +22848,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ105">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR105">
         <v>0.97</v>
@@ -22955,7 +22973,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q106">
         <v>5.5</v>
@@ -23448,7 +23466,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ108">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR108">
         <v>2.03</v>
@@ -23651,7 +23669,7 @@
         <v>3</v>
       </c>
       <c r="AP109">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ109">
         <v>2.18</v>
@@ -23779,7 +23797,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -23860,7 +23878,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ110">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR110">
         <v>1.54</v>
@@ -23985,7 +24003,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q111">
         <v>2.75</v>
@@ -24475,7 +24493,7 @@
         <v>0.5</v>
       </c>
       <c r="AP113">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ113">
         <v>0.73</v>
@@ -25711,7 +25729,7 @@
         <v>0.86</v>
       </c>
       <c r="AP119">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ119">
         <v>0.64</v>
@@ -25839,7 +25857,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -25917,7 +25935,7 @@
         <v>1.29</v>
       </c>
       <c r="AP120">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ120">
         <v>0.82</v>
@@ -26251,7 +26269,7 @@
         <v>167</v>
       </c>
       <c r="P122" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q122">
         <v>11</v>
@@ -26332,7 +26350,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ122">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR122">
         <v>1.11</v>
@@ -26457,7 +26475,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26538,7 +26556,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ123">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR123">
         <v>1.04</v>
@@ -26663,7 +26681,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -27075,7 +27093,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27281,7 +27299,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27359,10 +27377,10 @@
         <v>1.83</v>
       </c>
       <c r="AP127">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ127">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR127">
         <v>1.37</v>
@@ -27487,7 +27505,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27693,7 +27711,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -28105,7 +28123,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28183,7 +28201,7 @@
         <v>1.67</v>
       </c>
       <c r="AP131">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ131">
         <v>1.4</v>
@@ -28311,7 +28329,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28389,7 +28407,7 @@
         <v>2.17</v>
       </c>
       <c r="AP132">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ132">
         <v>2.5</v>
@@ -28723,7 +28741,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -29010,7 +29028,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ135">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR135">
         <v>2.03</v>
@@ -29547,7 +29565,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29753,7 +29771,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -30165,7 +30183,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30371,7 +30389,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30577,7 +30595,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -30658,7 +30676,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ143">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR143">
         <v>1.64</v>
@@ -30861,10 +30879,10 @@
         <v>2</v>
       </c>
       <c r="AP144">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ144">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR144">
         <v>2.11</v>
@@ -30989,7 +31007,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31195,7 +31213,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31401,7 +31419,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q147">
         <v>2.55</v>
@@ -31479,7 +31497,7 @@
         <v>0.57</v>
       </c>
       <c r="AP147">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ147">
         <v>0.5</v>
@@ -31607,7 +31625,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31813,7 +31831,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32097,7 +32115,7 @@
         <v>0.75</v>
       </c>
       <c r="AP150">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ150">
         <v>0.73</v>
@@ -32225,7 +32243,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32431,7 +32449,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32512,7 +32530,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ152">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR152">
         <v>1.17</v>
@@ -32637,7 +32655,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -32921,7 +32939,7 @@
         <v>1.86</v>
       </c>
       <c r="AP154">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ154">
         <v>1.4</v>
@@ -33255,7 +33273,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33333,10 +33351,10 @@
         <v>0.75</v>
       </c>
       <c r="AP156">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ156">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR156">
         <v>1.41</v>
@@ -33461,7 +33479,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33667,7 +33685,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33873,7 +33891,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -33951,7 +33969,7 @@
         <v>0.63</v>
       </c>
       <c r="AP159">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ159">
         <v>0.5</v>
@@ -34157,7 +34175,7 @@
         <v>0.78</v>
       </c>
       <c r="AP160">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ160">
         <v>0.73</v>
@@ -34285,7 +34303,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34491,7 +34509,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34697,7 +34715,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -34778,7 +34796,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ163">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR163">
         <v>1.32</v>
@@ -35109,7 +35127,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35602,7 +35620,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ167">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR167">
         <v>1.21</v>
@@ -35805,7 +35823,7 @@
         <v>0.33</v>
       </c>
       <c r="AP168">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ168">
         <v>0.55</v>
@@ -36139,7 +36157,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36757,7 +36775,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -37041,10 +37059,10 @@
         <v>1.56</v>
       </c>
       <c r="AP174">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ174">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR174">
         <v>1.43</v>
@@ -37169,7 +37187,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37247,7 +37265,7 @@
         <v>0.8</v>
       </c>
       <c r="AP175">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ175">
         <v>1</v>
@@ -37375,7 +37393,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -37456,7 +37474,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ176">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR176">
         <v>1.21</v>
@@ -37865,7 +37883,7 @@
         <v>0.8</v>
       </c>
       <c r="AP178">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ178">
         <v>0.73</v>
@@ -37993,7 +38011,7 @@
         <v>205</v>
       </c>
       <c r="P179" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q179">
         <v>8.5</v>
@@ -38074,7 +38092,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ179">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR179">
         <v>1.18</v>
@@ -38199,7 +38217,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q180">
         <v>4.75</v>
@@ -38277,7 +38295,7 @@
         <v>2.44</v>
       </c>
       <c r="AP180">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ180">
         <v>2.5</v>
@@ -38405,7 +38423,7 @@
         <v>207</v>
       </c>
       <c r="P181" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q181">
         <v>6.5</v>
@@ -38611,7 +38629,7 @@
         <v>167</v>
       </c>
       <c r="P182" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -39023,7 +39041,7 @@
         <v>208</v>
       </c>
       <c r="P184" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q184">
         <v>1.57</v>
@@ -39435,7 +39453,7 @@
         <v>209</v>
       </c>
       <c r="P186" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q186">
         <v>2.2</v>
@@ -40259,7 +40277,7 @@
         <v>184</v>
       </c>
       <c r="P190" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q190">
         <v>2.63</v>
@@ -40622,6 +40640,830 @@
       </c>
       <c r="BP191">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7574760</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45703.52083333334</v>
+      </c>
+      <c r="F192">
+        <v>22</v>
+      </c>
+      <c r="G192" t="s">
+        <v>84</v>
+      </c>
+      <c r="H192" t="s">
+        <v>72</v>
+      </c>
+      <c r="I192">
+        <v>3</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>3</v>
+      </c>
+      <c r="L192">
+        <v>3</v>
+      </c>
+      <c r="M192">
+        <v>2</v>
+      </c>
+      <c r="N192">
+        <v>5</v>
+      </c>
+      <c r="O192" t="s">
+        <v>212</v>
+      </c>
+      <c r="P192" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q192">
+        <v>2.95</v>
+      </c>
+      <c r="R192">
+        <v>1.93</v>
+      </c>
+      <c r="S192">
+        <v>3.8</v>
+      </c>
+      <c r="T192">
+        <v>1.5</v>
+      </c>
+      <c r="U192">
+        <v>2.37</v>
+      </c>
+      <c r="V192">
+        <v>3.3</v>
+      </c>
+      <c r="W192">
+        <v>1.28</v>
+      </c>
+      <c r="X192">
+        <v>9.5</v>
+      </c>
+      <c r="Y192">
+        <v>1.05</v>
+      </c>
+      <c r="Z192">
+        <v>2.2</v>
+      </c>
+      <c r="AA192">
+        <v>3.1</v>
+      </c>
+      <c r="AB192">
+        <v>3.3</v>
+      </c>
+      <c r="AC192">
+        <v>1.1</v>
+      </c>
+      <c r="AD192">
+        <v>6.5</v>
+      </c>
+      <c r="AE192">
+        <v>1.5</v>
+      </c>
+      <c r="AF192">
+        <v>2.45</v>
+      </c>
+      <c r="AG192">
+        <v>2.46</v>
+      </c>
+      <c r="AH192">
+        <v>1.51</v>
+      </c>
+      <c r="AI192">
+        <v>2</v>
+      </c>
+      <c r="AJ192">
+        <v>1.7</v>
+      </c>
+      <c r="AK192">
+        <v>1.32</v>
+      </c>
+      <c r="AL192">
+        <v>1.34</v>
+      </c>
+      <c r="AM192">
+        <v>1.6</v>
+      </c>
+      <c r="AN192">
+        <v>1.6</v>
+      </c>
+      <c r="AO192">
+        <v>1.4</v>
+      </c>
+      <c r="AP192">
+        <v>1.73</v>
+      </c>
+      <c r="AQ192">
+        <v>1.27</v>
+      </c>
+      <c r="AR192">
+        <v>1.22</v>
+      </c>
+      <c r="AS192">
+        <v>1.06</v>
+      </c>
+      <c r="AT192">
+        <v>2.28</v>
+      </c>
+      <c r="AU192">
+        <v>6</v>
+      </c>
+      <c r="AV192">
+        <v>4</v>
+      </c>
+      <c r="AW192">
+        <v>8</v>
+      </c>
+      <c r="AX192">
+        <v>11</v>
+      </c>
+      <c r="AY192">
+        <v>19</v>
+      </c>
+      <c r="AZ192">
+        <v>20</v>
+      </c>
+      <c r="BA192">
+        <v>4</v>
+      </c>
+      <c r="BB192">
+        <v>5</v>
+      </c>
+      <c r="BC192">
+        <v>9</v>
+      </c>
+      <c r="BD192">
+        <v>1.74</v>
+      </c>
+      <c r="BE192">
+        <v>6.4</v>
+      </c>
+      <c r="BF192">
+        <v>2.32</v>
+      </c>
+      <c r="BG192">
+        <v>1.34</v>
+      </c>
+      <c r="BH192">
+        <v>2.85</v>
+      </c>
+      <c r="BI192">
+        <v>1.6</v>
+      </c>
+      <c r="BJ192">
+        <v>2.15</v>
+      </c>
+      <c r="BK192">
+        <v>1.96</v>
+      </c>
+      <c r="BL192">
+        <v>1.71</v>
+      </c>
+      <c r="BM192">
+        <v>2.5</v>
+      </c>
+      <c r="BN192">
+        <v>1.44</v>
+      </c>
+      <c r="BO192">
+        <v>3.3</v>
+      </c>
+      <c r="BP192">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7574756</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45703.58333333334</v>
+      </c>
+      <c r="F193">
+        <v>22</v>
+      </c>
+      <c r="G193" t="s">
+        <v>82</v>
+      </c>
+      <c r="H193" t="s">
+        <v>74</v>
+      </c>
+      <c r="I193">
+        <v>1</v>
+      </c>
+      <c r="J193">
+        <v>1</v>
+      </c>
+      <c r="K193">
+        <v>2</v>
+      </c>
+      <c r="L193">
+        <v>2</v>
+      </c>
+      <c r="M193">
+        <v>2</v>
+      </c>
+      <c r="N193">
+        <v>4</v>
+      </c>
+      <c r="O193" t="s">
+        <v>213</v>
+      </c>
+      <c r="P193" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q193">
+        <v>2.8</v>
+      </c>
+      <c r="R193">
+        <v>2</v>
+      </c>
+      <c r="S193">
+        <v>3.7</v>
+      </c>
+      <c r="T193">
+        <v>1.44</v>
+      </c>
+      <c r="U193">
+        <v>2.6</v>
+      </c>
+      <c r="V193">
+        <v>3</v>
+      </c>
+      <c r="W193">
+        <v>1.33</v>
+      </c>
+      <c r="X193">
+        <v>8</v>
+      </c>
+      <c r="Y193">
+        <v>1.07</v>
+      </c>
+      <c r="Z193">
+        <v>2.15</v>
+      </c>
+      <c r="AA193">
+        <v>3.2</v>
+      </c>
+      <c r="AB193">
+        <v>3.3</v>
+      </c>
+      <c r="AC193">
+        <v>1.07</v>
+      </c>
+      <c r="AD193">
+        <v>8</v>
+      </c>
+      <c r="AE193">
+        <v>1.38</v>
+      </c>
+      <c r="AF193">
+        <v>3</v>
+      </c>
+      <c r="AG193">
+        <v>2.1</v>
+      </c>
+      <c r="AH193">
+        <v>1.67</v>
+      </c>
+      <c r="AI193">
+        <v>1.87</v>
+      </c>
+      <c r="AJ193">
+        <v>1.82</v>
+      </c>
+      <c r="AK193">
+        <v>1.33</v>
+      </c>
+      <c r="AL193">
+        <v>1.32</v>
+      </c>
+      <c r="AM193">
+        <v>1.63</v>
+      </c>
+      <c r="AN193">
+        <v>1.6</v>
+      </c>
+      <c r="AO193">
+        <v>1.2</v>
+      </c>
+      <c r="AP193">
+        <v>1.55</v>
+      </c>
+      <c r="AQ193">
+        <v>1.18</v>
+      </c>
+      <c r="AR193">
+        <v>1.34</v>
+      </c>
+      <c r="AS193">
+        <v>1.2</v>
+      </c>
+      <c r="AT193">
+        <v>2.54</v>
+      </c>
+      <c r="AU193">
+        <v>9</v>
+      </c>
+      <c r="AV193">
+        <v>5</v>
+      </c>
+      <c r="AW193">
+        <v>11</v>
+      </c>
+      <c r="AX193">
+        <v>3</v>
+      </c>
+      <c r="AY193">
+        <v>23</v>
+      </c>
+      <c r="AZ193">
+        <v>9</v>
+      </c>
+      <c r="BA193">
+        <v>7</v>
+      </c>
+      <c r="BB193">
+        <v>3</v>
+      </c>
+      <c r="BC193">
+        <v>10</v>
+      </c>
+      <c r="BD193">
+        <v>1.73</v>
+      </c>
+      <c r="BE193">
+        <v>6.5</v>
+      </c>
+      <c r="BF193">
+        <v>2.33</v>
+      </c>
+      <c r="BG193">
+        <v>1.38</v>
+      </c>
+      <c r="BH193">
+        <v>2.7</v>
+      </c>
+      <c r="BI193">
+        <v>1.65</v>
+      </c>
+      <c r="BJ193">
+        <v>2.05</v>
+      </c>
+      <c r="BK193">
+        <v>2.07</v>
+      </c>
+      <c r="BL193">
+        <v>1.64</v>
+      </c>
+      <c r="BM193">
+        <v>2.65</v>
+      </c>
+      <c r="BN193">
+        <v>1.4</v>
+      </c>
+      <c r="BO193">
+        <v>3.55</v>
+      </c>
+      <c r="BP193">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7574757</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45703.625</v>
+      </c>
+      <c r="F194">
+        <v>22</v>
+      </c>
+      <c r="G194" t="s">
+        <v>79</v>
+      </c>
+      <c r="H194" t="s">
+        <v>83</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="J194">
+        <v>0</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>0</v>
+      </c>
+      <c r="M194">
+        <v>1</v>
+      </c>
+      <c r="N194">
+        <v>1</v>
+      </c>
+      <c r="O194" t="s">
+        <v>90</v>
+      </c>
+      <c r="P194" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q194">
+        <v>5</v>
+      </c>
+      <c r="R194">
+        <v>2.05</v>
+      </c>
+      <c r="S194">
+        <v>2.3</v>
+      </c>
+      <c r="T194">
+        <v>1.44</v>
+      </c>
+      <c r="U194">
+        <v>2.55</v>
+      </c>
+      <c r="V194">
+        <v>3</v>
+      </c>
+      <c r="W194">
+        <v>1.33</v>
+      </c>
+      <c r="X194">
+        <v>8.25</v>
+      </c>
+      <c r="Y194">
+        <v>1.06</v>
+      </c>
+      <c r="Z194">
+        <v>4.75</v>
+      </c>
+      <c r="AA194">
+        <v>3.75</v>
+      </c>
+      <c r="AB194">
+        <v>1.67</v>
+      </c>
+      <c r="AC194">
+        <v>1.06</v>
+      </c>
+      <c r="AD194">
+        <v>9.5</v>
+      </c>
+      <c r="AE194">
+        <v>1.38</v>
+      </c>
+      <c r="AF194">
+        <v>3</v>
+      </c>
+      <c r="AG194">
+        <v>1.91</v>
+      </c>
+      <c r="AH194">
+        <v>1.8</v>
+      </c>
+      <c r="AI194">
+        <v>2.05</v>
+      </c>
+      <c r="AJ194">
+        <v>1.68</v>
+      </c>
+      <c r="AK194">
+        <v>2.1</v>
+      </c>
+      <c r="AL194">
+        <v>1.22</v>
+      </c>
+      <c r="AM194">
+        <v>1.18</v>
+      </c>
+      <c r="AN194">
+        <v>2</v>
+      </c>
+      <c r="AO194">
+        <v>1.7</v>
+      </c>
+      <c r="AP194">
+        <v>1.83</v>
+      </c>
+      <c r="AQ194">
+        <v>1.82</v>
+      </c>
+      <c r="AR194">
+        <v>1.46</v>
+      </c>
+      <c r="AS194">
+        <v>1.74</v>
+      </c>
+      <c r="AT194">
+        <v>3.2</v>
+      </c>
+      <c r="AU194">
+        <v>4</v>
+      </c>
+      <c r="AV194">
+        <v>8</v>
+      </c>
+      <c r="AW194">
+        <v>6</v>
+      </c>
+      <c r="AX194">
+        <v>11</v>
+      </c>
+      <c r="AY194">
+        <v>12</v>
+      </c>
+      <c r="AZ194">
+        <v>20</v>
+      </c>
+      <c r="BA194">
+        <v>2</v>
+      </c>
+      <c r="BB194">
+        <v>5</v>
+      </c>
+      <c r="BC194">
+        <v>7</v>
+      </c>
+      <c r="BD194">
+        <v>3.3</v>
+      </c>
+      <c r="BE194">
+        <v>7</v>
+      </c>
+      <c r="BF194">
+        <v>1.42</v>
+      </c>
+      <c r="BG194">
+        <v>1.42</v>
+      </c>
+      <c r="BH194">
+        <v>2.55</v>
+      </c>
+      <c r="BI194">
+        <v>1.7</v>
+      </c>
+      <c r="BJ194">
+        <v>1.97</v>
+      </c>
+      <c r="BK194">
+        <v>2.14</v>
+      </c>
+      <c r="BL194">
+        <v>1.6</v>
+      </c>
+      <c r="BM194">
+        <v>2.75</v>
+      </c>
+      <c r="BN194">
+        <v>1.37</v>
+      </c>
+      <c r="BO194">
+        <v>3.65</v>
+      </c>
+      <c r="BP194">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7574758</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45703.72916666666</v>
+      </c>
+      <c r="F195">
+        <v>22</v>
+      </c>
+      <c r="G195" t="s">
+        <v>70</v>
+      </c>
+      <c r="H195" t="s">
+        <v>78</v>
+      </c>
+      <c r="I195">
+        <v>1</v>
+      </c>
+      <c r="J195">
+        <v>2</v>
+      </c>
+      <c r="K195">
+        <v>3</v>
+      </c>
+      <c r="L195">
+        <v>2</v>
+      </c>
+      <c r="M195">
+        <v>2</v>
+      </c>
+      <c r="N195">
+        <v>4</v>
+      </c>
+      <c r="O195" t="s">
+        <v>214</v>
+      </c>
+      <c r="P195" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q195">
+        <v>1.67</v>
+      </c>
+      <c r="R195">
+        <v>2.75</v>
+      </c>
+      <c r="S195">
+        <v>9.5</v>
+      </c>
+      <c r="T195">
+        <v>1.29</v>
+      </c>
+      <c r="U195">
+        <v>3.5</v>
+      </c>
+      <c r="V195">
+        <v>2.25</v>
+      </c>
+      <c r="W195">
+        <v>1.57</v>
+      </c>
+      <c r="X195">
+        <v>5.5</v>
+      </c>
+      <c r="Y195">
+        <v>1.14</v>
+      </c>
+      <c r="Z195">
+        <v>999.99</v>
+      </c>
+      <c r="AA195">
+        <v>0</v>
+      </c>
+      <c r="AB195">
+        <v>999.99</v>
+      </c>
+      <c r="AC195">
+        <v>1.03</v>
+      </c>
+      <c r="AD195">
+        <v>11</v>
+      </c>
+      <c r="AE195">
+        <v>1.16</v>
+      </c>
+      <c r="AF195">
+        <v>5</v>
+      </c>
+      <c r="AG195">
+        <v>1.55</v>
+      </c>
+      <c r="AH195">
+        <v>2.36</v>
+      </c>
+      <c r="AI195">
+        <v>2.05</v>
+      </c>
+      <c r="AJ195">
+        <v>1.7</v>
+      </c>
+      <c r="AK195">
+        <v>1.04</v>
+      </c>
+      <c r="AL195">
+        <v>1.12</v>
+      </c>
+      <c r="AM195">
+        <v>4</v>
+      </c>
+      <c r="AN195">
+        <v>2.7</v>
+      </c>
+      <c r="AO195">
+        <v>1</v>
+      </c>
+      <c r="AP195">
+        <v>2.55</v>
+      </c>
+      <c r="AQ195">
+        <v>1</v>
+      </c>
+      <c r="AR195">
+        <v>2.07</v>
+      </c>
+      <c r="AS195">
+        <v>1.24</v>
+      </c>
+      <c r="AT195">
+        <v>3.31</v>
+      </c>
+      <c r="AU195">
+        <v>9</v>
+      </c>
+      <c r="AV195">
+        <v>8</v>
+      </c>
+      <c r="AW195">
+        <v>14</v>
+      </c>
+      <c r="AX195">
+        <v>10</v>
+      </c>
+      <c r="AY195">
+        <v>27</v>
+      </c>
+      <c r="AZ195">
+        <v>22</v>
+      </c>
+      <c r="BA195">
+        <v>9</v>
+      </c>
+      <c r="BB195">
+        <v>9</v>
+      </c>
+      <c r="BC195">
+        <v>18</v>
+      </c>
+      <c r="BD195">
+        <v>1.17</v>
+      </c>
+      <c r="BE195">
+        <v>9</v>
+      </c>
+      <c r="BF195">
+        <v>5.3</v>
+      </c>
+      <c r="BG195">
+        <v>1.26</v>
+      </c>
+      <c r="BH195">
+        <v>3.4</v>
+      </c>
+      <c r="BI195">
+        <v>1.44</v>
+      </c>
+      <c r="BJ195">
+        <v>2.5</v>
+      </c>
+      <c r="BK195">
+        <v>1.72</v>
+      </c>
+      <c r="BL195">
+        <v>1.96</v>
+      </c>
+      <c r="BM195">
+        <v>2.1</v>
+      </c>
+      <c r="BN195">
+        <v>1.62</v>
+      </c>
+      <c r="BO195">
+        <v>2.65</v>
+      </c>
+      <c r="BP195">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="307">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -661,6 +661,9 @@
     <t>['17', '74']</t>
   </si>
   <si>
+    <t>['62']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -1293,7 +1296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP195"/>
+  <dimension ref="A1:BP198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1755,7 +1758,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2373,7 +2376,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2785,7 +2788,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -2863,7 +2866,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ8">
         <v>0.64</v>
@@ -3403,7 +3406,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3484,7 +3487,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ11">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3609,7 +3612,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3690,7 +3693,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ12">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3893,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ13">
         <v>0.73</v>
@@ -4021,7 +4024,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4433,7 +4436,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4717,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ17">
         <v>1.18</v>
@@ -4845,7 +4848,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4926,7 +4929,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ18">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5051,7 +5054,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5257,7 +5260,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5335,7 +5338,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ20">
         <v>2.18</v>
@@ -5463,7 +5466,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -7111,7 +7114,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7317,7 +7320,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7398,7 +7401,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ30">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR30">
         <v>0.55</v>
@@ -7523,7 +7526,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -8016,7 +8019,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ33">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR33">
         <v>2.25</v>
@@ -8425,7 +8428,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -8553,7 +8556,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q36">
         <v>2.55</v>
@@ -8631,7 +8634,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ36">
         <v>1.3</v>
@@ -8840,7 +8843,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ37">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR37">
         <v>1.77</v>
@@ -8965,7 +8968,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9171,7 +9174,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9583,7 +9586,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9789,7 +9792,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -9995,7 +9998,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10407,7 +10410,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10613,7 +10616,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10819,7 +10822,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10900,7 +10903,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ47">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR47">
         <v>1.27</v>
@@ -11025,7 +11028,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11103,7 +11106,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ48">
         <v>1.18</v>
@@ -11437,7 +11440,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11515,10 +11518,10 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ50">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR50">
         <v>1.4</v>
@@ -11849,7 +11852,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -12133,7 +12136,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ53">
         <v>1</v>
@@ -12342,7 +12345,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ54">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR54">
         <v>1.92</v>
@@ -12467,7 +12470,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12673,7 +12676,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -13085,7 +13088,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13291,7 +13294,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -14605,7 +14608,7 @@
         <v>1.33</v>
       </c>
       <c r="AP65">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ65">
         <v>1.3</v>
@@ -15226,7 +15229,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ68">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR68">
         <v>0.83</v>
@@ -15635,7 +15638,7 @@
         <v>0.67</v>
       </c>
       <c r="AP70">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ70">
         <v>1.18</v>
@@ -15763,7 +15766,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -15841,7 +15844,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ71">
         <v>0.82</v>
@@ -15969,7 +15972,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16050,7 +16053,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ72">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR72">
         <v>2.36</v>
@@ -16381,7 +16384,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16587,7 +16590,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16793,7 +16796,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16999,7 +17002,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17617,7 +17620,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17823,7 +17826,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -17904,7 +17907,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ81">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR81">
         <v>1.3</v>
@@ -18029,7 +18032,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18235,7 +18238,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18313,7 +18316,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ83">
         <v>1.27</v>
@@ -18441,7 +18444,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18519,7 +18522,7 @@
         <v>1.33</v>
       </c>
       <c r="AP84">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ84">
         <v>1.82</v>
@@ -18647,7 +18650,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18853,7 +18856,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19137,7 +19140,7 @@
         <v>1.2</v>
       </c>
       <c r="AP87">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ87">
         <v>0.64</v>
@@ -19265,7 +19268,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19346,7 +19349,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ88">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR88">
         <v>0.89</v>
@@ -19883,7 +19886,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -20089,7 +20092,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20376,7 +20379,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ93">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR93">
         <v>0.99</v>
@@ -20707,7 +20710,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -21325,7 +21328,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21612,7 +21615,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ99">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR99">
         <v>2.36</v>
@@ -21815,7 +21818,7 @@
         <v>0.2</v>
       </c>
       <c r="AP100">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ100">
         <v>0.55</v>
@@ -21943,7 +21946,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22021,7 +22024,7 @@
         <v>1</v>
       </c>
       <c r="AP101">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ101">
         <v>0.64</v>
@@ -22355,7 +22358,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22767,7 +22770,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -22973,7 +22976,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q106">
         <v>5.5</v>
@@ -23054,7 +23057,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ106">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR106">
         <v>1.19</v>
@@ -23257,7 +23260,7 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ107">
         <v>0.55</v>
@@ -23797,7 +23800,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -24003,7 +24006,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q111">
         <v>2.75</v>
@@ -24702,7 +24705,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ114">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR114">
         <v>1.09</v>
@@ -25114,7 +25117,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ116">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR116">
         <v>1.23</v>
@@ -25523,7 +25526,7 @@
         <v>0.29</v>
       </c>
       <c r="AP118">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ118">
         <v>0.55</v>
@@ -25857,7 +25860,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26269,7 +26272,7 @@
         <v>167</v>
       </c>
       <c r="P122" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q122">
         <v>11</v>
@@ -26475,7 +26478,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26681,7 +26684,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -27093,7 +27096,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27171,7 +27174,7 @@
         <v>1.14</v>
       </c>
       <c r="AP126">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ126">
         <v>1</v>
@@ -27299,7 +27302,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27505,7 +27508,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27711,7 +27714,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27998,7 +28001,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ130">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR130">
         <v>1.33</v>
@@ -28123,7 +28126,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28204,7 +28207,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ131">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR131">
         <v>1.14</v>
@@ -28329,7 +28332,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28410,7 +28413,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ132">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR132">
         <v>1.35</v>
@@ -28741,7 +28744,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -28819,7 +28822,7 @@
         <v>0.29</v>
       </c>
       <c r="AP134">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ134">
         <v>0.55</v>
@@ -29565,7 +29568,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29771,7 +29774,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -30183,7 +30186,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30261,7 +30264,7 @@
         <v>1.13</v>
       </c>
       <c r="AP141">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ141">
         <v>1</v>
@@ -30389,7 +30392,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30467,7 +30470,7 @@
         <v>0.38</v>
       </c>
       <c r="AP142">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ142">
         <v>0.55</v>
@@ -30595,7 +30598,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -31007,7 +31010,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31213,7 +31216,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31291,7 +31294,7 @@
         <v>2.38</v>
       </c>
       <c r="AP146">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ146">
         <v>2.18</v>
@@ -31419,7 +31422,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q147">
         <v>2.55</v>
@@ -31500,7 +31503,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ147">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR147">
         <v>1.11</v>
@@ -31625,7 +31628,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31706,7 +31709,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ148">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR148">
         <v>2.01</v>
@@ -31831,7 +31834,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32243,7 +32246,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32449,7 +32452,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32655,7 +32658,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -32942,7 +32945,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ154">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR154">
         <v>1.23</v>
@@ -33273,7 +33276,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33479,7 +33482,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33557,7 +33560,7 @@
         <v>2.22</v>
       </c>
       <c r="AP157">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ157">
         <v>2.18</v>
@@ -33685,7 +33688,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33763,7 +33766,7 @@
         <v>0.78</v>
       </c>
       <c r="AP158">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ158">
         <v>1</v>
@@ -33891,7 +33894,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -33972,7 +33975,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ159">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR159">
         <v>1.19</v>
@@ -34303,7 +34306,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34384,7 +34387,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ161">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR161">
         <v>1.17</v>
@@ -34509,7 +34512,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34590,7 +34593,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ162">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR162">
         <v>1.23</v>
@@ -34715,7 +34718,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -35127,7 +35130,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35205,7 +35208,7 @@
         <v>0.44</v>
       </c>
       <c r="AP165">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ165">
         <v>0.73</v>
@@ -36157,7 +36160,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36775,7 +36778,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -37187,7 +37190,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37393,7 +37396,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -37677,10 +37680,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP177">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ177">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR177">
         <v>1.39</v>
@@ -38011,7 +38014,7 @@
         <v>205</v>
       </c>
       <c r="P179" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q179">
         <v>8.5</v>
@@ -38217,7 +38220,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q180">
         <v>4.75</v>
@@ -38298,7 +38301,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ180">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR180">
         <v>1.19</v>
@@ -38423,7 +38426,7 @@
         <v>207</v>
       </c>
       <c r="P181" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q181">
         <v>6.5</v>
@@ -38501,10 +38504,10 @@
         <v>1.44</v>
       </c>
       <c r="AP181">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ181">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR181">
         <v>1.3</v>
@@ -38629,7 +38632,7 @@
         <v>167</v>
       </c>
       <c r="P182" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -39041,7 +39044,7 @@
         <v>208</v>
       </c>
       <c r="P184" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q184">
         <v>1.57</v>
@@ -39453,7 +39456,7 @@
         <v>209</v>
       </c>
       <c r="P186" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q186">
         <v>2.2</v>
@@ -39737,7 +39740,7 @@
         <v>0.3</v>
       </c>
       <c r="AP187">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ187">
         <v>0.55</v>
@@ -40277,7 +40280,7 @@
         <v>184</v>
       </c>
       <c r="P190" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q190">
         <v>2.63</v>
@@ -40689,7 +40692,7 @@
         <v>212</v>
       </c>
       <c r="P192" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -40895,7 +40898,7 @@
         <v>213</v>
       </c>
       <c r="P193" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q193">
         <v>2.8</v>
@@ -41307,7 +41310,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q195">
         <v>1.67</v>
@@ -41464,6 +41467,624 @@
       </c>
       <c r="BP195">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7574752</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45704.52083333334</v>
+      </c>
+      <c r="F196">
+        <v>22</v>
+      </c>
+      <c r="G196" t="s">
+        <v>81</v>
+      </c>
+      <c r="H196" t="s">
+        <v>71</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="J196">
+        <v>1</v>
+      </c>
+      <c r="K196">
+        <v>1</v>
+      </c>
+      <c r="L196">
+        <v>1</v>
+      </c>
+      <c r="M196">
+        <v>1</v>
+      </c>
+      <c r="N196">
+        <v>2</v>
+      </c>
+      <c r="O196" t="s">
+        <v>215</v>
+      </c>
+      <c r="P196" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q196">
+        <v>2.88</v>
+      </c>
+      <c r="R196">
+        <v>2</v>
+      </c>
+      <c r="S196">
+        <v>4</v>
+      </c>
+      <c r="T196">
+        <v>1.5</v>
+      </c>
+      <c r="U196">
+        <v>2.5</v>
+      </c>
+      <c r="V196">
+        <v>3.4</v>
+      </c>
+      <c r="W196">
+        <v>1.3</v>
+      </c>
+      <c r="X196">
+        <v>10</v>
+      </c>
+      <c r="Y196">
+        <v>1.06</v>
+      </c>
+      <c r="Z196">
+        <v>999.99</v>
+      </c>
+      <c r="AA196">
+        <v>0</v>
+      </c>
+      <c r="AB196">
+        <v>999.99</v>
+      </c>
+      <c r="AC196">
+        <v>1.07</v>
+      </c>
+      <c r="AD196">
+        <v>9</v>
+      </c>
+      <c r="AE196">
+        <v>1.42</v>
+      </c>
+      <c r="AF196">
+        <v>2.85</v>
+      </c>
+      <c r="AG196">
+        <v>2.15</v>
+      </c>
+      <c r="AH196">
+        <v>1.61</v>
+      </c>
+      <c r="AI196">
+        <v>1.95</v>
+      </c>
+      <c r="AJ196">
+        <v>1.8</v>
+      </c>
+      <c r="AK196">
+        <v>1.32</v>
+      </c>
+      <c r="AL196">
+        <v>1.33</v>
+      </c>
+      <c r="AM196">
+        <v>1.63</v>
+      </c>
+      <c r="AN196">
+        <v>1.7</v>
+      </c>
+      <c r="AO196">
+        <v>0.5</v>
+      </c>
+      <c r="AP196">
+        <v>1.64</v>
+      </c>
+      <c r="AQ196">
+        <v>0.55</v>
+      </c>
+      <c r="AR196">
+        <v>1.29</v>
+      </c>
+      <c r="AS196">
+        <v>1.01</v>
+      </c>
+      <c r="AT196">
+        <v>2.3</v>
+      </c>
+      <c r="AU196">
+        <v>3</v>
+      </c>
+      <c r="AV196">
+        <v>3</v>
+      </c>
+      <c r="AW196">
+        <v>11</v>
+      </c>
+      <c r="AX196">
+        <v>10</v>
+      </c>
+      <c r="AY196">
+        <v>19</v>
+      </c>
+      <c r="AZ196">
+        <v>15</v>
+      </c>
+      <c r="BA196">
+        <v>2</v>
+      </c>
+      <c r="BB196">
+        <v>4</v>
+      </c>
+      <c r="BC196">
+        <v>6</v>
+      </c>
+      <c r="BD196">
+        <v>1.76</v>
+      </c>
+      <c r="BE196">
+        <v>6.75</v>
+      </c>
+      <c r="BF196">
+        <v>2.25</v>
+      </c>
+      <c r="BG196">
+        <v>1.32</v>
+      </c>
+      <c r="BH196">
+        <v>3</v>
+      </c>
+      <c r="BI196">
+        <v>1.54</v>
+      </c>
+      <c r="BJ196">
+        <v>2.25</v>
+      </c>
+      <c r="BK196">
+        <v>1.89</v>
+      </c>
+      <c r="BL196">
+        <v>1.77</v>
+      </c>
+      <c r="BM196">
+        <v>2.38</v>
+      </c>
+      <c r="BN196">
+        <v>1.49</v>
+      </c>
+      <c r="BO196">
+        <v>3.05</v>
+      </c>
+      <c r="BP196">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7574754</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45704.625</v>
+      </c>
+      <c r="F197">
+        <v>22</v>
+      </c>
+      <c r="G197" t="s">
+        <v>76</v>
+      </c>
+      <c r="H197" t="s">
+        <v>73</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>0</v>
+      </c>
+      <c r="L197">
+        <v>0</v>
+      </c>
+      <c r="M197">
+        <v>1</v>
+      </c>
+      <c r="N197">
+        <v>1</v>
+      </c>
+      <c r="O197" t="s">
+        <v>90</v>
+      </c>
+      <c r="P197" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q197">
+        <v>7.5</v>
+      </c>
+      <c r="R197">
+        <v>2.3</v>
+      </c>
+      <c r="S197">
+        <v>1.95</v>
+      </c>
+      <c r="T197">
+        <v>1.4</v>
+      </c>
+      <c r="U197">
+        <v>2.75</v>
+      </c>
+      <c r="V197">
+        <v>2.75</v>
+      </c>
+      <c r="W197">
+        <v>1.4</v>
+      </c>
+      <c r="X197">
+        <v>8</v>
+      </c>
+      <c r="Y197">
+        <v>1.08</v>
+      </c>
+      <c r="Z197">
+        <v>8</v>
+      </c>
+      <c r="AA197">
+        <v>4.6</v>
+      </c>
+      <c r="AB197">
+        <v>1.33</v>
+      </c>
+      <c r="AC197">
+        <v>1.04</v>
+      </c>
+      <c r="AD197">
+        <v>12</v>
+      </c>
+      <c r="AE197">
+        <v>1.3</v>
+      </c>
+      <c r="AF197">
+        <v>3.5</v>
+      </c>
+      <c r="AG197">
+        <v>1.83</v>
+      </c>
+      <c r="AH197">
+        <v>1.91</v>
+      </c>
+      <c r="AI197">
+        <v>2.2</v>
+      </c>
+      <c r="AJ197">
+        <v>1.62</v>
+      </c>
+      <c r="AK197">
+        <v>2.85</v>
+      </c>
+      <c r="AL197">
+        <v>1.19</v>
+      </c>
+      <c r="AM197">
+        <v>1.09</v>
+      </c>
+      <c r="AN197">
+        <v>0.7</v>
+      </c>
+      <c r="AO197">
+        <v>1.4</v>
+      </c>
+      <c r="AP197">
+        <v>0.64</v>
+      </c>
+      <c r="AQ197">
+        <v>1.55</v>
+      </c>
+      <c r="AR197">
+        <v>1.32</v>
+      </c>
+      <c r="AS197">
+        <v>1.49</v>
+      </c>
+      <c r="AT197">
+        <v>2.81</v>
+      </c>
+      <c r="AU197">
+        <v>3</v>
+      </c>
+      <c r="AV197">
+        <v>3</v>
+      </c>
+      <c r="AW197">
+        <v>7</v>
+      </c>
+      <c r="AX197">
+        <v>9</v>
+      </c>
+      <c r="AY197">
+        <v>10</v>
+      </c>
+      <c r="AZ197">
+        <v>17</v>
+      </c>
+      <c r="BA197">
+        <v>2</v>
+      </c>
+      <c r="BB197">
+        <v>4</v>
+      </c>
+      <c r="BC197">
+        <v>6</v>
+      </c>
+      <c r="BD197">
+        <v>4.35</v>
+      </c>
+      <c r="BE197">
+        <v>8</v>
+      </c>
+      <c r="BF197">
+        <v>1.24</v>
+      </c>
+      <c r="BG197">
+        <v>1.27</v>
+      </c>
+      <c r="BH197">
+        <v>3.3</v>
+      </c>
+      <c r="BI197">
+        <v>1.45</v>
+      </c>
+      <c r="BJ197">
+        <v>2.48</v>
+      </c>
+      <c r="BK197">
+        <v>1.73</v>
+      </c>
+      <c r="BL197">
+        <v>1.94</v>
+      </c>
+      <c r="BM197">
+        <v>2.14</v>
+      </c>
+      <c r="BN197">
+        <v>1.6</v>
+      </c>
+      <c r="BO197">
+        <v>2.65</v>
+      </c>
+      <c r="BP197">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:68">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>7574759</v>
+      </c>
+      <c r="C198" t="s">
+        <v>68</v>
+      </c>
+      <c r="D198" t="s">
+        <v>69</v>
+      </c>
+      <c r="E198" s="2">
+        <v>45704.72916666666</v>
+      </c>
+      <c r="F198">
+        <v>22</v>
+      </c>
+      <c r="G198" t="s">
+        <v>85</v>
+      </c>
+      <c r="H198" t="s">
+        <v>77</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+      <c r="J198">
+        <v>0</v>
+      </c>
+      <c r="K198">
+        <v>0</v>
+      </c>
+      <c r="L198">
+        <v>0</v>
+      </c>
+      <c r="M198">
+        <v>0</v>
+      </c>
+      <c r="N198">
+        <v>0</v>
+      </c>
+      <c r="O198" t="s">
+        <v>90</v>
+      </c>
+      <c r="P198" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q198">
+        <v>3.4</v>
+      </c>
+      <c r="R198">
+        <v>2.1</v>
+      </c>
+      <c r="S198">
+        <v>3.4</v>
+      </c>
+      <c r="T198">
+        <v>1.44</v>
+      </c>
+      <c r="U198">
+        <v>2.63</v>
+      </c>
+      <c r="V198">
+        <v>3.25</v>
+      </c>
+      <c r="W198">
+        <v>1.33</v>
+      </c>
+      <c r="X198">
+        <v>9</v>
+      </c>
+      <c r="Y198">
+        <v>1.07</v>
+      </c>
+      <c r="Z198">
+        <v>2.45</v>
+      </c>
+      <c r="AA198">
+        <v>3.1</v>
+      </c>
+      <c r="AB198">
+        <v>2.88</v>
+      </c>
+      <c r="AC198">
+        <v>1.06</v>
+      </c>
+      <c r="AD198">
+        <v>10</v>
+      </c>
+      <c r="AE198">
+        <v>1.33</v>
+      </c>
+      <c r="AF198">
+        <v>3.3</v>
+      </c>
+      <c r="AG198">
+        <v>1.95</v>
+      </c>
+      <c r="AH198">
+        <v>1.75</v>
+      </c>
+      <c r="AI198">
+        <v>1.8</v>
+      </c>
+      <c r="AJ198">
+        <v>1.95</v>
+      </c>
+      <c r="AK198">
+        <v>1.42</v>
+      </c>
+      <c r="AL198">
+        <v>1.28</v>
+      </c>
+      <c r="AM198">
+        <v>1.55</v>
+      </c>
+      <c r="AN198">
+        <v>1.9</v>
+      </c>
+      <c r="AO198">
+        <v>2.5</v>
+      </c>
+      <c r="AP198">
+        <v>1.82</v>
+      </c>
+      <c r="AQ198">
+        <v>2.36</v>
+      </c>
+      <c r="AR198">
+        <v>1.47</v>
+      </c>
+      <c r="AS198">
+        <v>1.5</v>
+      </c>
+      <c r="AT198">
+        <v>2.97</v>
+      </c>
+      <c r="AU198">
+        <v>-1</v>
+      </c>
+      <c r="AV198">
+        <v>-1</v>
+      </c>
+      <c r="AW198">
+        <v>-1</v>
+      </c>
+      <c r="AX198">
+        <v>-1</v>
+      </c>
+      <c r="AY198">
+        <v>-1</v>
+      </c>
+      <c r="AZ198">
+        <v>-1</v>
+      </c>
+      <c r="BA198">
+        <v>-1</v>
+      </c>
+      <c r="BB198">
+        <v>-1</v>
+      </c>
+      <c r="BC198">
+        <v>-1</v>
+      </c>
+      <c r="BD198">
+        <v>1.84</v>
+      </c>
+      <c r="BE198">
+        <v>6.5</v>
+      </c>
+      <c r="BF198">
+        <v>2.17</v>
+      </c>
+      <c r="BG198">
+        <v>1.29</v>
+      </c>
+      <c r="BH198">
+        <v>3.15</v>
+      </c>
+      <c r="BI198">
+        <v>1.52</v>
+      </c>
+      <c r="BJ198">
+        <v>2.3</v>
+      </c>
+      <c r="BK198">
+        <v>1.84</v>
+      </c>
+      <c r="BL198">
+        <v>1.82</v>
+      </c>
+      <c r="BM198">
+        <v>2.3</v>
+      </c>
+      <c r="BN198">
+        <v>1.52</v>
+      </c>
+      <c r="BO198">
+        <v>2.95</v>
+      </c>
+      <c r="BP198">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -42021,31 +42021,31 @@
         <v>2.97</v>
       </c>
       <c r="AU198">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AV198">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW198">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AX198">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY198">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AZ198">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BA198">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BB198">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC198">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD198">
         <v>1.84</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="308">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -936,6 +936,9 @@
   <si>
     <t>['8', '45+5']</t>
   </si>
+  <si>
+    <t>['45', '60']</t>
+  </si>
 </sst>
 </file>
 
@@ -1296,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP198"/>
+  <dimension ref="A1:BP199"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3690,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ12">
         <v>0.55</v>
@@ -5135,7 +5138,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ19">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -8637,7 +8640,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ36">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR36">
         <v>1.59</v>
@@ -8840,7 +8843,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ37">
         <v>2.36</v>
@@ -11727,7 +11730,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ51">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR51">
         <v>1.08</v>
@@ -11930,7 +11933,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ52">
         <v>1.27</v>
@@ -14611,7 +14614,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ65">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -14814,7 +14817,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ66">
         <v>0.55</v>
@@ -18728,7 +18731,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ85">
         <v>0.82</v>
@@ -18937,7 +18940,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ86">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR86">
         <v>1.12</v>
@@ -22645,7 +22648,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ104">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR104">
         <v>1</v>
@@ -24084,7 +24087,7 @@
         <v>0.33</v>
       </c>
       <c r="AP111">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ111">
         <v>0.55</v>
@@ -26765,7 +26768,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ124">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR124">
         <v>1.55</v>
@@ -28616,7 +28619,7 @@
         <v>2.57</v>
       </c>
       <c r="AP133">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ133">
         <v>2.18</v>
@@ -32327,7 +32330,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ151">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR151">
         <v>1.25</v>
@@ -32736,7 +32739,7 @@
         <v>0.38</v>
       </c>
       <c r="AP153">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ153">
         <v>0.73</v>
@@ -33151,7 +33154,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ155">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR155">
         <v>2.01</v>
@@ -34590,7 +34593,7 @@
         <v>1.63</v>
       </c>
       <c r="AP162">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ162">
         <v>1.55</v>
@@ -36859,7 +36862,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ173">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR173">
         <v>1.33</v>
@@ -37474,7 +37477,7 @@
         <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ176">
         <v>1.18</v>
@@ -42085,6 +42088,212 @@
       </c>
       <c r="BP198">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="199" spans="1:68">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>7574755</v>
+      </c>
+      <c r="C199" t="s">
+        <v>68</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="2">
+        <v>45705.71875</v>
+      </c>
+      <c r="F199">
+        <v>22</v>
+      </c>
+      <c r="G199" t="s">
+        <v>80</v>
+      </c>
+      <c r="H199" t="s">
+        <v>75</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>1</v>
+      </c>
+      <c r="K199">
+        <v>1</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+      <c r="M199">
+        <v>2</v>
+      </c>
+      <c r="N199">
+        <v>2</v>
+      </c>
+      <c r="O199" t="s">
+        <v>90</v>
+      </c>
+      <c r="P199" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q199">
+        <v>3.4</v>
+      </c>
+      <c r="R199">
+        <v>1.95</v>
+      </c>
+      <c r="S199">
+        <v>3.75</v>
+      </c>
+      <c r="T199">
+        <v>1.57</v>
+      </c>
+      <c r="U199">
+        <v>2.25</v>
+      </c>
+      <c r="V199">
+        <v>3.75</v>
+      </c>
+      <c r="W199">
+        <v>1.25</v>
+      </c>
+      <c r="X199">
+        <v>11</v>
+      </c>
+      <c r="Y199">
+        <v>1.05</v>
+      </c>
+      <c r="Z199">
+        <v>999.99</v>
+      </c>
+      <c r="AA199">
+        <v>0</v>
+      </c>
+      <c r="AB199">
+        <v>999.99</v>
+      </c>
+      <c r="AC199">
+        <v>1.1</v>
+      </c>
+      <c r="AD199">
+        <v>7</v>
+      </c>
+      <c r="AE199">
+        <v>1.54</v>
+      </c>
+      <c r="AF199">
+        <v>2.48</v>
+      </c>
+      <c r="AG199">
+        <v>2.37</v>
+      </c>
+      <c r="AH199">
+        <v>1.53</v>
+      </c>
+      <c r="AI199">
+        <v>2.05</v>
+      </c>
+      <c r="AJ199">
+        <v>1.7</v>
+      </c>
+      <c r="AK199">
+        <v>1.38</v>
+      </c>
+      <c r="AL199">
+        <v>1.35</v>
+      </c>
+      <c r="AM199">
+        <v>1.53</v>
+      </c>
+      <c r="AN199">
+        <v>1.6</v>
+      </c>
+      <c r="AO199">
+        <v>1.3</v>
+      </c>
+      <c r="AP199">
+        <v>1.45</v>
+      </c>
+      <c r="AQ199">
+        <v>1.45</v>
+      </c>
+      <c r="AR199">
+        <v>1.25</v>
+      </c>
+      <c r="AS199">
+        <v>1.31</v>
+      </c>
+      <c r="AT199">
+        <v>2.56</v>
+      </c>
+      <c r="AU199">
+        <v>3</v>
+      </c>
+      <c r="AV199">
+        <v>6</v>
+      </c>
+      <c r="AW199">
+        <v>11</v>
+      </c>
+      <c r="AX199">
+        <v>16</v>
+      </c>
+      <c r="AY199">
+        <v>16</v>
+      </c>
+      <c r="AZ199">
+        <v>27</v>
+      </c>
+      <c r="BA199">
+        <v>5</v>
+      </c>
+      <c r="BB199">
+        <v>11</v>
+      </c>
+      <c r="BC199">
+        <v>16</v>
+      </c>
+      <c r="BD199">
+        <v>1.77</v>
+      </c>
+      <c r="BE199">
+        <v>6.5</v>
+      </c>
+      <c r="BF199">
+        <v>2.23</v>
+      </c>
+      <c r="BG199">
+        <v>1.34</v>
+      </c>
+      <c r="BH199">
+        <v>2.88</v>
+      </c>
+      <c r="BI199">
+        <v>1.6</v>
+      </c>
+      <c r="BJ199">
+        <v>2.15</v>
+      </c>
+      <c r="BK199">
+        <v>1.94</v>
+      </c>
+      <c r="BL199">
+        <v>1.73</v>
+      </c>
+      <c r="BM199">
+        <v>2.48</v>
+      </c>
+      <c r="BN199">
+        <v>1.45</v>
+      </c>
+      <c r="BO199">
+        <v>3.2</v>
+      </c>
+      <c r="BP199">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="308">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1299,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP199"/>
+  <dimension ref="A1:BP200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1842,7 +1842,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ3">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ9">
         <v>0.55</v>
@@ -6374,7 +6374,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ25">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR25">
         <v>0.7</v>
@@ -6989,7 +6989,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ28">
         <v>0.64</v>
@@ -10288,7 +10288,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ44">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR44">
         <v>0.8100000000000001</v>
@@ -10491,7 +10491,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -13584,7 +13584,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ60">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR60">
         <v>1.14</v>
@@ -13993,7 +13993,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ62">
         <v>0.73</v>
@@ -16262,7 +16262,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ73">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR73">
         <v>1.21</v>
@@ -17289,7 +17289,7 @@
         <v>0.25</v>
       </c>
       <c r="AP78">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ78">
         <v>0.73</v>
@@ -21000,7 +21000,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ96">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR96">
         <v>1.15</v>
@@ -21409,7 +21409,7 @@
         <v>3</v>
       </c>
       <c r="AP98">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ98">
         <v>2.18</v>
@@ -23881,7 +23881,7 @@
         <v>0.4</v>
       </c>
       <c r="AP110">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ110">
         <v>1.18</v>
@@ -24090,7 +24090,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ111">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR111">
         <v>1.27</v>
@@ -26765,7 +26765,7 @@
         <v>1.33</v>
       </c>
       <c r="AP124">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ124">
         <v>1.45</v>
@@ -28828,7 +28828,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ134">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR134">
         <v>1.28</v>
@@ -30476,7 +30476,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ142">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR142">
         <v>1.33</v>
@@ -30679,7 +30679,7 @@
         <v>1.14</v>
       </c>
       <c r="AP143">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ143">
         <v>1.27</v>
@@ -35832,7 +35832,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ168">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR168">
         <v>2.03</v>
@@ -36447,7 +36447,7 @@
         <v>1</v>
       </c>
       <c r="AP171">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ171">
         <v>0.82</v>
@@ -39746,7 +39746,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ187">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR187">
         <v>1.2</v>
@@ -39949,7 +39949,7 @@
         <v>0.6</v>
       </c>
       <c r="AP188">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ188">
         <v>0.55</v>
@@ -42294,6 +42294,212 @@
       </c>
       <c r="BP199">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="200" spans="1:68">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>7574766</v>
+      </c>
+      <c r="C200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D200" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="2">
+        <v>45709.71875</v>
+      </c>
+      <c r="F200">
+        <v>23</v>
+      </c>
+      <c r="G200" t="s">
+        <v>77</v>
+      </c>
+      <c r="H200" t="s">
+        <v>82</v>
+      </c>
+      <c r="I200">
+        <v>1</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>1</v>
+      </c>
+      <c r="L200">
+        <v>1</v>
+      </c>
+      <c r="M200">
+        <v>0</v>
+      </c>
+      <c r="N200">
+        <v>1</v>
+      </c>
+      <c r="O200" t="s">
+        <v>211</v>
+      </c>
+      <c r="P200" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q200">
+        <v>1.97</v>
+      </c>
+      <c r="R200">
+        <v>2.53</v>
+      </c>
+      <c r="S200">
+        <v>6.41</v>
+      </c>
+      <c r="T200">
+        <v>1.31</v>
+      </c>
+      <c r="U200">
+        <v>3.1</v>
+      </c>
+      <c r="V200">
+        <v>2.58</v>
+      </c>
+      <c r="W200">
+        <v>1.5</v>
+      </c>
+      <c r="X200">
+        <v>5.75</v>
+      </c>
+      <c r="Y200">
+        <v>1.12</v>
+      </c>
+      <c r="Z200">
+        <v>1.47</v>
+      </c>
+      <c r="AA200">
+        <v>4.33</v>
+      </c>
+      <c r="AB200">
+        <v>6</v>
+      </c>
+      <c r="AC200">
+        <v>1.04</v>
+      </c>
+      <c r="AD200">
+        <v>10</v>
+      </c>
+      <c r="AE200">
+        <v>1.2</v>
+      </c>
+      <c r="AF200">
+        <v>4.33</v>
+      </c>
+      <c r="AG200">
+        <v>1.61</v>
+      </c>
+      <c r="AH200">
+        <v>2.15</v>
+      </c>
+      <c r="AI200">
+        <v>1.8</v>
+      </c>
+      <c r="AJ200">
+        <v>1.88</v>
+      </c>
+      <c r="AK200">
+        <v>1.12</v>
+      </c>
+      <c r="AL200">
+        <v>1.2</v>
+      </c>
+      <c r="AM200">
+        <v>2.55</v>
+      </c>
+      <c r="AN200">
+        <v>1.64</v>
+      </c>
+      <c r="AO200">
+        <v>0.55</v>
+      </c>
+      <c r="AP200">
+        <v>1.75</v>
+      </c>
+      <c r="AQ200">
+        <v>0.5</v>
+      </c>
+      <c r="AR200">
+        <v>1.68</v>
+      </c>
+      <c r="AS200">
+        <v>1.26</v>
+      </c>
+      <c r="AT200">
+        <v>2.94</v>
+      </c>
+      <c r="AU200">
+        <v>8</v>
+      </c>
+      <c r="AV200">
+        <v>4</v>
+      </c>
+      <c r="AW200">
+        <v>11</v>
+      </c>
+      <c r="AX200">
+        <v>5</v>
+      </c>
+      <c r="AY200">
+        <v>23</v>
+      </c>
+      <c r="AZ200">
+        <v>10</v>
+      </c>
+      <c r="BA200">
+        <v>7</v>
+      </c>
+      <c r="BB200">
+        <v>6</v>
+      </c>
+      <c r="BC200">
+        <v>13</v>
+      </c>
+      <c r="BD200">
+        <v>1.26</v>
+      </c>
+      <c r="BE200">
+        <v>8</v>
+      </c>
+      <c r="BF200">
+        <v>4.1</v>
+      </c>
+      <c r="BG200">
+        <v>1.22</v>
+      </c>
+      <c r="BH200">
+        <v>3.65</v>
+      </c>
+      <c r="BI200">
+        <v>1.4</v>
+      </c>
+      <c r="BJ200">
+        <v>2.65</v>
+      </c>
+      <c r="BK200">
+        <v>1.64</v>
+      </c>
+      <c r="BL200">
+        <v>2.08</v>
+      </c>
+      <c r="BM200">
+        <v>1.98</v>
+      </c>
+      <c r="BN200">
+        <v>1.7</v>
+      </c>
+      <c r="BO200">
+        <v>2.5</v>
+      </c>
+      <c r="BP200">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="311">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -664,6 +664,15 @@
     <t>['62']</t>
   </si>
   <si>
+    <t>['50']</t>
+  </si>
+  <si>
+    <t>['28', '70', '77']</t>
+  </si>
+  <si>
+    <t>['55', '90']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -814,9 +823,6 @@
     <t>['68', '82']</t>
   </si>
   <si>
-    <t>['50']</t>
-  </si>
-  <si>
     <t>['43', '58']</t>
   </si>
   <si>
@@ -938,6 +944,9 @@
   </si>
   <si>
     <t>['45', '60']</t>
+  </si>
+  <si>
+    <t>['83']</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP200"/>
+  <dimension ref="A1:BP203"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1636,7 +1645,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ2">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1761,7 +1770,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2045,10 +2054,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ4">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2254,7 +2263,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ5">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2379,7 +2388,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2457,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ6">
         <v>1.6</v>
@@ -2791,7 +2800,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -3409,7 +3418,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3615,7 +3624,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4027,7 +4036,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4311,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ15">
         <v>1.27</v>
@@ -4439,7 +4448,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4851,7 +4860,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -5057,7 +5066,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5263,7 +5272,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5469,7 +5478,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -5547,7 +5556,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ21">
         <v>1.6</v>
@@ -5756,7 +5765,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ22">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR22">
         <v>1.3</v>
@@ -5962,7 +5971,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ23">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR23">
         <v>1.27</v>
@@ -6165,7 +6174,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ24">
         <v>0.55</v>
@@ -6577,10 +6586,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ26">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR26">
         <v>0.6</v>
@@ -7117,7 +7126,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7323,7 +7332,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7529,7 +7538,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -8559,7 +8568,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q36">
         <v>2.55</v>
@@ -8971,7 +8980,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9177,7 +9186,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9255,7 +9264,7 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ39">
         <v>0.64</v>
@@ -9464,7 +9473,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ40">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR40">
         <v>1.32</v>
@@ -9589,7 +9598,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9670,7 +9679,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ41">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR41">
         <v>1.05</v>
@@ -9795,7 +9804,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -9873,7 +9882,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ42">
         <v>1.6</v>
@@ -10001,7 +10010,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10285,7 +10294,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ44">
         <v>0.5</v>
@@ -10413,7 +10422,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10619,7 +10628,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10700,7 +10709,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ46">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR46">
         <v>1.1</v>
@@ -10825,7 +10834,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -11031,7 +11040,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11443,7 +11452,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11855,7 +11864,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -12473,7 +12482,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12679,7 +12688,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -12757,7 +12766,7 @@
         <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ56">
         <v>2.18</v>
@@ -13091,7 +13100,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13169,7 +13178,7 @@
         <v>2</v>
       </c>
       <c r="AP58">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ58">
         <v>1</v>
@@ -13297,7 +13306,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -13375,10 +13384,10 @@
         <v>0.67</v>
       </c>
       <c r="AP59">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ59">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR59">
         <v>2.26</v>
@@ -13996,7 +14005,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ62">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR62">
         <v>1.53</v>
@@ -14202,7 +14211,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ63">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR63">
         <v>1.11</v>
@@ -15769,7 +15778,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -15850,7 +15859,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ71">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR71">
         <v>1.19</v>
@@ -15975,7 +15984,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16259,7 +16268,7 @@
         <v>0.5</v>
       </c>
       <c r="AP73">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ73">
         <v>0.5</v>
@@ -16387,7 +16396,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16468,7 +16477,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ74">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR74">
         <v>1.21</v>
@@ -16593,7 +16602,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16671,7 +16680,7 @@
         <v>0.75</v>
       </c>
       <c r="AP75">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -16799,7 +16808,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17005,7 +17014,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17495,10 +17504,10 @@
         <v>0</v>
       </c>
       <c r="AP79">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ79">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR79">
         <v>2.16</v>
@@ -17623,7 +17632,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17829,7 +17838,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -18035,7 +18044,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18241,7 +18250,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18447,7 +18456,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18653,7 +18662,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18734,7 +18743,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ85">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR85">
         <v>1.21</v>
@@ -18859,7 +18868,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19271,7 +19280,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19889,7 +19898,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -19970,7 +19979,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ91">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR91">
         <v>1.03</v>
@@ -20095,7 +20104,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20173,7 +20182,7 @@
         <v>0.2</v>
       </c>
       <c r="AP92">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ92">
         <v>0.73</v>
@@ -20379,7 +20388,7 @@
         <v>0.25</v>
       </c>
       <c r="AP93">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ93">
         <v>0.55</v>
@@ -20713,7 +20722,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -20794,7 +20803,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ95">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR95">
         <v>1.16</v>
@@ -21331,7 +21340,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21615,7 +21624,7 @@
         <v>2.25</v>
       </c>
       <c r="AP99">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ99">
         <v>1.55</v>
@@ -21949,7 +21958,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22236,7 +22245,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ102">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR102">
         <v>1.15</v>
@@ -22361,7 +22370,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22645,7 +22654,7 @@
         <v>1.6</v>
       </c>
       <c r="AP104">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ104">
         <v>1.45</v>
@@ -22773,7 +22782,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -22979,7 +22988,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q106">
         <v>5.5</v>
@@ -23266,7 +23275,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ107">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR107">
         <v>1.2</v>
@@ -23803,7 +23812,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -24009,7 +24018,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>266</v>
+        <v>216</v>
       </c>
       <c r="Q111">
         <v>2.75</v>
@@ -24293,7 +24302,7 @@
         <v>1.33</v>
       </c>
       <c r="AP112">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ112">
         <v>1</v>
@@ -24502,7 +24511,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ113">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR113">
         <v>1.38</v>
@@ -25117,7 +25126,7 @@
         <v>0.4</v>
       </c>
       <c r="AP116">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ116">
         <v>0.55</v>
@@ -25532,7 +25541,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ118">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR118">
         <v>1.14</v>
@@ -25863,7 +25872,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -25944,7 +25953,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ120">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR120">
         <v>2.02</v>
@@ -26275,7 +26284,7 @@
         <v>167</v>
       </c>
       <c r="P122" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q122">
         <v>11</v>
@@ -26481,7 +26490,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26559,7 +26568,7 @@
         <v>0.83</v>
       </c>
       <c r="AP123">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ123">
         <v>1.27</v>
@@ -26687,7 +26696,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -27099,7 +27108,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27305,7 +27314,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27511,7 +27520,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27589,7 +27598,7 @@
         <v>0.57</v>
       </c>
       <c r="AP128">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ128">
         <v>1</v>
@@ -27717,7 +27726,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -28129,7 +28138,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28335,7 +28344,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28747,7 +28756,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -29031,7 +29040,7 @@
         <v>0.5</v>
       </c>
       <c r="AP135">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ135">
         <v>1.18</v>
@@ -29240,7 +29249,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ136">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR136">
         <v>1.19</v>
@@ -29446,7 +29455,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ137">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR137">
         <v>1.07</v>
@@ -29571,7 +29580,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29777,7 +29786,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -29855,7 +29864,7 @@
         <v>0.75</v>
       </c>
       <c r="AP139">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ139">
         <v>0.64</v>
@@ -30064,7 +30073,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ140">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR140">
         <v>1.98</v>
@@ -30189,7 +30198,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30395,7 +30404,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30601,7 +30610,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -31013,7 +31022,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31219,7 +31228,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31425,7 +31434,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q147">
         <v>2.55</v>
@@ -31631,7 +31640,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31709,7 +31718,7 @@
         <v>2.29</v>
       </c>
       <c r="AP148">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ148">
         <v>2.36</v>
@@ -31837,7 +31846,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32249,7 +32258,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32327,7 +32336,7 @@
         <v>1.29</v>
       </c>
       <c r="AP151">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ151">
         <v>1.45</v>
@@ -32455,7 +32464,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32661,7 +32670,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -32742,7 +32751,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ153">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR153">
         <v>1.2</v>
@@ -33151,7 +33160,7 @@
         <v>1.25</v>
       </c>
       <c r="AP155">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ155">
         <v>1.45</v>
@@ -33279,7 +33288,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33485,7 +33494,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33691,7 +33700,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33897,7 +33906,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34309,7 +34318,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34515,7 +34524,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34721,7 +34730,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -35133,7 +35142,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35214,7 +35223,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ165">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR165">
         <v>1.12</v>
@@ -35623,7 +35632,7 @@
         <v>1.75</v>
       </c>
       <c r="AP167">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ167">
         <v>1.82</v>
@@ -36035,7 +36044,7 @@
         <v>1.11</v>
       </c>
       <c r="AP169">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ169">
         <v>1</v>
@@ -36163,7 +36172,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36450,7 +36459,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ171">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR171">
         <v>1.66</v>
@@ -36656,7 +36665,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ172">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR172">
         <v>1.24</v>
@@ -36781,7 +36790,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -37193,7 +37202,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37399,7 +37408,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -38017,7 +38026,7 @@
         <v>205</v>
       </c>
       <c r="P179" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q179">
         <v>8.5</v>
@@ -38223,7 +38232,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q180">
         <v>4.75</v>
@@ -38429,7 +38438,7 @@
         <v>207</v>
       </c>
       <c r="P181" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q181">
         <v>6.5</v>
@@ -38635,7 +38644,7 @@
         <v>167</v>
       </c>
       <c r="P182" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -39047,7 +39056,7 @@
         <v>208</v>
       </c>
       <c r="P184" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q184">
         <v>1.57</v>
@@ -39125,7 +39134,7 @@
         <v>0.7</v>
       </c>
       <c r="AP184">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ184">
         <v>0.64</v>
@@ -39459,7 +39468,7 @@
         <v>209</v>
       </c>
       <c r="P186" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q186">
         <v>2.2</v>
@@ -39537,10 +39546,10 @@
         <v>0.9</v>
       </c>
       <c r="AP186">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ186">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR186">
         <v>1.19</v>
@@ -39952,7 +39961,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ188">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR188">
         <v>1.68</v>
@@ -40155,7 +40164,7 @@
         <v>0.33</v>
       </c>
       <c r="AP189">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ189">
         <v>0.55</v>
@@ -40283,7 +40292,7 @@
         <v>184</v>
       </c>
       <c r="P190" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q190">
         <v>2.63</v>
@@ -40364,7 +40373,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ190">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR190">
         <v>1.16</v>
@@ -40695,7 +40704,7 @@
         <v>212</v>
       </c>
       <c r="P192" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -40901,7 +40910,7 @@
         <v>213</v>
       </c>
       <c r="P193" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q193">
         <v>2.8</v>
@@ -41313,7 +41322,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q195">
         <v>1.67</v>
@@ -41725,7 +41734,7 @@
         <v>90</v>
       </c>
       <c r="P197" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q197">
         <v>7.5</v>
@@ -42137,7 +42146,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42500,6 +42509,624 @@
       </c>
       <c r="BP200">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7574761</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45710.52083333334</v>
+      </c>
+      <c r="F201">
+        <v>23</v>
+      </c>
+      <c r="G201" t="s">
+        <v>72</v>
+      </c>
+      <c r="H201" t="s">
+        <v>80</v>
+      </c>
+      <c r="I201">
+        <v>0</v>
+      </c>
+      <c r="J201">
+        <v>0</v>
+      </c>
+      <c r="K201">
+        <v>0</v>
+      </c>
+      <c r="L201">
+        <v>1</v>
+      </c>
+      <c r="M201">
+        <v>0</v>
+      </c>
+      <c r="N201">
+        <v>1</v>
+      </c>
+      <c r="O201" t="s">
+        <v>216</v>
+      </c>
+      <c r="P201" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q201">
+        <v>3.1</v>
+      </c>
+      <c r="R201">
+        <v>1.95</v>
+      </c>
+      <c r="S201">
+        <v>4.33</v>
+      </c>
+      <c r="T201">
+        <v>1.57</v>
+      </c>
+      <c r="U201">
+        <v>2.25</v>
+      </c>
+      <c r="V201">
+        <v>3.75</v>
+      </c>
+      <c r="W201">
+        <v>1.25</v>
+      </c>
+      <c r="X201">
+        <v>11</v>
+      </c>
+      <c r="Y201">
+        <v>1.05</v>
+      </c>
+      <c r="Z201">
+        <v>2.2</v>
+      </c>
+      <c r="AA201">
+        <v>3</v>
+      </c>
+      <c r="AB201">
+        <v>3.4</v>
+      </c>
+      <c r="AC201">
+        <v>1.1</v>
+      </c>
+      <c r="AD201">
+        <v>7.5</v>
+      </c>
+      <c r="AE201">
+        <v>1.47</v>
+      </c>
+      <c r="AF201">
+        <v>2.7</v>
+      </c>
+      <c r="AG201">
+        <v>2.4</v>
+      </c>
+      <c r="AH201">
+        <v>1.5</v>
+      </c>
+      <c r="AI201">
+        <v>2.05</v>
+      </c>
+      <c r="AJ201">
+        <v>1.7</v>
+      </c>
+      <c r="AK201">
+        <v>1.31</v>
+      </c>
+      <c r="AL201">
+        <v>1.34</v>
+      </c>
+      <c r="AM201">
+        <v>1.63</v>
+      </c>
+      <c r="AN201">
+        <v>1.73</v>
+      </c>
+      <c r="AO201">
+        <v>0.55</v>
+      </c>
+      <c r="AP201">
+        <v>1.83</v>
+      </c>
+      <c r="AQ201">
+        <v>0.5</v>
+      </c>
+      <c r="AR201">
+        <v>1.24</v>
+      </c>
+      <c r="AS201">
+        <v>0.92</v>
+      </c>
+      <c r="AT201">
+        <v>2.16</v>
+      </c>
+      <c r="AU201">
+        <v>3</v>
+      </c>
+      <c r="AV201">
+        <v>2</v>
+      </c>
+      <c r="AW201">
+        <v>9</v>
+      </c>
+      <c r="AX201">
+        <v>4</v>
+      </c>
+      <c r="AY201">
+        <v>13</v>
+      </c>
+      <c r="AZ201">
+        <v>8</v>
+      </c>
+      <c r="BA201">
+        <v>2</v>
+      </c>
+      <c r="BB201">
+        <v>5</v>
+      </c>
+      <c r="BC201">
+        <v>7</v>
+      </c>
+      <c r="BD201">
+        <v>1.7</v>
+      </c>
+      <c r="BE201">
+        <v>6.75</v>
+      </c>
+      <c r="BF201">
+        <v>2.35</v>
+      </c>
+      <c r="BG201">
+        <v>1.33</v>
+      </c>
+      <c r="BH201">
+        <v>2.95</v>
+      </c>
+      <c r="BI201">
+        <v>1.56</v>
+      </c>
+      <c r="BJ201">
+        <v>2.23</v>
+      </c>
+      <c r="BK201">
+        <v>1.91</v>
+      </c>
+      <c r="BL201">
+        <v>1.8</v>
+      </c>
+      <c r="BM201">
+        <v>2.4</v>
+      </c>
+      <c r="BN201">
+        <v>1.47</v>
+      </c>
+      <c r="BO201">
+        <v>3.15</v>
+      </c>
+      <c r="BP201">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7574769</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45710.625</v>
+      </c>
+      <c r="F202">
+        <v>23</v>
+      </c>
+      <c r="G202" t="s">
+        <v>83</v>
+      </c>
+      <c r="H202" t="s">
+        <v>86</v>
+      </c>
+      <c r="I202">
+        <v>1</v>
+      </c>
+      <c r="J202">
+        <v>0</v>
+      </c>
+      <c r="K202">
+        <v>1</v>
+      </c>
+      <c r="L202">
+        <v>3</v>
+      </c>
+      <c r="M202">
+        <v>0</v>
+      </c>
+      <c r="N202">
+        <v>3</v>
+      </c>
+      <c r="O202" t="s">
+        <v>217</v>
+      </c>
+      <c r="P202" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q202">
+        <v>1.43</v>
+      </c>
+      <c r="R202">
+        <v>3.4</v>
+      </c>
+      <c r="S202">
+        <v>12.83</v>
+      </c>
+      <c r="T202">
+        <v>1.2</v>
+      </c>
+      <c r="U202">
+        <v>4</v>
+      </c>
+      <c r="V202">
+        <v>2.05</v>
+      </c>
+      <c r="W202">
+        <v>1.77</v>
+      </c>
+      <c r="X202">
+        <v>4</v>
+      </c>
+      <c r="Y202">
+        <v>1.2</v>
+      </c>
+      <c r="Z202">
+        <v>1.1</v>
+      </c>
+      <c r="AA202">
+        <v>9</v>
+      </c>
+      <c r="AB202">
+        <v>17</v>
+      </c>
+      <c r="AC202">
+        <v>1.01</v>
+      </c>
+      <c r="AD202">
+        <v>23</v>
+      </c>
+      <c r="AE202">
+        <v>1.11</v>
+      </c>
+      <c r="AF202">
+        <v>5.5</v>
+      </c>
+      <c r="AG202">
+        <v>1.36</v>
+      </c>
+      <c r="AH202">
+        <v>2.99</v>
+      </c>
+      <c r="AI202">
+        <v>2.3</v>
+      </c>
+      <c r="AJ202">
+        <v>1.55</v>
+      </c>
+      <c r="AK202">
+        <v>1.02</v>
+      </c>
+      <c r="AL202">
+        <v>1.06</v>
+      </c>
+      <c r="AM202">
+        <v>5.75</v>
+      </c>
+      <c r="AN202">
+        <v>2.73</v>
+      </c>
+      <c r="AO202">
+        <v>0.82</v>
+      </c>
+      <c r="AP202">
+        <v>2.75</v>
+      </c>
+      <c r="AQ202">
+        <v>0.75</v>
+      </c>
+      <c r="AR202">
+        <v>2.01</v>
+      </c>
+      <c r="AS202">
+        <v>0.98</v>
+      </c>
+      <c r="AT202">
+        <v>2.99</v>
+      </c>
+      <c r="AU202">
+        <v>14</v>
+      </c>
+      <c r="AV202">
+        <v>3</v>
+      </c>
+      <c r="AW202">
+        <v>18</v>
+      </c>
+      <c r="AX202">
+        <v>3</v>
+      </c>
+      <c r="AY202">
+        <v>37</v>
+      </c>
+      <c r="AZ202">
+        <v>7</v>
+      </c>
+      <c r="BA202">
+        <v>13</v>
+      </c>
+      <c r="BB202">
+        <v>2</v>
+      </c>
+      <c r="BC202">
+        <v>15</v>
+      </c>
+      <c r="BD202">
+        <v>1.1</v>
+      </c>
+      <c r="BE202">
+        <v>10.5</v>
+      </c>
+      <c r="BF202">
+        <v>7</v>
+      </c>
+      <c r="BG202">
+        <v>1.27</v>
+      </c>
+      <c r="BH202">
+        <v>3.25</v>
+      </c>
+      <c r="BI202">
+        <v>1.47</v>
+      </c>
+      <c r="BJ202">
+        <v>2.43</v>
+      </c>
+      <c r="BK202">
+        <v>1.8</v>
+      </c>
+      <c r="BL202">
+        <v>1.91</v>
+      </c>
+      <c r="BM202">
+        <v>2.18</v>
+      </c>
+      <c r="BN202">
+        <v>1.58</v>
+      </c>
+      <c r="BO202">
+        <v>2.7</v>
+      </c>
+      <c r="BP202">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7574762</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45710.72916666666</v>
+      </c>
+      <c r="F203">
+        <v>23</v>
+      </c>
+      <c r="G203" t="s">
+        <v>74</v>
+      </c>
+      <c r="H203" t="s">
+        <v>81</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+      <c r="L203">
+        <v>2</v>
+      </c>
+      <c r="M203">
+        <v>1</v>
+      </c>
+      <c r="N203">
+        <v>3</v>
+      </c>
+      <c r="O203" t="s">
+        <v>218</v>
+      </c>
+      <c r="P203" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q203">
+        <v>2.55</v>
+      </c>
+      <c r="R203">
+        <v>2.05</v>
+      </c>
+      <c r="S203">
+        <v>4.2</v>
+      </c>
+      <c r="T203">
+        <v>1.4</v>
+      </c>
+      <c r="U203">
+        <v>2.7</v>
+      </c>
+      <c r="V203">
+        <v>2.8</v>
+      </c>
+      <c r="W203">
+        <v>1.38</v>
+      </c>
+      <c r="X203">
+        <v>6.5</v>
+      </c>
+      <c r="Y203">
+        <v>1.08</v>
+      </c>
+      <c r="Z203">
+        <v>1.95</v>
+      </c>
+      <c r="AA203">
+        <v>3.3</v>
+      </c>
+      <c r="AB203">
+        <v>3.8</v>
+      </c>
+      <c r="AC203">
+        <v>1.06</v>
+      </c>
+      <c r="AD203">
+        <v>8.5</v>
+      </c>
+      <c r="AE203">
+        <v>1.33</v>
+      </c>
+      <c r="AF203">
+        <v>3.2</v>
+      </c>
+      <c r="AG203">
+        <v>2</v>
+      </c>
+      <c r="AH203">
+        <v>1.75</v>
+      </c>
+      <c r="AI203">
+        <v>1.77</v>
+      </c>
+      <c r="AJ203">
+        <v>1.95</v>
+      </c>
+      <c r="AK203">
+        <v>1.25</v>
+      </c>
+      <c r="AL203">
+        <v>1.25</v>
+      </c>
+      <c r="AM203">
+        <v>1.75</v>
+      </c>
+      <c r="AN203">
+        <v>1.64</v>
+      </c>
+      <c r="AO203">
+        <v>0.73</v>
+      </c>
+      <c r="AP203">
+        <v>1.75</v>
+      </c>
+      <c r="AQ203">
+        <v>0.67</v>
+      </c>
+      <c r="AR203">
+        <v>1.23</v>
+      </c>
+      <c r="AS203">
+        <v>0.97</v>
+      </c>
+      <c r="AT203">
+        <v>2.2</v>
+      </c>
+      <c r="AU203">
+        <v>5</v>
+      </c>
+      <c r="AV203">
+        <v>5</v>
+      </c>
+      <c r="AW203">
+        <v>8</v>
+      </c>
+      <c r="AX203">
+        <v>8</v>
+      </c>
+      <c r="AY203">
+        <v>15</v>
+      </c>
+      <c r="AZ203">
+        <v>14</v>
+      </c>
+      <c r="BA203">
+        <v>0</v>
+      </c>
+      <c r="BB203">
+        <v>4</v>
+      </c>
+      <c r="BC203">
+        <v>4</v>
+      </c>
+      <c r="BD203">
+        <v>1.6</v>
+      </c>
+      <c r="BE203">
+        <v>6.75</v>
+      </c>
+      <c r="BF203">
+        <v>2.55</v>
+      </c>
+      <c r="BG203">
+        <v>1.23</v>
+      </c>
+      <c r="BH203">
+        <v>3.6</v>
+      </c>
+      <c r="BI203">
+        <v>1.58</v>
+      </c>
+      <c r="BJ203">
+        <v>2.15</v>
+      </c>
+      <c r="BK203">
+        <v>1.96</v>
+      </c>
+      <c r="BL203">
+        <v>1.72</v>
+      </c>
+      <c r="BM203">
+        <v>2.5</v>
+      </c>
+      <c r="BN203">
+        <v>1.44</v>
+      </c>
+      <c r="BO203">
+        <v>3.25</v>
+      </c>
+      <c r="BP203">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="316">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -673,6 +673,15 @@
     <t>['55', '90']</t>
   </si>
   <si>
+    <t>['56', '67']</t>
+  </si>
+  <si>
+    <t>['71', '90+6']</t>
+  </si>
+  <si>
+    <t>['47', '58']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -947,6 +956,12 @@
   </si>
   <si>
     <t>['83']</t>
+  </si>
+  <si>
+    <t>['44', '89']</t>
+  </si>
+  <si>
+    <t>['8', '33']</t>
   </si>
 </sst>
 </file>
@@ -1308,7 +1323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP203"/>
+  <dimension ref="A1:BP207"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1770,7 +1785,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -1848,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ3">
         <v>0.5</v>
@@ -2388,7 +2403,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2469,7 +2484,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ6">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2672,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ7">
         <v>1.82</v>
@@ -2800,7 +2815,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -2881,7 +2896,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ8">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3290,7 +3305,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3418,7 +3433,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3624,7 +3639,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3911,7 +3926,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ13">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4036,7 +4051,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4117,7 +4132,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ14">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4448,7 +4463,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4860,7 +4875,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -5066,7 +5081,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5144,7 +5159,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ19">
         <v>1.45</v>
@@ -5272,7 +5287,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5353,7 +5368,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ20">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR20">
         <v>1.56</v>
@@ -5478,7 +5493,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -5559,7 +5574,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ21">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR21">
         <v>1.57</v>
@@ -5968,7 +5983,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ23">
         <v>0.75</v>
@@ -6380,7 +6395,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ25">
         <v>0.5</v>
@@ -6792,7 +6807,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -7001,7 +7016,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ28">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR28">
         <v>1.72</v>
@@ -7126,7 +7141,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7332,7 +7347,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7538,7 +7553,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -7616,7 +7631,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ31">
         <v>1.27</v>
@@ -8237,7 +8252,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ34">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR34">
         <v>1.18</v>
@@ -8568,7 +8583,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q36">
         <v>2.55</v>
@@ -8980,7 +8995,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9058,10 +9073,10 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ38">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR38">
         <v>0.93</v>
@@ -9186,7 +9201,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9267,7 +9282,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ39">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR39">
         <v>1.27</v>
@@ -9470,7 +9485,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ40">
         <v>0.67</v>
@@ -9598,7 +9613,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9676,7 +9691,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ41">
         <v>0.5</v>
@@ -9804,7 +9819,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -9885,7 +9900,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ42">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR42">
         <v>2.4</v>
@@ -10010,7 +10025,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10091,7 +10106,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ43">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR43">
         <v>2.13</v>
@@ -10422,7 +10437,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10628,7 +10643,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10706,7 +10721,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ46">
         <v>0.75</v>
@@ -10834,7 +10849,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -11040,7 +11055,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11452,7 +11467,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11864,7 +11879,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -12482,7 +12497,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12688,7 +12703,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -12769,7 +12784,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ56">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR56">
         <v>0.98</v>
@@ -12972,10 +12987,10 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ57">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR57">
         <v>1.33</v>
@@ -13100,7 +13115,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13306,7 +13321,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -13590,7 +13605,7 @@
         <v>0.33</v>
       </c>
       <c r="AP60">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ60">
         <v>0.5</v>
@@ -14414,10 +14429,10 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ64">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR64">
         <v>1.27</v>
@@ -15035,7 +15050,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ67">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR67">
         <v>1.08</v>
@@ -15238,7 +15253,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ68">
         <v>0.55</v>
@@ -15778,7 +15793,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -15984,7 +15999,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16396,7 +16411,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16602,7 +16617,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16808,7 +16823,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16889,7 +16904,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ76">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR76">
         <v>1.15</v>
@@ -17014,7 +17029,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17092,10 +17107,10 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ77">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR77">
         <v>1.24</v>
@@ -17301,7 +17316,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ78">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR78">
         <v>1.68</v>
@@ -17632,7 +17647,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17710,7 +17725,7 @@
         <v>1.75</v>
       </c>
       <c r="AP80">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ80">
         <v>1</v>
@@ -17838,7 +17853,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -17916,7 +17931,7 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ81">
         <v>1.55</v>
@@ -18044,7 +18059,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18250,7 +18265,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18456,7 +18471,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18662,7 +18677,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18868,7 +18883,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -18946,7 +18961,7 @@
         <v>1.25</v>
       </c>
       <c r="AP86">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ86">
         <v>1.45</v>
@@ -19155,7 +19170,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ87">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR87">
         <v>1.16</v>
@@ -19280,7 +19295,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19358,7 +19373,7 @@
         <v>1.75</v>
       </c>
       <c r="AP88">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ88">
         <v>2.36</v>
@@ -19773,7 +19788,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ90">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR90">
         <v>1.22</v>
@@ -19898,7 +19913,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -20104,7 +20119,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20185,7 +20200,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ92">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR92">
         <v>1.25</v>
@@ -20594,7 +20609,7 @@
         <v>0.6</v>
       </c>
       <c r="AP94">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -20722,7 +20737,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -21006,7 +21021,7 @@
         <v>0.4</v>
       </c>
       <c r="AP96">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ96">
         <v>0.5</v>
@@ -21340,7 +21355,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21421,7 +21436,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ98">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR98">
         <v>1.75</v>
@@ -21958,7 +21973,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22039,7 +22054,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ101">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR101">
         <v>1.42</v>
@@ -22370,7 +22385,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22451,7 +22466,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ103">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR103">
         <v>2.02</v>
@@ -22782,7 +22797,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -22860,7 +22875,7 @@
         <v>1.75</v>
       </c>
       <c r="AP105">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ105">
         <v>1.82</v>
@@ -22988,7 +23003,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q106">
         <v>5.5</v>
@@ -23066,7 +23081,7 @@
         <v>2</v>
       </c>
       <c r="AP106">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ106">
         <v>2.36</v>
@@ -23687,7 +23702,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ109">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR109">
         <v>1.17</v>
@@ -23812,7 +23827,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -24714,7 +24729,7 @@
         <v>1.8</v>
       </c>
       <c r="AP114">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ114">
         <v>1.55</v>
@@ -24923,7 +24938,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ115">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR115">
         <v>1.28</v>
@@ -25332,7 +25347,7 @@
         <v>0.67</v>
       </c>
       <c r="AP117">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ117">
         <v>1</v>
@@ -25747,7 +25762,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ119">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR119">
         <v>1.33</v>
@@ -25872,7 +25887,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26156,10 +26171,10 @@
         <v>1.5</v>
       </c>
       <c r="AP121">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ121">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR121">
         <v>1.05</v>
@@ -26284,7 +26299,7 @@
         <v>167</v>
       </c>
       <c r="P122" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q122">
         <v>11</v>
@@ -26362,7 +26377,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ122">
         <v>1.82</v>
@@ -26490,7 +26505,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26696,7 +26711,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -27108,7 +27123,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27314,7 +27329,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27520,7 +27535,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27726,7 +27741,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27804,10 +27819,10 @@
         <v>0.43</v>
       </c>
       <c r="AP129">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ129">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR129">
         <v>1.02</v>
@@ -28138,7 +28153,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28344,7 +28359,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28631,7 +28646,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ133">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR133">
         <v>1.29</v>
@@ -28756,7 +28771,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -29246,7 +29261,7 @@
         <v>0.43</v>
       </c>
       <c r="AP136">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ136">
         <v>0.67</v>
@@ -29452,7 +29467,7 @@
         <v>0.63</v>
       </c>
       <c r="AP137">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ137">
         <v>0.5</v>
@@ -29580,7 +29595,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29658,7 +29673,7 @@
         <v>0.14</v>
       </c>
       <c r="AP138">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ138">
         <v>0.55</v>
@@ -29786,7 +29801,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -29867,7 +29882,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ139">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR139">
         <v>1.09</v>
@@ -30198,7 +30213,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30404,7 +30419,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30610,7 +30625,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -31022,7 +31037,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31100,10 +31115,10 @@
         <v>1.29</v>
       </c>
       <c r="AP145">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ145">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR145">
         <v>1.04</v>
@@ -31228,7 +31243,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31309,7 +31324,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ146">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR146">
         <v>1.3</v>
@@ -31434,7 +31449,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q147">
         <v>2.55</v>
@@ -31640,7 +31655,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31846,7 +31861,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32133,7 +32148,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ150">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR150">
         <v>1.34</v>
@@ -32258,7 +32273,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32464,7 +32479,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32542,7 +32557,7 @@
         <v>0.43</v>
       </c>
       <c r="AP152">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ152">
         <v>1.18</v>
@@ -32670,7 +32685,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -33288,7 +33303,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33494,7 +33509,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33575,7 +33590,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ157">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR157">
         <v>1.39</v>
@@ -33700,7 +33715,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33906,7 +33921,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34193,7 +34208,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ160">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR160">
         <v>1.14</v>
@@ -34318,7 +34333,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34396,7 +34411,7 @@
         <v>2.38</v>
       </c>
       <c r="AP161">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ161">
         <v>2.36</v>
@@ -34524,7 +34539,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34730,7 +34745,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -35014,10 +35029,10 @@
         <v>0.78</v>
       </c>
       <c r="AP164">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ164">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR164">
         <v>1.09</v>
@@ -35142,7 +35157,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35426,7 +35441,7 @@
         <v>0.25</v>
       </c>
       <c r="AP166">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ166">
         <v>0.55</v>
@@ -36172,7 +36187,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36253,7 +36268,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ170">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR170">
         <v>1.95</v>
@@ -36662,7 +36677,7 @@
         <v>0.67</v>
       </c>
       <c r="AP172">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ172">
         <v>0.5</v>
@@ -36790,7 +36805,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -37202,7 +37217,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37408,7 +37423,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -37901,7 +37916,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ178">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR178">
         <v>2.03</v>
@@ -38026,7 +38041,7 @@
         <v>205</v>
       </c>
       <c r="P179" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q179">
         <v>8.5</v>
@@ -38104,7 +38119,7 @@
         <v>1.56</v>
       </c>
       <c r="AP179">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ179">
         <v>1.82</v>
@@ -38232,7 +38247,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q180">
         <v>4.75</v>
@@ -38438,7 +38453,7 @@
         <v>207</v>
       </c>
       <c r="P181" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q181">
         <v>6.5</v>
@@ -38644,7 +38659,7 @@
         <v>167</v>
       </c>
       <c r="P182" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -38725,7 +38740,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ182">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR182">
         <v>2.01</v>
@@ -38928,10 +38943,10 @@
         <v>1.44</v>
       </c>
       <c r="AP183">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ183">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR183">
         <v>1.2</v>
@@ -39056,7 +39071,7 @@
         <v>208</v>
       </c>
       <c r="P184" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q184">
         <v>1.57</v>
@@ -39137,7 +39152,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ184">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR184">
         <v>2.05</v>
@@ -39340,7 +39355,7 @@
         <v>1</v>
       </c>
       <c r="AP185">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ185">
         <v>1</v>
@@ -39468,7 +39483,7 @@
         <v>209</v>
       </c>
       <c r="P186" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q186">
         <v>2.2</v>
@@ -40292,7 +40307,7 @@
         <v>184</v>
       </c>
       <c r="P190" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q190">
         <v>2.63</v>
@@ -40370,7 +40385,7 @@
         <v>0.7</v>
       </c>
       <c r="AP190">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ190">
         <v>0.67</v>
@@ -40704,7 +40719,7 @@
         <v>212</v>
       </c>
       <c r="P192" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -40910,7 +40925,7 @@
         <v>213</v>
       </c>
       <c r="P193" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q193">
         <v>2.8</v>
@@ -41322,7 +41337,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q195">
         <v>1.67</v>
@@ -41734,7 +41749,7 @@
         <v>90</v>
       </c>
       <c r="P197" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q197">
         <v>7.5</v>
@@ -42146,7 +42161,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42970,7 +42985,7 @@
         <v>218</v>
       </c>
       <c r="P203" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q203">
         <v>2.55</v>
@@ -43127,6 +43142,830 @@
       </c>
       <c r="BP203">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7574764</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45711.52083333334</v>
+      </c>
+      <c r="F204">
+        <v>23</v>
+      </c>
+      <c r="G204" t="s">
+        <v>78</v>
+      </c>
+      <c r="H204" t="s">
+        <v>76</v>
+      </c>
+      <c r="I204">
+        <v>0</v>
+      </c>
+      <c r="J204">
+        <v>1</v>
+      </c>
+      <c r="K204">
+        <v>1</v>
+      </c>
+      <c r="L204">
+        <v>2</v>
+      </c>
+      <c r="M204">
+        <v>2</v>
+      </c>
+      <c r="N204">
+        <v>4</v>
+      </c>
+      <c r="O204" t="s">
+        <v>219</v>
+      </c>
+      <c r="P204" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q204">
+        <v>2.45</v>
+      </c>
+      <c r="R204">
+        <v>2.05</v>
+      </c>
+      <c r="S204">
+        <v>4.5</v>
+      </c>
+      <c r="T204">
+        <v>1.45</v>
+      </c>
+      <c r="U204">
+        <v>2.55</v>
+      </c>
+      <c r="V204">
+        <v>3</v>
+      </c>
+      <c r="W204">
+        <v>1.33</v>
+      </c>
+      <c r="X204">
+        <v>7.5</v>
+      </c>
+      <c r="Y204">
+        <v>1.06</v>
+      </c>
+      <c r="Z204">
+        <v>1.85</v>
+      </c>
+      <c r="AA204">
+        <v>3.3</v>
+      </c>
+      <c r="AB204">
+        <v>4.2</v>
+      </c>
+      <c r="AC204">
+        <v>1.07</v>
+      </c>
+      <c r="AD204">
+        <v>8</v>
+      </c>
+      <c r="AE204">
+        <v>1.4</v>
+      </c>
+      <c r="AF204">
+        <v>2.9</v>
+      </c>
+      <c r="AG204">
+        <v>2.15</v>
+      </c>
+      <c r="AH204">
+        <v>1.65</v>
+      </c>
+      <c r="AI204">
+        <v>1.95</v>
+      </c>
+      <c r="AJ204">
+        <v>1.77</v>
+      </c>
+      <c r="AK204">
+        <v>1.22</v>
+      </c>
+      <c r="AL204">
+        <v>1.25</v>
+      </c>
+      <c r="AM204">
+        <v>1.85</v>
+      </c>
+      <c r="AN204">
+        <v>1.2</v>
+      </c>
+      <c r="AO204">
+        <v>0.73</v>
+      </c>
+      <c r="AP204">
+        <v>1.18</v>
+      </c>
+      <c r="AQ204">
+        <v>0.75</v>
+      </c>
+      <c r="AR204">
+        <v>1.23</v>
+      </c>
+      <c r="AS204">
+        <v>0.98</v>
+      </c>
+      <c r="AT204">
+        <v>2.21</v>
+      </c>
+      <c r="AU204">
+        <v>4</v>
+      </c>
+      <c r="AV204">
+        <v>9</v>
+      </c>
+      <c r="AW204">
+        <v>5</v>
+      </c>
+      <c r="AX204">
+        <v>10</v>
+      </c>
+      <c r="AY204">
+        <v>13</v>
+      </c>
+      <c r="AZ204">
+        <v>20</v>
+      </c>
+      <c r="BA204">
+        <v>4</v>
+      </c>
+      <c r="BB204">
+        <v>8</v>
+      </c>
+      <c r="BC204">
+        <v>12</v>
+      </c>
+      <c r="BD204">
+        <v>1.27</v>
+      </c>
+      <c r="BE204">
+        <v>8</v>
+      </c>
+      <c r="BF204">
+        <v>4</v>
+      </c>
+      <c r="BG204">
+        <v>1.18</v>
+      </c>
+      <c r="BH204">
+        <v>4</v>
+      </c>
+      <c r="BI204">
+        <v>1.34</v>
+      </c>
+      <c r="BJ204">
+        <v>2.9</v>
+      </c>
+      <c r="BK204">
+        <v>1.56</v>
+      </c>
+      <c r="BL204">
+        <v>2.23</v>
+      </c>
+      <c r="BM204">
+        <v>1.85</v>
+      </c>
+      <c r="BN204">
+        <v>1.82</v>
+      </c>
+      <c r="BO204">
+        <v>2.25</v>
+      </c>
+      <c r="BP204">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7574767</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45711.52083333334</v>
+      </c>
+      <c r="F205">
+        <v>23</v>
+      </c>
+      <c r="G205" t="s">
+        <v>87</v>
+      </c>
+      <c r="H205" t="s">
+        <v>79</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>0</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="M205">
+        <v>0</v>
+      </c>
+      <c r="N205">
+        <v>0</v>
+      </c>
+      <c r="O205" t="s">
+        <v>90</v>
+      </c>
+      <c r="P205" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q205">
+        <v>4.33</v>
+      </c>
+      <c r="R205">
+        <v>1.85</v>
+      </c>
+      <c r="S205">
+        <v>2.85</v>
+      </c>
+      <c r="T205">
+        <v>1.6</v>
+      </c>
+      <c r="U205">
+        <v>2.2</v>
+      </c>
+      <c r="V205">
+        <v>3.8</v>
+      </c>
+      <c r="W205">
+        <v>1.22</v>
+      </c>
+      <c r="X205">
+        <v>11.5</v>
+      </c>
+      <c r="Y205">
+        <v>1.04</v>
+      </c>
+      <c r="Z205">
+        <v>3.4</v>
+      </c>
+      <c r="AA205">
+        <v>3.2</v>
+      </c>
+      <c r="AB205">
+        <v>2.1</v>
+      </c>
+      <c r="AC205">
+        <v>1.1</v>
+      </c>
+      <c r="AD205">
+        <v>6.5</v>
+      </c>
+      <c r="AE205">
+        <v>1.53</v>
+      </c>
+      <c r="AF205">
+        <v>2.37</v>
+      </c>
+      <c r="AG205">
+        <v>2.86</v>
+      </c>
+      <c r="AH205">
+        <v>1.39</v>
+      </c>
+      <c r="AI205">
+        <v>2.25</v>
+      </c>
+      <c r="AJ205">
+        <v>1.57</v>
+      </c>
+      <c r="AK205">
+        <v>1.67</v>
+      </c>
+      <c r="AL205">
+        <v>1.3</v>
+      </c>
+      <c r="AM205">
+        <v>1.28</v>
+      </c>
+      <c r="AN205">
+        <v>1.27</v>
+      </c>
+      <c r="AO205">
+        <v>1.6</v>
+      </c>
+      <c r="AP205">
+        <v>1.25</v>
+      </c>
+      <c r="AQ205">
+        <v>1.55</v>
+      </c>
+      <c r="AR205">
+        <v>1.15</v>
+      </c>
+      <c r="AS205">
+        <v>0.99</v>
+      </c>
+      <c r="AT205">
+        <v>2.14</v>
+      </c>
+      <c r="AU205">
+        <v>3</v>
+      </c>
+      <c r="AV205">
+        <v>2</v>
+      </c>
+      <c r="AW205">
+        <v>9</v>
+      </c>
+      <c r="AX205">
+        <v>4</v>
+      </c>
+      <c r="AY205">
+        <v>15</v>
+      </c>
+      <c r="AZ205">
+        <v>7</v>
+      </c>
+      <c r="BA205">
+        <v>5</v>
+      </c>
+      <c r="BB205">
+        <v>2</v>
+      </c>
+      <c r="BC205">
+        <v>7</v>
+      </c>
+      <c r="BD205">
+        <v>2.12</v>
+      </c>
+      <c r="BE205">
+        <v>6.5</v>
+      </c>
+      <c r="BF205">
+        <v>1.86</v>
+      </c>
+      <c r="BG205">
+        <v>1.34</v>
+      </c>
+      <c r="BH205">
+        <v>2.85</v>
+      </c>
+      <c r="BI205">
+        <v>1.58</v>
+      </c>
+      <c r="BJ205">
+        <v>2.16</v>
+      </c>
+      <c r="BK205">
+        <v>1.95</v>
+      </c>
+      <c r="BL205">
+        <v>1.72</v>
+      </c>
+      <c r="BM205">
+        <v>2.48</v>
+      </c>
+      <c r="BN205">
+        <v>1.45</v>
+      </c>
+      <c r="BO205">
+        <v>3.2</v>
+      </c>
+      <c r="BP205">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7574765</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45711.625</v>
+      </c>
+      <c r="F206">
+        <v>23</v>
+      </c>
+      <c r="G206" t="s">
+        <v>71</v>
+      </c>
+      <c r="H206" t="s">
+        <v>70</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>2</v>
+      </c>
+      <c r="K206">
+        <v>2</v>
+      </c>
+      <c r="L206">
+        <v>2</v>
+      </c>
+      <c r="M206">
+        <v>2</v>
+      </c>
+      <c r="N206">
+        <v>4</v>
+      </c>
+      <c r="O206" t="s">
+        <v>220</v>
+      </c>
+      <c r="P206" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q206">
+        <v>7</v>
+      </c>
+      <c r="R206">
+        <v>2.45</v>
+      </c>
+      <c r="S206">
+        <v>1.75</v>
+      </c>
+      <c r="T206">
+        <v>1.3</v>
+      </c>
+      <c r="U206">
+        <v>3.25</v>
+      </c>
+      <c r="V206">
+        <v>2.4</v>
+      </c>
+      <c r="W206">
+        <v>1.5</v>
+      </c>
+      <c r="X206">
+        <v>5.5</v>
+      </c>
+      <c r="Y206">
+        <v>1.11</v>
+      </c>
+      <c r="Z206">
+        <v>8.5</v>
+      </c>
+      <c r="AA206">
+        <v>5</v>
+      </c>
+      <c r="AB206">
+        <v>1.3</v>
+      </c>
+      <c r="AC206">
+        <v>1.04</v>
+      </c>
+      <c r="AD206">
+        <v>10</v>
+      </c>
+      <c r="AE206">
+        <v>1.22</v>
+      </c>
+      <c r="AF206">
+        <v>4.2</v>
+      </c>
+      <c r="AG206">
+        <v>1.73</v>
+      </c>
+      <c r="AH206">
+        <v>2.05</v>
+      </c>
+      <c r="AI206">
+        <v>2.05</v>
+      </c>
+      <c r="AJ206">
+        <v>1.7</v>
+      </c>
+      <c r="AK206">
+        <v>3.1</v>
+      </c>
+      <c r="AL206">
+        <v>1.12</v>
+      </c>
+      <c r="AM206">
+        <v>1.06</v>
+      </c>
+      <c r="AN206">
+        <v>1.18</v>
+      </c>
+      <c r="AO206">
+        <v>2.18</v>
+      </c>
+      <c r="AP206">
+        <v>1.17</v>
+      </c>
+      <c r="AQ206">
+        <v>2.08</v>
+      </c>
+      <c r="AR206">
+        <v>1.22</v>
+      </c>
+      <c r="AS206">
+        <v>1.96</v>
+      </c>
+      <c r="AT206">
+        <v>3.18</v>
+      </c>
+      <c r="AU206">
+        <v>5</v>
+      </c>
+      <c r="AV206">
+        <v>4</v>
+      </c>
+      <c r="AW206">
+        <v>6</v>
+      </c>
+      <c r="AX206">
+        <v>6</v>
+      </c>
+      <c r="AY206">
+        <v>14</v>
+      </c>
+      <c r="AZ206">
+        <v>12</v>
+      </c>
+      <c r="BA206">
+        <v>4</v>
+      </c>
+      <c r="BB206">
+        <v>5</v>
+      </c>
+      <c r="BC206">
+        <v>9</v>
+      </c>
+      <c r="BD206">
+        <v>4.3</v>
+      </c>
+      <c r="BE206">
+        <v>7.5</v>
+      </c>
+      <c r="BF206">
+        <v>1.26</v>
+      </c>
+      <c r="BG206">
+        <v>1.34</v>
+      </c>
+      <c r="BH206">
+        <v>2.88</v>
+      </c>
+      <c r="BI206">
+        <v>1.58</v>
+      </c>
+      <c r="BJ206">
+        <v>2.17</v>
+      </c>
+      <c r="BK206">
+        <v>1.93</v>
+      </c>
+      <c r="BL206">
+        <v>1.74</v>
+      </c>
+      <c r="BM206">
+        <v>2.43</v>
+      </c>
+      <c r="BN206">
+        <v>1.47</v>
+      </c>
+      <c r="BO206">
+        <v>3.15</v>
+      </c>
+      <c r="BP206">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7574763</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45711.72916666666</v>
+      </c>
+      <c r="F207">
+        <v>23</v>
+      </c>
+      <c r="G207" t="s">
+        <v>75</v>
+      </c>
+      <c r="H207" t="s">
+        <v>84</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="J207">
+        <v>0</v>
+      </c>
+      <c r="K207">
+        <v>0</v>
+      </c>
+      <c r="L207">
+        <v>2</v>
+      </c>
+      <c r="M207">
+        <v>0</v>
+      </c>
+      <c r="N207">
+        <v>2</v>
+      </c>
+      <c r="O207" t="s">
+        <v>221</v>
+      </c>
+      <c r="P207" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q207">
+        <v>3</v>
+      </c>
+      <c r="R207">
+        <v>1.95</v>
+      </c>
+      <c r="S207">
+        <v>4.33</v>
+      </c>
+      <c r="T207">
+        <v>1.57</v>
+      </c>
+      <c r="U207">
+        <v>2.25</v>
+      </c>
+      <c r="V207">
+        <v>3.75</v>
+      </c>
+      <c r="W207">
+        <v>1.25</v>
+      </c>
+      <c r="X207">
+        <v>11</v>
+      </c>
+      <c r="Y207">
+        <v>1.05</v>
+      </c>
+      <c r="Z207">
+        <v>2.1</v>
+      </c>
+      <c r="AA207">
+        <v>3</v>
+      </c>
+      <c r="AB207">
+        <v>3.6</v>
+      </c>
+      <c r="AC207">
+        <v>1.1</v>
+      </c>
+      <c r="AD207">
+        <v>7</v>
+      </c>
+      <c r="AE207">
+        <v>1.5</v>
+      </c>
+      <c r="AF207">
+        <v>2.4</v>
+      </c>
+      <c r="AG207">
+        <v>2.4</v>
+      </c>
+      <c r="AH207">
+        <v>1.5</v>
+      </c>
+      <c r="AI207">
+        <v>2.1</v>
+      </c>
+      <c r="AJ207">
+        <v>1.67</v>
+      </c>
+      <c r="AK207">
+        <v>1.29</v>
+      </c>
+      <c r="AL207">
+        <v>1.34</v>
+      </c>
+      <c r="AM207">
+        <v>1.66</v>
+      </c>
+      <c r="AN207">
+        <v>1.09</v>
+      </c>
+      <c r="AO207">
+        <v>0.64</v>
+      </c>
+      <c r="AP207">
+        <v>1.25</v>
+      </c>
+      <c r="AQ207">
+        <v>0.58</v>
+      </c>
+      <c r="AR207">
+        <v>1.11</v>
+      </c>
+      <c r="AS207">
+        <v>1.17</v>
+      </c>
+      <c r="AT207">
+        <v>2.28</v>
+      </c>
+      <c r="AU207">
+        <v>7</v>
+      </c>
+      <c r="AV207">
+        <v>7</v>
+      </c>
+      <c r="AW207">
+        <v>12</v>
+      </c>
+      <c r="AX207">
+        <v>2</v>
+      </c>
+      <c r="AY207">
+        <v>22</v>
+      </c>
+      <c r="AZ207">
+        <v>9</v>
+      </c>
+      <c r="BA207">
+        <v>3</v>
+      </c>
+      <c r="BB207">
+        <v>1</v>
+      </c>
+      <c r="BC207">
+        <v>4</v>
+      </c>
+      <c r="BD207">
+        <v>1.5</v>
+      </c>
+      <c r="BE207">
+        <v>6.5</v>
+      </c>
+      <c r="BF207">
+        <v>2.9</v>
+      </c>
+      <c r="BG207">
+        <v>1.38</v>
+      </c>
+      <c r="BH207">
+        <v>2.7</v>
+      </c>
+      <c r="BI207">
+        <v>1.65</v>
+      </c>
+      <c r="BJ207">
+        <v>2.06</v>
+      </c>
+      <c r="BK207">
+        <v>2.05</v>
+      </c>
+      <c r="BL207">
+        <v>1.7</v>
+      </c>
+      <c r="BM207">
+        <v>2.63</v>
+      </c>
+      <c r="BN207">
+        <v>1.4</v>
+      </c>
+      <c r="BO207">
+        <v>3.4</v>
+      </c>
+      <c r="BP207">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="317">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -963,6 +963,9 @@
   <si>
     <t>['8', '33']</t>
   </si>
+  <si>
+    <t>['86']</t>
+  </si>
 </sst>
 </file>
 
@@ -1323,7 +1326,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP207"/>
+  <dimension ref="A1:BP208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2275,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ5">
         <v>0.5</v>
@@ -5777,7 +5780,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ22">
         <v>0.67</v>
@@ -10103,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ43">
         <v>0.75</v>
@@ -13811,7 +13814,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ61">
         <v>1</v>
@@ -16077,7 +16080,7 @@
         <v>2.33</v>
       </c>
       <c r="AP72">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ72">
         <v>2.36</v>
@@ -19579,7 +19582,7 @@
         <v>0.5</v>
       </c>
       <c r="AP89">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ89">
         <v>1.18</v>
@@ -23493,7 +23496,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ108">
         <v>1.27</v>
@@ -26995,7 +26998,7 @@
         <v>0.17</v>
       </c>
       <c r="AP125">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ125">
         <v>0.55</v>
@@ -30085,7 +30088,7 @@
         <v>1.13</v>
       </c>
       <c r="AP140">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ140">
         <v>0.75</v>
@@ -36265,7 +36268,7 @@
         <v>1.5</v>
       </c>
       <c r="AP170">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ170">
         <v>1.55</v>
@@ -38737,7 +38740,7 @@
         <v>2.3</v>
       </c>
       <c r="AP182">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ182">
         <v>2.08</v>
@@ -43305,10 +43308,10 @@
         <v>4</v>
       </c>
       <c r="BB204">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC204">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD204">
         <v>1.27</v>
@@ -43966,6 +43969,212 @@
       </c>
       <c r="BP207">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7574768</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45712.71875</v>
+      </c>
+      <c r="F208">
+        <v>23</v>
+      </c>
+      <c r="G208" t="s">
+        <v>73</v>
+      </c>
+      <c r="H208" t="s">
+        <v>85</v>
+      </c>
+      <c r="I208">
+        <v>0</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <v>1</v>
+      </c>
+      <c r="M208">
+        <v>1</v>
+      </c>
+      <c r="N208">
+        <v>2</v>
+      </c>
+      <c r="O208" t="s">
+        <v>166</v>
+      </c>
+      <c r="P208" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q208">
+        <v>2.3</v>
+      </c>
+      <c r="R208">
+        <v>2.1</v>
+      </c>
+      <c r="S208">
+        <v>5.5</v>
+      </c>
+      <c r="T208">
+        <v>1.44</v>
+      </c>
+      <c r="U208">
+        <v>2.63</v>
+      </c>
+      <c r="V208">
+        <v>3.25</v>
+      </c>
+      <c r="W208">
+        <v>1.33</v>
+      </c>
+      <c r="X208">
+        <v>9</v>
+      </c>
+      <c r="Y208">
+        <v>1.07</v>
+      </c>
+      <c r="Z208">
+        <v>1.57</v>
+      </c>
+      <c r="AA208">
+        <v>3.8</v>
+      </c>
+      <c r="AB208">
+        <v>5.6</v>
+      </c>
+      <c r="AC208">
+        <v>1.06</v>
+      </c>
+      <c r="AD208">
+        <v>10</v>
+      </c>
+      <c r="AE208">
+        <v>1.36</v>
+      </c>
+      <c r="AF208">
+        <v>3.1</v>
+      </c>
+      <c r="AG208">
+        <v>2</v>
+      </c>
+      <c r="AH208">
+        <v>1.73</v>
+      </c>
+      <c r="AI208">
+        <v>2</v>
+      </c>
+      <c r="AJ208">
+        <v>1.75</v>
+      </c>
+      <c r="AK208">
+        <v>1.16</v>
+      </c>
+      <c r="AL208">
+        <v>1.25</v>
+      </c>
+      <c r="AM208">
+        <v>2.2</v>
+      </c>
+      <c r="AN208">
+        <v>2.64</v>
+      </c>
+      <c r="AO208">
+        <v>1</v>
+      </c>
+      <c r="AP208">
+        <v>2.5</v>
+      </c>
+      <c r="AQ208">
+        <v>1</v>
+      </c>
+      <c r="AR208">
+        <v>2.01</v>
+      </c>
+      <c r="AS208">
+        <v>1.46</v>
+      </c>
+      <c r="AT208">
+        <v>3.47</v>
+      </c>
+      <c r="AU208">
+        <v>4</v>
+      </c>
+      <c r="AV208">
+        <v>6</v>
+      </c>
+      <c r="AW208">
+        <v>12</v>
+      </c>
+      <c r="AX208">
+        <v>7</v>
+      </c>
+      <c r="AY208">
+        <v>22</v>
+      </c>
+      <c r="AZ208">
+        <v>16</v>
+      </c>
+      <c r="BA208">
+        <v>6</v>
+      </c>
+      <c r="BB208">
+        <v>7</v>
+      </c>
+      <c r="BC208">
+        <v>13</v>
+      </c>
+      <c r="BD208">
+        <v>1.36</v>
+      </c>
+      <c r="BE208">
+        <v>8</v>
+      </c>
+      <c r="BF208">
+        <v>3.4</v>
+      </c>
+      <c r="BG208">
+        <v>1.12</v>
+      </c>
+      <c r="BH208">
+        <v>4.8</v>
+      </c>
+      <c r="BI208">
+        <v>1.23</v>
+      </c>
+      <c r="BJ208">
+        <v>3.55</v>
+      </c>
+      <c r="BK208">
+        <v>1.4</v>
+      </c>
+      <c r="BL208">
+        <v>2.65</v>
+      </c>
+      <c r="BM208">
+        <v>1.8</v>
+      </c>
+      <c r="BN208">
+        <v>1.91</v>
+      </c>
+      <c r="BO208">
+        <v>1.98</v>
+      </c>
+      <c r="BP208">
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -43152,7 +43152,7 @@
         <v>203</v>
       </c>
       <c r="B204">
-        <v>7574764</v>
+        <v>7574767</v>
       </c>
       <c r="C204" t="s">
         <v>68</v>
@@ -43167,190 +43167,190 @@
         <v>23</v>
       </c>
       <c r="G204" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H204" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I204">
         <v>0</v>
       </c>
       <c r="J204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L204">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M204">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N204">
+        <v>0</v>
+      </c>
+      <c r="O204" t="s">
+        <v>90</v>
+      </c>
+      <c r="P204" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q204">
+        <v>4.33</v>
+      </c>
+      <c r="R204">
+        <v>1.85</v>
+      </c>
+      <c r="S204">
+        <v>2.85</v>
+      </c>
+      <c r="T204">
+        <v>1.6</v>
+      </c>
+      <c r="U204">
+        <v>2.2</v>
+      </c>
+      <c r="V204">
+        <v>3.8</v>
+      </c>
+      <c r="W204">
+        <v>1.22</v>
+      </c>
+      <c r="X204">
+        <v>11.5</v>
+      </c>
+      <c r="Y204">
+        <v>1.04</v>
+      </c>
+      <c r="Z204">
+        <v>3.4</v>
+      </c>
+      <c r="AA204">
+        <v>3.2</v>
+      </c>
+      <c r="AB204">
+        <v>2.1</v>
+      </c>
+      <c r="AC204">
+        <v>1.1</v>
+      </c>
+      <c r="AD204">
+        <v>6.5</v>
+      </c>
+      <c r="AE204">
+        <v>1.53</v>
+      </c>
+      <c r="AF204">
+        <v>2.37</v>
+      </c>
+      <c r="AG204">
+        <v>2.86</v>
+      </c>
+      <c r="AH204">
+        <v>1.39</v>
+      </c>
+      <c r="AI204">
+        <v>2.25</v>
+      </c>
+      <c r="AJ204">
+        <v>1.57</v>
+      </c>
+      <c r="AK204">
+        <v>1.67</v>
+      </c>
+      <c r="AL204">
+        <v>1.3</v>
+      </c>
+      <c r="AM204">
+        <v>1.28</v>
+      </c>
+      <c r="AN204">
+        <v>1.27</v>
+      </c>
+      <c r="AO204">
+        <v>1.6</v>
+      </c>
+      <c r="AP204">
+        <v>1.25</v>
+      </c>
+      <c r="AQ204">
+        <v>1.55</v>
+      </c>
+      <c r="AR204">
+        <v>1.15</v>
+      </c>
+      <c r="AS204">
+        <v>0.99</v>
+      </c>
+      <c r="AT204">
+        <v>2.14</v>
+      </c>
+      <c r="AU204">
+        <v>3</v>
+      </c>
+      <c r="AV204">
+        <v>2</v>
+      </c>
+      <c r="AW204">
+        <v>9</v>
+      </c>
+      <c r="AX204">
         <v>4</v>
       </c>
-      <c r="O204" t="s">
-        <v>219</v>
-      </c>
-      <c r="P204" t="s">
-        <v>314</v>
-      </c>
-      <c r="Q204">
-        <v>2.45</v>
-      </c>
-      <c r="R204">
-        <v>2.05</v>
-      </c>
-      <c r="S204">
-        <v>4.5</v>
-      </c>
-      <c r="T204">
+      <c r="AY204">
+        <v>15</v>
+      </c>
+      <c r="AZ204">
+        <v>7</v>
+      </c>
+      <c r="BA204">
+        <v>5</v>
+      </c>
+      <c r="BB204">
+        <v>2</v>
+      </c>
+      <c r="BC204">
+        <v>7</v>
+      </c>
+      <c r="BD204">
+        <v>2.12</v>
+      </c>
+      <c r="BE204">
+        <v>6.5</v>
+      </c>
+      <c r="BF204">
+        <v>1.86</v>
+      </c>
+      <c r="BG204">
+        <v>1.34</v>
+      </c>
+      <c r="BH204">
+        <v>2.85</v>
+      </c>
+      <c r="BI204">
+        <v>1.58</v>
+      </c>
+      <c r="BJ204">
+        <v>2.16</v>
+      </c>
+      <c r="BK204">
+        <v>1.95</v>
+      </c>
+      <c r="BL204">
+        <v>1.72</v>
+      </c>
+      <c r="BM204">
+        <v>2.48</v>
+      </c>
+      <c r="BN204">
         <v>1.45</v>
       </c>
-      <c r="U204">
-        <v>2.55</v>
-      </c>
-      <c r="V204">
-        <v>3</v>
-      </c>
-      <c r="W204">
-        <v>1.33</v>
-      </c>
-      <c r="X204">
-        <v>7.5</v>
-      </c>
-      <c r="Y204">
-        <v>1.06</v>
-      </c>
-      <c r="Z204">
-        <v>1.85</v>
-      </c>
-      <c r="AA204">
-        <v>3.3</v>
-      </c>
-      <c r="AB204">
-        <v>4.2</v>
-      </c>
-      <c r="AC204">
-        <v>1.07</v>
-      </c>
-      <c r="AD204">
-        <v>8</v>
-      </c>
-      <c r="AE204">
-        <v>1.4</v>
-      </c>
-      <c r="AF204">
-        <v>2.9</v>
-      </c>
-      <c r="AG204">
-        <v>2.15</v>
-      </c>
-      <c r="AH204">
-        <v>1.65</v>
-      </c>
-      <c r="AI204">
-        <v>1.95</v>
-      </c>
-      <c r="AJ204">
-        <v>1.77</v>
-      </c>
-      <c r="AK204">
-        <v>1.22</v>
-      </c>
-      <c r="AL204">
-        <v>1.25</v>
-      </c>
-      <c r="AM204">
-        <v>1.85</v>
-      </c>
-      <c r="AN204">
-        <v>1.2</v>
-      </c>
-      <c r="AO204">
-        <v>0.73</v>
-      </c>
-      <c r="AP204">
-        <v>1.18</v>
-      </c>
-      <c r="AQ204">
-        <v>0.75</v>
-      </c>
-      <c r="AR204">
-        <v>1.23</v>
-      </c>
-      <c r="AS204">
-        <v>0.98</v>
-      </c>
-      <c r="AT204">
-        <v>2.21</v>
-      </c>
-      <c r="AU204">
-        <v>4</v>
-      </c>
-      <c r="AV204">
-        <v>9</v>
-      </c>
-      <c r="AW204">
-        <v>5</v>
-      </c>
-      <c r="AX204">
-        <v>10</v>
-      </c>
-      <c r="AY204">
-        <v>13</v>
-      </c>
-      <c r="AZ204">
-        <v>20</v>
-      </c>
-      <c r="BA204">
-        <v>4</v>
-      </c>
-      <c r="BB204">
-        <v>9</v>
-      </c>
-      <c r="BC204">
-        <v>13</v>
-      </c>
-      <c r="BD204">
-        <v>1.27</v>
-      </c>
-      <c r="BE204">
-        <v>8</v>
-      </c>
-      <c r="BF204">
-        <v>4</v>
-      </c>
-      <c r="BG204">
-        <v>1.18</v>
-      </c>
-      <c r="BH204">
-        <v>4</v>
-      </c>
-      <c r="BI204">
-        <v>1.34</v>
-      </c>
-      <c r="BJ204">
-        <v>2.9</v>
-      </c>
-      <c r="BK204">
-        <v>1.56</v>
-      </c>
-      <c r="BL204">
-        <v>2.23</v>
-      </c>
-      <c r="BM204">
-        <v>1.85</v>
-      </c>
-      <c r="BN204">
-        <v>1.82</v>
-      </c>
       <c r="BO204">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="BP204">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="205" spans="1:68">
@@ -43358,7 +43358,7 @@
         <v>204</v>
       </c>
       <c r="B205">
-        <v>7574767</v>
+        <v>7574764</v>
       </c>
       <c r="C205" t="s">
         <v>68</v>
@@ -43373,190 +43373,190 @@
         <v>23</v>
       </c>
       <c r="G205" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H205" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I205">
         <v>0</v>
       </c>
       <c r="J205">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K205">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L205">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M205">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N205">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O205" t="s">
-        <v>90</v>
+        <v>219</v>
       </c>
       <c r="P205" t="s">
-        <v>90</v>
+        <v>314</v>
       </c>
       <c r="Q205">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
       <c r="R205">
+        <v>2.05</v>
+      </c>
+      <c r="S205">
+        <v>4.5</v>
+      </c>
+      <c r="T205">
+        <v>1.45</v>
+      </c>
+      <c r="U205">
+        <v>2.55</v>
+      </c>
+      <c r="V205">
+        <v>3</v>
+      </c>
+      <c r="W205">
+        <v>1.33</v>
+      </c>
+      <c r="X205">
+        <v>7.5</v>
+      </c>
+      <c r="Y205">
+        <v>1.06</v>
+      </c>
+      <c r="Z205">
         <v>1.85</v>
       </c>
-      <c r="S205">
-        <v>2.85</v>
-      </c>
-      <c r="T205">
-        <v>1.6</v>
-      </c>
-      <c r="U205">
-        <v>2.2</v>
-      </c>
-      <c r="V205">
-        <v>3.8</v>
-      </c>
-      <c r="W205">
+      <c r="AA205">
+        <v>3.3</v>
+      </c>
+      <c r="AB205">
+        <v>4.2</v>
+      </c>
+      <c r="AC205">
+        <v>1.07</v>
+      </c>
+      <c r="AD205">
+        <v>8</v>
+      </c>
+      <c r="AE205">
+        <v>1.4</v>
+      </c>
+      <c r="AF205">
+        <v>2.9</v>
+      </c>
+      <c r="AG205">
+        <v>2.15</v>
+      </c>
+      <c r="AH205">
+        <v>1.65</v>
+      </c>
+      <c r="AI205">
+        <v>1.95</v>
+      </c>
+      <c r="AJ205">
+        <v>1.77</v>
+      </c>
+      <c r="AK205">
         <v>1.22</v>
       </c>
-      <c r="X205">
-        <v>11.5</v>
-      </c>
-      <c r="Y205">
-        <v>1.04</v>
-      </c>
-      <c r="Z205">
-        <v>3.4</v>
-      </c>
-      <c r="AA205">
-        <v>3.2</v>
-      </c>
-      <c r="AB205">
-        <v>2.1</v>
-      </c>
-      <c r="AC205">
-        <v>1.1</v>
-      </c>
-      <c r="AD205">
-        <v>6.5</v>
-      </c>
-      <c r="AE205">
-        <v>1.53</v>
-      </c>
-      <c r="AF205">
-        <v>2.37</v>
-      </c>
-      <c r="AG205">
-        <v>2.86</v>
-      </c>
-      <c r="AH205">
-        <v>1.39</v>
-      </c>
-      <c r="AI205">
+      <c r="AL205">
+        <v>1.25</v>
+      </c>
+      <c r="AM205">
+        <v>1.85</v>
+      </c>
+      <c r="AN205">
+        <v>1.2</v>
+      </c>
+      <c r="AO205">
+        <v>0.73</v>
+      </c>
+      <c r="AP205">
+        <v>1.18</v>
+      </c>
+      <c r="AQ205">
+        <v>0.75</v>
+      </c>
+      <c r="AR205">
+        <v>1.23</v>
+      </c>
+      <c r="AS205">
+        <v>0.98</v>
+      </c>
+      <c r="AT205">
+        <v>2.21</v>
+      </c>
+      <c r="AU205">
+        <v>4</v>
+      </c>
+      <c r="AV205">
+        <v>9</v>
+      </c>
+      <c r="AW205">
+        <v>5</v>
+      </c>
+      <c r="AX205">
+        <v>10</v>
+      </c>
+      <c r="AY205">
+        <v>13</v>
+      </c>
+      <c r="AZ205">
+        <v>20</v>
+      </c>
+      <c r="BA205">
+        <v>4</v>
+      </c>
+      <c r="BB205">
+        <v>9</v>
+      </c>
+      <c r="BC205">
+        <v>13</v>
+      </c>
+      <c r="BD205">
+        <v>1.27</v>
+      </c>
+      <c r="BE205">
+        <v>8</v>
+      </c>
+      <c r="BF205">
+        <v>4</v>
+      </c>
+      <c r="BG205">
+        <v>1.18</v>
+      </c>
+      <c r="BH205">
+        <v>4</v>
+      </c>
+      <c r="BI205">
+        <v>1.34</v>
+      </c>
+      <c r="BJ205">
+        <v>2.9</v>
+      </c>
+      <c r="BK205">
+        <v>1.56</v>
+      </c>
+      <c r="BL205">
+        <v>2.23</v>
+      </c>
+      <c r="BM205">
+        <v>1.85</v>
+      </c>
+      <c r="BN205">
+        <v>1.82</v>
+      </c>
+      <c r="BO205">
         <v>2.25</v>
       </c>
-      <c r="AJ205">
-        <v>1.57</v>
-      </c>
-      <c r="AK205">
-        <v>1.67</v>
-      </c>
-      <c r="AL205">
-        <v>1.3</v>
-      </c>
-      <c r="AM205">
-        <v>1.28</v>
-      </c>
-      <c r="AN205">
-        <v>1.27</v>
-      </c>
-      <c r="AO205">
-        <v>1.6</v>
-      </c>
-      <c r="AP205">
-        <v>1.25</v>
-      </c>
-      <c r="AQ205">
-        <v>1.55</v>
-      </c>
-      <c r="AR205">
-        <v>1.15</v>
-      </c>
-      <c r="AS205">
-        <v>0.99</v>
-      </c>
-      <c r="AT205">
-        <v>2.14</v>
-      </c>
-      <c r="AU205">
-        <v>3</v>
-      </c>
-      <c r="AV205">
-        <v>2</v>
-      </c>
-      <c r="AW205">
-        <v>9</v>
-      </c>
-      <c r="AX205">
-        <v>4</v>
-      </c>
-      <c r="AY205">
-        <v>15</v>
-      </c>
-      <c r="AZ205">
-        <v>7</v>
-      </c>
-      <c r="BA205">
-        <v>5</v>
-      </c>
-      <c r="BB205">
-        <v>2</v>
-      </c>
-      <c r="BC205">
-        <v>7</v>
-      </c>
-      <c r="BD205">
-        <v>2.12</v>
-      </c>
-      <c r="BE205">
-        <v>6.5</v>
-      </c>
-      <c r="BF205">
-        <v>1.86</v>
-      </c>
-      <c r="BG205">
-        <v>1.34</v>
-      </c>
-      <c r="BH205">
-        <v>2.85</v>
-      </c>
-      <c r="BI205">
-        <v>1.58</v>
-      </c>
-      <c r="BJ205">
-        <v>2.16</v>
-      </c>
-      <c r="BK205">
-        <v>1.95</v>
-      </c>
-      <c r="BL205">
-        <v>1.72</v>
-      </c>
-      <c r="BM205">
-        <v>2.48</v>
-      </c>
-      <c r="BN205">
-        <v>1.45</v>
-      </c>
-      <c r="BO205">
-        <v>3.2</v>
-      </c>
       <c r="BP205">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="206" spans="1:68">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="319">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -682,6 +682,9 @@
     <t>['47', '58']</t>
   </si>
   <si>
+    <t>['14', '90+4']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -965,6 +968,9 @@
   </si>
   <si>
     <t>['86']</t>
+  </si>
+  <si>
+    <t>['13', '77']</t>
   </si>
 </sst>
 </file>
@@ -1326,7 +1332,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP208"/>
+  <dimension ref="A1:BP211"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1788,7 +1794,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2406,7 +2412,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2818,7 +2824,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -3308,7 +3314,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3436,7 +3442,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3517,7 +3523,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ11">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3642,7 +3648,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4054,7 +4060,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4132,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ14">
         <v>2.08</v>
@@ -4341,7 +4347,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ15">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4466,7 +4472,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4750,7 +4756,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ17">
         <v>1.18</v>
@@ -4878,7 +4884,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -5084,7 +5090,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5165,7 +5171,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ19">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5290,7 +5296,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5496,7 +5502,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -6398,7 +6404,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ25">
         <v>0.5</v>
@@ -7144,7 +7150,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7350,7 +7356,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7556,7 +7562,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -7637,7 +7643,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ31">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR31">
         <v>1</v>
@@ -8049,7 +8055,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ33">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR33">
         <v>2.25</v>
@@ -8252,7 +8258,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ34">
         <v>0.75</v>
@@ -8586,7 +8592,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q36">
         <v>2.55</v>
@@ -8664,10 +8670,10 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ36">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR36">
         <v>1.59</v>
@@ -8998,7 +9004,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9076,7 +9082,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ38">
         <v>2.08</v>
@@ -9204,7 +9210,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9616,7 +9622,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9822,7 +9828,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -10028,7 +10034,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10440,7 +10446,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10646,7 +10652,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10852,7 +10858,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10930,7 +10936,7 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ47">
         <v>2.36</v>
@@ -11058,7 +11064,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11470,7 +11476,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11548,10 +11554,10 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ50">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR50">
         <v>1.4</v>
@@ -11757,7 +11763,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ51">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR51">
         <v>1.08</v>
@@ -11882,7 +11888,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -11963,7 +11969,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ52">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR52">
         <v>1.51</v>
@@ -12500,7 +12506,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12706,7 +12712,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -13118,7 +13124,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13324,7 +13330,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -14641,7 +14647,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ65">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -15256,7 +15262,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ68">
         <v>0.55</v>
@@ -15465,7 +15471,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ69">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR69">
         <v>2.1</v>
@@ -15796,7 +15802,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -15874,7 +15880,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ71">
         <v>0.75</v>
@@ -16002,7 +16008,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16414,7 +16420,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16620,7 +16626,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16826,7 +16832,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17032,7 +17038,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17650,7 +17656,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17856,7 +17862,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -17937,7 +17943,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ81">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR81">
         <v>1.3</v>
@@ -18062,7 +18068,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18268,7 +18274,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18349,7 +18355,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ83">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR83">
         <v>1.47</v>
@@ -18474,7 +18480,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18680,7 +18686,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18886,7 +18892,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -18967,7 +18973,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ86">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR86">
         <v>1.12</v>
@@ -19170,7 +19176,7 @@
         <v>1.2</v>
       </c>
       <c r="AP87">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ87">
         <v>0.58</v>
@@ -19298,7 +19304,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19376,7 +19382,7 @@
         <v>1.75</v>
       </c>
       <c r="AP88">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ88">
         <v>2.36</v>
@@ -19788,7 +19794,7 @@
         <v>1.5</v>
       </c>
       <c r="AP90">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ90">
         <v>1.55</v>
@@ -19916,7 +19922,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -20122,7 +20128,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20740,7 +20746,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -21358,7 +21364,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21645,7 +21651,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ99">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR99">
         <v>2.36</v>
@@ -21976,7 +21982,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22260,7 +22266,7 @@
         <v>1.33</v>
       </c>
       <c r="AP102">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ102">
         <v>0.75</v>
@@ -22388,7 +22394,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22675,7 +22681,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ104">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR104">
         <v>1</v>
@@ -22800,7 +22806,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -22878,7 +22884,7 @@
         <v>1.75</v>
       </c>
       <c r="AP105">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ105">
         <v>1.82</v>
@@ -23006,7 +23012,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q106">
         <v>5.5</v>
@@ -23290,7 +23296,7 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ107">
         <v>0.5</v>
@@ -23499,7 +23505,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ108">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR108">
         <v>2.03</v>
@@ -23830,7 +23836,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -24735,7 +24741,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ114">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR114">
         <v>1.09</v>
@@ -25762,7 +25768,7 @@
         <v>0.86</v>
       </c>
       <c r="AP119">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ119">
         <v>0.58</v>
@@ -25890,7 +25896,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26174,7 +26180,7 @@
         <v>1.5</v>
       </c>
       <c r="AP121">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ121">
         <v>1.55</v>
@@ -26302,7 +26308,7 @@
         <v>167</v>
       </c>
       <c r="P122" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q122">
         <v>11</v>
@@ -26508,7 +26514,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26589,7 +26595,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ123">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR123">
         <v>1.04</v>
@@ -26714,7 +26720,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -26795,7 +26801,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ124">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR124">
         <v>1.55</v>
@@ -27126,7 +27132,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27332,7 +27338,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27410,7 +27416,7 @@
         <v>1.83</v>
       </c>
       <c r="AP127">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ127">
         <v>1.82</v>
@@ -27538,7 +27544,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27744,7 +27750,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -28156,7 +28162,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28237,7 +28243,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ131">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR131">
         <v>1.14</v>
@@ -28362,7 +28368,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28774,7 +28780,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -28852,7 +28858,7 @@
         <v>0.29</v>
       </c>
       <c r="AP134">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ134">
         <v>0.5</v>
@@ -29470,7 +29476,7 @@
         <v>0.63</v>
       </c>
       <c r="AP137">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ137">
         <v>0.5</v>
@@ -29598,7 +29604,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29804,7 +29810,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -30216,7 +30222,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30422,7 +30428,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30628,7 +30634,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -30709,7 +30715,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ143">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR143">
         <v>1.64</v>
@@ -31040,7 +31046,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31246,7 +31252,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31324,7 +31330,7 @@
         <v>2.38</v>
       </c>
       <c r="AP146">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ146">
         <v>2.08</v>
@@ -31452,7 +31458,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q147">
         <v>2.55</v>
@@ -31658,7 +31664,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31864,7 +31870,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32276,7 +32282,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32357,7 +32363,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ151">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR151">
         <v>1.25</v>
@@ -32482,7 +32488,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32688,7 +32694,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -32972,10 +32978,10 @@
         <v>1.86</v>
       </c>
       <c r="AP154">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ154">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR154">
         <v>1.23</v>
@@ -33181,7 +33187,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ155">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR155">
         <v>2.01</v>
@@ -33306,7 +33312,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33512,7 +33518,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33718,7 +33724,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33796,7 +33802,7 @@
         <v>0.78</v>
       </c>
       <c r="AP158">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ158">
         <v>1</v>
@@ -33924,7 +33930,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34002,7 +34008,7 @@
         <v>0.63</v>
       </c>
       <c r="AP159">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ159">
         <v>0.55</v>
@@ -34336,7 +34342,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34542,7 +34548,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34623,7 +34629,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ162">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR162">
         <v>1.23</v>
@@ -34748,7 +34754,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -34829,7 +34835,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ163">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR163">
         <v>1.32</v>
@@ -35032,7 +35038,7 @@
         <v>0.78</v>
       </c>
       <c r="AP164">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ164">
         <v>0.58</v>
@@ -35160,7 +35166,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -36190,7 +36196,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36808,7 +36814,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -36889,7 +36895,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ173">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR173">
         <v>1.33</v>
@@ -37095,7 +37101,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ174">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR174">
         <v>1.43</v>
@@ -37220,7 +37226,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37298,7 +37304,7 @@
         <v>0.8</v>
       </c>
       <c r="AP175">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ175">
         <v>1</v>
@@ -37426,7 +37432,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -37710,7 +37716,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP177">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ177">
         <v>0.55</v>
@@ -38044,7 +38050,7 @@
         <v>205</v>
       </c>
       <c r="P179" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q179">
         <v>8.5</v>
@@ -38250,7 +38256,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q180">
         <v>4.75</v>
@@ -38456,7 +38462,7 @@
         <v>207</v>
       </c>
       <c r="P181" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q181">
         <v>6.5</v>
@@ -38537,7 +38543,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ181">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR181">
         <v>1.3</v>
@@ -38662,7 +38668,7 @@
         <v>167</v>
       </c>
       <c r="P182" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -39074,7 +39080,7 @@
         <v>208</v>
       </c>
       <c r="P184" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q184">
         <v>1.57</v>
@@ -39486,7 +39492,7 @@
         <v>209</v>
       </c>
       <c r="P186" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q186">
         <v>2.2</v>
@@ -40310,7 +40316,7 @@
         <v>184</v>
       </c>
       <c r="P190" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q190">
         <v>2.63</v>
@@ -40388,7 +40394,7 @@
         <v>0.7</v>
       </c>
       <c r="AP190">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ190">
         <v>0.67</v>
@@ -40722,7 +40728,7 @@
         <v>212</v>
       </c>
       <c r="P192" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -40803,7 +40809,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ192">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR192">
         <v>1.22</v>
@@ -40928,7 +40934,7 @@
         <v>213</v>
       </c>
       <c r="P193" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q193">
         <v>2.8</v>
@@ -41006,7 +41012,7 @@
         <v>1.2</v>
       </c>
       <c r="AP193">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ193">
         <v>1.18</v>
@@ -41340,7 +41346,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q195">
         <v>1.67</v>
@@ -41752,7 +41758,7 @@
         <v>90</v>
       </c>
       <c r="P197" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q197">
         <v>7.5</v>
@@ -41833,7 +41839,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ197">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR197">
         <v>1.32</v>
@@ -42036,7 +42042,7 @@
         <v>2.5</v>
       </c>
       <c r="AP198">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ198">
         <v>2.36</v>
@@ -42164,7 +42170,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42245,7 +42251,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ199">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR199">
         <v>1.25</v>
@@ -42988,7 +42994,7 @@
         <v>218</v>
       </c>
       <c r="P203" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q203">
         <v>2.55</v>
@@ -43400,7 +43406,7 @@
         <v>219</v>
       </c>
       <c r="P205" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q205">
         <v>2.45</v>
@@ -43478,7 +43484,7 @@
         <v>0.73</v>
       </c>
       <c r="AP205">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ205">
         <v>0.75</v>
@@ -43606,7 +43612,7 @@
         <v>220</v>
       </c>
       <c r="P206" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q206">
         <v>7</v>
@@ -44018,7 +44024,7 @@
         <v>166</v>
       </c>
       <c r="P208" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44175,6 +44181,624 @@
       </c>
       <c r="BP208">
         <v>1.7</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7574770</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45717.52083333334</v>
+      </c>
+      <c r="F209">
+        <v>24</v>
+      </c>
+      <c r="G209" t="s">
+        <v>82</v>
+      </c>
+      <c r="H209" t="s">
+        <v>75</v>
+      </c>
+      <c r="I209">
+        <v>1</v>
+      </c>
+      <c r="J209">
+        <v>0</v>
+      </c>
+      <c r="K209">
+        <v>1</v>
+      </c>
+      <c r="L209">
+        <v>2</v>
+      </c>
+      <c r="M209">
+        <v>1</v>
+      </c>
+      <c r="N209">
+        <v>3</v>
+      </c>
+      <c r="O209" t="s">
+        <v>222</v>
+      </c>
+      <c r="P209" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q209">
+        <v>3</v>
+      </c>
+      <c r="R209">
+        <v>1.98</v>
+      </c>
+      <c r="S209">
+        <v>3.5</v>
+      </c>
+      <c r="T209">
+        <v>1.46</v>
+      </c>
+      <c r="U209">
+        <v>2.5</v>
+      </c>
+      <c r="V209">
+        <v>3.1</v>
+      </c>
+      <c r="W209">
+        <v>1.32</v>
+      </c>
+      <c r="X209">
+        <v>8.5</v>
+      </c>
+      <c r="Y209">
+        <v>1.06</v>
+      </c>
+      <c r="Z209">
+        <v>2.45</v>
+      </c>
+      <c r="AA209">
+        <v>3</v>
+      </c>
+      <c r="AB209">
+        <v>3</v>
+      </c>
+      <c r="AC209">
+        <v>1.08</v>
+      </c>
+      <c r="AD209">
+        <v>7.5</v>
+      </c>
+      <c r="AE209">
+        <v>1.42</v>
+      </c>
+      <c r="AF209">
+        <v>2.85</v>
+      </c>
+      <c r="AG209">
+        <v>2.2</v>
+      </c>
+      <c r="AH209">
+        <v>1.61</v>
+      </c>
+      <c r="AI209">
+        <v>1.9</v>
+      </c>
+      <c r="AJ209">
+        <v>1.78</v>
+      </c>
+      <c r="AK209">
+        <v>1.38</v>
+      </c>
+      <c r="AL209">
+        <v>1.34</v>
+      </c>
+      <c r="AM209">
+        <v>1.53</v>
+      </c>
+      <c r="AN209">
+        <v>1.55</v>
+      </c>
+      <c r="AO209">
+        <v>1.45</v>
+      </c>
+      <c r="AP209">
+        <v>1.67</v>
+      </c>
+      <c r="AQ209">
+        <v>1.33</v>
+      </c>
+      <c r="AR209">
+        <v>1.41</v>
+      </c>
+      <c r="AS209">
+        <v>1.39</v>
+      </c>
+      <c r="AT209">
+        <v>2.8</v>
+      </c>
+      <c r="AU209">
+        <v>6</v>
+      </c>
+      <c r="AV209">
+        <v>3</v>
+      </c>
+      <c r="AW209">
+        <v>11</v>
+      </c>
+      <c r="AX209">
+        <v>13</v>
+      </c>
+      <c r="AY209">
+        <v>19</v>
+      </c>
+      <c r="AZ209">
+        <v>20</v>
+      </c>
+      <c r="BA209">
+        <v>1</v>
+      </c>
+      <c r="BB209">
+        <v>6</v>
+      </c>
+      <c r="BC209">
+        <v>7</v>
+      </c>
+      <c r="BD209">
+        <v>1.92</v>
+      </c>
+      <c r="BE209">
+        <v>6.75</v>
+      </c>
+      <c r="BF209">
+        <v>2.07</v>
+      </c>
+      <c r="BG209">
+        <v>1.3</v>
+      </c>
+      <c r="BH209">
+        <v>3.05</v>
+      </c>
+      <c r="BI209">
+        <v>1.53</v>
+      </c>
+      <c r="BJ209">
+        <v>2.28</v>
+      </c>
+      <c r="BK209">
+        <v>1.85</v>
+      </c>
+      <c r="BL209">
+        <v>1.81</v>
+      </c>
+      <c r="BM209">
+        <v>2.33</v>
+      </c>
+      <c r="BN209">
+        <v>1.5</v>
+      </c>
+      <c r="BO209">
+        <v>3.05</v>
+      </c>
+      <c r="BP209">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7574772</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45717.625</v>
+      </c>
+      <c r="F210">
+        <v>24</v>
+      </c>
+      <c r="G210" t="s">
+        <v>78</v>
+      </c>
+      <c r="H210" t="s">
+        <v>73</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="J210">
+        <v>1</v>
+      </c>
+      <c r="K210">
+        <v>1</v>
+      </c>
+      <c r="L210">
+        <v>0</v>
+      </c>
+      <c r="M210">
+        <v>2</v>
+      </c>
+      <c r="N210">
+        <v>2</v>
+      </c>
+      <c r="O210" t="s">
+        <v>90</v>
+      </c>
+      <c r="P210" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q210">
+        <v>5.5</v>
+      </c>
+      <c r="R210">
+        <v>2.2</v>
+      </c>
+      <c r="S210">
+        <v>2.3</v>
+      </c>
+      <c r="T210">
+        <v>1.4</v>
+      </c>
+      <c r="U210">
+        <v>2.75</v>
+      </c>
+      <c r="V210">
+        <v>3</v>
+      </c>
+      <c r="W210">
+        <v>1.36</v>
+      </c>
+      <c r="X210">
+        <v>8</v>
+      </c>
+      <c r="Y210">
+        <v>1.08</v>
+      </c>
+      <c r="Z210">
+        <v>4.75</v>
+      </c>
+      <c r="AA210">
+        <v>3.6</v>
+      </c>
+      <c r="AB210">
+        <v>1.67</v>
+      </c>
+      <c r="AC210">
+        <v>1.04</v>
+      </c>
+      <c r="AD210">
+        <v>13</v>
+      </c>
+      <c r="AE210">
+        <v>1.25</v>
+      </c>
+      <c r="AF210">
+        <v>3.75</v>
+      </c>
+      <c r="AG210">
+        <v>1.91</v>
+      </c>
+      <c r="AH210">
+        <v>1.8</v>
+      </c>
+      <c r="AI210">
+        <v>1.95</v>
+      </c>
+      <c r="AJ210">
+        <v>1.8</v>
+      </c>
+      <c r="AK210">
+        <v>2.05</v>
+      </c>
+      <c r="AL210">
+        <v>1.28</v>
+      </c>
+      <c r="AM210">
+        <v>1.17</v>
+      </c>
+      <c r="AN210">
+        <v>1.18</v>
+      </c>
+      <c r="AO210">
+        <v>1.55</v>
+      </c>
+      <c r="AP210">
+        <v>1.08</v>
+      </c>
+      <c r="AQ210">
+        <v>1.67</v>
+      </c>
+      <c r="AR210">
+        <v>1.22</v>
+      </c>
+      <c r="AS210">
+        <v>1.47</v>
+      </c>
+      <c r="AT210">
+        <v>2.69</v>
+      </c>
+      <c r="AU210">
+        <v>6</v>
+      </c>
+      <c r="AV210">
+        <v>3</v>
+      </c>
+      <c r="AW210">
+        <v>3</v>
+      </c>
+      <c r="AX210">
+        <v>7</v>
+      </c>
+      <c r="AY210">
+        <v>10</v>
+      </c>
+      <c r="AZ210">
+        <v>13</v>
+      </c>
+      <c r="BA210">
+        <v>4</v>
+      </c>
+      <c r="BB210">
+        <v>2</v>
+      </c>
+      <c r="BC210">
+        <v>6</v>
+      </c>
+      <c r="BD210">
+        <v>2.7</v>
+      </c>
+      <c r="BE210">
+        <v>6.75</v>
+      </c>
+      <c r="BF210">
+        <v>1.54</v>
+      </c>
+      <c r="BG210">
+        <v>1.29</v>
+      </c>
+      <c r="BH210">
+        <v>3.15</v>
+      </c>
+      <c r="BI210">
+        <v>1.5</v>
+      </c>
+      <c r="BJ210">
+        <v>2.33</v>
+      </c>
+      <c r="BK210">
+        <v>1.82</v>
+      </c>
+      <c r="BL210">
+        <v>1.84</v>
+      </c>
+      <c r="BM210">
+        <v>2.28</v>
+      </c>
+      <c r="BN210">
+        <v>1.52</v>
+      </c>
+      <c r="BO210">
+        <v>2.95</v>
+      </c>
+      <c r="BP210">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7574778</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45717.72916666666</v>
+      </c>
+      <c r="F211">
+        <v>24</v>
+      </c>
+      <c r="G211" t="s">
+        <v>85</v>
+      </c>
+      <c r="H211" t="s">
+        <v>72</v>
+      </c>
+      <c r="I211">
+        <v>0</v>
+      </c>
+      <c r="J211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>0</v>
+      </c>
+      <c r="L211">
+        <v>1</v>
+      </c>
+      <c r="M211">
+        <v>0</v>
+      </c>
+      <c r="N211">
+        <v>1</v>
+      </c>
+      <c r="O211" t="s">
+        <v>128</v>
+      </c>
+      <c r="P211" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q211">
+        <v>2.5</v>
+      </c>
+      <c r="R211">
+        <v>2.05</v>
+      </c>
+      <c r="S211">
+        <v>5.5</v>
+      </c>
+      <c r="T211">
+        <v>1.5</v>
+      </c>
+      <c r="U211">
+        <v>2.5</v>
+      </c>
+      <c r="V211">
+        <v>3.4</v>
+      </c>
+      <c r="W211">
+        <v>1.3</v>
+      </c>
+      <c r="X211">
+        <v>10</v>
+      </c>
+      <c r="Y211">
+        <v>1.06</v>
+      </c>
+      <c r="Z211">
+        <v>1.75</v>
+      </c>
+      <c r="AA211">
+        <v>3.5</v>
+      </c>
+      <c r="AB211">
+        <v>4.6</v>
+      </c>
+      <c r="AC211">
+        <v>1.05</v>
+      </c>
+      <c r="AD211">
+        <v>10</v>
+      </c>
+      <c r="AE211">
+        <v>1.35</v>
+      </c>
+      <c r="AF211">
+        <v>3.2</v>
+      </c>
+      <c r="AG211">
+        <v>2.1</v>
+      </c>
+      <c r="AH211">
+        <v>1.67</v>
+      </c>
+      <c r="AI211">
+        <v>2.05</v>
+      </c>
+      <c r="AJ211">
+        <v>1.7</v>
+      </c>
+      <c r="AK211">
+        <v>1.18</v>
+      </c>
+      <c r="AL211">
+        <v>1.31</v>
+      </c>
+      <c r="AM211">
+        <v>1.95</v>
+      </c>
+      <c r="AN211">
+        <v>1.82</v>
+      </c>
+      <c r="AO211">
+        <v>1.27</v>
+      </c>
+      <c r="AP211">
+        <v>1.92</v>
+      </c>
+      <c r="AQ211">
+        <v>1.17</v>
+      </c>
+      <c r="AR211">
+        <v>1.51</v>
+      </c>
+      <c r="AS211">
+        <v>1.12</v>
+      </c>
+      <c r="AT211">
+        <v>2.63</v>
+      </c>
+      <c r="AU211">
+        <v>7</v>
+      </c>
+      <c r="AV211">
+        <v>4</v>
+      </c>
+      <c r="AW211">
+        <v>13</v>
+      </c>
+      <c r="AX211">
+        <v>7</v>
+      </c>
+      <c r="AY211">
+        <v>22</v>
+      </c>
+      <c r="AZ211">
+        <v>12</v>
+      </c>
+      <c r="BA211">
+        <v>7</v>
+      </c>
+      <c r="BB211">
+        <v>2</v>
+      </c>
+      <c r="BC211">
+        <v>9</v>
+      </c>
+      <c r="BD211">
+        <v>1.38</v>
+      </c>
+      <c r="BE211">
+        <v>7.5</v>
+      </c>
+      <c r="BF211">
+        <v>3.4</v>
+      </c>
+      <c r="BG211">
+        <v>1.22</v>
+      </c>
+      <c r="BH211">
+        <v>3.7</v>
+      </c>
+      <c r="BI211">
+        <v>1.38</v>
+      </c>
+      <c r="BJ211">
+        <v>2.7</v>
+      </c>
+      <c r="BK211">
+        <v>1.62</v>
+      </c>
+      <c r="BL211">
+        <v>2.12</v>
+      </c>
+      <c r="BM211">
+        <v>1.96</v>
+      </c>
+      <c r="BN211">
+        <v>1.71</v>
+      </c>
+      <c r="BO211">
+        <v>2.45</v>
+      </c>
+      <c r="BP211">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="320">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -685,6 +685,9 @@
     <t>['14', '90+4']</t>
   </si>
   <si>
+    <t>['78']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -1332,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP211"/>
+  <dimension ref="A1:BP213"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1794,7 +1797,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2412,7 +2415,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2493,7 +2496,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ6">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2824,7 +2827,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -3111,7 +3114,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ9">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3442,7 +3445,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3648,7 +3651,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4060,7 +4063,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4472,7 +4475,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4550,7 +4553,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ16">
         <v>1</v>
@@ -4884,7 +4887,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4962,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ18">
         <v>2.36</v>
@@ -5090,7 +5093,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5296,7 +5299,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5502,7 +5505,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -5583,7 +5586,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ21">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR21">
         <v>1.57</v>
@@ -6201,7 +6204,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ24">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR24">
         <v>2.62</v>
@@ -7150,7 +7153,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7228,7 +7231,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ29">
         <v>1.82</v>
@@ -7356,7 +7359,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7562,7 +7565,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -7846,7 +7849,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ32">
         <v>1.18</v>
@@ -8592,7 +8595,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q36">
         <v>2.55</v>
@@ -9004,7 +9007,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9210,7 +9213,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9622,7 +9625,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9828,7 +9831,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -9909,7 +9912,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ42">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR42">
         <v>2.4</v>
@@ -10034,7 +10037,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10446,7 +10449,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10652,7 +10655,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10858,7 +10861,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -11064,7 +11067,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11351,7 +11354,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ49">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR49">
         <v>1.09</v>
@@ -11476,7 +11479,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11760,7 +11763,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ51">
         <v>1.33</v>
@@ -11888,7 +11891,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -12506,7 +12509,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12584,7 +12587,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ55">
         <v>1.82</v>
@@ -12712,7 +12715,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -13124,7 +13127,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13330,7 +13333,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -14853,7 +14856,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ66">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR66">
         <v>1.45</v>
@@ -15056,10 +15059,10 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ67">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR67">
         <v>1.08</v>
@@ -15802,7 +15805,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -16008,7 +16011,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16420,7 +16423,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16626,7 +16629,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16832,7 +16835,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16910,7 +16913,7 @@
         <v>0.75</v>
       </c>
       <c r="AP76">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ76">
         <v>0.58</v>
@@ -17038,7 +17041,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17656,7 +17659,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17862,7 +17865,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -18068,7 +18071,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18149,7 +18152,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ82">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR82">
         <v>2.06</v>
@@ -18274,7 +18277,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18480,7 +18483,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18686,7 +18689,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18892,7 +18895,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19304,7 +19307,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19797,7 +19800,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ90">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR90">
         <v>1.22</v>
@@ -19922,7 +19925,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -20000,7 +20003,7 @@
         <v>0.4</v>
       </c>
       <c r="AP91">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ91">
         <v>0.5</v>
@@ -20128,7 +20131,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20746,7 +20749,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -20824,7 +20827,7 @@
         <v>0</v>
       </c>
       <c r="AP95">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ95">
         <v>0.67</v>
@@ -21364,7 +21367,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21857,7 +21860,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ100">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR100">
         <v>1.15</v>
@@ -21982,7 +21985,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22394,7 +22397,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22475,7 +22478,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ103">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR103">
         <v>2.02</v>
@@ -22806,7 +22809,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -23012,7 +23015,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q106">
         <v>5.5</v>
@@ -23708,7 +23711,7 @@
         <v>3</v>
       </c>
       <c r="AP109">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ109">
         <v>2.08</v>
@@ -23836,7 +23839,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -24944,7 +24947,7 @@
         <v>0.33</v>
       </c>
       <c r="AP115">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ115">
         <v>0.75</v>
@@ -25896,7 +25899,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26183,7 +26186,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ121">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR121">
         <v>1.05</v>
@@ -26308,7 +26311,7 @@
         <v>167</v>
       </c>
       <c r="P122" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q122">
         <v>11</v>
@@ -26514,7 +26517,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26720,7 +26723,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -27007,7 +27010,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ125">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR125">
         <v>2.03</v>
@@ -27132,7 +27135,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27338,7 +27341,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27544,7 +27547,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27750,7 +27753,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -28034,7 +28037,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ130">
         <v>0.55</v>
@@ -28162,7 +28165,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28240,7 +28243,7 @@
         <v>1.67</v>
       </c>
       <c r="AP131">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ131">
         <v>1.67</v>
@@ -28368,7 +28371,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28780,7 +28783,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -29604,7 +29607,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29685,7 +29688,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ138">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR138">
         <v>1.22</v>
@@ -29810,7 +29813,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -30222,7 +30225,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30428,7 +30431,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30634,7 +30637,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -31046,7 +31049,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31127,7 +31130,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ145">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR145">
         <v>1.04</v>
@@ -31252,7 +31255,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31458,7 +31461,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q147">
         <v>2.55</v>
@@ -31536,7 +31539,7 @@
         <v>0.57</v>
       </c>
       <c r="AP147">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ147">
         <v>0.55</v>
@@ -31664,7 +31667,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31870,7 +31873,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -31948,7 +31951,7 @@
         <v>0.5</v>
       </c>
       <c r="AP149">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ149">
         <v>1</v>
@@ -32282,7 +32285,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32488,7 +32491,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32694,7 +32697,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -33312,7 +33315,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33518,7 +33521,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33724,7 +33727,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33930,7 +33933,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34214,7 +34217,7 @@
         <v>0.78</v>
       </c>
       <c r="AP160">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ160">
         <v>0.75</v>
@@ -34342,7 +34345,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34548,7 +34551,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34754,7 +34757,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -34832,7 +34835,7 @@
         <v>1.38</v>
       </c>
       <c r="AP163">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ163">
         <v>1.17</v>
@@ -35166,7 +35169,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35453,7 +35456,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ166">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR166">
         <v>1.12</v>
@@ -36196,7 +36199,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36277,7 +36280,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ170">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR170">
         <v>1.95</v>
@@ -36814,7 +36817,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -36892,7 +36895,7 @@
         <v>1.11</v>
       </c>
       <c r="AP173">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ173">
         <v>1.33</v>
@@ -37226,7 +37229,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37432,7 +37435,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -38050,7 +38053,7 @@
         <v>205</v>
       </c>
       <c r="P179" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q179">
         <v>8.5</v>
@@ -38256,7 +38259,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q180">
         <v>4.75</v>
@@ -38334,7 +38337,7 @@
         <v>2.44</v>
       </c>
       <c r="AP180">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ180">
         <v>2.36</v>
@@ -38462,7 +38465,7 @@
         <v>207</v>
       </c>
       <c r="P181" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q181">
         <v>6.5</v>
@@ -38668,7 +38671,7 @@
         <v>167</v>
       </c>
       <c r="P182" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -38955,7 +38958,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ183">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR183">
         <v>1.2</v>
@@ -39080,7 +39083,7 @@
         <v>208</v>
       </c>
       <c r="P184" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q184">
         <v>1.57</v>
@@ -39492,7 +39495,7 @@
         <v>209</v>
       </c>
       <c r="P186" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q186">
         <v>2.2</v>
@@ -40191,7 +40194,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ189">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR189">
         <v>1.19</v>
@@ -40316,7 +40319,7 @@
         <v>184</v>
       </c>
       <c r="P190" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q190">
         <v>2.63</v>
@@ -40600,10 +40603,10 @@
         <v>0.3</v>
       </c>
       <c r="AP191">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AQ191">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR191">
         <v>1.28</v>
@@ -40728,7 +40731,7 @@
         <v>212</v>
       </c>
       <c r="P192" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -40806,7 +40809,7 @@
         <v>1.4</v>
       </c>
       <c r="AP192">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ192">
         <v>1.17</v>
@@ -40934,7 +40937,7 @@
         <v>213</v>
       </c>
       <c r="P193" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q193">
         <v>2.8</v>
@@ -41346,7 +41349,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q195">
         <v>1.67</v>
@@ -41758,7 +41761,7 @@
         <v>90</v>
       </c>
       <c r="P197" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q197">
         <v>7.5</v>
@@ -42170,7 +42173,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42994,7 +42997,7 @@
         <v>218</v>
       </c>
       <c r="P203" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q203">
         <v>2.55</v>
@@ -43281,7 +43284,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ204">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR204">
         <v>1.15</v>
@@ -43406,7 +43409,7 @@
         <v>219</v>
       </c>
       <c r="P205" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q205">
         <v>2.45</v>
@@ -43612,7 +43615,7 @@
         <v>220</v>
       </c>
       <c r="P206" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q206">
         <v>7</v>
@@ -44024,7 +44027,7 @@
         <v>166</v>
       </c>
       <c r="P208" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44436,7 +44439,7 @@
         <v>90</v>
       </c>
       <c r="P210" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q210">
         <v>5.5</v>
@@ -44799,6 +44802,418 @@
       </c>
       <c r="BP211">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7574773</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45718.52083333334</v>
+      </c>
+      <c r="F212">
+        <v>24</v>
+      </c>
+      <c r="G212" t="s">
+        <v>84</v>
+      </c>
+      <c r="H212" t="s">
+        <v>87</v>
+      </c>
+      <c r="I212">
+        <v>0</v>
+      </c>
+      <c r="J212">
+        <v>0</v>
+      </c>
+      <c r="K212">
+        <v>0</v>
+      </c>
+      <c r="L212">
+        <v>1</v>
+      </c>
+      <c r="M212">
+        <v>1</v>
+      </c>
+      <c r="N212">
+        <v>2</v>
+      </c>
+      <c r="O212" t="s">
+        <v>223</v>
+      </c>
+      <c r="P212" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q212">
+        <v>2.5</v>
+      </c>
+      <c r="R212">
+        <v>1.93</v>
+      </c>
+      <c r="S212">
+        <v>5</v>
+      </c>
+      <c r="T212">
+        <v>1.53</v>
+      </c>
+      <c r="U212">
+        <v>2.38</v>
+      </c>
+      <c r="V212">
+        <v>3.3</v>
+      </c>
+      <c r="W212">
+        <v>1.28</v>
+      </c>
+      <c r="X212">
+        <v>8</v>
+      </c>
+      <c r="Y212">
+        <v>1.05</v>
+      </c>
+      <c r="Z212">
+        <v>1.91</v>
+      </c>
+      <c r="AA212">
+        <v>2.9</v>
+      </c>
+      <c r="AB212">
+        <v>4.75</v>
+      </c>
+      <c r="AC212">
+        <v>1.1</v>
+      </c>
+      <c r="AD212">
+        <v>6.5</v>
+      </c>
+      <c r="AE212">
+        <v>1.5</v>
+      </c>
+      <c r="AF212">
+        <v>2.55</v>
+      </c>
+      <c r="AG212">
+        <v>2.4</v>
+      </c>
+      <c r="AH212">
+        <v>1.5</v>
+      </c>
+      <c r="AI212">
+        <v>2.1</v>
+      </c>
+      <c r="AJ212">
+        <v>1.65</v>
+      </c>
+      <c r="AK212">
+        <v>1.2</v>
+      </c>
+      <c r="AL212">
+        <v>1.3</v>
+      </c>
+      <c r="AM212">
+        <v>1.83</v>
+      </c>
+      <c r="AN212">
+        <v>1.73</v>
+      </c>
+      <c r="AO212">
+        <v>0.55</v>
+      </c>
+      <c r="AP212">
+        <v>1.67</v>
+      </c>
+      <c r="AQ212">
+        <v>0.58</v>
+      </c>
+      <c r="AR212">
+        <v>1.24</v>
+      </c>
+      <c r="AS212">
+        <v>1.09</v>
+      </c>
+      <c r="AT212">
+        <v>2.33</v>
+      </c>
+      <c r="AU212">
+        <v>3</v>
+      </c>
+      <c r="AV212">
+        <v>2</v>
+      </c>
+      <c r="AW212">
+        <v>9</v>
+      </c>
+      <c r="AX212">
+        <v>6</v>
+      </c>
+      <c r="AY212">
+        <v>14</v>
+      </c>
+      <c r="AZ212">
+        <v>9</v>
+      </c>
+      <c r="BA212">
+        <v>4</v>
+      </c>
+      <c r="BB212">
+        <v>1</v>
+      </c>
+      <c r="BC212">
+        <v>5</v>
+      </c>
+      <c r="BD212">
+        <v>1.55</v>
+      </c>
+      <c r="BE212">
+        <v>6.75</v>
+      </c>
+      <c r="BF212">
+        <v>2.7</v>
+      </c>
+      <c r="BG212">
+        <v>1.29</v>
+      </c>
+      <c r="BH212">
+        <v>3.15</v>
+      </c>
+      <c r="BI212">
+        <v>1.5</v>
+      </c>
+      <c r="BJ212">
+        <v>2.33</v>
+      </c>
+      <c r="BK212">
+        <v>1.84</v>
+      </c>
+      <c r="BL212">
+        <v>1.83</v>
+      </c>
+      <c r="BM212">
+        <v>2.28</v>
+      </c>
+      <c r="BN212">
+        <v>1.52</v>
+      </c>
+      <c r="BO212">
+        <v>2.95</v>
+      </c>
+      <c r="BP212">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7574774</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45718.52083333334</v>
+      </c>
+      <c r="F213">
+        <v>24</v>
+      </c>
+      <c r="G213" t="s">
+        <v>86</v>
+      </c>
+      <c r="H213" t="s">
+        <v>79</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <v>1</v>
+      </c>
+      <c r="M213">
+        <v>0</v>
+      </c>
+      <c r="N213">
+        <v>1</v>
+      </c>
+      <c r="O213" t="s">
+        <v>119</v>
+      </c>
+      <c r="P213" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q213">
+        <v>4.75</v>
+      </c>
+      <c r="R213">
+        <v>1.95</v>
+      </c>
+      <c r="S213">
+        <v>2.8</v>
+      </c>
+      <c r="T213">
+        <v>1.55</v>
+      </c>
+      <c r="U213">
+        <v>2.32</v>
+      </c>
+      <c r="V213">
+        <v>3.7</v>
+      </c>
+      <c r="W213">
+        <v>1.24</v>
+      </c>
+      <c r="X213">
+        <v>10.5</v>
+      </c>
+      <c r="Y213">
+        <v>1.02</v>
+      </c>
+      <c r="Z213">
+        <v>4.2</v>
+      </c>
+      <c r="AA213">
+        <v>3.1</v>
+      </c>
+      <c r="AB213">
+        <v>1.95</v>
+      </c>
+      <c r="AC213">
+        <v>1.09</v>
+      </c>
+      <c r="AD213">
+        <v>8</v>
+      </c>
+      <c r="AE213">
+        <v>1.53</v>
+      </c>
+      <c r="AF213">
+        <v>2.37</v>
+      </c>
+      <c r="AG213">
+        <v>2.4</v>
+      </c>
+      <c r="AH213">
+        <v>1.57</v>
+      </c>
+      <c r="AI213">
+        <v>2.15</v>
+      </c>
+      <c r="AJ213">
+        <v>1.68</v>
+      </c>
+      <c r="AK213">
+        <v>1.87</v>
+      </c>
+      <c r="AL213">
+        <v>1.28</v>
+      </c>
+      <c r="AM213">
+        <v>1.22</v>
+      </c>
+      <c r="AN213">
+        <v>0.27</v>
+      </c>
+      <c r="AO213">
+        <v>1.55</v>
+      </c>
+      <c r="AP213">
+        <v>0.5</v>
+      </c>
+      <c r="AQ213">
+        <v>1.42</v>
+      </c>
+      <c r="AR213">
+        <v>1.28</v>
+      </c>
+      <c r="AS213">
+        <v>0.96</v>
+      </c>
+      <c r="AT213">
+        <v>2.24</v>
+      </c>
+      <c r="AU213">
+        <v>6</v>
+      </c>
+      <c r="AV213">
+        <v>2</v>
+      </c>
+      <c r="AW213">
+        <v>8</v>
+      </c>
+      <c r="AX213">
+        <v>10</v>
+      </c>
+      <c r="AY213">
+        <v>15</v>
+      </c>
+      <c r="AZ213">
+        <v>18</v>
+      </c>
+      <c r="BA213">
+        <v>9</v>
+      </c>
+      <c r="BB213">
+        <v>5</v>
+      </c>
+      <c r="BC213">
+        <v>14</v>
+      </c>
+      <c r="BD213">
+        <v>3.15</v>
+      </c>
+      <c r="BE213">
+        <v>6.6</v>
+      </c>
+      <c r="BF213">
+        <v>1.6</v>
+      </c>
+      <c r="BG213">
+        <v>1.43</v>
+      </c>
+      <c r="BH213">
+        <v>2.62</v>
+      </c>
+      <c r="BI213">
+        <v>1.75</v>
+      </c>
+      <c r="BJ213">
+        <v>2.01</v>
+      </c>
+      <c r="BK213">
+        <v>2.23</v>
+      </c>
+      <c r="BL213">
+        <v>1.61</v>
+      </c>
+      <c r="BM213">
+        <v>2.87</v>
+      </c>
+      <c r="BN213">
+        <v>1.37</v>
+      </c>
+      <c r="BO213">
+        <v>3.95</v>
+      </c>
+      <c r="BP213">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="322">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -688,6 +688,9 @@
     <t>['78']</t>
   </si>
   <si>
+    <t>['5', '70']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -974,6 +977,9 @@
   </si>
   <si>
     <t>['13', '77']</t>
+  </si>
+  <si>
+    <t>['10']</t>
   </si>
 </sst>
 </file>
@@ -1335,7 +1341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP213"/>
+  <dimension ref="A1:BP215"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1797,7 +1803,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2415,7 +2421,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2827,7 +2833,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -2905,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ8">
         <v>0.58</v>
@@ -3445,7 +3451,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3651,7 +3657,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3732,7 +3738,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ12">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3935,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ13">
         <v>0.75</v>
@@ -4063,7 +4069,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4475,7 +4481,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4887,7 +4893,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4968,7 +4974,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ18">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5093,7 +5099,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5299,7 +5305,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5377,7 +5383,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ20">
         <v>2.08</v>
@@ -5505,7 +5511,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -7153,7 +7159,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7359,7 +7365,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7440,7 +7446,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ30">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR30">
         <v>0.55</v>
@@ -7565,7 +7571,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -8467,7 +8473,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -8595,7 +8601,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q36">
         <v>2.55</v>
@@ -8882,7 +8888,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ37">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR37">
         <v>1.77</v>
@@ -9007,7 +9013,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9213,7 +9219,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9625,7 +9631,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9831,7 +9837,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -10037,7 +10043,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10449,7 +10455,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10655,7 +10661,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10861,7 +10867,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10942,7 +10948,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ47">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR47">
         <v>1.27</v>
@@ -11067,7 +11073,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11145,7 +11151,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ48">
         <v>1.18</v>
@@ -11479,7 +11485,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11891,7 +11897,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -12175,7 +12181,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ53">
         <v>1</v>
@@ -12384,7 +12390,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ54">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR54">
         <v>1.92</v>
@@ -12509,7 +12515,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12715,7 +12721,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -13127,7 +13133,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13333,7 +13339,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -14647,7 +14653,7 @@
         <v>1.33</v>
       </c>
       <c r="AP65">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ65">
         <v>1.33</v>
@@ -15268,7 +15274,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ68">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR68">
         <v>0.83</v>
@@ -15677,7 +15683,7 @@
         <v>0.67</v>
       </c>
       <c r="AP70">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ70">
         <v>1.18</v>
@@ -15805,7 +15811,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -16011,7 +16017,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16092,7 +16098,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ72">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR72">
         <v>2.36</v>
@@ -16423,7 +16429,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16629,7 +16635,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16835,7 +16841,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17041,7 +17047,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17659,7 +17665,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17865,7 +17871,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -18071,7 +18077,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18277,7 +18283,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18355,7 +18361,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ83">
         <v>1.17</v>
@@ -18483,7 +18489,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18561,7 +18567,7 @@
         <v>1.33</v>
       </c>
       <c r="AP84">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ84">
         <v>1.82</v>
@@ -18689,7 +18695,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18895,7 +18901,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19307,7 +19313,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19388,7 +19394,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ88">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR88">
         <v>0.89</v>
@@ -19925,7 +19931,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -20131,7 +20137,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20418,7 +20424,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ93">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR93">
         <v>0.99</v>
@@ -20749,7 +20755,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -21367,7 +21373,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21857,7 +21863,7 @@
         <v>0.2</v>
       </c>
       <c r="AP100">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ100">
         <v>0.58</v>
@@ -21985,7 +21991,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22063,7 +22069,7 @@
         <v>1</v>
       </c>
       <c r="AP101">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ101">
         <v>0.58</v>
@@ -22397,7 +22403,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22809,7 +22815,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -23015,7 +23021,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q106">
         <v>5.5</v>
@@ -23096,7 +23102,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ106">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR106">
         <v>1.19</v>
@@ -23839,7 +23845,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -25156,7 +25162,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ116">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR116">
         <v>1.23</v>
@@ -25565,7 +25571,7 @@
         <v>0.29</v>
       </c>
       <c r="AP118">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ118">
         <v>0.5</v>
@@ -25899,7 +25905,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26311,7 +26317,7 @@
         <v>167</v>
       </c>
       <c r="P122" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q122">
         <v>11</v>
@@ -26517,7 +26523,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26723,7 +26729,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -27135,7 +27141,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27213,7 +27219,7 @@
         <v>1.14</v>
       </c>
       <c r="AP126">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ126">
         <v>1</v>
@@ -27341,7 +27347,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27547,7 +27553,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27753,7 +27759,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -28040,7 +28046,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ130">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR130">
         <v>1.33</v>
@@ -28165,7 +28171,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28371,7 +28377,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28452,7 +28458,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ132">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR132">
         <v>1.35</v>
@@ -28783,7 +28789,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -29607,7 +29613,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29813,7 +29819,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -30225,7 +30231,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30303,7 +30309,7 @@
         <v>1.13</v>
       </c>
       <c r="AP141">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ141">
         <v>1</v>
@@ -30431,7 +30437,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30509,7 +30515,7 @@
         <v>0.38</v>
       </c>
       <c r="AP142">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ142">
         <v>0.5</v>
@@ -30637,7 +30643,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -31049,7 +31055,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31255,7 +31261,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31461,7 +31467,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q147">
         <v>2.55</v>
@@ -31542,7 +31548,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ147">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR147">
         <v>1.11</v>
@@ -31667,7 +31673,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31748,7 +31754,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ148">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR148">
         <v>2.01</v>
@@ -31873,7 +31879,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32285,7 +32291,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32491,7 +32497,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32697,7 +32703,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -33315,7 +33321,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33521,7 +33527,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33599,7 +33605,7 @@
         <v>2.22</v>
       </c>
       <c r="AP157">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ157">
         <v>2.08</v>
@@ -33727,7 +33733,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33933,7 +33939,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34014,7 +34020,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ159">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR159">
         <v>1.19</v>
@@ -34345,7 +34351,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34426,7 +34432,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ161">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR161">
         <v>1.17</v>
@@ -34551,7 +34557,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34757,7 +34763,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -35169,7 +35175,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35247,7 +35253,7 @@
         <v>0.44</v>
       </c>
       <c r="AP165">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ165">
         <v>0.67</v>
@@ -36199,7 +36205,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36817,7 +36823,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -37229,7 +37235,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37435,7 +37441,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -37722,7 +37728,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ177">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR177">
         <v>1.39</v>
@@ -38053,7 +38059,7 @@
         <v>205</v>
       </c>
       <c r="P179" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q179">
         <v>8.5</v>
@@ -38259,7 +38265,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q180">
         <v>4.75</v>
@@ -38340,7 +38346,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ180">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR180">
         <v>1.19</v>
@@ -38465,7 +38471,7 @@
         <v>207</v>
       </c>
       <c r="P181" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q181">
         <v>6.5</v>
@@ -38543,7 +38549,7 @@
         <v>1.44</v>
       </c>
       <c r="AP181">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ181">
         <v>1.67</v>
@@ -38671,7 +38677,7 @@
         <v>167</v>
       </c>
       <c r="P182" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -39083,7 +39089,7 @@
         <v>208</v>
       </c>
       <c r="P184" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q184">
         <v>1.57</v>
@@ -39495,7 +39501,7 @@
         <v>209</v>
       </c>
       <c r="P186" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q186">
         <v>2.2</v>
@@ -39779,7 +39785,7 @@
         <v>0.3</v>
       </c>
       <c r="AP187">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ187">
         <v>0.5</v>
@@ -40319,7 +40325,7 @@
         <v>184</v>
       </c>
       <c r="P190" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q190">
         <v>2.63</v>
@@ -40731,7 +40737,7 @@
         <v>212</v>
       </c>
       <c r="P192" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -40937,7 +40943,7 @@
         <v>213</v>
       </c>
       <c r="P193" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q193">
         <v>2.8</v>
@@ -41349,7 +41355,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q195">
         <v>1.67</v>
@@ -41633,10 +41639,10 @@
         <v>0.5</v>
       </c>
       <c r="AP196">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ196">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR196">
         <v>1.29</v>
@@ -41761,7 +41767,7 @@
         <v>90</v>
       </c>
       <c r="P197" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q197">
         <v>7.5</v>
@@ -41839,7 +41845,7 @@
         <v>1.4</v>
       </c>
       <c r="AP197">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ197">
         <v>1.67</v>
@@ -42048,7 +42054,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ198">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR198">
         <v>1.47</v>
@@ -42173,7 +42179,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42997,7 +43003,7 @@
         <v>218</v>
       </c>
       <c r="P203" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q203">
         <v>2.55</v>
@@ -43409,7 +43415,7 @@
         <v>219</v>
       </c>
       <c r="P205" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q205">
         <v>2.45</v>
@@ -43615,7 +43621,7 @@
         <v>220</v>
       </c>
       <c r="P206" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q206">
         <v>7</v>
@@ -44027,7 +44033,7 @@
         <v>166</v>
       </c>
       <c r="P208" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44439,7 +44445,7 @@
         <v>90</v>
       </c>
       <c r="P210" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q210">
         <v>5.5</v>
@@ -45214,6 +45220,418 @@
       </c>
       <c r="BP213">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7574771</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45718.625</v>
+      </c>
+      <c r="F214">
+        <v>24</v>
+      </c>
+      <c r="G214" t="s">
+        <v>76</v>
+      </c>
+      <c r="H214" t="s">
+        <v>71</v>
+      </c>
+      <c r="I214">
+        <v>0</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>0</v>
+      </c>
+      <c r="L214">
+        <v>0</v>
+      </c>
+      <c r="M214">
+        <v>1</v>
+      </c>
+      <c r="N214">
+        <v>1</v>
+      </c>
+      <c r="O214" t="s">
+        <v>90</v>
+      </c>
+      <c r="P214" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q214">
+        <v>3.1</v>
+      </c>
+      <c r="R214">
+        <v>1.95</v>
+      </c>
+      <c r="S214">
+        <v>4.2</v>
+      </c>
+      <c r="T214">
+        <v>1.52</v>
+      </c>
+      <c r="U214">
+        <v>2.4</v>
+      </c>
+      <c r="V214">
+        <v>3.45</v>
+      </c>
+      <c r="W214">
+        <v>1.27</v>
+      </c>
+      <c r="X214">
+        <v>9.4</v>
+      </c>
+      <c r="Y214">
+        <v>1.03</v>
+      </c>
+      <c r="Z214">
+        <v>2.25</v>
+      </c>
+      <c r="AA214">
+        <v>3</v>
+      </c>
+      <c r="AB214">
+        <v>3.3</v>
+      </c>
+      <c r="AC214">
+        <v>1.08</v>
+      </c>
+      <c r="AD214">
+        <v>8.5</v>
+      </c>
+      <c r="AE214">
+        <v>1.5</v>
+      </c>
+      <c r="AF214">
+        <v>2.4</v>
+      </c>
+      <c r="AG214">
+        <v>2.4</v>
+      </c>
+      <c r="AH214">
+        <v>1.53</v>
+      </c>
+      <c r="AI214">
+        <v>1.95</v>
+      </c>
+      <c r="AJ214">
+        <v>1.83</v>
+      </c>
+      <c r="AK214">
+        <v>1.33</v>
+      </c>
+      <c r="AL214">
+        <v>1.3</v>
+      </c>
+      <c r="AM214">
+        <v>1.63</v>
+      </c>
+      <c r="AN214">
+        <v>0.64</v>
+      </c>
+      <c r="AO214">
+        <v>0.55</v>
+      </c>
+      <c r="AP214">
+        <v>0.58</v>
+      </c>
+      <c r="AQ214">
+        <v>0.75</v>
+      </c>
+      <c r="AR214">
+        <v>1.29</v>
+      </c>
+      <c r="AS214">
+        <v>1.04</v>
+      </c>
+      <c r="AT214">
+        <v>2.33</v>
+      </c>
+      <c r="AU214">
+        <v>5</v>
+      </c>
+      <c r="AV214">
+        <v>4</v>
+      </c>
+      <c r="AW214">
+        <v>14</v>
+      </c>
+      <c r="AX214">
+        <v>3</v>
+      </c>
+      <c r="AY214">
+        <v>20</v>
+      </c>
+      <c r="AZ214">
+        <v>7</v>
+      </c>
+      <c r="BA214">
+        <v>7</v>
+      </c>
+      <c r="BB214">
+        <v>1</v>
+      </c>
+      <c r="BC214">
+        <v>8</v>
+      </c>
+      <c r="BD214">
+        <v>1.81</v>
+      </c>
+      <c r="BE214">
+        <v>6.5</v>
+      </c>
+      <c r="BF214">
+        <v>2.18</v>
+      </c>
+      <c r="BG214">
+        <v>1.36</v>
+      </c>
+      <c r="BH214">
+        <v>2.8</v>
+      </c>
+      <c r="BI214">
+        <v>1.62</v>
+      </c>
+      <c r="BJ214">
+        <v>2.1</v>
+      </c>
+      <c r="BK214">
+        <v>2</v>
+      </c>
+      <c r="BL214">
+        <v>1.68</v>
+      </c>
+      <c r="BM214">
+        <v>2.55</v>
+      </c>
+      <c r="BN214">
+        <v>1.43</v>
+      </c>
+      <c r="BO214">
+        <v>3.3</v>
+      </c>
+      <c r="BP214">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7574776</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45718.72916666666</v>
+      </c>
+      <c r="F215">
+        <v>24</v>
+      </c>
+      <c r="G215" t="s">
+        <v>81</v>
+      </c>
+      <c r="H215" t="s">
+        <v>77</v>
+      </c>
+      <c r="I215">
+        <v>1</v>
+      </c>
+      <c r="J215">
+        <v>1</v>
+      </c>
+      <c r="K215">
+        <v>2</v>
+      </c>
+      <c r="L215">
+        <v>2</v>
+      </c>
+      <c r="M215">
+        <v>1</v>
+      </c>
+      <c r="N215">
+        <v>3</v>
+      </c>
+      <c r="O215" t="s">
+        <v>224</v>
+      </c>
+      <c r="P215" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q215">
+        <v>4.33</v>
+      </c>
+      <c r="R215">
+        <v>2.2</v>
+      </c>
+      <c r="S215">
+        <v>2.3</v>
+      </c>
+      <c r="T215">
+        <v>1.35</v>
+      </c>
+      <c r="U215">
+        <v>2.95</v>
+      </c>
+      <c r="V215">
+        <v>2.55</v>
+      </c>
+      <c r="W215">
+        <v>1.45</v>
+      </c>
+      <c r="X215">
+        <v>6</v>
+      </c>
+      <c r="Y215">
+        <v>1.09</v>
+      </c>
+      <c r="Z215">
+        <v>4</v>
+      </c>
+      <c r="AA215">
+        <v>3.75</v>
+      </c>
+      <c r="AB215">
+        <v>1.75</v>
+      </c>
+      <c r="AC215">
+        <v>1.05</v>
+      </c>
+      <c r="AD215">
+        <v>9.5</v>
+      </c>
+      <c r="AE215">
+        <v>1.25</v>
+      </c>
+      <c r="AF215">
+        <v>3.7</v>
+      </c>
+      <c r="AG215">
+        <v>1.8</v>
+      </c>
+      <c r="AH215">
+        <v>1.95</v>
+      </c>
+      <c r="AI215">
+        <v>1.73</v>
+      </c>
+      <c r="AJ215">
+        <v>2</v>
+      </c>
+      <c r="AK215">
+        <v>1.95</v>
+      </c>
+      <c r="AL215">
+        <v>1.22</v>
+      </c>
+      <c r="AM215">
+        <v>1.22</v>
+      </c>
+      <c r="AN215">
+        <v>1.64</v>
+      </c>
+      <c r="AO215">
+        <v>2.36</v>
+      </c>
+      <c r="AP215">
+        <v>1.75</v>
+      </c>
+      <c r="AQ215">
+        <v>2.17</v>
+      </c>
+      <c r="AR215">
+        <v>1.31</v>
+      </c>
+      <c r="AS215">
+        <v>1.43</v>
+      </c>
+      <c r="AT215">
+        <v>2.74</v>
+      </c>
+      <c r="AU215">
+        <v>-1</v>
+      </c>
+      <c r="AV215">
+        <v>-1</v>
+      </c>
+      <c r="AW215">
+        <v>-1</v>
+      </c>
+      <c r="AX215">
+        <v>-1</v>
+      </c>
+      <c r="AY215">
+        <v>-1</v>
+      </c>
+      <c r="AZ215">
+        <v>-1</v>
+      </c>
+      <c r="BA215">
+        <v>-1</v>
+      </c>
+      <c r="BB215">
+        <v>-1</v>
+      </c>
+      <c r="BC215">
+        <v>-1</v>
+      </c>
+      <c r="BD215">
+        <v>2.65</v>
+      </c>
+      <c r="BE215">
+        <v>7</v>
+      </c>
+      <c r="BF215">
+        <v>1.57</v>
+      </c>
+      <c r="BG215">
+        <v>1.28</v>
+      </c>
+      <c r="BH215">
+        <v>3.2</v>
+      </c>
+      <c r="BI215">
+        <v>1.49</v>
+      </c>
+      <c r="BJ215">
+        <v>2.38</v>
+      </c>
+      <c r="BK215">
+        <v>1.8</v>
+      </c>
+      <c r="BL215">
+        <v>1.86</v>
+      </c>
+      <c r="BM215">
+        <v>2.25</v>
+      </c>
+      <c r="BN215">
+        <v>1.55</v>
+      </c>
+      <c r="BO215">
+        <v>2.9</v>
+      </c>
+      <c r="BP215">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -45568,31 +45568,31 @@
         <v>2.74</v>
       </c>
       <c r="AU215">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AV215">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AW215">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AX215">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AY215">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AZ215">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="BA215">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB215">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BC215">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BD215">
         <v>2.65</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="323">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -691,6 +691,9 @@
     <t>['5', '70']</t>
   </si>
   <si>
+    <t>['5', '36', '90+6']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -1341,7 +1344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP215"/>
+  <dimension ref="A1:BP216"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1675,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ2">
         <v>0.67</v>
@@ -1803,7 +1806,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2421,7 +2424,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2833,7 +2836,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -3451,7 +3454,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3657,7 +3660,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4069,7 +4072,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4481,7 +4484,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4768,7 +4771,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ17">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4893,7 +4896,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -5099,7 +5102,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5305,7 +5308,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5511,7 +5514,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -7159,7 +7162,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7365,7 +7368,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7571,7 +7574,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -7858,7 +7861,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ32">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR32">
         <v>0.64</v>
@@ -8061,7 +8064,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ33">
         <v>1.67</v>
@@ -8601,7 +8604,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q36">
         <v>2.55</v>
@@ -9013,7 +9016,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9219,7 +9222,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9631,7 +9634,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9837,7 +9840,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -10043,7 +10046,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10455,7 +10458,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10661,7 +10664,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10867,7 +10870,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -11073,7 +11076,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11154,7 +11157,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ48">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR48">
         <v>1.23</v>
@@ -11485,7 +11488,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11897,7 +11900,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -12387,7 +12390,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ54">
         <v>0.75</v>
@@ -12515,7 +12518,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12721,7 +12724,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -13133,7 +13136,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13339,7 +13342,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -15477,7 +15480,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ69">
         <v>1.17</v>
@@ -15686,7 +15689,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ70">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR70">
         <v>1.2</v>
@@ -15811,7 +15814,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -16017,7 +16020,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16429,7 +16432,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16635,7 +16638,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16841,7 +16844,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17047,7 +17050,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17665,7 +17668,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17871,7 +17874,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -18077,7 +18080,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18155,7 +18158,7 @@
         <v>0.25</v>
       </c>
       <c r="AP82">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ82">
         <v>0.58</v>
@@ -18283,7 +18286,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18489,7 +18492,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18695,7 +18698,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18901,7 +18904,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19313,7 +19316,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19600,7 +19603,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ89">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR89">
         <v>2.03</v>
@@ -19931,7 +19934,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -20137,7 +20140,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20755,7 +20758,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -21373,7 +21376,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21991,7 +21994,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22403,7 +22406,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22481,7 +22484,7 @@
         <v>1.2</v>
       </c>
       <c r="AP103">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ103">
         <v>1.42</v>
@@ -22815,7 +22818,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -23021,7 +23024,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q106">
         <v>5.5</v>
@@ -23845,7 +23848,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -23926,7 +23929,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ110">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR110">
         <v>1.54</v>
@@ -25905,7 +25908,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -25983,7 +25986,7 @@
         <v>1.29</v>
       </c>
       <c r="AP120">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ120">
         <v>0.75</v>
@@ -26317,7 +26320,7 @@
         <v>167</v>
       </c>
       <c r="P122" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q122">
         <v>11</v>
@@ -26523,7 +26526,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26729,7 +26732,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -27141,7 +27144,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27347,7 +27350,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27553,7 +27556,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27759,7 +27762,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -28171,7 +28174,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28377,7 +28380,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28789,7 +28792,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -29076,7 +29079,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ135">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR135">
         <v>2.03</v>
@@ -29613,7 +29616,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29819,7 +29822,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -30231,7 +30234,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30437,7 +30440,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30643,7 +30646,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -30927,7 +30930,7 @@
         <v>2</v>
       </c>
       <c r="AP144">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ144">
         <v>1.82</v>
@@ -31055,7 +31058,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31261,7 +31264,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31467,7 +31470,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q147">
         <v>2.55</v>
@@ -31673,7 +31676,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31879,7 +31882,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32291,7 +32294,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32497,7 +32500,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32578,7 +32581,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ152">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR152">
         <v>1.17</v>
@@ -32703,7 +32706,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -33321,7 +33324,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33402,7 +33405,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ156">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR156">
         <v>1.41</v>
@@ -33527,7 +33530,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33733,7 +33736,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33939,7 +33942,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34351,7 +34354,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34557,7 +34560,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34763,7 +34766,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -35175,7 +35178,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35871,7 +35874,7 @@
         <v>0.33</v>
       </c>
       <c r="AP168">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ168">
         <v>0.5</v>
@@ -36205,7 +36208,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36823,7 +36826,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -37235,7 +37238,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37441,7 +37444,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -37522,7 +37525,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ176">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR176">
         <v>1.21</v>
@@ -37931,7 +37934,7 @@
         <v>0.8</v>
       </c>
       <c r="AP178">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ178">
         <v>0.75</v>
@@ -38059,7 +38062,7 @@
         <v>205</v>
       </c>
       <c r="P179" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q179">
         <v>8.5</v>
@@ -38265,7 +38268,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q180">
         <v>4.75</v>
@@ -38471,7 +38474,7 @@
         <v>207</v>
       </c>
       <c r="P181" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q181">
         <v>6.5</v>
@@ -38677,7 +38680,7 @@
         <v>167</v>
       </c>
       <c r="P182" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -39089,7 +39092,7 @@
         <v>208</v>
       </c>
       <c r="P184" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q184">
         <v>1.57</v>
@@ -39501,7 +39504,7 @@
         <v>209</v>
       </c>
       <c r="P186" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q186">
         <v>2.2</v>
@@ -40325,7 +40328,7 @@
         <v>184</v>
       </c>
       <c r="P190" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q190">
         <v>2.63</v>
@@ -40737,7 +40740,7 @@
         <v>212</v>
       </c>
       <c r="P192" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -40943,7 +40946,7 @@
         <v>213</v>
       </c>
       <c r="P193" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q193">
         <v>2.8</v>
@@ -41024,7 +41027,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ193">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR193">
         <v>1.34</v>
@@ -41355,7 +41358,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q195">
         <v>1.67</v>
@@ -41433,7 +41436,7 @@
         <v>1</v>
       </c>
       <c r="AP195">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ195">
         <v>1</v>
@@ -41767,7 +41770,7 @@
         <v>90</v>
       </c>
       <c r="P197" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q197">
         <v>7.5</v>
@@ -42179,7 +42182,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -43003,7 +43006,7 @@
         <v>218</v>
       </c>
       <c r="P203" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q203">
         <v>2.55</v>
@@ -43415,7 +43418,7 @@
         <v>219</v>
       </c>
       <c r="P205" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q205">
         <v>2.45</v>
@@ -43621,7 +43624,7 @@
         <v>220</v>
       </c>
       <c r="P206" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q206">
         <v>7</v>
@@ -44033,7 +44036,7 @@
         <v>166</v>
       </c>
       <c r="P208" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44445,7 +44448,7 @@
         <v>90</v>
       </c>
       <c r="P210" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q210">
         <v>5.5</v>
@@ -45269,7 +45272,7 @@
         <v>90</v>
       </c>
       <c r="P214" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q214">
         <v>3.1</v>
@@ -45475,7 +45478,7 @@
         <v>224</v>
       </c>
       <c r="P215" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q215">
         <v>4.33</v>
@@ -45631,6 +45634,212 @@
         <v>2.9</v>
       </c>
       <c r="BP215">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7574775</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45719.71875</v>
+      </c>
+      <c r="F216">
+        <v>24</v>
+      </c>
+      <c r="G216" t="s">
+        <v>70</v>
+      </c>
+      <c r="H216" t="s">
+        <v>74</v>
+      </c>
+      <c r="I216">
+        <v>2</v>
+      </c>
+      <c r="J216">
+        <v>0</v>
+      </c>
+      <c r="K216">
+        <v>2</v>
+      </c>
+      <c r="L216">
+        <v>3</v>
+      </c>
+      <c r="M216">
+        <v>1</v>
+      </c>
+      <c r="N216">
+        <v>4</v>
+      </c>
+      <c r="O216" t="s">
+        <v>225</v>
+      </c>
+      <c r="P216" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q216">
+        <v>1.62</v>
+      </c>
+      <c r="R216">
+        <v>2.88</v>
+      </c>
+      <c r="S216">
+        <v>9.5</v>
+      </c>
+      <c r="T216">
+        <v>1.25</v>
+      </c>
+      <c r="U216">
+        <v>3.75</v>
+      </c>
+      <c r="V216">
+        <v>2.1</v>
+      </c>
+      <c r="W216">
+        <v>1.67</v>
+      </c>
+      <c r="X216">
+        <v>4.5</v>
+      </c>
+      <c r="Y216">
+        <v>1.18</v>
+      </c>
+      <c r="Z216">
+        <v>1.18</v>
+      </c>
+      <c r="AA216">
+        <v>7</v>
+      </c>
+      <c r="AB216">
+        <v>12</v>
+      </c>
+      <c r="AC216">
+        <v>1.03</v>
+      </c>
+      <c r="AD216">
+        <v>11</v>
+      </c>
+      <c r="AE216">
+        <v>1.1</v>
+      </c>
+      <c r="AF216">
+        <v>6.5</v>
+      </c>
+      <c r="AG216">
+        <v>1.6</v>
+      </c>
+      <c r="AH216">
+        <v>2.34</v>
+      </c>
+      <c r="AI216">
+        <v>2</v>
+      </c>
+      <c r="AJ216">
+        <v>1.75</v>
+      </c>
+      <c r="AK216">
+        <v>1.03</v>
+      </c>
+      <c r="AL216">
+        <v>1.12</v>
+      </c>
+      <c r="AM216">
+        <v>4.2</v>
+      </c>
+      <c r="AN216">
+        <v>2.55</v>
+      </c>
+      <c r="AO216">
+        <v>1.18</v>
+      </c>
+      <c r="AP216">
+        <v>2.58</v>
+      </c>
+      <c r="AQ216">
+        <v>1.08</v>
+      </c>
+      <c r="AR216">
+        <v>2.12</v>
+      </c>
+      <c r="AS216">
+        <v>1.19</v>
+      </c>
+      <c r="AT216">
+        <v>3.31</v>
+      </c>
+      <c r="AU216">
+        <v>-1</v>
+      </c>
+      <c r="AV216">
+        <v>-1</v>
+      </c>
+      <c r="AW216">
+        <v>-1</v>
+      </c>
+      <c r="AX216">
+        <v>-1</v>
+      </c>
+      <c r="AY216">
+        <v>-1</v>
+      </c>
+      <c r="AZ216">
+        <v>-1</v>
+      </c>
+      <c r="BA216">
+        <v>-1</v>
+      </c>
+      <c r="BB216">
+        <v>-1</v>
+      </c>
+      <c r="BC216">
+        <v>-1</v>
+      </c>
+      <c r="BD216">
+        <v>1.13</v>
+      </c>
+      <c r="BE216">
+        <v>10</v>
+      </c>
+      <c r="BF216">
+        <v>6.25</v>
+      </c>
+      <c r="BG216">
+        <v>1.3</v>
+      </c>
+      <c r="BH216">
+        <v>3.05</v>
+      </c>
+      <c r="BI216">
+        <v>1.52</v>
+      </c>
+      <c r="BJ216">
+        <v>2.3</v>
+      </c>
+      <c r="BK216">
+        <v>1.83</v>
+      </c>
+      <c r="BL216">
+        <v>1.83</v>
+      </c>
+      <c r="BM216">
+        <v>2.28</v>
+      </c>
+      <c r="BN216">
+        <v>1.53</v>
+      </c>
+      <c r="BO216">
+        <v>2.9</v>
+      </c>
+      <c r="BP216">
         <v>1.34</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -45383,13 +45383,13 @@
         <v>7</v>
       </c>
       <c r="BA214">
+        <v>6</v>
+      </c>
+      <c r="BB214">
+        <v>1</v>
+      </c>
+      <c r="BC214">
         <v>7</v>
-      </c>
-      <c r="BB214">
-        <v>1</v>
-      </c>
-      <c r="BC214">
-        <v>8</v>
       </c>
       <c r="BD214">
         <v>1.81</v>
@@ -45777,31 +45777,31 @@
         <v>3.31</v>
       </c>
       <c r="AU216">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AV216">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AW216">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AX216">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AY216">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AZ216">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BA216">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB216">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC216">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BD216">
         <v>1.13</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="327">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -694,6 +694,18 @@
     <t>['5', '36', '90+6']</t>
   </si>
   <si>
+    <t>['69']</t>
+  </si>
+  <si>
+    <t>['50', '54']</t>
+  </si>
+  <si>
+    <t>['5', '23', '90+2']</t>
+  </si>
+  <si>
+    <t>['17']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -734,9 +746,6 @@
   </si>
   <si>
     <t>['61']</t>
-  </si>
-  <si>
-    <t>['17']</t>
   </si>
   <si>
     <t>['24', '73', '80']</t>
@@ -836,9 +845,6 @@
   </si>
   <si>
     <t>['12', '71']</t>
-  </si>
-  <si>
-    <t>['69']</t>
   </si>
   <si>
     <t>['68', '82']</t>
@@ -983,6 +989,12 @@
   </si>
   <si>
     <t>['10']</t>
+  </si>
+  <si>
+    <t>['89']</t>
+  </si>
+  <si>
+    <t>['85', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -1344,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP216"/>
+  <dimension ref="A1:BP221"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1806,7 +1818,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -1884,10 +1896,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ3">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2299,7 +2311,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ5">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2424,7 +2436,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2502,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ6">
         <v>1.42</v>
@@ -2836,7 +2848,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -3120,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ9">
         <v>0.58</v>
@@ -3454,7 +3466,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3535,7 +3547,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ11">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3660,7 +3672,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3947,7 +3959,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ13">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4072,7 +4084,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4356,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AQ15">
         <v>1.17</v>
@@ -4484,7 +4496,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4565,7 +4577,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ16">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4896,7 +4908,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -5102,7 +5114,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5180,7 +5192,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ19">
         <v>1.33</v>
@@ -5308,7 +5320,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5514,7 +5526,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -6210,7 +6222,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AQ24">
         <v>0.58</v>
@@ -6419,7 +6431,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ25">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR25">
         <v>0.7</v>
@@ -6622,10 +6634,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ26">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR26">
         <v>0.6</v>
@@ -6828,7 +6840,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -7034,7 +7046,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ28">
         <v>0.58</v>
@@ -7162,7 +7174,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7368,7 +7380,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7574,7 +7586,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -7652,7 +7664,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ31">
         <v>1.17</v>
@@ -8067,7 +8079,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ33">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR33">
         <v>2.25</v>
@@ -8273,7 +8285,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ34">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR34">
         <v>1.18</v>
@@ -8479,7 +8491,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR35">
         <v>1.11</v>
@@ -8604,7 +8616,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="Q36">
         <v>2.55</v>
@@ -9016,7 +9028,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9222,7 +9234,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9506,7 +9518,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ40">
         <v>0.67</v>
@@ -9634,7 +9646,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9715,7 +9727,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ41">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR41">
         <v>1.05</v>
@@ -9840,7 +9852,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -9918,7 +9930,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AQ42">
         <v>1.42</v>
@@ -10046,7 +10058,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10127,7 +10139,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ43">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR43">
         <v>2.13</v>
@@ -10330,10 +10342,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ44">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR44">
         <v>0.8100000000000001</v>
@@ -10458,7 +10470,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10536,7 +10548,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -10664,7 +10676,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10742,7 +10754,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ46">
         <v>0.75</v>
@@ -10870,7 +10882,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -11076,7 +11088,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11488,7 +11500,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11569,7 +11581,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ50">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR50">
         <v>1.4</v>
@@ -11900,7 +11912,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -12187,7 +12199,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ53">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR53">
         <v>1</v>
@@ -12518,7 +12530,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12724,7 +12736,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -12802,7 +12814,7 @@
         <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ56">
         <v>2.08</v>
@@ -13008,7 +13020,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ57">
         <v>0.58</v>
@@ -13136,7 +13148,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13342,7 +13354,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -13420,10 +13432,10 @@
         <v>0.67</v>
       </c>
       <c r="AP59">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AQ59">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR59">
         <v>2.26</v>
@@ -13629,7 +13641,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ60">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR60">
         <v>1.14</v>
@@ -13835,7 +13847,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ61">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR61">
         <v>2.38</v>
@@ -14038,7 +14050,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ62">
         <v>0.67</v>
@@ -14450,10 +14462,10 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ64">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR64">
         <v>1.27</v>
@@ -15814,7 +15826,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -16020,7 +16032,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16307,7 +16319,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ73">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR73">
         <v>1.21</v>
@@ -16432,7 +16444,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16513,7 +16525,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ74">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR74">
         <v>1.21</v>
@@ -16638,7 +16650,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16716,10 +16728,10 @@
         <v>0.75</v>
       </c>
       <c r="AP75">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ75">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR75">
         <v>0.89</v>
@@ -16844,7 +16856,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17050,7 +17062,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17334,10 +17346,10 @@
         <v>0.25</v>
       </c>
       <c r="AP78">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ78">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR78">
         <v>1.68</v>
@@ -17540,7 +17552,7 @@
         <v>0</v>
       </c>
       <c r="AP79">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AQ79">
         <v>0.67</v>
@@ -17668,7 +17680,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17746,7 +17758,7 @@
         <v>1.75</v>
       </c>
       <c r="AP80">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ80">
         <v>1</v>
@@ -17874,7 +17886,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -17952,10 +17964,10 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ81">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR81">
         <v>1.3</v>
@@ -18080,7 +18092,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18286,7 +18298,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18492,7 +18504,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18698,7 +18710,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18904,7 +18916,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -18982,7 +18994,7 @@
         <v>1.25</v>
       </c>
       <c r="AP86">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ86">
         <v>1.33</v>
@@ -19316,7 +19328,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19934,7 +19946,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -20015,7 +20027,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ91">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR91">
         <v>1.03</v>
@@ -20140,7 +20152,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20221,7 +20233,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ92">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR92">
         <v>1.25</v>
@@ -20424,7 +20436,7 @@
         <v>0.25</v>
       </c>
       <c r="AP93">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ93">
         <v>0.75</v>
@@ -20633,7 +20645,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ94">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR94">
         <v>1.13</v>
@@ -20758,7 +20770,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -21042,10 +21054,10 @@
         <v>0.4</v>
       </c>
       <c r="AP96">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ96">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR96">
         <v>1.15</v>
@@ -21376,7 +21388,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21454,7 +21466,7 @@
         <v>3</v>
       </c>
       <c r="AP98">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ98">
         <v>2.08</v>
@@ -21660,10 +21672,10 @@
         <v>2.25</v>
       </c>
       <c r="AP99">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AQ99">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR99">
         <v>2.36</v>
@@ -21994,7 +22006,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22406,7 +22418,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22690,7 +22702,7 @@
         <v>1.6</v>
       </c>
       <c r="AP104">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ104">
         <v>1.33</v>
@@ -22818,7 +22830,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -23024,7 +23036,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="Q106">
         <v>5.5</v>
@@ -23102,7 +23114,7 @@
         <v>2</v>
       </c>
       <c r="AP106">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ106">
         <v>2.17</v>
@@ -23311,7 +23323,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ107">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR107">
         <v>1.2</v>
@@ -23848,7 +23860,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -23926,7 +23938,7 @@
         <v>0.4</v>
       </c>
       <c r="AP110">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ110">
         <v>1.08</v>
@@ -24135,7 +24147,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ111">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR111">
         <v>1.27</v>
@@ -24338,7 +24350,7 @@
         <v>1.33</v>
       </c>
       <c r="AP112">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AQ112">
         <v>1</v>
@@ -24753,7 +24765,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ114">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR114">
         <v>1.09</v>
@@ -24959,7 +24971,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ115">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR115">
         <v>1.28</v>
@@ -25368,10 +25380,10 @@
         <v>0.67</v>
       </c>
       <c r="AP117">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ117">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR117">
         <v>1.23</v>
@@ -25577,7 +25589,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ118">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR118">
         <v>1.14</v>
@@ -25908,7 +25920,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26320,7 +26332,7 @@
         <v>167</v>
       </c>
       <c r="P122" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="Q122">
         <v>11</v>
@@ -26398,7 +26410,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ122">
         <v>1.82</v>
@@ -26526,7 +26538,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26604,7 +26616,7 @@
         <v>0.83</v>
       </c>
       <c r="AP123">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ123">
         <v>1.17</v>
@@ -26732,7 +26744,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -26810,7 +26822,7 @@
         <v>1.33</v>
       </c>
       <c r="AP124">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ124">
         <v>1.33</v>
@@ -27144,7 +27156,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27350,7 +27362,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27556,7 +27568,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27637,7 +27649,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ128">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR128">
         <v>1.24</v>
@@ -27762,7 +27774,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27843,7 +27855,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ129">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR129">
         <v>1.02</v>
@@ -28174,7 +28186,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28255,7 +28267,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ131">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR131">
         <v>1.14</v>
@@ -28380,7 +28392,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28792,7 +28804,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -28873,7 +28885,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ134">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR134">
         <v>1.28</v>
@@ -29076,7 +29088,7 @@
         <v>0.5</v>
       </c>
       <c r="AP135">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AQ135">
         <v>1.08</v>
@@ -29282,7 +29294,7 @@
         <v>0.43</v>
       </c>
       <c r="AP136">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ136">
         <v>0.67</v>
@@ -29491,7 +29503,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ137">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR137">
         <v>1.07</v>
@@ -29616,7 +29628,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29694,7 +29706,7 @@
         <v>0.14</v>
       </c>
       <c r="AP138">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ138">
         <v>0.58</v>
@@ -29822,7 +29834,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -29900,7 +29912,7 @@
         <v>0.75</v>
       </c>
       <c r="AP139">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ139">
         <v>0.58</v>
@@ -30234,7 +30246,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30440,7 +30452,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30521,7 +30533,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ142">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR142">
         <v>1.33</v>
@@ -30646,7 +30658,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -30724,7 +30736,7 @@
         <v>1.14</v>
       </c>
       <c r="AP143">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ143">
         <v>1.17</v>
@@ -31058,7 +31070,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31264,7 +31276,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31470,7 +31482,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q147">
         <v>2.55</v>
@@ -31676,7 +31688,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31754,7 +31766,7 @@
         <v>2.29</v>
       </c>
       <c r="AP148">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AQ148">
         <v>2.17</v>
@@ -31882,7 +31894,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -31963,7 +31975,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ149">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR149">
         <v>1.35</v>
@@ -32169,7 +32181,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ150">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR150">
         <v>1.34</v>
@@ -32294,7 +32306,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32500,7 +32512,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32578,7 +32590,7 @@
         <v>0.43</v>
       </c>
       <c r="AP152">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ152">
         <v>1.08</v>
@@ -32706,7 +32718,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -32993,7 +33005,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ154">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR154">
         <v>1.23</v>
@@ -33196,7 +33208,7 @@
         <v>1.25</v>
       </c>
       <c r="AP155">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AQ155">
         <v>1.33</v>
@@ -33324,7 +33336,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33530,7 +33542,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33736,7 +33748,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33817,7 +33829,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ158">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR158">
         <v>1.33</v>
@@ -33942,7 +33954,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34229,7 +34241,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ160">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR160">
         <v>1.14</v>
@@ -34354,7 +34366,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34432,7 +34444,7 @@
         <v>2.38</v>
       </c>
       <c r="AP161">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ161">
         <v>2.17</v>
@@ -34560,7 +34572,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34641,7 +34653,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ162">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR162">
         <v>1.23</v>
@@ -34766,7 +34778,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -35178,7 +35190,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35877,7 +35889,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ168">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR168">
         <v>2.03</v>
@@ -36080,7 +36092,7 @@
         <v>1.11</v>
       </c>
       <c r="AP169">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ169">
         <v>1</v>
@@ -36208,7 +36220,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36492,7 +36504,7 @@
         <v>1</v>
       </c>
       <c r="AP171">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ171">
         <v>0.75</v>
@@ -36698,10 +36710,10 @@
         <v>0.67</v>
       </c>
       <c r="AP172">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ172">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR172">
         <v>1.24</v>
@@ -36826,7 +36838,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -37238,7 +37250,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37319,7 +37331,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ175">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR175">
         <v>1.25</v>
@@ -37444,7 +37456,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -37937,7 +37949,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ178">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR178">
         <v>2.03</v>
@@ -38062,7 +38074,7 @@
         <v>205</v>
       </c>
       <c r="P179" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q179">
         <v>8.5</v>
@@ -38140,7 +38152,7 @@
         <v>1.56</v>
       </c>
       <c r="AP179">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ179">
         <v>1.82</v>
@@ -38268,7 +38280,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q180">
         <v>4.75</v>
@@ -38474,7 +38486,7 @@
         <v>207</v>
       </c>
       <c r="P181" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q181">
         <v>6.5</v>
@@ -38555,7 +38567,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ181">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR181">
         <v>1.3</v>
@@ -38680,7 +38692,7 @@
         <v>167</v>
       </c>
       <c r="P182" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -38964,7 +38976,7 @@
         <v>1.44</v>
       </c>
       <c r="AP183">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ183">
         <v>1.42</v>
@@ -39092,7 +39104,7 @@
         <v>208</v>
       </c>
       <c r="P184" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q184">
         <v>1.57</v>
@@ -39170,7 +39182,7 @@
         <v>0.7</v>
       </c>
       <c r="AP184">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AQ184">
         <v>0.58</v>
@@ -39504,7 +39516,7 @@
         <v>209</v>
       </c>
       <c r="P186" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q186">
         <v>2.2</v>
@@ -39582,7 +39594,7 @@
         <v>0.9</v>
       </c>
       <c r="AP186">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ186">
         <v>0.75</v>
@@ -39791,7 +39803,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ187">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR187">
         <v>1.2</v>
@@ -39994,10 +40006,10 @@
         <v>0.6</v>
       </c>
       <c r="AP188">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ188">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR188">
         <v>1.68</v>
@@ -40328,7 +40340,7 @@
         <v>184</v>
       </c>
       <c r="P190" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q190">
         <v>2.63</v>
@@ -40740,7 +40752,7 @@
         <v>212</v>
       </c>
       <c r="P192" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -40946,7 +40958,7 @@
         <v>213</v>
       </c>
       <c r="P193" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q193">
         <v>2.8</v>
@@ -41358,7 +41370,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q195">
         <v>1.67</v>
@@ -41439,7 +41451,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ195">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR195">
         <v>2.07</v>
@@ -41770,7 +41782,7 @@
         <v>90</v>
       </c>
       <c r="P197" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q197">
         <v>7.5</v>
@@ -41851,7 +41863,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ197">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR197">
         <v>1.32</v>
@@ -42182,7 +42194,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42466,10 +42478,10 @@
         <v>0.55</v>
       </c>
       <c r="AP200">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ200">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR200">
         <v>1.68</v>
@@ -42675,7 +42687,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ201">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR201">
         <v>1.24</v>
@@ -42878,7 +42890,7 @@
         <v>0.82</v>
       </c>
       <c r="AP202">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AQ202">
         <v>0.75</v>
@@ -43006,7 +43018,7 @@
         <v>218</v>
       </c>
       <c r="P203" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q203">
         <v>2.55</v>
@@ -43084,7 +43096,7 @@
         <v>0.73</v>
       </c>
       <c r="AP203">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ203">
         <v>0.67</v>
@@ -43290,7 +43302,7 @@
         <v>1.6</v>
       </c>
       <c r="AP204">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ204">
         <v>1.42</v>
@@ -43418,7 +43430,7 @@
         <v>219</v>
       </c>
       <c r="P205" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q205">
         <v>2.45</v>
@@ -43499,7 +43511,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ205">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR205">
         <v>1.23</v>
@@ -43624,7 +43636,7 @@
         <v>220</v>
       </c>
       <c r="P206" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q206">
         <v>7</v>
@@ -43702,7 +43714,7 @@
         <v>2.18</v>
       </c>
       <c r="AP206">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ206">
         <v>2.08</v>
@@ -44036,7 +44048,7 @@
         <v>166</v>
       </c>
       <c r="P208" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44448,7 +44460,7 @@
         <v>90</v>
       </c>
       <c r="P210" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q210">
         <v>5.5</v>
@@ -44529,7 +44541,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ210">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR210">
         <v>1.22</v>
@@ -45272,7 +45284,7 @@
         <v>90</v>
       </c>
       <c r="P214" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q214">
         <v>3.1</v>
@@ -45478,7 +45490,7 @@
         <v>224</v>
       </c>
       <c r="P215" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q215">
         <v>4.33</v>
@@ -45841,6 +45853,1036 @@
       </c>
       <c r="BP216">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7574780</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45723.71875</v>
+      </c>
+      <c r="F217">
+        <v>25</v>
+      </c>
+      <c r="G217" t="s">
+        <v>87</v>
+      </c>
+      <c r="H217" t="s">
+        <v>80</v>
+      </c>
+      <c r="I217">
+        <v>0</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>0</v>
+      </c>
+      <c r="L217">
+        <v>1</v>
+      </c>
+      <c r="M217">
+        <v>1</v>
+      </c>
+      <c r="N217">
+        <v>2</v>
+      </c>
+      <c r="O217" t="s">
+        <v>226</v>
+      </c>
+      <c r="P217" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q217">
+        <v>3.3</v>
+      </c>
+      <c r="R217">
+        <v>1.9</v>
+      </c>
+      <c r="S217">
+        <v>3.4</v>
+      </c>
+      <c r="T217">
+        <v>1.5</v>
+      </c>
+      <c r="U217">
+        <v>2.4</v>
+      </c>
+      <c r="V217">
+        <v>3.2</v>
+      </c>
+      <c r="W217">
+        <v>1.31</v>
+      </c>
+      <c r="X217">
+        <v>8.75</v>
+      </c>
+      <c r="Y217">
+        <v>1.06</v>
+      </c>
+      <c r="Z217">
+        <v>2.65</v>
+      </c>
+      <c r="AA217">
+        <v>2.9</v>
+      </c>
+      <c r="AB217">
+        <v>2.8</v>
+      </c>
+      <c r="AC217">
+        <v>1.1</v>
+      </c>
+      <c r="AD217">
+        <v>6.5</v>
+      </c>
+      <c r="AE217">
+        <v>1.5</v>
+      </c>
+      <c r="AF217">
+        <v>2.4</v>
+      </c>
+      <c r="AG217">
+        <v>2.25</v>
+      </c>
+      <c r="AH217">
+        <v>1.6</v>
+      </c>
+      <c r="AI217">
+        <v>1.93</v>
+      </c>
+      <c r="AJ217">
+        <v>1.77</v>
+      </c>
+      <c r="AK217">
+        <v>1.41</v>
+      </c>
+      <c r="AL217">
+        <v>1.38</v>
+      </c>
+      <c r="AM217">
+        <v>1.44</v>
+      </c>
+      <c r="AN217">
+        <v>1.25</v>
+      </c>
+      <c r="AO217">
+        <v>0.5</v>
+      </c>
+      <c r="AP217">
+        <v>1.23</v>
+      </c>
+      <c r="AQ217">
+        <v>0.54</v>
+      </c>
+      <c r="AR217">
+        <v>1.16</v>
+      </c>
+      <c r="AS217">
+        <v>0.91</v>
+      </c>
+      <c r="AT217">
+        <v>2.07</v>
+      </c>
+      <c r="AU217">
+        <v>3</v>
+      </c>
+      <c r="AV217">
+        <v>3</v>
+      </c>
+      <c r="AW217">
+        <v>4</v>
+      </c>
+      <c r="AX217">
+        <v>8</v>
+      </c>
+      <c r="AY217">
+        <v>8</v>
+      </c>
+      <c r="AZ217">
+        <v>13</v>
+      </c>
+      <c r="BA217">
+        <v>7</v>
+      </c>
+      <c r="BB217">
+        <v>7</v>
+      </c>
+      <c r="BC217">
+        <v>14</v>
+      </c>
+      <c r="BD217">
+        <v>0</v>
+      </c>
+      <c r="BE217">
+        <v>0</v>
+      </c>
+      <c r="BF217">
+        <v>0</v>
+      </c>
+      <c r="BG217">
+        <v>0</v>
+      </c>
+      <c r="BH217">
+        <v>0</v>
+      </c>
+      <c r="BI217">
+        <v>0</v>
+      </c>
+      <c r="BJ217">
+        <v>0</v>
+      </c>
+      <c r="BK217">
+        <v>0</v>
+      </c>
+      <c r="BL217">
+        <v>0</v>
+      </c>
+      <c r="BM217">
+        <v>2.23</v>
+      </c>
+      <c r="BN217">
+        <v>1.56</v>
+      </c>
+      <c r="BO217">
+        <v>0</v>
+      </c>
+      <c r="BP217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7574786</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45724.52083333334</v>
+      </c>
+      <c r="F218">
+        <v>25</v>
+      </c>
+      <c r="G218" t="s">
+        <v>71</v>
+      </c>
+      <c r="H218" t="s">
+        <v>78</v>
+      </c>
+      <c r="I218">
+        <v>0</v>
+      </c>
+      <c r="J218">
+        <v>0</v>
+      </c>
+      <c r="K218">
+        <v>0</v>
+      </c>
+      <c r="L218">
+        <v>0</v>
+      </c>
+      <c r="M218">
+        <v>1</v>
+      </c>
+      <c r="N218">
+        <v>1</v>
+      </c>
+      <c r="O218" t="s">
+        <v>90</v>
+      </c>
+      <c r="P218" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q218">
+        <v>3.4</v>
+      </c>
+      <c r="R218">
+        <v>1.95</v>
+      </c>
+      <c r="S218">
+        <v>3.2</v>
+      </c>
+      <c r="T218">
+        <v>1.47</v>
+      </c>
+      <c r="U218">
+        <v>2.45</v>
+      </c>
+      <c r="V218">
+        <v>3.2</v>
+      </c>
+      <c r="W218">
+        <v>1.3</v>
+      </c>
+      <c r="X218">
+        <v>8.75</v>
+      </c>
+      <c r="Y218">
+        <v>1.06</v>
+      </c>
+      <c r="Z218">
+        <v>2.9</v>
+      </c>
+      <c r="AA218">
+        <v>3</v>
+      </c>
+      <c r="AB218">
+        <v>2.5</v>
+      </c>
+      <c r="AC218">
+        <v>1.09</v>
+      </c>
+      <c r="AD218">
+        <v>7</v>
+      </c>
+      <c r="AE218">
+        <v>1.42</v>
+      </c>
+      <c r="AF218">
+        <v>2.8</v>
+      </c>
+      <c r="AG218">
+        <v>2.25</v>
+      </c>
+      <c r="AH218">
+        <v>1.6</v>
+      </c>
+      <c r="AI218">
+        <v>1.93</v>
+      </c>
+      <c r="AJ218">
+        <v>1.75</v>
+      </c>
+      <c r="AK218">
+        <v>1.49</v>
+      </c>
+      <c r="AL218">
+        <v>1.34</v>
+      </c>
+      <c r="AM218">
+        <v>1.41</v>
+      </c>
+      <c r="AN218">
+        <v>1.17</v>
+      </c>
+      <c r="AO218">
+        <v>1</v>
+      </c>
+      <c r="AP218">
+        <v>1.08</v>
+      </c>
+      <c r="AQ218">
+        <v>1.15</v>
+      </c>
+      <c r="AR218">
+        <v>1.22</v>
+      </c>
+      <c r="AS218">
+        <v>1.3</v>
+      </c>
+      <c r="AT218">
+        <v>2.52</v>
+      </c>
+      <c r="AU218">
+        <v>0</v>
+      </c>
+      <c r="AV218">
+        <v>6</v>
+      </c>
+      <c r="AW218">
+        <v>10</v>
+      </c>
+      <c r="AX218">
+        <v>14</v>
+      </c>
+      <c r="AY218">
+        <v>11</v>
+      </c>
+      <c r="AZ218">
+        <v>22</v>
+      </c>
+      <c r="BA218">
+        <v>1</v>
+      </c>
+      <c r="BB218">
+        <v>7</v>
+      </c>
+      <c r="BC218">
+        <v>8</v>
+      </c>
+      <c r="BD218">
+        <v>2.07</v>
+      </c>
+      <c r="BE218">
+        <v>6.5</v>
+      </c>
+      <c r="BF218">
+        <v>1.92</v>
+      </c>
+      <c r="BG218">
+        <v>1.29</v>
+      </c>
+      <c r="BH218">
+        <v>3.15</v>
+      </c>
+      <c r="BI218">
+        <v>1.49</v>
+      </c>
+      <c r="BJ218">
+        <v>2.38</v>
+      </c>
+      <c r="BK218">
+        <v>1.8</v>
+      </c>
+      <c r="BL218">
+        <v>1.86</v>
+      </c>
+      <c r="BM218">
+        <v>2.25</v>
+      </c>
+      <c r="BN218">
+        <v>1.54</v>
+      </c>
+      <c r="BO218">
+        <v>2.9</v>
+      </c>
+      <c r="BP218">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7574779</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45724.625</v>
+      </c>
+      <c r="F219">
+        <v>25</v>
+      </c>
+      <c r="G219" t="s">
+        <v>74</v>
+      </c>
+      <c r="H219" t="s">
+        <v>76</v>
+      </c>
+      <c r="I219">
+        <v>0</v>
+      </c>
+      <c r="J219">
+        <v>0</v>
+      </c>
+      <c r="K219">
+        <v>0</v>
+      </c>
+      <c r="L219">
+        <v>2</v>
+      </c>
+      <c r="M219">
+        <v>2</v>
+      </c>
+      <c r="N219">
+        <v>4</v>
+      </c>
+      <c r="O219" t="s">
+        <v>227</v>
+      </c>
+      <c r="P219" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q219">
+        <v>2.88</v>
+      </c>
+      <c r="R219">
+        <v>2.05</v>
+      </c>
+      <c r="S219">
+        <v>4.33</v>
+      </c>
+      <c r="T219">
+        <v>1.5</v>
+      </c>
+      <c r="U219">
+        <v>2.5</v>
+      </c>
+      <c r="V219">
+        <v>3.4</v>
+      </c>
+      <c r="W219">
+        <v>1.3</v>
+      </c>
+      <c r="X219">
+        <v>10</v>
+      </c>
+      <c r="Y219">
+        <v>1.06</v>
+      </c>
+      <c r="Z219">
+        <v>2.05</v>
+      </c>
+      <c r="AA219">
+        <v>3.1</v>
+      </c>
+      <c r="AB219">
+        <v>3.6</v>
+      </c>
+      <c r="AC219">
+        <v>0</v>
+      </c>
+      <c r="AD219">
+        <v>0</v>
+      </c>
+      <c r="AE219">
+        <v>1.5</v>
+      </c>
+      <c r="AF219">
+        <v>2.45</v>
+      </c>
+      <c r="AG219">
+        <v>1.91</v>
+      </c>
+      <c r="AH219">
+        <v>1.8</v>
+      </c>
+      <c r="AI219">
+        <v>1.95</v>
+      </c>
+      <c r="AJ219">
+        <v>1.8</v>
+      </c>
+      <c r="AK219">
+        <v>0</v>
+      </c>
+      <c r="AL219">
+        <v>0</v>
+      </c>
+      <c r="AM219">
+        <v>0</v>
+      </c>
+      <c r="AN219">
+        <v>1.75</v>
+      </c>
+      <c r="AO219">
+        <v>0.75</v>
+      </c>
+      <c r="AP219">
+        <v>1.69</v>
+      </c>
+      <c r="AQ219">
+        <v>0.77</v>
+      </c>
+      <c r="AR219">
+        <v>1.24</v>
+      </c>
+      <c r="AS219">
+        <v>1.07</v>
+      </c>
+      <c r="AT219">
+        <v>2.31</v>
+      </c>
+      <c r="AU219">
+        <v>4</v>
+      </c>
+      <c r="AV219">
+        <v>6</v>
+      </c>
+      <c r="AW219">
+        <v>9</v>
+      </c>
+      <c r="AX219">
+        <v>10</v>
+      </c>
+      <c r="AY219">
+        <v>15</v>
+      </c>
+      <c r="AZ219">
+        <v>18</v>
+      </c>
+      <c r="BA219">
+        <v>4</v>
+      </c>
+      <c r="BB219">
+        <v>7</v>
+      </c>
+      <c r="BC219">
+        <v>11</v>
+      </c>
+      <c r="BD219">
+        <v>0</v>
+      </c>
+      <c r="BE219">
+        <v>0</v>
+      </c>
+      <c r="BF219">
+        <v>0</v>
+      </c>
+      <c r="BG219">
+        <v>0</v>
+      </c>
+      <c r="BH219">
+        <v>0</v>
+      </c>
+      <c r="BI219">
+        <v>0</v>
+      </c>
+      <c r="BJ219">
+        <v>0</v>
+      </c>
+      <c r="BK219">
+        <v>0</v>
+      </c>
+      <c r="BL219">
+        <v>0</v>
+      </c>
+      <c r="BM219">
+        <v>0</v>
+      </c>
+      <c r="BN219">
+        <v>0</v>
+      </c>
+      <c r="BO219">
+        <v>0</v>
+      </c>
+      <c r="BP219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7574785</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45724.625</v>
+      </c>
+      <c r="F220">
+        <v>25</v>
+      </c>
+      <c r="G220" t="s">
+        <v>83</v>
+      </c>
+      <c r="H220" t="s">
+        <v>82</v>
+      </c>
+      <c r="I220">
+        <v>2</v>
+      </c>
+      <c r="J220">
+        <v>0</v>
+      </c>
+      <c r="K220">
+        <v>2</v>
+      </c>
+      <c r="L220">
+        <v>3</v>
+      </c>
+      <c r="M220">
+        <v>0</v>
+      </c>
+      <c r="N220">
+        <v>3</v>
+      </c>
+      <c r="O220" t="s">
+        <v>228</v>
+      </c>
+      <c r="P220" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q220">
+        <v>1.62</v>
+      </c>
+      <c r="R220">
+        <v>2.65</v>
+      </c>
+      <c r="S220">
+        <v>8</v>
+      </c>
+      <c r="T220">
+        <v>1.25</v>
+      </c>
+      <c r="U220">
+        <v>3.55</v>
+      </c>
+      <c r="V220">
+        <v>2.25</v>
+      </c>
+      <c r="W220">
+        <v>1.57</v>
+      </c>
+      <c r="X220">
+        <v>5</v>
+      </c>
+      <c r="Y220">
+        <v>1.14</v>
+      </c>
+      <c r="Z220">
+        <v>1.16</v>
+      </c>
+      <c r="AA220">
+        <v>7</v>
+      </c>
+      <c r="AB220">
+        <v>12</v>
+      </c>
+      <c r="AC220">
+        <v>1.03</v>
+      </c>
+      <c r="AD220">
+        <v>11</v>
+      </c>
+      <c r="AE220">
+        <v>1.2</v>
+      </c>
+      <c r="AF220">
+        <v>4.5</v>
+      </c>
+      <c r="AG220">
+        <v>1.49</v>
+      </c>
+      <c r="AH220">
+        <v>2.51</v>
+      </c>
+      <c r="AI220">
+        <v>2.15</v>
+      </c>
+      <c r="AJ220">
+        <v>1.62</v>
+      </c>
+      <c r="AK220">
+        <v>1.05</v>
+      </c>
+      <c r="AL220">
+        <v>1.12</v>
+      </c>
+      <c r="AM220">
+        <v>3.75</v>
+      </c>
+      <c r="AN220">
+        <v>2.75</v>
+      </c>
+      <c r="AO220">
+        <v>0.5</v>
+      </c>
+      <c r="AP220">
+        <v>2.77</v>
+      </c>
+      <c r="AQ220">
+        <v>0.46</v>
+      </c>
+      <c r="AR220">
+        <v>2.13</v>
+      </c>
+      <c r="AS220">
+        <v>1.25</v>
+      </c>
+      <c r="AT220">
+        <v>3.38</v>
+      </c>
+      <c r="AU220">
+        <v>14</v>
+      </c>
+      <c r="AV220">
+        <v>6</v>
+      </c>
+      <c r="AW220">
+        <v>7</v>
+      </c>
+      <c r="AX220">
+        <v>8</v>
+      </c>
+      <c r="AY220">
+        <v>23</v>
+      </c>
+      <c r="AZ220">
+        <v>17</v>
+      </c>
+      <c r="BA220">
+        <v>5</v>
+      </c>
+      <c r="BB220">
+        <v>3</v>
+      </c>
+      <c r="BC220">
+        <v>8</v>
+      </c>
+      <c r="BD220">
+        <v>0</v>
+      </c>
+      <c r="BE220">
+        <v>0</v>
+      </c>
+      <c r="BF220">
+        <v>0</v>
+      </c>
+      <c r="BG220">
+        <v>0</v>
+      </c>
+      <c r="BH220">
+        <v>0</v>
+      </c>
+      <c r="BI220">
+        <v>0</v>
+      </c>
+      <c r="BJ220">
+        <v>0</v>
+      </c>
+      <c r="BK220">
+        <v>0</v>
+      </c>
+      <c r="BL220">
+        <v>0</v>
+      </c>
+      <c r="BM220">
+        <v>1.95</v>
+      </c>
+      <c r="BN220">
+        <v>1.73</v>
+      </c>
+      <c r="BO220">
+        <v>2.43</v>
+      </c>
+      <c r="BP220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7574787</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45724.72916666666</v>
+      </c>
+      <c r="F221">
+        <v>25</v>
+      </c>
+      <c r="G221" t="s">
+        <v>77</v>
+      </c>
+      <c r="H221" t="s">
+        <v>73</v>
+      </c>
+      <c r="I221">
+        <v>1</v>
+      </c>
+      <c r="J221">
+        <v>0</v>
+      </c>
+      <c r="K221">
+        <v>1</v>
+      </c>
+      <c r="L221">
+        <v>1</v>
+      </c>
+      <c r="M221">
+        <v>0</v>
+      </c>
+      <c r="N221">
+        <v>1</v>
+      </c>
+      <c r="O221" t="s">
+        <v>229</v>
+      </c>
+      <c r="P221" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q221">
+        <v>3.7</v>
+      </c>
+      <c r="R221">
+        <v>2.05</v>
+      </c>
+      <c r="S221">
+        <v>2.7</v>
+      </c>
+      <c r="T221">
+        <v>1.4</v>
+      </c>
+      <c r="U221">
+        <v>2.75</v>
+      </c>
+      <c r="V221">
+        <v>2.8</v>
+      </c>
+      <c r="W221">
+        <v>1.38</v>
+      </c>
+      <c r="X221">
+        <v>7.25</v>
+      </c>
+      <c r="Y221">
+        <v>1.08</v>
+      </c>
+      <c r="Z221">
+        <v>3.3</v>
+      </c>
+      <c r="AA221">
+        <v>3.25</v>
+      </c>
+      <c r="AB221">
+        <v>2.15</v>
+      </c>
+      <c r="AC221">
+        <v>1.06</v>
+      </c>
+      <c r="AD221">
+        <v>8.5</v>
+      </c>
+      <c r="AE221">
+        <v>1.33</v>
+      </c>
+      <c r="AF221">
+        <v>3.25</v>
+      </c>
+      <c r="AG221">
+        <v>1.95</v>
+      </c>
+      <c r="AH221">
+        <v>1.75</v>
+      </c>
+      <c r="AI221">
+        <v>1.77</v>
+      </c>
+      <c r="AJ221">
+        <v>1.93</v>
+      </c>
+      <c r="AK221">
+        <v>1.66</v>
+      </c>
+      <c r="AL221">
+        <v>1.3</v>
+      </c>
+      <c r="AM221">
+        <v>1.33</v>
+      </c>
+      <c r="AN221">
+        <v>1.75</v>
+      </c>
+      <c r="AO221">
+        <v>1.67</v>
+      </c>
+      <c r="AP221">
+        <v>1.85</v>
+      </c>
+      <c r="AQ221">
+        <v>1.54</v>
+      </c>
+      <c r="AR221">
+        <v>1.72</v>
+      </c>
+      <c r="AS221">
+        <v>1.44</v>
+      </c>
+      <c r="AT221">
+        <v>3.16</v>
+      </c>
+      <c r="AU221">
+        <v>5</v>
+      </c>
+      <c r="AV221">
+        <v>4</v>
+      </c>
+      <c r="AW221">
+        <v>4</v>
+      </c>
+      <c r="AX221">
+        <v>3</v>
+      </c>
+      <c r="AY221">
+        <v>9</v>
+      </c>
+      <c r="AZ221">
+        <v>8</v>
+      </c>
+      <c r="BA221">
+        <v>7</v>
+      </c>
+      <c r="BB221">
+        <v>3</v>
+      </c>
+      <c r="BC221">
+        <v>10</v>
+      </c>
+      <c r="BD221">
+        <v>2.23</v>
+      </c>
+      <c r="BE221">
+        <v>6.4</v>
+      </c>
+      <c r="BF221">
+        <v>1.79</v>
+      </c>
+      <c r="BG221">
+        <v>1.38</v>
+      </c>
+      <c r="BH221">
+        <v>2.7</v>
+      </c>
+      <c r="BI221">
+        <v>1.64</v>
+      </c>
+      <c r="BJ221">
+        <v>2.06</v>
+      </c>
+      <c r="BK221">
+        <v>2.04</v>
+      </c>
+      <c r="BL221">
+        <v>1.66</v>
+      </c>
+      <c r="BM221">
+        <v>2.6</v>
+      </c>
+      <c r="BN221">
+        <v>1.41</v>
+      </c>
+      <c r="BO221">
+        <v>3.4</v>
+      </c>
+      <c r="BP221">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="330">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -706,6 +706,9 @@
     <t>['17']</t>
   </si>
   <si>
+    <t>['45']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -895,9 +898,6 @@
     <t>['2', '14', '57', '90+5']</t>
   </si>
   <si>
-    <t>['45']</t>
-  </si>
-  <si>
     <t>['17', '40']</t>
   </si>
   <si>
@@ -995,6 +995,15 @@
   </si>
   <si>
     <t>['85', '90+3']</t>
+  </si>
+  <si>
+    <t>['87']</t>
+  </si>
+  <si>
+    <t>['12', '34', '77']</t>
+  </si>
+  <si>
+    <t>['50', '76']</t>
   </si>
 </sst>
 </file>
@@ -1356,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP221"/>
+  <dimension ref="A1:BP224"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1818,7 +1827,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2102,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ4">
         <v>0.75</v>
@@ -2436,7 +2445,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2848,7 +2857,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -2929,7 +2938,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ8">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3341,7 +3350,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3466,7 +3475,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3544,7 +3553,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ11">
         <v>1.54</v>
@@ -3672,7 +3681,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4084,7 +4093,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4165,7 +4174,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ14">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4496,7 +4505,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4908,7 +4917,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4986,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AQ18">
         <v>2.17</v>
@@ -5114,7 +5123,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5320,7 +5329,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5401,7 +5410,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ20">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR20">
         <v>1.56</v>
@@ -5526,7 +5535,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -5604,7 +5613,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ21">
         <v>1.42</v>
@@ -6843,7 +6852,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR27">
         <v>1.62</v>
@@ -7049,7 +7058,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ28">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR28">
         <v>1.72</v>
@@ -7174,7 +7183,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7380,7 +7389,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7458,7 +7467,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ30">
         <v>0.75</v>
@@ -7586,7 +7595,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -7870,7 +7879,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AQ32">
         <v>1.08</v>
@@ -9028,7 +9037,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9109,7 +9118,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ38">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR38">
         <v>0.93</v>
@@ -9234,7 +9243,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9312,10 +9321,10 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ39">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR39">
         <v>1.27</v>
@@ -9646,7 +9655,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9852,7 +9861,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -10058,7 +10067,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10470,7 +10479,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10551,7 +10560,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ45">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR45">
         <v>1.78</v>
@@ -10676,7 +10685,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10882,7 +10891,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -11088,7 +11097,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11372,7 +11381,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ49">
         <v>0.58</v>
@@ -11500,7 +11509,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11912,7 +11921,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -12530,7 +12539,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12608,7 +12617,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AQ55">
         <v>1.82</v>
@@ -12736,7 +12745,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -12817,7 +12826,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ56">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR56">
         <v>0.98</v>
@@ -13023,7 +13032,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ57">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR57">
         <v>1.33</v>
@@ -13148,7 +13157,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13226,10 +13235,10 @@
         <v>2</v>
       </c>
       <c r="AP58">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR58">
         <v>1.27</v>
@@ -13354,7 +13363,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -14256,7 +14265,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ63">
         <v>0.75</v>
@@ -15826,7 +15835,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -16032,7 +16041,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16316,7 +16325,7 @@
         <v>0.5</v>
       </c>
       <c r="AP73">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ73">
         <v>0.46</v>
@@ -16444,7 +16453,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16522,7 +16531,7 @@
         <v>0.5</v>
       </c>
       <c r="AP74">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ74">
         <v>0.54</v>
@@ -16650,7 +16659,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16856,7 +16865,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16934,10 +16943,10 @@
         <v>0.75</v>
       </c>
       <c r="AP76">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AQ76">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR76">
         <v>1.15</v>
@@ -17062,7 +17071,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17143,7 +17152,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ77">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR77">
         <v>1.24</v>
@@ -17680,7 +17689,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17761,7 +17770,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ80">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR80">
         <v>1.2</v>
@@ -17886,7 +17895,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -18092,7 +18101,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18298,7 +18307,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18504,7 +18513,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18710,7 +18719,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18916,7 +18925,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19203,7 +19212,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ87">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR87">
         <v>1.16</v>
@@ -19328,7 +19337,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19946,7 +19955,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -20152,7 +20161,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20230,7 +20239,7 @@
         <v>0.2</v>
       </c>
       <c r="AP92">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ92">
         <v>0.77</v>
@@ -20770,7 +20779,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -20848,7 +20857,7 @@
         <v>0</v>
       </c>
       <c r="AP95">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AQ95">
         <v>0.67</v>
@@ -21260,10 +21269,10 @@
         <v>1.6</v>
       </c>
       <c r="AP97">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ97">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR97">
         <v>1.23</v>
@@ -21388,7 +21397,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21469,7 +21478,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ98">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR98">
         <v>1.75</v>
@@ -22006,7 +22015,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22087,7 +22096,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ101">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR101">
         <v>1.42</v>
@@ -22418,7 +22427,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22830,7 +22839,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -23735,7 +23744,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ109">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR109">
         <v>1.17</v>
@@ -23860,7 +23869,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -24353,7 +24362,7 @@
         <v>2.77</v>
       </c>
       <c r="AQ112">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR112">
         <v>2.24</v>
@@ -24556,7 +24565,7 @@
         <v>0.5</v>
       </c>
       <c r="AP113">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ113">
         <v>0.67</v>
@@ -24968,7 +24977,7 @@
         <v>0.33</v>
       </c>
       <c r="AP115">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AQ115">
         <v>0.77</v>
@@ -25174,7 +25183,7 @@
         <v>0.4</v>
       </c>
       <c r="AP116">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ116">
         <v>0.75</v>
@@ -25795,7 +25804,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ119">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR119">
         <v>1.33</v>
@@ -25920,7 +25929,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26538,7 +26547,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26744,7 +26753,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -27156,7 +27165,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27237,7 +27246,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ126">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR126">
         <v>1.4</v>
@@ -27362,7 +27371,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27568,7 +27577,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27646,7 +27655,7 @@
         <v>0.57</v>
       </c>
       <c r="AP128">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ128">
         <v>1.15</v>
@@ -27774,7 +27783,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -28058,7 +28067,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AQ130">
         <v>0.75</v>
@@ -28186,7 +28195,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28392,7 +28401,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28470,7 +28479,7 @@
         <v>2.17</v>
       </c>
       <c r="AP132">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ132">
         <v>2.17</v>
@@ -28679,7 +28688,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ133">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR133">
         <v>1.29</v>
@@ -28804,7 +28813,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -29628,7 +29637,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29834,7 +29843,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -29915,7 +29924,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ139">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR139">
         <v>1.09</v>
@@ -30246,7 +30255,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30327,7 +30336,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ141">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR141">
         <v>1.17</v>
@@ -30452,7 +30461,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30658,7 +30667,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -31070,7 +31079,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31276,7 +31285,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31357,7 +31366,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ146">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR146">
         <v>1.3</v>
@@ -31482,7 +31491,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>293</v>
+        <v>230</v>
       </c>
       <c r="Q147">
         <v>2.55</v>
@@ -31972,7 +31981,7 @@
         <v>0.5</v>
       </c>
       <c r="AP149">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AQ149">
         <v>1.15</v>
@@ -32178,7 +32187,7 @@
         <v>0.75</v>
       </c>
       <c r="AP150">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ150">
         <v>0.77</v>
@@ -32306,7 +32315,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32384,7 +32393,7 @@
         <v>1.29</v>
       </c>
       <c r="AP151">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ151">
         <v>1.33</v>
@@ -33414,7 +33423,7 @@
         <v>0.75</v>
       </c>
       <c r="AP156">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ156">
         <v>1.08</v>
@@ -33623,7 +33632,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ157">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR157">
         <v>1.39</v>
@@ -34856,7 +34865,7 @@
         <v>1.38</v>
       </c>
       <c r="AP163">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AQ163">
         <v>1.17</v>
@@ -35065,7 +35074,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ164">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR164">
         <v>1.09</v>
@@ -35680,7 +35689,7 @@
         <v>1.75</v>
       </c>
       <c r="AP167">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ167">
         <v>1.82</v>
@@ -36095,7 +36104,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ169">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR169">
         <v>1.15</v>
@@ -36220,7 +36229,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36916,7 +36925,7 @@
         <v>1.11</v>
       </c>
       <c r="AP173">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AQ173">
         <v>1.33</v>
@@ -37122,7 +37131,7 @@
         <v>1.56</v>
       </c>
       <c r="AP174">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ174">
         <v>1.17</v>
@@ -38773,7 +38782,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ182">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR182">
         <v>2.01</v>
@@ -39185,7 +39194,7 @@
         <v>2.77</v>
       </c>
       <c r="AQ184">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR184">
         <v>2.05</v>
@@ -39391,7 +39400,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ185">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR185">
         <v>1.11</v>
@@ -39516,7 +39525,7 @@
         <v>209</v>
       </c>
       <c r="P186" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q186">
         <v>2.2</v>
@@ -40212,7 +40221,7 @@
         <v>0.33</v>
       </c>
       <c r="AP189">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ189">
         <v>0.58</v>
@@ -40624,7 +40633,7 @@
         <v>0.3</v>
       </c>
       <c r="AP191">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AQ191">
         <v>0.58</v>
@@ -41242,7 +41251,7 @@
         <v>1.7</v>
       </c>
       <c r="AP194">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ194">
         <v>1.82</v>
@@ -42684,7 +42693,7 @@
         <v>0.55</v>
       </c>
       <c r="AP201">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ201">
         <v>0.54</v>
@@ -43717,7 +43726,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ206">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR206">
         <v>1.22</v>
@@ -43923,7 +43932,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ207">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR207">
         <v>1.11</v>
@@ -44129,7 +44138,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ208">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR208">
         <v>2.01</v>
@@ -45156,7 +45165,7 @@
         <v>1.55</v>
       </c>
       <c r="AP213">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AQ213">
         <v>1.42</v>
@@ -46883,6 +46892,624 @@
       </c>
       <c r="BP221">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7574782</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45725.52083333334</v>
+      </c>
+      <c r="F222">
+        <v>25</v>
+      </c>
+      <c r="G222" t="s">
+        <v>79</v>
+      </c>
+      <c r="H222" t="s">
+        <v>84</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>0</v>
+      </c>
+      <c r="L222">
+        <v>1</v>
+      </c>
+      <c r="M222">
+        <v>1</v>
+      </c>
+      <c r="N222">
+        <v>2</v>
+      </c>
+      <c r="O222" t="s">
+        <v>226</v>
+      </c>
+      <c r="P222" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q222">
+        <v>2.7</v>
+      </c>
+      <c r="R222">
+        <v>1.85</v>
+      </c>
+      <c r="S222">
+        <v>4.75</v>
+      </c>
+      <c r="T222">
+        <v>1.57</v>
+      </c>
+      <c r="U222">
+        <v>2.25</v>
+      </c>
+      <c r="V222">
+        <v>3.55</v>
+      </c>
+      <c r="W222">
+        <v>1.25</v>
+      </c>
+      <c r="X222">
+        <v>10.5</v>
+      </c>
+      <c r="Y222">
+        <v>1.04</v>
+      </c>
+      <c r="Z222">
+        <v>2</v>
+      </c>
+      <c r="AA222">
+        <v>3</v>
+      </c>
+      <c r="AB222">
+        <v>4.1</v>
+      </c>
+      <c r="AC222">
+        <v>1.11</v>
+      </c>
+      <c r="AD222">
+        <v>6.25</v>
+      </c>
+      <c r="AE222">
+        <v>1.53</v>
+      </c>
+      <c r="AF222">
+        <v>2.37</v>
+      </c>
+      <c r="AG222">
+        <v>2.7</v>
+      </c>
+      <c r="AH222">
+        <v>1.43</v>
+      </c>
+      <c r="AI222">
+        <v>2.15</v>
+      </c>
+      <c r="AJ222">
+        <v>1.62</v>
+      </c>
+      <c r="AK222">
+        <v>1.22</v>
+      </c>
+      <c r="AL222">
+        <v>1.33</v>
+      </c>
+      <c r="AM222">
+        <v>1.75</v>
+      </c>
+      <c r="AN222">
+        <v>1.83</v>
+      </c>
+      <c r="AO222">
+        <v>0.58</v>
+      </c>
+      <c r="AP222">
+        <v>1.77</v>
+      </c>
+      <c r="AQ222">
+        <v>0.62</v>
+      </c>
+      <c r="AR222">
+        <v>1.43</v>
+      </c>
+      <c r="AS222">
+        <v>1.19</v>
+      </c>
+      <c r="AT222">
+        <v>2.62</v>
+      </c>
+      <c r="AU222">
+        <v>5</v>
+      </c>
+      <c r="AV222">
+        <v>4</v>
+      </c>
+      <c r="AW222">
+        <v>7</v>
+      </c>
+      <c r="AX222">
+        <v>6</v>
+      </c>
+      <c r="AY222">
+        <v>15</v>
+      </c>
+      <c r="AZ222">
+        <v>13</v>
+      </c>
+      <c r="BA222">
+        <v>4</v>
+      </c>
+      <c r="BB222">
+        <v>3</v>
+      </c>
+      <c r="BC222">
+        <v>7</v>
+      </c>
+      <c r="BD222">
+        <v>0</v>
+      </c>
+      <c r="BE222">
+        <v>0</v>
+      </c>
+      <c r="BF222">
+        <v>0</v>
+      </c>
+      <c r="BG222">
+        <v>0</v>
+      </c>
+      <c r="BH222">
+        <v>0</v>
+      </c>
+      <c r="BI222">
+        <v>1.72</v>
+      </c>
+      <c r="BJ222">
+        <v>1.95</v>
+      </c>
+      <c r="BK222">
+        <v>0</v>
+      </c>
+      <c r="BL222">
+        <v>0</v>
+      </c>
+      <c r="BM222">
+        <v>0</v>
+      </c>
+      <c r="BN222">
+        <v>0</v>
+      </c>
+      <c r="BO222">
+        <v>0</v>
+      </c>
+      <c r="BP222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7574783</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45725.625</v>
+      </c>
+      <c r="F223">
+        <v>25</v>
+      </c>
+      <c r="G223" t="s">
+        <v>72</v>
+      </c>
+      <c r="H223" t="s">
+        <v>70</v>
+      </c>
+      <c r="I223">
+        <v>1</v>
+      </c>
+      <c r="J223">
+        <v>2</v>
+      </c>
+      <c r="K223">
+        <v>3</v>
+      </c>
+      <c r="L223">
+        <v>1</v>
+      </c>
+      <c r="M223">
+        <v>3</v>
+      </c>
+      <c r="N223">
+        <v>4</v>
+      </c>
+      <c r="O223" t="s">
+        <v>230</v>
+      </c>
+      <c r="P223" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q223">
+        <v>6</v>
+      </c>
+      <c r="R223">
+        <v>2.3</v>
+      </c>
+      <c r="S223">
+        <v>2.1</v>
+      </c>
+      <c r="T223">
+        <v>1.36</v>
+      </c>
+      <c r="U223">
+        <v>3</v>
+      </c>
+      <c r="V223">
+        <v>2.63</v>
+      </c>
+      <c r="W223">
+        <v>1.44</v>
+      </c>
+      <c r="X223">
+        <v>7</v>
+      </c>
+      <c r="Y223">
+        <v>1.1</v>
+      </c>
+      <c r="Z223">
+        <v>6</v>
+      </c>
+      <c r="AA223">
+        <v>4.2</v>
+      </c>
+      <c r="AB223">
+        <v>1.48</v>
+      </c>
+      <c r="AC223">
+        <v>1.05</v>
+      </c>
+      <c r="AD223">
+        <v>11.6</v>
+      </c>
+      <c r="AE223">
+        <v>1.31</v>
+      </c>
+      <c r="AF223">
+        <v>3.58</v>
+      </c>
+      <c r="AG223">
+        <v>1.6</v>
+      </c>
+      <c r="AH223">
+        <v>2.25</v>
+      </c>
+      <c r="AI223">
+        <v>1.91</v>
+      </c>
+      <c r="AJ223">
+        <v>1.91</v>
+      </c>
+      <c r="AK223">
+        <v>2.6</v>
+      </c>
+      <c r="AL223">
+        <v>1.21</v>
+      </c>
+      <c r="AM223">
+        <v>1.1</v>
+      </c>
+      <c r="AN223">
+        <v>1.83</v>
+      </c>
+      <c r="AO223">
+        <v>2.08</v>
+      </c>
+      <c r="AP223">
+        <v>1.69</v>
+      </c>
+      <c r="AQ223">
+        <v>2.15</v>
+      </c>
+      <c r="AR223">
+        <v>1.24</v>
+      </c>
+      <c r="AS223">
+        <v>1.91</v>
+      </c>
+      <c r="AT223">
+        <v>3.15</v>
+      </c>
+      <c r="AU223">
+        <v>5</v>
+      </c>
+      <c r="AV223">
+        <v>7</v>
+      </c>
+      <c r="AW223">
+        <v>6</v>
+      </c>
+      <c r="AX223">
+        <v>11</v>
+      </c>
+      <c r="AY223">
+        <v>11</v>
+      </c>
+      <c r="AZ223">
+        <v>18</v>
+      </c>
+      <c r="BA223">
+        <v>4</v>
+      </c>
+      <c r="BB223">
+        <v>4</v>
+      </c>
+      <c r="BC223">
+        <v>8</v>
+      </c>
+      <c r="BD223">
+        <v>4.33</v>
+      </c>
+      <c r="BE223">
+        <v>7.5</v>
+      </c>
+      <c r="BF223">
+        <v>1.31</v>
+      </c>
+      <c r="BG223">
+        <v>1.22</v>
+      </c>
+      <c r="BH223">
+        <v>3.7</v>
+      </c>
+      <c r="BI223">
+        <v>1.41</v>
+      </c>
+      <c r="BJ223">
+        <v>2.6</v>
+      </c>
+      <c r="BK223">
+        <v>1.73</v>
+      </c>
+      <c r="BL223">
+        <v>1.9</v>
+      </c>
+      <c r="BM223">
+        <v>2.25</v>
+      </c>
+      <c r="BN223">
+        <v>1.53</v>
+      </c>
+      <c r="BO223">
+        <v>3.1</v>
+      </c>
+      <c r="BP223">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7574784</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45725.72916666666</v>
+      </c>
+      <c r="F224">
+        <v>25</v>
+      </c>
+      <c r="G224" t="s">
+        <v>86</v>
+      </c>
+      <c r="H224" t="s">
+        <v>85</v>
+      </c>
+      <c r="I224">
+        <v>1</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>1</v>
+      </c>
+      <c r="L224">
+        <v>1</v>
+      </c>
+      <c r="M224">
+        <v>2</v>
+      </c>
+      <c r="N224">
+        <v>3</v>
+      </c>
+      <c r="O224" t="s">
+        <v>179</v>
+      </c>
+      <c r="P224" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q224">
+        <v>6.25</v>
+      </c>
+      <c r="R224">
+        <v>2.1</v>
+      </c>
+      <c r="S224">
+        <v>2.05</v>
+      </c>
+      <c r="T224">
+        <v>1.42</v>
+      </c>
+      <c r="U224">
+        <v>2.65</v>
+      </c>
+      <c r="V224">
+        <v>2.95</v>
+      </c>
+      <c r="W224">
+        <v>1.35</v>
+      </c>
+      <c r="X224">
+        <v>7</v>
+      </c>
+      <c r="Y224">
+        <v>1.07</v>
+      </c>
+      <c r="Z224">
+        <v>6</v>
+      </c>
+      <c r="AA224">
+        <v>3.8</v>
+      </c>
+      <c r="AB224">
+        <v>1.54</v>
+      </c>
+      <c r="AC224">
+        <v>1.07</v>
+      </c>
+      <c r="AD224">
+        <v>8</v>
+      </c>
+      <c r="AE224">
+        <v>1.36</v>
+      </c>
+      <c r="AF224">
+        <v>3.1</v>
+      </c>
+      <c r="AG224">
+        <v>2.1</v>
+      </c>
+      <c r="AH224">
+        <v>1.67</v>
+      </c>
+      <c r="AI224">
+        <v>2.1</v>
+      </c>
+      <c r="AJ224">
+        <v>1.65</v>
+      </c>
+      <c r="AK224">
+        <v>2.38</v>
+      </c>
+      <c r="AL224">
+        <v>1.2</v>
+      </c>
+      <c r="AM224">
+        <v>1.11</v>
+      </c>
+      <c r="AN224">
+        <v>0.5</v>
+      </c>
+      <c r="AO224">
+        <v>1</v>
+      </c>
+      <c r="AP224">
+        <v>0.46</v>
+      </c>
+      <c r="AQ224">
+        <v>1.15</v>
+      </c>
+      <c r="AR224">
+        <v>1.29</v>
+      </c>
+      <c r="AS224">
+        <v>1.46</v>
+      </c>
+      <c r="AT224">
+        <v>2.75</v>
+      </c>
+      <c r="AU224">
+        <v>4</v>
+      </c>
+      <c r="AV224">
+        <v>11</v>
+      </c>
+      <c r="AW224">
+        <v>3</v>
+      </c>
+      <c r="AX224">
+        <v>11</v>
+      </c>
+      <c r="AY224">
+        <v>8</v>
+      </c>
+      <c r="AZ224">
+        <v>24</v>
+      </c>
+      <c r="BA224">
+        <v>2</v>
+      </c>
+      <c r="BB224">
+        <v>7</v>
+      </c>
+      <c r="BC224">
+        <v>9</v>
+      </c>
+      <c r="BD224">
+        <v>3.55</v>
+      </c>
+      <c r="BE224">
+        <v>7.5</v>
+      </c>
+      <c r="BF224">
+        <v>1.34</v>
+      </c>
+      <c r="BG224">
+        <v>1.3</v>
+      </c>
+      <c r="BH224">
+        <v>3.05</v>
+      </c>
+      <c r="BI224">
+        <v>1.53</v>
+      </c>
+      <c r="BJ224">
+        <v>2.28</v>
+      </c>
+      <c r="BK224">
+        <v>1.86</v>
+      </c>
+      <c r="BL224">
+        <v>1.81</v>
+      </c>
+      <c r="BM224">
+        <v>2.33</v>
+      </c>
+      <c r="BN224">
+        <v>1.5</v>
+      </c>
+      <c r="BO224">
+        <v>3.05</v>
+      </c>
+      <c r="BP224">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="330">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1365,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP224"/>
+  <dimension ref="A1:BP225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1702,7 +1702,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ2">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2729,7 +2729,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ7">
         <v>1.82</v>
@@ -5822,7 +5822,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ22">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR22">
         <v>1.3</v>
@@ -6025,7 +6025,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ23">
         <v>0.75</v>
@@ -9530,7 +9530,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ40">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR40">
         <v>1.32</v>
@@ -9733,7 +9733,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ41">
         <v>0.54</v>
@@ -13647,7 +13647,7 @@
         <v>0.33</v>
       </c>
       <c r="AP60">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ60">
         <v>0.46</v>
@@ -14062,7 +14062,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ62">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR62">
         <v>1.53</v>
@@ -17149,7 +17149,7 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ77">
         <v>2.15</v>
@@ -17564,7 +17564,7 @@
         <v>2.77</v>
       </c>
       <c r="AQ79">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR79">
         <v>2.16</v>
@@ -20651,7 +20651,7 @@
         <v>0.6</v>
       </c>
       <c r="AP94">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ94">
         <v>1.15</v>
@@ -20860,7 +20860,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ95">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR95">
         <v>1.16</v>
@@ -24568,7 +24568,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ113">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR113">
         <v>1.38</v>
@@ -24771,7 +24771,7 @@
         <v>1.8</v>
       </c>
       <c r="AP114">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ114">
         <v>1.54</v>
@@ -27861,7 +27861,7 @@
         <v>0.43</v>
       </c>
       <c r="AP129">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ129">
         <v>0.77</v>
@@ -29306,7 +29306,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ136">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR136">
         <v>1.19</v>
@@ -31157,7 +31157,7 @@
         <v>1.29</v>
       </c>
       <c r="AP145">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ145">
         <v>1.42</v>
@@ -32808,7 +32808,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ153">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR153">
         <v>1.2</v>
@@ -35280,7 +35280,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ165">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR165">
         <v>1.12</v>
@@ -35483,7 +35483,7 @@
         <v>0.25</v>
       </c>
       <c r="AP166">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ166">
         <v>0.58</v>
@@ -39397,7 +39397,7 @@
         <v>1</v>
       </c>
       <c r="AP185">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ185">
         <v>1.15</v>
@@ -40430,7 +40430,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ190">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR190">
         <v>1.16</v>
@@ -43108,7 +43108,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ203">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR203">
         <v>1.23</v>
@@ -43929,7 +43929,7 @@
         <v>0.64</v>
       </c>
       <c r="AP207">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ207">
         <v>0.62</v>
@@ -47509,6 +47509,212 @@
         <v>3.05</v>
       </c>
       <c r="BP224">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="225" spans="1:68">
+      <c r="A225" s="1">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7574781</v>
+      </c>
+      <c r="C225" t="s">
+        <v>68</v>
+      </c>
+      <c r="D225" t="s">
+        <v>69</v>
+      </c>
+      <c r="E225" s="2">
+        <v>45726.71875</v>
+      </c>
+      <c r="F225">
+        <v>25</v>
+      </c>
+      <c r="G225" t="s">
+        <v>75</v>
+      </c>
+      <c r="H225" t="s">
+        <v>81</v>
+      </c>
+      <c r="I225">
+        <v>1</v>
+      </c>
+      <c r="J225">
+        <v>0</v>
+      </c>
+      <c r="K225">
+        <v>1</v>
+      </c>
+      <c r="L225">
+        <v>1</v>
+      </c>
+      <c r="M225">
+        <v>0</v>
+      </c>
+      <c r="N225">
+        <v>1</v>
+      </c>
+      <c r="O225" t="s">
+        <v>92</v>
+      </c>
+      <c r="P225" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q225">
+        <v>2.63</v>
+      </c>
+      <c r="R225">
+        <v>2.05</v>
+      </c>
+      <c r="S225">
+        <v>4.5</v>
+      </c>
+      <c r="T225">
+        <v>1.44</v>
+      </c>
+      <c r="U225">
+        <v>2.63</v>
+      </c>
+      <c r="V225">
+        <v>3.25</v>
+      </c>
+      <c r="W225">
+        <v>1.33</v>
+      </c>
+      <c r="X225">
+        <v>10</v>
+      </c>
+      <c r="Y225">
+        <v>1.06</v>
+      </c>
+      <c r="Z225">
+        <v>2</v>
+      </c>
+      <c r="AA225">
+        <v>2.75</v>
+      </c>
+      <c r="AB225">
+        <v>4.7</v>
+      </c>
+      <c r="AC225">
+        <v>1.08</v>
+      </c>
+      <c r="AD225">
+        <v>7.5</v>
+      </c>
+      <c r="AE225">
+        <v>1.38</v>
+      </c>
+      <c r="AF225">
+        <v>3</v>
+      </c>
+      <c r="AG225">
+        <v>2.1</v>
+      </c>
+      <c r="AH225">
+        <v>1.67</v>
+      </c>
+      <c r="AI225">
+        <v>1.95</v>
+      </c>
+      <c r="AJ225">
+        <v>1.8</v>
+      </c>
+      <c r="AK225">
+        <v>1.2</v>
+      </c>
+      <c r="AL225">
+        <v>1.33</v>
+      </c>
+      <c r="AM225">
+        <v>1.85</v>
+      </c>
+      <c r="AN225">
+        <v>1.25</v>
+      </c>
+      <c r="AO225">
+        <v>0.67</v>
+      </c>
+      <c r="AP225">
+        <v>1.38</v>
+      </c>
+      <c r="AQ225">
+        <v>0.62</v>
+      </c>
+      <c r="AR225">
+        <v>1.18</v>
+      </c>
+      <c r="AS225">
+        <v>1.01</v>
+      </c>
+      <c r="AT225">
+        <v>2.19</v>
+      </c>
+      <c r="AU225">
+        <v>10</v>
+      </c>
+      <c r="AV225">
+        <v>2</v>
+      </c>
+      <c r="AW225">
+        <v>7</v>
+      </c>
+      <c r="AX225">
+        <v>10</v>
+      </c>
+      <c r="AY225">
+        <v>18</v>
+      </c>
+      <c r="AZ225">
+        <v>13</v>
+      </c>
+      <c r="BA225">
+        <v>5</v>
+      </c>
+      <c r="BB225">
+        <v>1</v>
+      </c>
+      <c r="BC225">
+        <v>6</v>
+      </c>
+      <c r="BD225">
+        <v>1.44</v>
+      </c>
+      <c r="BE225">
+        <v>7</v>
+      </c>
+      <c r="BF225">
+        <v>3.4</v>
+      </c>
+      <c r="BG225">
+        <v>1.22</v>
+      </c>
+      <c r="BH225">
+        <v>3.7</v>
+      </c>
+      <c r="BI225">
+        <v>1.42</v>
+      </c>
+      <c r="BJ225">
+        <v>2.55</v>
+      </c>
+      <c r="BK225">
+        <v>1.75</v>
+      </c>
+      <c r="BL225">
+        <v>1.9</v>
+      </c>
+      <c r="BM225">
+        <v>2.25</v>
+      </c>
+      <c r="BN225">
+        <v>1.52</v>
+      </c>
+      <c r="BO225">
+        <v>3.1</v>
+      </c>
+      <c r="BP225">
         <v>1.3</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="333">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -709,6 +709,12 @@
     <t>['45']</t>
   </si>
   <si>
+    <t>['18', '61']</t>
+  </si>
+  <si>
+    <t>['1', '64', '88']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -1004,6 +1010,9 @@
   </si>
   <si>
     <t>['50', '76']</t>
+  </si>
+  <si>
+    <t>['70']</t>
   </si>
 </sst>
 </file>
@@ -1365,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP225"/>
+  <dimension ref="A1:BP229"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1699,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ2">
         <v>0.62</v>
@@ -1827,7 +1836,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2317,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ5">
         <v>0.54</v>
@@ -2445,7 +2454,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2526,7 +2535,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ6">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2857,7 +2866,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -2935,7 +2944,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ8">
         <v>0.62</v>
@@ -3475,7 +3484,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3681,7 +3690,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3759,10 +3768,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4093,7 +4102,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4505,7 +4514,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4917,7 +4926,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4998,7 +5007,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ18">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5123,7 +5132,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5204,7 +5213,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ19">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5329,7 +5338,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5407,7 +5416,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ20">
         <v>2.15</v>
@@ -5535,7 +5544,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -5616,7 +5625,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ21">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR21">
         <v>1.57</v>
@@ -5819,7 +5828,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ22">
         <v>0.62</v>
@@ -7183,7 +7192,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7389,7 +7398,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7470,7 +7479,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ30">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR30">
         <v>0.55</v>
@@ -7595,7 +7604,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -8085,7 +8094,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ33">
         <v>1.54</v>
@@ -8706,7 +8715,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ36">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR36">
         <v>1.59</v>
@@ -8909,10 +8918,10 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ37">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR37">
         <v>1.77</v>
@@ -9037,7 +9046,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9243,7 +9252,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9655,7 +9664,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9861,7 +9870,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -9942,7 +9951,7 @@
         <v>2.77</v>
       </c>
       <c r="AQ42">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR42">
         <v>2.4</v>
@@ -10067,7 +10076,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10145,7 +10154,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ43">
         <v>0.77</v>
@@ -10479,7 +10488,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10685,7 +10694,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10891,7 +10900,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10972,7 +10981,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ47">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR47">
         <v>1.27</v>
@@ -11097,7 +11106,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11509,7 +11518,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11796,7 +11805,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ51">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR51">
         <v>1.08</v>
@@ -11921,7 +11930,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -11999,7 +12008,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ52">
         <v>1.17</v>
@@ -12205,7 +12214,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ53">
         <v>1.15</v>
@@ -12411,10 +12420,10 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ54">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR54">
         <v>1.92</v>
@@ -12539,7 +12548,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12745,7 +12754,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -13157,7 +13166,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13363,7 +13372,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -13853,7 +13862,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ61">
         <v>1.15</v>
@@ -14680,7 +14689,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ65">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -14883,7 +14892,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ66">
         <v>0.58</v>
@@ -15092,7 +15101,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ67">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR67">
         <v>1.08</v>
@@ -15298,7 +15307,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ68">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR68">
         <v>0.83</v>
@@ -15501,7 +15510,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ69">
         <v>1.17</v>
@@ -15707,7 +15716,7 @@
         <v>0.67</v>
       </c>
       <c r="AP70">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ70">
         <v>1.08</v>
@@ -15835,7 +15844,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -16041,7 +16050,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16119,10 +16128,10 @@
         <v>2.33</v>
       </c>
       <c r="AP72">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ72">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR72">
         <v>2.36</v>
@@ -16453,7 +16462,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16659,7 +16668,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16865,7 +16874,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17071,7 +17080,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17689,7 +17698,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17895,7 +17904,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -18101,7 +18110,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18179,7 +18188,7 @@
         <v>0.25</v>
       </c>
       <c r="AP82">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ82">
         <v>0.58</v>
@@ -18307,7 +18316,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18513,7 +18522,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18591,7 +18600,7 @@
         <v>1.33</v>
       </c>
       <c r="AP84">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ84">
         <v>1.82</v>
@@ -18719,7 +18728,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18797,7 +18806,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ85">
         <v>0.75</v>
@@ -18925,7 +18934,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19006,7 +19015,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ86">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR86">
         <v>1.12</v>
@@ -19337,7 +19346,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19418,7 +19427,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ88">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR88">
         <v>0.89</v>
@@ -19621,7 +19630,7 @@
         <v>0.5</v>
       </c>
       <c r="AP89">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ89">
         <v>1.08</v>
@@ -19830,7 +19839,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ90">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR90">
         <v>1.22</v>
@@ -19955,7 +19964,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -20161,7 +20170,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20448,7 +20457,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ93">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR93">
         <v>0.99</v>
@@ -20779,7 +20788,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -21397,7 +21406,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21887,7 +21896,7 @@
         <v>0.2</v>
       </c>
       <c r="AP100">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ100">
         <v>0.58</v>
@@ -22015,7 +22024,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22427,7 +22436,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22505,10 +22514,10 @@
         <v>1.2</v>
       </c>
       <c r="AP103">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ103">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR103">
         <v>2.02</v>
@@ -22714,7 +22723,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ104">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR104">
         <v>1</v>
@@ -22839,7 +22848,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -23126,7 +23135,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ106">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR106">
         <v>1.19</v>
@@ -23535,7 +23544,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ108">
         <v>1.17</v>
@@ -23869,7 +23878,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -24153,7 +24162,7 @@
         <v>0.33</v>
       </c>
       <c r="AP111">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ111">
         <v>0.46</v>
@@ -25186,7 +25195,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ116">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR116">
         <v>1.23</v>
@@ -25595,7 +25604,7 @@
         <v>0.29</v>
       </c>
       <c r="AP118">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ118">
         <v>0.54</v>
@@ -25929,7 +25938,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26007,7 +26016,7 @@
         <v>1.29</v>
       </c>
       <c r="AP120">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ120">
         <v>0.75</v>
@@ -26216,7 +26225,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ121">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR121">
         <v>1.05</v>
@@ -26547,7 +26556,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26753,7 +26762,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -26834,7 +26843,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ124">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR124">
         <v>1.55</v>
@@ -27037,7 +27046,7 @@
         <v>0.17</v>
       </c>
       <c r="AP125">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ125">
         <v>0.58</v>
@@ -27165,7 +27174,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27371,7 +27380,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27577,7 +27586,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27783,7 +27792,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -28070,7 +28079,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ130">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR130">
         <v>1.33</v>
@@ -28195,7 +28204,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28401,7 +28410,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28482,7 +28491,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ132">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR132">
         <v>1.35</v>
@@ -28685,7 +28694,7 @@
         <v>2.57</v>
       </c>
       <c r="AP133">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ133">
         <v>2.15</v>
@@ -28813,7 +28822,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -29637,7 +29646,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29843,7 +29852,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -30127,7 +30136,7 @@
         <v>1.13</v>
       </c>
       <c r="AP140">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ140">
         <v>0.75</v>
@@ -30255,7 +30264,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30333,7 +30342,7 @@
         <v>1.13</v>
       </c>
       <c r="AP141">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ141">
         <v>1.15</v>
@@ -30461,7 +30470,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30667,7 +30676,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -30951,7 +30960,7 @@
         <v>2</v>
       </c>
       <c r="AP144">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ144">
         <v>1.82</v>
@@ -31079,7 +31088,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31160,7 +31169,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ145">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR145">
         <v>1.04</v>
@@ -31285,7 +31294,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31572,7 +31581,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ147">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR147">
         <v>1.11</v>
@@ -31697,7 +31706,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31778,7 +31787,7 @@
         <v>2.77</v>
       </c>
       <c r="AQ148">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR148">
         <v>2.01</v>
@@ -31903,7 +31912,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32315,7 +32324,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32396,7 +32405,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ151">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR151">
         <v>1.25</v>
@@ -32521,7 +32530,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32727,7 +32736,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -32805,7 +32814,7 @@
         <v>0.38</v>
       </c>
       <c r="AP153">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ153">
         <v>0.62</v>
@@ -33220,7 +33229,7 @@
         <v>2.77</v>
       </c>
       <c r="AQ155">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR155">
         <v>2.01</v>
@@ -33345,7 +33354,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33551,7 +33560,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33757,7 +33766,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33963,7 +33972,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34044,7 +34053,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ159">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR159">
         <v>1.19</v>
@@ -34375,7 +34384,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34456,7 +34465,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ161">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR161">
         <v>1.17</v>
@@ -34581,7 +34590,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34659,7 +34668,7 @@
         <v>1.63</v>
       </c>
       <c r="AP162">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ162">
         <v>1.54</v>
@@ -34787,7 +34796,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -35199,7 +35208,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35277,7 +35286,7 @@
         <v>0.44</v>
       </c>
       <c r="AP165">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ165">
         <v>0.62</v>
@@ -35895,7 +35904,7 @@
         <v>0.33</v>
       </c>
       <c r="AP168">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ168">
         <v>0.46</v>
@@ -36229,7 +36238,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36307,10 +36316,10 @@
         <v>1.5</v>
       </c>
       <c r="AP170">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ170">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR170">
         <v>1.95</v>
@@ -36847,7 +36856,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -36928,7 +36937,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ173">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR173">
         <v>1.33</v>
@@ -37259,7 +37268,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37465,7 +37474,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -37543,7 +37552,7 @@
         <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ176">
         <v>1.08</v>
@@ -37752,7 +37761,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ177">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR177">
         <v>1.39</v>
@@ -37955,7 +37964,7 @@
         <v>0.8</v>
       </c>
       <c r="AP178">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ178">
         <v>0.77</v>
@@ -38083,7 +38092,7 @@
         <v>205</v>
       </c>
       <c r="P179" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q179">
         <v>8.5</v>
@@ -38289,7 +38298,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q180">
         <v>4.75</v>
@@ -38370,7 +38379,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ180">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR180">
         <v>1.19</v>
@@ -38495,7 +38504,7 @@
         <v>207</v>
       </c>
       <c r="P181" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q181">
         <v>6.5</v>
@@ -38701,7 +38710,7 @@
         <v>167</v>
       </c>
       <c r="P182" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -38779,7 +38788,7 @@
         <v>2.3</v>
       </c>
       <c r="AP182">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ182">
         <v>2.15</v>
@@ -38988,7 +38997,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ183">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR183">
         <v>1.2</v>
@@ -39113,7 +39122,7 @@
         <v>208</v>
       </c>
       <c r="P184" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q184">
         <v>1.57</v>
@@ -39525,7 +39534,7 @@
         <v>209</v>
       </c>
       <c r="P186" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q186">
         <v>2.2</v>
@@ -39809,7 +39818,7 @@
         <v>0.3</v>
       </c>
       <c r="AP187">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ187">
         <v>0.46</v>
@@ -40349,7 +40358,7 @@
         <v>184</v>
       </c>
       <c r="P190" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q190">
         <v>2.63</v>
@@ -40761,7 +40770,7 @@
         <v>212</v>
       </c>
       <c r="P192" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -40967,7 +40976,7 @@
         <v>213</v>
       </c>
       <c r="P193" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q193">
         <v>2.8</v>
@@ -41379,7 +41388,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q195">
         <v>1.67</v>
@@ -41457,7 +41466,7 @@
         <v>1</v>
       </c>
       <c r="AP195">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ195">
         <v>1.15</v>
@@ -41666,7 +41675,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ196">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR196">
         <v>1.29</v>
@@ -41791,7 +41800,7 @@
         <v>90</v>
       </c>
       <c r="P197" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q197">
         <v>7.5</v>
@@ -41869,7 +41878,7 @@
         <v>1.4</v>
       </c>
       <c r="AP197">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ197">
         <v>1.54</v>
@@ -42078,7 +42087,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ198">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR198">
         <v>1.47</v>
@@ -42203,7 +42212,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42281,10 +42290,10 @@
         <v>1.3</v>
       </c>
       <c r="AP199">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ199">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR199">
         <v>1.25</v>
@@ -43027,7 +43036,7 @@
         <v>218</v>
       </c>
       <c r="P203" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q203">
         <v>2.55</v>
@@ -43314,7 +43323,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ204">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR204">
         <v>1.15</v>
@@ -43439,7 +43448,7 @@
         <v>219</v>
       </c>
       <c r="P205" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q205">
         <v>2.45</v>
@@ -43645,7 +43654,7 @@
         <v>220</v>
       </c>
       <c r="P206" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q206">
         <v>7</v>
@@ -44057,7 +44066,7 @@
         <v>166</v>
       </c>
       <c r="P208" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44135,7 +44144,7 @@
         <v>1</v>
       </c>
       <c r="AP208">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ208">
         <v>1.15</v>
@@ -44344,7 +44353,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ209">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR209">
         <v>1.41</v>
@@ -44469,7 +44478,7 @@
         <v>90</v>
       </c>
       <c r="P210" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q210">
         <v>5.5</v>
@@ -45168,7 +45177,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ213">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR213">
         <v>1.28</v>
@@ -45293,7 +45302,7 @@
         <v>90</v>
       </c>
       <c r="P214" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q214">
         <v>3.1</v>
@@ -45371,10 +45380,10 @@
         <v>0.55</v>
       </c>
       <c r="AP214">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ214">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR214">
         <v>1.29</v>
@@ -45499,7 +45508,7 @@
         <v>224</v>
       </c>
       <c r="P215" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q215">
         <v>4.33</v>
@@ -45580,7 +45589,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ215">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR215">
         <v>1.31</v>
@@ -45783,7 +45792,7 @@
         <v>1.18</v>
       </c>
       <c r="AP216">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ216">
         <v>1.08</v>
@@ -45911,7 +45920,7 @@
         <v>226</v>
       </c>
       <c r="P217" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q217">
         <v>3.3</v>
@@ -46117,7 +46126,7 @@
         <v>90</v>
       </c>
       <c r="P218" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q218">
         <v>3.4</v>
@@ -46323,7 +46332,7 @@
         <v>227</v>
       </c>
       <c r="P219" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q219">
         <v>2.88</v>
@@ -46941,7 +46950,7 @@
         <v>226</v>
       </c>
       <c r="P222" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q222">
         <v>2.7</v>
@@ -47147,7 +47156,7 @@
         <v>230</v>
       </c>
       <c r="P223" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q223">
         <v>6</v>
@@ -47353,7 +47362,7 @@
         <v>179</v>
       </c>
       <c r="P224" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q224">
         <v>6.25</v>
@@ -47716,6 +47725,830 @@
       </c>
       <c r="BP225">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:68">
+      <c r="A226" s="1">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>7574794</v>
+      </c>
+      <c r="C226" t="s">
+        <v>68</v>
+      </c>
+      <c r="D226" t="s">
+        <v>69</v>
+      </c>
+      <c r="E226" s="2">
+        <v>45731.52083333334</v>
+      </c>
+      <c r="F226">
+        <v>26</v>
+      </c>
+      <c r="G226" t="s">
+        <v>76</v>
+      </c>
+      <c r="H226" t="s">
+        <v>77</v>
+      </c>
+      <c r="I226">
+        <v>0</v>
+      </c>
+      <c r="J226">
+        <v>0</v>
+      </c>
+      <c r="K226">
+        <v>0</v>
+      </c>
+      <c r="L226">
+        <v>0</v>
+      </c>
+      <c r="M226">
+        <v>1</v>
+      </c>
+      <c r="N226">
+        <v>1</v>
+      </c>
+      <c r="O226" t="s">
+        <v>90</v>
+      </c>
+      <c r="P226" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q226">
+        <v>5</v>
+      </c>
+      <c r="R226">
+        <v>2.05</v>
+      </c>
+      <c r="S226">
+        <v>2.5</v>
+      </c>
+      <c r="T226">
+        <v>1.5</v>
+      </c>
+      <c r="U226">
+        <v>2.5</v>
+      </c>
+      <c r="V226">
+        <v>3.4</v>
+      </c>
+      <c r="W226">
+        <v>1.3</v>
+      </c>
+      <c r="X226">
+        <v>10</v>
+      </c>
+      <c r="Y226">
+        <v>1.06</v>
+      </c>
+      <c r="Z226">
+        <v>4.2</v>
+      </c>
+      <c r="AA226">
+        <v>3.45</v>
+      </c>
+      <c r="AB226">
+        <v>1.8</v>
+      </c>
+      <c r="AC226">
+        <v>1.03</v>
+      </c>
+      <c r="AD226">
+        <v>10.5</v>
+      </c>
+      <c r="AE226">
+        <v>1.39</v>
+      </c>
+      <c r="AF226">
+        <v>2.98</v>
+      </c>
+      <c r="AG226">
+        <v>1.91</v>
+      </c>
+      <c r="AH226">
+        <v>1.8</v>
+      </c>
+      <c r="AI226">
+        <v>2</v>
+      </c>
+      <c r="AJ226">
+        <v>1.75</v>
+      </c>
+      <c r="AK226">
+        <v>1.9</v>
+      </c>
+      <c r="AL226">
+        <v>1.29</v>
+      </c>
+      <c r="AM226">
+        <v>1.22</v>
+      </c>
+      <c r="AN226">
+        <v>0.58</v>
+      </c>
+      <c r="AO226">
+        <v>2.17</v>
+      </c>
+      <c r="AP226">
+        <v>0.54</v>
+      </c>
+      <c r="AQ226">
+        <v>2.23</v>
+      </c>
+      <c r="AR226">
+        <v>1.35</v>
+      </c>
+      <c r="AS226">
+        <v>1.48</v>
+      </c>
+      <c r="AT226">
+        <v>2.83</v>
+      </c>
+      <c r="AU226">
+        <v>6</v>
+      </c>
+      <c r="AV226">
+        <v>5</v>
+      </c>
+      <c r="AW226">
+        <v>8</v>
+      </c>
+      <c r="AX226">
+        <v>5</v>
+      </c>
+      <c r="AY226">
+        <v>18</v>
+      </c>
+      <c r="AZ226">
+        <v>13</v>
+      </c>
+      <c r="BA226">
+        <v>12</v>
+      </c>
+      <c r="BB226">
+        <v>4</v>
+      </c>
+      <c r="BC226">
+        <v>16</v>
+      </c>
+      <c r="BD226">
+        <v>2.88</v>
+      </c>
+      <c r="BE226">
+        <v>7</v>
+      </c>
+      <c r="BF226">
+        <v>1.49</v>
+      </c>
+      <c r="BG226">
+        <v>1.27</v>
+      </c>
+      <c r="BH226">
+        <v>3.3</v>
+      </c>
+      <c r="BI226">
+        <v>1.46</v>
+      </c>
+      <c r="BJ226">
+        <v>2.45</v>
+      </c>
+      <c r="BK226">
+        <v>1.75</v>
+      </c>
+      <c r="BL226">
+        <v>1.92</v>
+      </c>
+      <c r="BM226">
+        <v>2.18</v>
+      </c>
+      <c r="BN226">
+        <v>1.58</v>
+      </c>
+      <c r="BO226">
+        <v>2.8</v>
+      </c>
+      <c r="BP226">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="227" spans="1:68">
+      <c r="A227" s="1">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>7574790</v>
+      </c>
+      <c r="C227" t="s">
+        <v>68</v>
+      </c>
+      <c r="D227" t="s">
+        <v>69</v>
+      </c>
+      <c r="E227" s="2">
+        <v>45731.52083333334</v>
+      </c>
+      <c r="F227">
+        <v>26</v>
+      </c>
+      <c r="G227" t="s">
+        <v>80</v>
+      </c>
+      <c r="H227" t="s">
+        <v>79</v>
+      </c>
+      <c r="I227">
+        <v>0</v>
+      </c>
+      <c r="J227">
+        <v>1</v>
+      </c>
+      <c r="K227">
+        <v>1</v>
+      </c>
+      <c r="L227">
+        <v>0</v>
+      </c>
+      <c r="M227">
+        <v>1</v>
+      </c>
+      <c r="N227">
+        <v>1</v>
+      </c>
+      <c r="O227" t="s">
+        <v>90</v>
+      </c>
+      <c r="P227" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q227">
+        <v>4</v>
+      </c>
+      <c r="R227">
+        <v>1.83</v>
+      </c>
+      <c r="S227">
+        <v>3.5</v>
+      </c>
+      <c r="T227">
+        <v>1.62</v>
+      </c>
+      <c r="U227">
+        <v>2.2</v>
+      </c>
+      <c r="V227">
+        <v>4</v>
+      </c>
+      <c r="W227">
+        <v>1.22</v>
+      </c>
+      <c r="X227">
+        <v>13</v>
+      </c>
+      <c r="Y227">
+        <v>1.04</v>
+      </c>
+      <c r="Z227">
+        <v>2.75</v>
+      </c>
+      <c r="AA227">
+        <v>3</v>
+      </c>
+      <c r="AB227">
+        <v>2.65</v>
+      </c>
+      <c r="AC227">
+        <v>1.12</v>
+      </c>
+      <c r="AD227">
+        <v>6.17</v>
+      </c>
+      <c r="AE227">
+        <v>1.53</v>
+      </c>
+      <c r="AF227">
+        <v>2.37</v>
+      </c>
+      <c r="AG227">
+        <v>2.77</v>
+      </c>
+      <c r="AH227">
+        <v>1.39</v>
+      </c>
+      <c r="AI227">
+        <v>2.2</v>
+      </c>
+      <c r="AJ227">
+        <v>1.62</v>
+      </c>
+      <c r="AK227">
+        <v>1.46</v>
+      </c>
+      <c r="AL227">
+        <v>1.37</v>
+      </c>
+      <c r="AM227">
+        <v>1.41</v>
+      </c>
+      <c r="AN227">
+        <v>1.45</v>
+      </c>
+      <c r="AO227">
+        <v>1.42</v>
+      </c>
+      <c r="AP227">
+        <v>1.33</v>
+      </c>
+      <c r="AQ227">
+        <v>1.54</v>
+      </c>
+      <c r="AR227">
+        <v>1.27</v>
+      </c>
+      <c r="AS227">
+        <v>0.99</v>
+      </c>
+      <c r="AT227">
+        <v>2.26</v>
+      </c>
+      <c r="AU227">
+        <v>2</v>
+      </c>
+      <c r="AV227">
+        <v>4</v>
+      </c>
+      <c r="AW227">
+        <v>9</v>
+      </c>
+      <c r="AX227">
+        <v>1</v>
+      </c>
+      <c r="AY227">
+        <v>14</v>
+      </c>
+      <c r="AZ227">
+        <v>5</v>
+      </c>
+      <c r="BA227">
+        <v>5</v>
+      </c>
+      <c r="BB227">
+        <v>0</v>
+      </c>
+      <c r="BC227">
+        <v>5</v>
+      </c>
+      <c r="BD227">
+        <v>1.95</v>
+      </c>
+      <c r="BE227">
+        <v>6.4</v>
+      </c>
+      <c r="BF227">
+        <v>2.05</v>
+      </c>
+      <c r="BG227">
+        <v>1.4</v>
+      </c>
+      <c r="BH227">
+        <v>2.63</v>
+      </c>
+      <c r="BI227">
+        <v>1.68</v>
+      </c>
+      <c r="BJ227">
+        <v>2.02</v>
+      </c>
+      <c r="BK227">
+        <v>2.1</v>
+      </c>
+      <c r="BL227">
+        <v>1.63</v>
+      </c>
+      <c r="BM227">
+        <v>2.65</v>
+      </c>
+      <c r="BN227">
+        <v>1.4</v>
+      </c>
+      <c r="BO227">
+        <v>3.55</v>
+      </c>
+      <c r="BP227">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="228" spans="1:68">
+      <c r="A228" s="1">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>7574788</v>
+      </c>
+      <c r="C228" t="s">
+        <v>68</v>
+      </c>
+      <c r="D228" t="s">
+        <v>69</v>
+      </c>
+      <c r="E228" s="2">
+        <v>45731.625</v>
+      </c>
+      <c r="F228">
+        <v>26</v>
+      </c>
+      <c r="G228" t="s">
+        <v>73</v>
+      </c>
+      <c r="H228" t="s">
+        <v>71</v>
+      </c>
+      <c r="I228">
+        <v>1</v>
+      </c>
+      <c r="J228">
+        <v>0</v>
+      </c>
+      <c r="K228">
+        <v>1</v>
+      </c>
+      <c r="L228">
+        <v>2</v>
+      </c>
+      <c r="M228">
+        <v>0</v>
+      </c>
+      <c r="N228">
+        <v>2</v>
+      </c>
+      <c r="O228" t="s">
+        <v>231</v>
+      </c>
+      <c r="P228" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q228">
+        <v>1.73</v>
+      </c>
+      <c r="R228">
+        <v>2.6</v>
+      </c>
+      <c r="S228">
+        <v>9.5</v>
+      </c>
+      <c r="T228">
+        <v>1.3</v>
+      </c>
+      <c r="U228">
+        <v>3.4</v>
+      </c>
+      <c r="V228">
+        <v>2.5</v>
+      </c>
+      <c r="W228">
+        <v>1.5</v>
+      </c>
+      <c r="X228">
+        <v>6</v>
+      </c>
+      <c r="Y228">
+        <v>1.13</v>
+      </c>
+      <c r="Z228">
+        <v>1.25</v>
+      </c>
+      <c r="AA228">
+        <v>5.5</v>
+      </c>
+      <c r="AB228">
+        <v>10.5</v>
+      </c>
+      <c r="AC228">
+        <v>1.01</v>
+      </c>
+      <c r="AD228">
+        <v>13</v>
+      </c>
+      <c r="AE228">
+        <v>1.22</v>
+      </c>
+      <c r="AF228">
+        <v>4.22</v>
+      </c>
+      <c r="AG228">
+        <v>1.75</v>
+      </c>
+      <c r="AH228">
+        <v>1.95</v>
+      </c>
+      <c r="AI228">
+        <v>2.2</v>
+      </c>
+      <c r="AJ228">
+        <v>1.62</v>
+      </c>
+      <c r="AK228">
+        <v>1.04</v>
+      </c>
+      <c r="AL228">
+        <v>1.14</v>
+      </c>
+      <c r="AM228">
+        <v>3.7</v>
+      </c>
+      <c r="AN228">
+        <v>2.5</v>
+      </c>
+      <c r="AO228">
+        <v>0.75</v>
+      </c>
+      <c r="AP228">
+        <v>2.54</v>
+      </c>
+      <c r="AQ228">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR228">
+        <v>1.98</v>
+      </c>
+      <c r="AS228">
+        <v>1.04</v>
+      </c>
+      <c r="AT228">
+        <v>3.02</v>
+      </c>
+      <c r="AU228">
+        <v>9</v>
+      </c>
+      <c r="AV228">
+        <v>3</v>
+      </c>
+      <c r="AW228">
+        <v>12</v>
+      </c>
+      <c r="AX228">
+        <v>5</v>
+      </c>
+      <c r="AY228">
+        <v>24</v>
+      </c>
+      <c r="AZ228">
+        <v>9</v>
+      </c>
+      <c r="BA228">
+        <v>4</v>
+      </c>
+      <c r="BB228">
+        <v>3</v>
+      </c>
+      <c r="BC228">
+        <v>7</v>
+      </c>
+      <c r="BD228">
+        <v>1.18</v>
+      </c>
+      <c r="BE228">
+        <v>9</v>
+      </c>
+      <c r="BF228">
+        <v>5.3</v>
+      </c>
+      <c r="BG228">
+        <v>1.3</v>
+      </c>
+      <c r="BH228">
+        <v>3.05</v>
+      </c>
+      <c r="BI228">
+        <v>1.52</v>
+      </c>
+      <c r="BJ228">
+        <v>2.3</v>
+      </c>
+      <c r="BK228">
+        <v>1.83</v>
+      </c>
+      <c r="BL228">
+        <v>1.83</v>
+      </c>
+      <c r="BM228">
+        <v>2.28</v>
+      </c>
+      <c r="BN228">
+        <v>1.53</v>
+      </c>
+      <c r="BO228">
+        <v>2.9</v>
+      </c>
+      <c r="BP228">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="229" spans="1:68">
+      <c r="A229" s="1">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>7574789</v>
+      </c>
+      <c r="C229" t="s">
+        <v>68</v>
+      </c>
+      <c r="D229" t="s">
+        <v>69</v>
+      </c>
+      <c r="E229" s="2">
+        <v>45731.72916666666</v>
+      </c>
+      <c r="F229">
+        <v>26</v>
+      </c>
+      <c r="G229" t="s">
+        <v>70</v>
+      </c>
+      <c r="H229" t="s">
+        <v>75</v>
+      </c>
+      <c r="I229">
+        <v>1</v>
+      </c>
+      <c r="J229">
+        <v>1</v>
+      </c>
+      <c r="K229">
+        <v>2</v>
+      </c>
+      <c r="L229">
+        <v>3</v>
+      </c>
+      <c r="M229">
+        <v>1</v>
+      </c>
+      <c r="N229">
+        <v>4</v>
+      </c>
+      <c r="O229" t="s">
+        <v>232</v>
+      </c>
+      <c r="P229" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q229">
+        <v>1.8</v>
+      </c>
+      <c r="R229">
+        <v>2.5</v>
+      </c>
+      <c r="S229">
+        <v>8</v>
+      </c>
+      <c r="T229">
+        <v>1.33</v>
+      </c>
+      <c r="U229">
+        <v>3.25</v>
+      </c>
+      <c r="V229">
+        <v>2.5</v>
+      </c>
+      <c r="W229">
+        <v>1.5</v>
+      </c>
+      <c r="X229">
+        <v>6</v>
+      </c>
+      <c r="Y229">
+        <v>1.13</v>
+      </c>
+      <c r="Z229">
+        <v>1.28</v>
+      </c>
+      <c r="AA229">
+        <v>5</v>
+      </c>
+      <c r="AB229">
+        <v>10</v>
+      </c>
+      <c r="AC229">
+        <v>1.03</v>
+      </c>
+      <c r="AD229">
+        <v>12</v>
+      </c>
+      <c r="AE229">
+        <v>1.21</v>
+      </c>
+      <c r="AF229">
+        <v>4</v>
+      </c>
+      <c r="AG229">
+        <v>1.6</v>
+      </c>
+      <c r="AH229">
+        <v>2.19</v>
+      </c>
+      <c r="AI229">
+        <v>2.05</v>
+      </c>
+      <c r="AJ229">
+        <v>1.7</v>
+      </c>
+      <c r="AK229">
+        <v>1.07</v>
+      </c>
+      <c r="AL229">
+        <v>1.16</v>
+      </c>
+      <c r="AM229">
+        <v>3.25</v>
+      </c>
+      <c r="AN229">
+        <v>2.58</v>
+      </c>
+      <c r="AO229">
+        <v>1.33</v>
+      </c>
+      <c r="AP229">
+        <v>2.62</v>
+      </c>
+      <c r="AQ229">
+        <v>1.23</v>
+      </c>
+      <c r="AR229">
+        <v>2.09</v>
+      </c>
+      <c r="AS229">
+        <v>1.4</v>
+      </c>
+      <c r="AT229">
+        <v>3.49</v>
+      </c>
+      <c r="AU229">
+        <v>-1</v>
+      </c>
+      <c r="AV229">
+        <v>-1</v>
+      </c>
+      <c r="AW229">
+        <v>-1</v>
+      </c>
+      <c r="AX229">
+        <v>-1</v>
+      </c>
+      <c r="AY229">
+        <v>-1</v>
+      </c>
+      <c r="AZ229">
+        <v>-1</v>
+      </c>
+      <c r="BA229">
+        <v>-1</v>
+      </c>
+      <c r="BB229">
+        <v>-1</v>
+      </c>
+      <c r="BC229">
+        <v>-1</v>
+      </c>
+      <c r="BD229">
+        <v>1.17</v>
+      </c>
+      <c r="BE229">
+        <v>9</v>
+      </c>
+      <c r="BF229">
+        <v>5.3</v>
+      </c>
+      <c r="BG229">
+        <v>1.3</v>
+      </c>
+      <c r="BH229">
+        <v>3.05</v>
+      </c>
+      <c r="BI229">
+        <v>1.52</v>
+      </c>
+      <c r="BJ229">
+        <v>2.3</v>
+      </c>
+      <c r="BK229">
+        <v>1.83</v>
+      </c>
+      <c r="BL229">
+        <v>1.83</v>
+      </c>
+      <c r="BM229">
+        <v>2.28</v>
+      </c>
+      <c r="BN229">
+        <v>1.52</v>
+      </c>
+      <c r="BO229">
+        <v>2.9</v>
+      </c>
+      <c r="BP229">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -48485,31 +48485,31 @@
         <v>3.49</v>
       </c>
       <c r="AU229">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AV229">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW229">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AX229">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AY229">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AZ229">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BA229">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BB229">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC229">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="BD229">
         <v>1.17</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="340">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -715,6 +715,21 @@
     <t>['1', '64', '88']</t>
   </si>
   <si>
+    <t>['13']</t>
+  </si>
+  <si>
+    <t>['45+4', '60', '75']</t>
+  </si>
+  <si>
+    <t>['64', '75']</t>
+  </si>
+  <si>
+    <t>['31']</t>
+  </si>
+  <si>
+    <t>['10', '66']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -1013,6 +1028,12 @@
   </si>
   <si>
     <t>['70']</t>
+  </si>
+  <si>
+    <t>['90+2']</t>
+  </si>
+  <si>
+    <t>['30', '53', '80']</t>
   </si>
 </sst>
 </file>
@@ -1374,7 +1395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP229"/>
+  <dimension ref="A1:BP234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1836,7 +1857,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2123,7 +2144,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ4">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2454,7 +2475,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2741,7 +2762,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ7">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2866,7 +2887,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -3153,7 +3174,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ9">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3484,7 +3505,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3690,7 +3711,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3974,7 +3995,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ13">
         <v>0.77</v>
@@ -4102,7 +4123,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4180,7 +4201,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ14">
         <v>2.15</v>
@@ -4389,7 +4410,7 @@
         <v>2.77</v>
       </c>
       <c r="AQ15">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4514,7 +4535,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4592,7 +4613,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ16">
         <v>1.15</v>
@@ -4798,7 +4819,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ17">
         <v>1.08</v>
@@ -4926,7 +4947,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -5132,7 +5153,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5338,7 +5359,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5544,7 +5565,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -6037,7 +6058,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ23">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR23">
         <v>1.27</v>
@@ -6243,7 +6264,7 @@
         <v>2.77</v>
       </c>
       <c r="AQ24">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR24">
         <v>2.62</v>
@@ -7192,7 +7213,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7270,10 +7291,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ29">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR29">
         <v>1.3</v>
@@ -7398,7 +7419,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7604,7 +7625,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -7685,7 +7706,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ31">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR31">
         <v>1</v>
@@ -8300,7 +8321,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ34">
         <v>0.77</v>
@@ -8506,7 +8527,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ35">
         <v>1.15</v>
@@ -8712,7 +8733,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
         <v>1.23</v>
@@ -9046,7 +9067,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9252,7 +9273,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9664,7 +9685,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9870,7 +9891,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -10076,7 +10097,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10488,7 +10509,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10694,7 +10715,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10775,7 +10796,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ46">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR46">
         <v>1.1</v>
@@ -10900,7 +10921,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10978,7 +10999,7 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ47">
         <v>2.23</v>
@@ -11106,7 +11127,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11184,7 +11205,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ48">
         <v>1.08</v>
@@ -11393,7 +11414,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ49">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR49">
         <v>1.09</v>
@@ -11518,7 +11539,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11596,7 +11617,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ50">
         <v>1.54</v>
@@ -11802,7 +11823,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ51">
         <v>1.23</v>
@@ -11930,7 +11951,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -12011,7 +12032,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ52">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR52">
         <v>1.51</v>
@@ -12548,7 +12569,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12629,7 +12650,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ55">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR55">
         <v>1.28</v>
@@ -12754,7 +12775,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -13166,7 +13187,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13372,7 +13393,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -14277,7 +14298,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ63">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR63">
         <v>1.11</v>
@@ -14686,7 +14707,7 @@
         <v>1.33</v>
       </c>
       <c r="AP65">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ65">
         <v>1.23</v>
@@ -14895,7 +14916,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ66">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR66">
         <v>1.45</v>
@@ -15098,7 +15119,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ67">
         <v>1.54</v>
@@ -15513,7 +15534,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ69">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR69">
         <v>2.1</v>
@@ -15844,7 +15865,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -15922,10 +15943,10 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ71">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR71">
         <v>1.19</v>
@@ -16050,7 +16071,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16462,7 +16483,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16668,7 +16689,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16874,7 +16895,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17080,7 +17101,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17698,7 +17719,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17904,7 +17925,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -18110,7 +18131,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18191,7 +18212,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ82">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR82">
         <v>2.06</v>
@@ -18316,7 +18337,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18394,10 +18415,10 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ83">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR83">
         <v>1.47</v>
@@ -18522,7 +18543,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18603,7 +18624,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ84">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR84">
         <v>1.17</v>
@@ -18728,7 +18749,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18809,7 +18830,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ85">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR85">
         <v>1.21</v>
@@ -18934,7 +18955,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19218,7 +19239,7 @@
         <v>1.2</v>
       </c>
       <c r="AP87">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ87">
         <v>0.62</v>
@@ -19346,7 +19367,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19836,7 +19857,7 @@
         <v>1.5</v>
       </c>
       <c r="AP90">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ90">
         <v>1.54</v>
@@ -19964,7 +19985,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -20042,7 +20063,7 @@
         <v>0.4</v>
       </c>
       <c r="AP91">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ91">
         <v>0.54</v>
@@ -20170,7 +20191,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20788,7 +20809,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -21406,7 +21427,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21899,7 +21920,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ100">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR100">
         <v>1.15</v>
@@ -22024,7 +22045,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22102,7 +22123,7 @@
         <v>1</v>
       </c>
       <c r="AP101">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ101">
         <v>0.62</v>
@@ -22308,10 +22329,10 @@
         <v>1.33</v>
       </c>
       <c r="AP102">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ102">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR102">
         <v>1.15</v>
@@ -22436,7 +22457,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22848,7 +22869,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -22929,7 +22950,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ105">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR105">
         <v>0.97</v>
@@ -23338,7 +23359,7 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ107">
         <v>0.54</v>
@@ -23547,7 +23568,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ108">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR108">
         <v>2.03</v>
@@ -23750,7 +23771,7 @@
         <v>3</v>
       </c>
       <c r="AP109">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ109">
         <v>2.15</v>
@@ -23878,7 +23899,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -25810,7 +25831,7 @@
         <v>0.86</v>
       </c>
       <c r="AP119">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ119">
         <v>0.62</v>
@@ -25938,7 +25959,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26019,7 +26040,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ120">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR120">
         <v>2.02</v>
@@ -26431,7 +26452,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ122">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR122">
         <v>1.11</v>
@@ -26556,7 +26577,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26637,7 +26658,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ123">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR123">
         <v>1.04</v>
@@ -26762,7 +26783,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -27049,7 +27070,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ125">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR125">
         <v>2.03</v>
@@ -27174,7 +27195,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27252,7 +27273,7 @@
         <v>1.14</v>
       </c>
       <c r="AP126">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ126">
         <v>1.15</v>
@@ -27380,7 +27401,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27458,10 +27479,10 @@
         <v>1.83</v>
       </c>
       <c r="AP127">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ127">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR127">
         <v>1.37</v>
@@ -27586,7 +27607,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27792,7 +27813,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -28204,7 +28225,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28282,7 +28303,7 @@
         <v>1.67</v>
       </c>
       <c r="AP131">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ131">
         <v>1.54</v>
@@ -28410,7 +28431,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28822,7 +28843,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -28900,7 +28921,7 @@
         <v>0.29</v>
       </c>
       <c r="AP134">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ134">
         <v>0.46</v>
@@ -29646,7 +29667,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29727,7 +29748,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ138">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR138">
         <v>1.22</v>
@@ -29852,7 +29873,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -30139,7 +30160,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ140">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR140">
         <v>1.98</v>
@@ -30264,7 +30285,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30470,7 +30491,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30548,7 +30569,7 @@
         <v>0.38</v>
       </c>
       <c r="AP142">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ142">
         <v>0.46</v>
@@ -30676,7 +30697,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -30757,7 +30778,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ143">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR143">
         <v>1.64</v>
@@ -30963,7 +30984,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ144">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR144">
         <v>2.11</v>
@@ -31088,7 +31109,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31294,7 +31315,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31372,7 +31393,7 @@
         <v>2.38</v>
       </c>
       <c r="AP146">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ146">
         <v>2.15</v>
@@ -31578,7 +31599,7 @@
         <v>0.57</v>
       </c>
       <c r="AP147">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ147">
         <v>0.6899999999999999</v>
@@ -31706,7 +31727,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31912,7 +31933,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32324,7 +32345,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32530,7 +32551,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32736,7 +32757,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -33020,7 +33041,7 @@
         <v>1.86</v>
       </c>
       <c r="AP154">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ154">
         <v>1.54</v>
@@ -33354,7 +33375,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33560,7 +33581,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33638,7 +33659,7 @@
         <v>2.22</v>
       </c>
       <c r="AP157">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ157">
         <v>2.15</v>
@@ -33766,7 +33787,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33844,7 +33865,7 @@
         <v>0.78</v>
       </c>
       <c r="AP158">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ158">
         <v>1.15</v>
@@ -33972,7 +33993,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34050,7 +34071,7 @@
         <v>0.63</v>
       </c>
       <c r="AP159">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ159">
         <v>0.6899999999999999</v>
@@ -34256,7 +34277,7 @@
         <v>0.78</v>
       </c>
       <c r="AP160">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ160">
         <v>0.77</v>
@@ -34384,7 +34405,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34590,7 +34611,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34796,7 +34817,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -34877,7 +34898,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ163">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR163">
         <v>1.32</v>
@@ -35208,7 +35229,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35495,7 +35516,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ166">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR166">
         <v>1.12</v>
@@ -35701,7 +35722,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ167">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR167">
         <v>1.21</v>
@@ -36238,7 +36259,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36525,7 +36546,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ171">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR171">
         <v>1.66</v>
@@ -36856,7 +36877,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -37143,7 +37164,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ174">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR174">
         <v>1.43</v>
@@ -37268,7 +37289,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37346,7 +37367,7 @@
         <v>0.8</v>
       </c>
       <c r="AP175">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ175">
         <v>1.15</v>
@@ -37474,7 +37495,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -37758,7 +37779,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP177">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ177">
         <v>0.6899999999999999</v>
@@ -38092,7 +38113,7 @@
         <v>205</v>
       </c>
       <c r="P179" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="Q179">
         <v>8.5</v>
@@ -38173,7 +38194,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ179">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR179">
         <v>1.18</v>
@@ -38298,7 +38319,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="Q180">
         <v>4.75</v>
@@ -38376,7 +38397,7 @@
         <v>2.44</v>
       </c>
       <c r="AP180">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ180">
         <v>2.23</v>
@@ -38504,7 +38525,7 @@
         <v>207</v>
       </c>
       <c r="P181" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Q181">
         <v>6.5</v>
@@ -38582,7 +38603,7 @@
         <v>1.44</v>
       </c>
       <c r="AP181">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ181">
         <v>1.54</v>
@@ -38710,7 +38731,7 @@
         <v>167</v>
       </c>
       <c r="P182" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -39122,7 +39143,7 @@
         <v>208</v>
       </c>
       <c r="P184" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="Q184">
         <v>1.57</v>
@@ -39534,7 +39555,7 @@
         <v>209</v>
       </c>
       <c r="P186" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="Q186">
         <v>2.2</v>
@@ -39615,7 +39636,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ186">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR186">
         <v>1.19</v>
@@ -40233,7 +40254,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ189">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR189">
         <v>1.19</v>
@@ -40358,7 +40379,7 @@
         <v>184</v>
       </c>
       <c r="P190" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="Q190">
         <v>2.63</v>
@@ -40645,7 +40666,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ191">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR191">
         <v>1.28</v>
@@ -40770,7 +40791,7 @@
         <v>212</v>
       </c>
       <c r="P192" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -40848,10 +40869,10 @@
         <v>1.4</v>
       </c>
       <c r="AP192">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ192">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR192">
         <v>1.22</v>
@@ -40976,7 +40997,7 @@
         <v>213</v>
       </c>
       <c r="P193" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Q193">
         <v>2.8</v>
@@ -41054,7 +41075,7 @@
         <v>1.2</v>
       </c>
       <c r="AP193">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ193">
         <v>1.08</v>
@@ -41263,7 +41284,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ194">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR194">
         <v>1.46</v>
@@ -41388,7 +41409,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Q195">
         <v>1.67</v>
@@ -41672,7 +41693,7 @@
         <v>0.5</v>
       </c>
       <c r="AP196">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ196">
         <v>0.6899999999999999</v>
@@ -41800,7 +41821,7 @@
         <v>90</v>
       </c>
       <c r="P197" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q197">
         <v>7.5</v>
@@ -42084,7 +42105,7 @@
         <v>2.5</v>
       </c>
       <c r="AP198">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ198">
         <v>2.23</v>
@@ -42212,7 +42233,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42911,7 +42932,7 @@
         <v>2.77</v>
       </c>
       <c r="AQ202">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR202">
         <v>2.01</v>
@@ -43036,7 +43057,7 @@
         <v>218</v>
       </c>
       <c r="P203" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="Q203">
         <v>2.55</v>
@@ -43448,7 +43469,7 @@
         <v>219</v>
       </c>
       <c r="P205" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="Q205">
         <v>2.45</v>
@@ -43654,7 +43675,7 @@
         <v>220</v>
       </c>
       <c r="P206" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="Q206">
         <v>7</v>
@@ -44066,7 +44087,7 @@
         <v>166</v>
       </c>
       <c r="P208" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44350,7 +44371,7 @@
         <v>1.45</v>
       </c>
       <c r="AP209">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ209">
         <v>1.23</v>
@@ -44478,7 +44499,7 @@
         <v>90</v>
       </c>
       <c r="P210" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="Q210">
         <v>5.5</v>
@@ -44762,10 +44783,10 @@
         <v>1.27</v>
       </c>
       <c r="AP211">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ211">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR211">
         <v>1.51</v>
@@ -44968,10 +44989,10 @@
         <v>0.55</v>
       </c>
       <c r="AP212">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ212">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR212">
         <v>1.24</v>
@@ -45302,7 +45323,7 @@
         <v>90</v>
       </c>
       <c r="P214" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="Q214">
         <v>3.1</v>
@@ -45508,7 +45529,7 @@
         <v>224</v>
       </c>
       <c r="P215" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="Q215">
         <v>4.33</v>
@@ -45586,7 +45607,7 @@
         <v>2.36</v>
       </c>
       <c r="AP215">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ215">
         <v>2.23</v>
@@ -45920,7 +45941,7 @@
         <v>226</v>
       </c>
       <c r="P217" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="Q217">
         <v>3.3</v>
@@ -46126,7 +46147,7 @@
         <v>90</v>
       </c>
       <c r="P218" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="Q218">
         <v>3.4</v>
@@ -46332,7 +46353,7 @@
         <v>227</v>
       </c>
       <c r="P219" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="Q219">
         <v>2.88</v>
@@ -46950,7 +46971,7 @@
         <v>226</v>
       </c>
       <c r="P222" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q222">
         <v>2.7</v>
@@ -47156,7 +47177,7 @@
         <v>230</v>
       </c>
       <c r="P223" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="Q223">
         <v>6</v>
@@ -47362,7 +47383,7 @@
         <v>179</v>
       </c>
       <c r="P224" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="Q224">
         <v>6.25</v>
@@ -47774,7 +47795,7 @@
         <v>90</v>
       </c>
       <c r="P226" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="Q226">
         <v>5</v>
@@ -48392,7 +48413,7 @@
         <v>232</v>
       </c>
       <c r="P229" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="Q229">
         <v>1.8</v>
@@ -48549,6 +48570,1036 @@
       </c>
       <c r="BP229">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="230" spans="1:68">
+      <c r="A230" s="1">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>7574791</v>
+      </c>
+      <c r="C230" t="s">
+        <v>68</v>
+      </c>
+      <c r="D230" t="s">
+        <v>69</v>
+      </c>
+      <c r="E230" s="2">
+        <v>45732.52083333334</v>
+      </c>
+      <c r="F230">
+        <v>26</v>
+      </c>
+      <c r="G230" t="s">
+        <v>78</v>
+      </c>
+      <c r="H230" t="s">
+        <v>74</v>
+      </c>
+      <c r="I230">
+        <v>1</v>
+      </c>
+      <c r="J230">
+        <v>0</v>
+      </c>
+      <c r="K230">
+        <v>1</v>
+      </c>
+      <c r="L230">
+        <v>1</v>
+      </c>
+      <c r="M230">
+        <v>1</v>
+      </c>
+      <c r="N230">
+        <v>2</v>
+      </c>
+      <c r="O230" t="s">
+        <v>233</v>
+      </c>
+      <c r="P230" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q230">
+        <v>2.63</v>
+      </c>
+      <c r="R230">
+        <v>2.1</v>
+      </c>
+      <c r="S230">
+        <v>4.33</v>
+      </c>
+      <c r="T230">
+        <v>1.44</v>
+      </c>
+      <c r="U230">
+        <v>2.63</v>
+      </c>
+      <c r="V230">
+        <v>3.25</v>
+      </c>
+      <c r="W230">
+        <v>1.33</v>
+      </c>
+      <c r="X230">
+        <v>9</v>
+      </c>
+      <c r="Y230">
+        <v>1.07</v>
+      </c>
+      <c r="Z230">
+        <v>1.95</v>
+      </c>
+      <c r="AA230">
+        <v>3.3</v>
+      </c>
+      <c r="AB230">
+        <v>3.8</v>
+      </c>
+      <c r="AC230">
+        <v>1.06</v>
+      </c>
+      <c r="AD230">
+        <v>8.5</v>
+      </c>
+      <c r="AE230">
+        <v>1.36</v>
+      </c>
+      <c r="AF230">
+        <v>3.1</v>
+      </c>
+      <c r="AG230">
+        <v>2</v>
+      </c>
+      <c r="AH230">
+        <v>1.73</v>
+      </c>
+      <c r="AI230">
+        <v>1.91</v>
+      </c>
+      <c r="AJ230">
+        <v>1.91</v>
+      </c>
+      <c r="AK230">
+        <v>1.25</v>
+      </c>
+      <c r="AL230">
+        <v>1.31</v>
+      </c>
+      <c r="AM230">
+        <v>1.78</v>
+      </c>
+      <c r="AN230">
+        <v>1.08</v>
+      </c>
+      <c r="AO230">
+        <v>1.08</v>
+      </c>
+      <c r="AP230">
+        <v>1.08</v>
+      </c>
+      <c r="AQ230">
+        <v>1.08</v>
+      </c>
+      <c r="AR230">
+        <v>1.23</v>
+      </c>
+      <c r="AS230">
+        <v>1.2</v>
+      </c>
+      <c r="AT230">
+        <v>2.43</v>
+      </c>
+      <c r="AU230">
+        <v>3</v>
+      </c>
+      <c r="AV230">
+        <v>4</v>
+      </c>
+      <c r="AW230">
+        <v>2</v>
+      </c>
+      <c r="AX230">
+        <v>7</v>
+      </c>
+      <c r="AY230">
+        <v>6</v>
+      </c>
+      <c r="AZ230">
+        <v>15</v>
+      </c>
+      <c r="BA230">
+        <v>3</v>
+      </c>
+      <c r="BB230">
+        <v>4</v>
+      </c>
+      <c r="BC230">
+        <v>7</v>
+      </c>
+      <c r="BD230">
+        <v>1.53</v>
+      </c>
+      <c r="BE230">
+        <v>6.75</v>
+      </c>
+      <c r="BF230">
+        <v>2.8</v>
+      </c>
+      <c r="BG230">
+        <v>1.3</v>
+      </c>
+      <c r="BH230">
+        <v>3.05</v>
+      </c>
+      <c r="BI230">
+        <v>1.55</v>
+      </c>
+      <c r="BJ230">
+        <v>2.25</v>
+      </c>
+      <c r="BK230">
+        <v>1.88</v>
+      </c>
+      <c r="BL230">
+        <v>1.78</v>
+      </c>
+      <c r="BM230">
+        <v>2.4</v>
+      </c>
+      <c r="BN230">
+        <v>1.48</v>
+      </c>
+      <c r="BO230">
+        <v>3.1</v>
+      </c>
+      <c r="BP230">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="231" spans="1:68">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>7574796</v>
+      </c>
+      <c r="C231" t="s">
+        <v>68</v>
+      </c>
+      <c r="D231" t="s">
+        <v>69</v>
+      </c>
+      <c r="E231" s="2">
+        <v>45732.52083333334</v>
+      </c>
+      <c r="F231">
+        <v>26</v>
+      </c>
+      <c r="G231" t="s">
+        <v>82</v>
+      </c>
+      <c r="H231" t="s">
+        <v>72</v>
+      </c>
+      <c r="I231">
+        <v>1</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231">
+        <v>1</v>
+      </c>
+      <c r="L231">
+        <v>3</v>
+      </c>
+      <c r="M231">
+        <v>1</v>
+      </c>
+      <c r="N231">
+        <v>4</v>
+      </c>
+      <c r="O231" t="s">
+        <v>234</v>
+      </c>
+      <c r="P231" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q231">
+        <v>3.2</v>
+      </c>
+      <c r="R231">
+        <v>2</v>
+      </c>
+      <c r="S231">
+        <v>3.75</v>
+      </c>
+      <c r="T231">
+        <v>1.5</v>
+      </c>
+      <c r="U231">
+        <v>2.5</v>
+      </c>
+      <c r="V231">
+        <v>3.4</v>
+      </c>
+      <c r="W231">
+        <v>1.3</v>
+      </c>
+      <c r="X231">
+        <v>10</v>
+      </c>
+      <c r="Y231">
+        <v>1.06</v>
+      </c>
+      <c r="Z231">
+        <v>2.25</v>
+      </c>
+      <c r="AA231">
+        <v>3.2</v>
+      </c>
+      <c r="AB231">
+        <v>3.1</v>
+      </c>
+      <c r="AC231">
+        <v>1.07</v>
+      </c>
+      <c r="AD231">
+        <v>8</v>
+      </c>
+      <c r="AE231">
+        <v>1.4</v>
+      </c>
+      <c r="AF231">
+        <v>2.88</v>
+      </c>
+      <c r="AG231">
+        <v>2.2</v>
+      </c>
+      <c r="AH231">
+        <v>1.61</v>
+      </c>
+      <c r="AI231">
+        <v>1.95</v>
+      </c>
+      <c r="AJ231">
+        <v>1.8</v>
+      </c>
+      <c r="AK231">
+        <v>1.38</v>
+      </c>
+      <c r="AL231">
+        <v>1.33</v>
+      </c>
+      <c r="AM231">
+        <v>1.53</v>
+      </c>
+      <c r="AN231">
+        <v>1.67</v>
+      </c>
+      <c r="AO231">
+        <v>1.17</v>
+      </c>
+      <c r="AP231">
+        <v>1.77</v>
+      </c>
+      <c r="AQ231">
+        <v>1.08</v>
+      </c>
+      <c r="AR231">
+        <v>1.44</v>
+      </c>
+      <c r="AS231">
+        <v>1.13</v>
+      </c>
+      <c r="AT231">
+        <v>2.57</v>
+      </c>
+      <c r="AU231">
+        <v>7</v>
+      </c>
+      <c r="AV231">
+        <v>4</v>
+      </c>
+      <c r="AW231">
+        <v>6</v>
+      </c>
+      <c r="AX231">
+        <v>8</v>
+      </c>
+      <c r="AY231">
+        <v>15</v>
+      </c>
+      <c r="AZ231">
+        <v>14</v>
+      </c>
+      <c r="BA231">
+        <v>2</v>
+      </c>
+      <c r="BB231">
+        <v>5</v>
+      </c>
+      <c r="BC231">
+        <v>7</v>
+      </c>
+      <c r="BD231">
+        <v>1.86</v>
+      </c>
+      <c r="BE231">
+        <v>6.75</v>
+      </c>
+      <c r="BF231">
+        <v>2.12</v>
+      </c>
+      <c r="BG231">
+        <v>1.29</v>
+      </c>
+      <c r="BH231">
+        <v>3.15</v>
+      </c>
+      <c r="BI231">
+        <v>1.5</v>
+      </c>
+      <c r="BJ231">
+        <v>2.33</v>
+      </c>
+      <c r="BK231">
+        <v>1.82</v>
+      </c>
+      <c r="BL231">
+        <v>1.84</v>
+      </c>
+      <c r="BM231">
+        <v>2.3</v>
+      </c>
+      <c r="BN231">
+        <v>1.52</v>
+      </c>
+      <c r="BO231">
+        <v>2.95</v>
+      </c>
+      <c r="BP231">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="232" spans="1:68">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>7574795</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>69</v>
+      </c>
+      <c r="E232" s="2">
+        <v>45732.625</v>
+      </c>
+      <c r="F232">
+        <v>26</v>
+      </c>
+      <c r="G232" t="s">
+        <v>81</v>
+      </c>
+      <c r="H232" t="s">
+        <v>83</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>1</v>
+      </c>
+      <c r="K232">
+        <v>1</v>
+      </c>
+      <c r="L232">
+        <v>2</v>
+      </c>
+      <c r="M232">
+        <v>3</v>
+      </c>
+      <c r="N232">
+        <v>5</v>
+      </c>
+      <c r="O232" t="s">
+        <v>235</v>
+      </c>
+      <c r="P232" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q232">
+        <v>7</v>
+      </c>
+      <c r="R232">
+        <v>2.5</v>
+      </c>
+      <c r="S232">
+        <v>1.83</v>
+      </c>
+      <c r="T232">
+        <v>1.29</v>
+      </c>
+      <c r="U232">
+        <v>3.5</v>
+      </c>
+      <c r="V232">
+        <v>2.38</v>
+      </c>
+      <c r="W232">
+        <v>1.53</v>
+      </c>
+      <c r="X232">
+        <v>5.5</v>
+      </c>
+      <c r="Y232">
+        <v>1.14</v>
+      </c>
+      <c r="Z232">
+        <v>8</v>
+      </c>
+      <c r="AA232">
+        <v>5</v>
+      </c>
+      <c r="AB232">
+        <v>1.31</v>
+      </c>
+      <c r="AC232">
+        <v>1.03</v>
+      </c>
+      <c r="AD232">
+        <v>11</v>
+      </c>
+      <c r="AE232">
+        <v>1.18</v>
+      </c>
+      <c r="AF232">
+        <v>4.75</v>
+      </c>
+      <c r="AG232">
+        <v>1.6</v>
+      </c>
+      <c r="AH232">
+        <v>2.2</v>
+      </c>
+      <c r="AI232">
+        <v>1.91</v>
+      </c>
+      <c r="AJ232">
+        <v>1.91</v>
+      </c>
+      <c r="AK232">
+        <v>3</v>
+      </c>
+      <c r="AL232">
+        <v>1.16</v>
+      </c>
+      <c r="AM232">
+        <v>1.09</v>
+      </c>
+      <c r="AN232">
+        <v>1.75</v>
+      </c>
+      <c r="AO232">
+        <v>1.82</v>
+      </c>
+      <c r="AP232">
+        <v>1.62</v>
+      </c>
+      <c r="AQ232">
+        <v>1.92</v>
+      </c>
+      <c r="AR232">
+        <v>1.33</v>
+      </c>
+      <c r="AS232">
+        <v>1.79</v>
+      </c>
+      <c r="AT232">
+        <v>3.12</v>
+      </c>
+      <c r="AU232">
+        <v>3</v>
+      </c>
+      <c r="AV232">
+        <v>9</v>
+      </c>
+      <c r="AW232">
+        <v>5</v>
+      </c>
+      <c r="AX232">
+        <v>13</v>
+      </c>
+      <c r="AY232">
+        <v>9</v>
+      </c>
+      <c r="AZ232">
+        <v>24</v>
+      </c>
+      <c r="BA232">
+        <v>3</v>
+      </c>
+      <c r="BB232">
+        <v>11</v>
+      </c>
+      <c r="BC232">
+        <v>14</v>
+      </c>
+      <c r="BD232">
+        <v>4.3</v>
+      </c>
+      <c r="BE232">
+        <v>8</v>
+      </c>
+      <c r="BF232">
+        <v>1.25</v>
+      </c>
+      <c r="BG232">
+        <v>1.26</v>
+      </c>
+      <c r="BH232">
+        <v>3.3</v>
+      </c>
+      <c r="BI232">
+        <v>1.47</v>
+      </c>
+      <c r="BJ232">
+        <v>2.43</v>
+      </c>
+      <c r="BK232">
+        <v>1.76</v>
+      </c>
+      <c r="BL232">
+        <v>1.9</v>
+      </c>
+      <c r="BM232">
+        <v>2.18</v>
+      </c>
+      <c r="BN232">
+        <v>1.58</v>
+      </c>
+      <c r="BO232">
+        <v>2.8</v>
+      </c>
+      <c r="BP232">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7574792</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45732.72916666666</v>
+      </c>
+      <c r="F233">
+        <v>26</v>
+      </c>
+      <c r="G233" t="s">
+        <v>84</v>
+      </c>
+      <c r="H233" t="s">
+        <v>86</v>
+      </c>
+      <c r="I233">
+        <v>1</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>1</v>
+      </c>
+      <c r="L233">
+        <v>1</v>
+      </c>
+      <c r="M233">
+        <v>0</v>
+      </c>
+      <c r="N233">
+        <v>1</v>
+      </c>
+      <c r="O233" t="s">
+        <v>236</v>
+      </c>
+      <c r="P233" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q233">
+        <v>2.5</v>
+      </c>
+      <c r="R233">
+        <v>2</v>
+      </c>
+      <c r="S233">
+        <v>5.5</v>
+      </c>
+      <c r="T233">
+        <v>1.53</v>
+      </c>
+      <c r="U233">
+        <v>2.38</v>
+      </c>
+      <c r="V233">
+        <v>3.5</v>
+      </c>
+      <c r="W233">
+        <v>1.29</v>
+      </c>
+      <c r="X233">
+        <v>11</v>
+      </c>
+      <c r="Y233">
+        <v>1.05</v>
+      </c>
+      <c r="Z233">
+        <v>1.68</v>
+      </c>
+      <c r="AA233">
+        <v>3.45</v>
+      </c>
+      <c r="AB233">
+        <v>5</v>
+      </c>
+      <c r="AC233">
+        <v>1.09</v>
+      </c>
+      <c r="AD233">
+        <v>7</v>
+      </c>
+      <c r="AE233">
+        <v>1.45</v>
+      </c>
+      <c r="AF233">
+        <v>2.7</v>
+      </c>
+      <c r="AG233">
+        <v>2.3</v>
+      </c>
+      <c r="AH233">
+        <v>1.55</v>
+      </c>
+      <c r="AI233">
+        <v>2.2</v>
+      </c>
+      <c r="AJ233">
+        <v>1.62</v>
+      </c>
+      <c r="AK233">
+        <v>1.17</v>
+      </c>
+      <c r="AL233">
+        <v>1.31</v>
+      </c>
+      <c r="AM233">
+        <v>1.98</v>
+      </c>
+      <c r="AN233">
+        <v>1.67</v>
+      </c>
+      <c r="AO233">
+        <v>0.75</v>
+      </c>
+      <c r="AP233">
+        <v>1.77</v>
+      </c>
+      <c r="AQ233">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR233">
+        <v>1.25</v>
+      </c>
+      <c r="AS233">
+        <v>0.95</v>
+      </c>
+      <c r="AT233">
+        <v>2.2</v>
+      </c>
+      <c r="AU233">
+        <v>4</v>
+      </c>
+      <c r="AV233">
+        <v>4</v>
+      </c>
+      <c r="AW233">
+        <v>17</v>
+      </c>
+      <c r="AX233">
+        <v>4</v>
+      </c>
+      <c r="AY233">
+        <v>26</v>
+      </c>
+      <c r="AZ233">
+        <v>12</v>
+      </c>
+      <c r="BA233">
+        <v>6</v>
+      </c>
+      <c r="BB233">
+        <v>3</v>
+      </c>
+      <c r="BC233">
+        <v>9</v>
+      </c>
+      <c r="BD233">
+        <v>1.64</v>
+      </c>
+      <c r="BE233">
+        <v>8</v>
+      </c>
+      <c r="BF233">
+        <v>2.77</v>
+      </c>
+      <c r="BG233">
+        <v>1.43</v>
+      </c>
+      <c r="BH233">
+        <v>2.63</v>
+      </c>
+      <c r="BI233">
+        <v>1.74</v>
+      </c>
+      <c r="BJ233">
+        <v>2.02</v>
+      </c>
+      <c r="BK233">
+        <v>2.22</v>
+      </c>
+      <c r="BL233">
+        <v>1.62</v>
+      </c>
+      <c r="BM233">
+        <v>2.85</v>
+      </c>
+      <c r="BN233">
+        <v>1.37</v>
+      </c>
+      <c r="BO233">
+        <v>3.9</v>
+      </c>
+      <c r="BP233">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7574793</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45732.72916666666</v>
+      </c>
+      <c r="F234">
+        <v>26</v>
+      </c>
+      <c r="G234" t="s">
+        <v>85</v>
+      </c>
+      <c r="H234" t="s">
+        <v>87</v>
+      </c>
+      <c r="I234">
+        <v>1</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>1</v>
+      </c>
+      <c r="L234">
+        <v>2</v>
+      </c>
+      <c r="M234">
+        <v>0</v>
+      </c>
+      <c r="N234">
+        <v>2</v>
+      </c>
+      <c r="O234" t="s">
+        <v>237</v>
+      </c>
+      <c r="P234" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q234">
+        <v>2.05</v>
+      </c>
+      <c r="R234">
+        <v>2.2</v>
+      </c>
+      <c r="S234">
+        <v>7.5</v>
+      </c>
+      <c r="T234">
+        <v>1.44</v>
+      </c>
+      <c r="U234">
+        <v>2.63</v>
+      </c>
+      <c r="V234">
+        <v>3.25</v>
+      </c>
+      <c r="W234">
+        <v>1.33</v>
+      </c>
+      <c r="X234">
+        <v>9</v>
+      </c>
+      <c r="Y234">
+        <v>1.07</v>
+      </c>
+      <c r="Z234">
+        <v>1.44</v>
+      </c>
+      <c r="AA234">
+        <v>3.8</v>
+      </c>
+      <c r="AB234">
+        <v>7</v>
+      </c>
+      <c r="AC234">
+        <v>1.06</v>
+      </c>
+      <c r="AD234">
+        <v>8.5</v>
+      </c>
+      <c r="AE234">
+        <v>1.35</v>
+      </c>
+      <c r="AF234">
+        <v>3.1</v>
+      </c>
+      <c r="AG234">
+        <v>2.02</v>
+      </c>
+      <c r="AH234">
+        <v>1.75</v>
+      </c>
+      <c r="AI234">
+        <v>2.25</v>
+      </c>
+      <c r="AJ234">
+        <v>1.57</v>
+      </c>
+      <c r="AK234">
+        <v>1.09</v>
+      </c>
+      <c r="AL234">
+        <v>1.22</v>
+      </c>
+      <c r="AM234">
+        <v>2.65</v>
+      </c>
+      <c r="AN234">
+        <v>1.92</v>
+      </c>
+      <c r="AO234">
+        <v>0.58</v>
+      </c>
+      <c r="AP234">
+        <v>2</v>
+      </c>
+      <c r="AQ234">
+        <v>0.54</v>
+      </c>
+      <c r="AR234">
+        <v>1.56</v>
+      </c>
+      <c r="AS234">
+        <v>1.07</v>
+      </c>
+      <c r="AT234">
+        <v>2.63</v>
+      </c>
+      <c r="AU234">
+        <v>7</v>
+      </c>
+      <c r="AV234">
+        <v>2</v>
+      </c>
+      <c r="AW234">
+        <v>6</v>
+      </c>
+      <c r="AX234">
+        <v>6</v>
+      </c>
+      <c r="AY234">
+        <v>15</v>
+      </c>
+      <c r="AZ234">
+        <v>8</v>
+      </c>
+      <c r="BA234">
+        <v>8</v>
+      </c>
+      <c r="BB234">
+        <v>2</v>
+      </c>
+      <c r="BC234">
+        <v>10</v>
+      </c>
+      <c r="BD234">
+        <v>1.23</v>
+      </c>
+      <c r="BE234">
+        <v>8.5</v>
+      </c>
+      <c r="BF234">
+        <v>4.4</v>
+      </c>
+      <c r="BG234">
+        <v>1.2</v>
+      </c>
+      <c r="BH234">
+        <v>3.9</v>
+      </c>
+      <c r="BI234">
+        <v>1.36</v>
+      </c>
+      <c r="BJ234">
+        <v>2.8</v>
+      </c>
+      <c r="BK234">
+        <v>1.58</v>
+      </c>
+      <c r="BL234">
+        <v>2.15</v>
+      </c>
+      <c r="BM234">
+        <v>1.9</v>
+      </c>
+      <c r="BN234">
+        <v>1.76</v>
+      </c>
+      <c r="BO234">
+        <v>2.4</v>
+      </c>
+      <c r="BP234">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="346">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -730,6 +730,12 @@
     <t>['10', '66']</t>
   </si>
   <si>
+    <t>['30', '62']</t>
+  </si>
+  <si>
+    <t>['39', '44']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -1034,6 +1040,18 @@
   </si>
   <si>
     <t>['30', '53', '80']</t>
+  </si>
+  <si>
+    <t>['22', '51', '90+7']</t>
+  </si>
+  <si>
+    <t>['21']</t>
+  </si>
+  <si>
+    <t>['52', '81', '89']</t>
+  </si>
+  <si>
+    <t>['68']</t>
   </si>
 </sst>
 </file>
@@ -1395,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP234"/>
+  <dimension ref="A1:BP238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1732,7 +1750,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ2">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1857,7 +1875,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2141,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ4">
         <v>0.6899999999999999</v>
@@ -2475,7 +2493,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2762,7 +2780,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ7">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2887,7 +2905,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -3171,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ9">
         <v>0.54</v>
@@ -3505,7 +3523,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3711,7 +3729,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3789,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ12">
         <v>0.6899999999999999</v>
@@ -4123,7 +4141,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4204,7 +4222,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ14">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4535,7 +4553,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4616,7 +4634,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ16">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4947,7 +4965,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -5153,7 +5171,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5231,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ19">
         <v>1.23</v>
@@ -5359,7 +5377,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5440,7 +5458,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ20">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR20">
         <v>1.56</v>
@@ -5565,7 +5583,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -5643,7 +5661,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ21">
         <v>1.54</v>
@@ -5852,7 +5870,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ22">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR22">
         <v>1.3</v>
@@ -7085,7 +7103,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ28">
         <v>0.62</v>
@@ -7213,7 +7231,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7294,7 +7312,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ29">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR29">
         <v>1.3</v>
@@ -7419,7 +7437,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7625,7 +7643,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -7703,7 +7721,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ31">
         <v>1.08</v>
@@ -8530,7 +8548,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ35">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR35">
         <v>1.11</v>
@@ -8939,7 +8957,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ37">
         <v>2.23</v>
@@ -9067,7 +9085,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9148,7 +9166,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ38">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR38">
         <v>0.93</v>
@@ -9273,7 +9291,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9351,7 +9369,7 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ39">
         <v>0.62</v>
@@ -9560,7 +9578,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ40">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR40">
         <v>1.32</v>
@@ -9685,7 +9703,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9891,7 +9909,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -10097,7 +10115,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10509,7 +10527,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10587,7 +10605,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ45">
         <v>1.15</v>
@@ -10715,7 +10733,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10793,7 +10811,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ46">
         <v>0.6899999999999999</v>
@@ -10921,7 +10939,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -11127,7 +11145,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11539,7 +11557,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11951,7 +11969,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -12029,7 +12047,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ52">
         <v>1.08</v>
@@ -12238,7 +12256,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ53">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR53">
         <v>1</v>
@@ -12569,7 +12587,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12650,7 +12668,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ55">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR55">
         <v>1.28</v>
@@ -12775,7 +12793,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -12856,7 +12874,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ56">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR56">
         <v>0.98</v>
@@ -13059,7 +13077,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ57">
         <v>0.62</v>
@@ -13187,7 +13205,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13265,7 +13283,7 @@
         <v>2</v>
       </c>
       <c r="AP58">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ58">
         <v>1.15</v>
@@ -13393,7 +13411,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -13886,7 +13904,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ61">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR61">
         <v>2.38</v>
@@ -14089,10 +14107,10 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ62">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR62">
         <v>1.53</v>
@@ -14913,7 +14931,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ66">
         <v>0.54</v>
@@ -15865,7 +15883,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -16071,7 +16089,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16355,7 +16373,7 @@
         <v>0.5</v>
       </c>
       <c r="AP73">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ73">
         <v>0.46</v>
@@ -16483,7 +16501,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16689,7 +16707,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16770,7 +16788,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ75">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR75">
         <v>0.89</v>
@@ -16895,7 +16913,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17101,7 +17119,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17182,7 +17200,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ77">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR77">
         <v>1.24</v>
@@ -17385,7 +17403,7 @@
         <v>0.25</v>
       </c>
       <c r="AP78">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ78">
         <v>0.77</v>
@@ -17594,7 +17612,7 @@
         <v>2.77</v>
       </c>
       <c r="AQ79">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR79">
         <v>2.16</v>
@@ -17719,7 +17737,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17797,7 +17815,7 @@
         <v>1.75</v>
       </c>
       <c r="AP80">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ80">
         <v>1.15</v>
@@ -17925,7 +17943,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -18131,7 +18149,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18337,7 +18355,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18543,7 +18561,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18624,7 +18642,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ84">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR84">
         <v>1.17</v>
@@ -18749,7 +18767,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18827,7 +18845,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ85">
         <v>0.6899999999999999</v>
@@ -18955,7 +18973,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19367,7 +19385,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19985,7 +20003,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -20191,7 +20209,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20269,7 +20287,7 @@
         <v>0.2</v>
       </c>
       <c r="AP92">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ92">
         <v>0.77</v>
@@ -20684,7 +20702,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ94">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR94">
         <v>1.13</v>
@@ -20809,7 +20827,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -20890,7 +20908,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ95">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR95">
         <v>1.16</v>
@@ -21093,7 +21111,7 @@
         <v>0.4</v>
       </c>
       <c r="AP96">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ96">
         <v>0.46</v>
@@ -21427,7 +21445,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21505,10 +21523,10 @@
         <v>3</v>
       </c>
       <c r="AP98">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ98">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR98">
         <v>1.75</v>
@@ -22045,7 +22063,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22457,7 +22475,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22869,7 +22887,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -22950,7 +22968,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ105">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR105">
         <v>0.97</v>
@@ -23774,7 +23792,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ109">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR109">
         <v>1.17</v>
@@ -23899,7 +23917,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -23977,7 +23995,7 @@
         <v>0.4</v>
       </c>
       <c r="AP110">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ110">
         <v>1.08</v>
@@ -24183,7 +24201,7 @@
         <v>0.33</v>
       </c>
       <c r="AP111">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ111">
         <v>0.46</v>
@@ -24598,7 +24616,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ113">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR113">
         <v>1.38</v>
@@ -25213,7 +25231,7 @@
         <v>0.4</v>
       </c>
       <c r="AP116">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ116">
         <v>0.6899999999999999</v>
@@ -25419,10 +25437,10 @@
         <v>0.67</v>
       </c>
       <c r="AP117">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ117">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR117">
         <v>1.23</v>
@@ -25959,7 +25977,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26452,7 +26470,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ122">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR122">
         <v>1.11</v>
@@ -26577,7 +26595,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26783,7 +26801,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -26861,7 +26879,7 @@
         <v>1.33</v>
       </c>
       <c r="AP124">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ124">
         <v>1.23</v>
@@ -27195,7 +27213,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27401,7 +27419,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27482,7 +27500,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ127">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR127">
         <v>1.37</v>
@@ -27607,7 +27625,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27685,10 +27703,10 @@
         <v>0.57</v>
       </c>
       <c r="AP128">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ128">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR128">
         <v>1.24</v>
@@ -27813,7 +27831,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -28225,7 +28243,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28431,7 +28449,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28715,10 +28733,10 @@
         <v>2.57</v>
       </c>
       <c r="AP133">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ133">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR133">
         <v>1.29</v>
@@ -28843,7 +28861,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -29333,10 +29351,10 @@
         <v>0.43</v>
       </c>
       <c r="AP136">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ136">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR136">
         <v>1.19</v>
@@ -29667,7 +29685,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29873,7 +29891,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -30285,7 +30303,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30491,7 +30509,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30697,7 +30715,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -30775,7 +30793,7 @@
         <v>1.14</v>
       </c>
       <c r="AP143">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ143">
         <v>1.08</v>
@@ -30984,7 +31002,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ144">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR144">
         <v>2.11</v>
@@ -31109,7 +31127,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31315,7 +31333,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31396,7 +31414,7 @@
         <v>2</v>
       </c>
       <c r="AQ146">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR146">
         <v>1.3</v>
@@ -31727,7 +31745,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31933,7 +31951,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32014,7 +32032,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ149">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR149">
         <v>1.35</v>
@@ -32345,7 +32363,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32423,7 +32441,7 @@
         <v>1.29</v>
       </c>
       <c r="AP151">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ151">
         <v>1.23</v>
@@ -32551,7 +32569,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32629,7 +32647,7 @@
         <v>0.43</v>
       </c>
       <c r="AP152">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ152">
         <v>1.08</v>
@@ -32757,7 +32775,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -32835,10 +32853,10 @@
         <v>0.38</v>
       </c>
       <c r="AP153">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ153">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR153">
         <v>1.2</v>
@@ -33375,7 +33393,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33581,7 +33599,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33662,7 +33680,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ157">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR157">
         <v>1.39</v>
@@ -33787,7 +33805,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33868,7 +33886,7 @@
         <v>2</v>
       </c>
       <c r="AQ158">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR158">
         <v>1.33</v>
@@ -33993,7 +34011,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34405,7 +34423,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34483,7 +34501,7 @@
         <v>2.38</v>
       </c>
       <c r="AP161">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ161">
         <v>2.23</v>
@@ -34611,7 +34629,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34689,7 +34707,7 @@
         <v>1.63</v>
       </c>
       <c r="AP162">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ162">
         <v>1.54</v>
@@ -34817,7 +34835,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -35229,7 +35247,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35310,7 +35328,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ165">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR165">
         <v>1.12</v>
@@ -35719,10 +35737,10 @@
         <v>1.75</v>
       </c>
       <c r="AP167">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ167">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR167">
         <v>1.21</v>
@@ -36259,7 +36277,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36543,7 +36561,7 @@
         <v>1</v>
       </c>
       <c r="AP171">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ171">
         <v>0.6899999999999999</v>
@@ -36877,7 +36895,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -37289,7 +37307,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37370,7 +37388,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ175">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR175">
         <v>1.25</v>
@@ -37495,7 +37513,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -37573,7 +37591,7 @@
         <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ176">
         <v>1.08</v>
@@ -38113,7 +38131,7 @@
         <v>205</v>
       </c>
       <c r="P179" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q179">
         <v>8.5</v>
@@ -38191,10 +38209,10 @@
         <v>1.56</v>
       </c>
       <c r="AP179">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ179">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR179">
         <v>1.18</v>
@@ -38319,7 +38337,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q180">
         <v>4.75</v>
@@ -38525,7 +38543,7 @@
         <v>207</v>
       </c>
       <c r="P181" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q181">
         <v>6.5</v>
@@ -38731,7 +38749,7 @@
         <v>167</v>
       </c>
       <c r="P182" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -38812,7 +38830,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ182">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR182">
         <v>2.01</v>
@@ -39143,7 +39161,7 @@
         <v>208</v>
       </c>
       <c r="P184" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q184">
         <v>1.57</v>
@@ -39555,7 +39573,7 @@
         <v>209</v>
       </c>
       <c r="P186" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q186">
         <v>2.2</v>
@@ -40045,7 +40063,7 @@
         <v>0.6</v>
       </c>
       <c r="AP188">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ188">
         <v>0.54</v>
@@ -40251,7 +40269,7 @@
         <v>0.33</v>
       </c>
       <c r="AP189">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ189">
         <v>0.54</v>
@@ -40379,7 +40397,7 @@
         <v>184</v>
       </c>
       <c r="P190" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q190">
         <v>2.63</v>
@@ -40460,7 +40478,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ190">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR190">
         <v>1.16</v>
@@ -40791,7 +40809,7 @@
         <v>212</v>
       </c>
       <c r="P192" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -40997,7 +41015,7 @@
         <v>213</v>
       </c>
       <c r="P193" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q193">
         <v>2.8</v>
@@ -41284,7 +41302,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ194">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR194">
         <v>1.46</v>
@@ -41409,7 +41427,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q195">
         <v>1.67</v>
@@ -41490,7 +41508,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ195">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR195">
         <v>2.07</v>
@@ -41821,7 +41839,7 @@
         <v>90</v>
       </c>
       <c r="P197" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q197">
         <v>7.5</v>
@@ -42233,7 +42251,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42311,7 +42329,7 @@
         <v>1.3</v>
       </c>
       <c r="AP199">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ199">
         <v>1.23</v>
@@ -42517,7 +42535,7 @@
         <v>0.55</v>
       </c>
       <c r="AP200">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ200">
         <v>0.46</v>
@@ -42723,7 +42741,7 @@
         <v>0.55</v>
       </c>
       <c r="AP201">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ201">
         <v>0.54</v>
@@ -43057,7 +43075,7 @@
         <v>218</v>
       </c>
       <c r="P203" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q203">
         <v>2.55</v>
@@ -43138,7 +43156,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ203">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR203">
         <v>1.23</v>
@@ -43341,7 +43359,7 @@
         <v>1.6</v>
       </c>
       <c r="AP204">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ204">
         <v>1.54</v>
@@ -43469,7 +43487,7 @@
         <v>219</v>
       </c>
       <c r="P205" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q205">
         <v>2.45</v>
@@ -43675,7 +43693,7 @@
         <v>220</v>
       </c>
       <c r="P206" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q206">
         <v>7</v>
@@ -43756,7 +43774,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ206">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR206">
         <v>1.22</v>
@@ -44087,7 +44105,7 @@
         <v>166</v>
       </c>
       <c r="P208" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44499,7 +44517,7 @@
         <v>90</v>
       </c>
       <c r="P210" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q210">
         <v>5.5</v>
@@ -45323,7 +45341,7 @@
         <v>90</v>
       </c>
       <c r="P214" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q214">
         <v>3.1</v>
@@ -45529,7 +45547,7 @@
         <v>224</v>
       </c>
       <c r="P215" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q215">
         <v>4.33</v>
@@ -45941,7 +45959,7 @@
         <v>226</v>
       </c>
       <c r="P217" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q217">
         <v>3.3</v>
@@ -46019,7 +46037,7 @@
         <v>0.5</v>
       </c>
       <c r="AP217">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ217">
         <v>0.54</v>
@@ -46147,7 +46165,7 @@
         <v>90</v>
       </c>
       <c r="P218" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q218">
         <v>3.4</v>
@@ -46228,7 +46246,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ218">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR218">
         <v>1.22</v>
@@ -46353,7 +46371,7 @@
         <v>227</v>
       </c>
       <c r="P219" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q219">
         <v>2.88</v>
@@ -46843,7 +46861,7 @@
         <v>1.67</v>
       </c>
       <c r="AP221">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ221">
         <v>1.54</v>
@@ -46971,7 +46989,7 @@
         <v>226</v>
       </c>
       <c r="P222" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q222">
         <v>2.7</v>
@@ -47177,7 +47195,7 @@
         <v>230</v>
       </c>
       <c r="P223" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q223">
         <v>6</v>
@@ -47255,10 +47273,10 @@
         <v>2.08</v>
       </c>
       <c r="AP223">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ223">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR223">
         <v>1.24</v>
@@ -47383,7 +47401,7 @@
         <v>179</v>
       </c>
       <c r="P224" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q224">
         <v>6.25</v>
@@ -47670,7 +47688,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ225">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR225">
         <v>1.18</v>
@@ -47795,7 +47813,7 @@
         <v>90</v>
       </c>
       <c r="P226" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q226">
         <v>5</v>
@@ -48079,7 +48097,7 @@
         <v>1.42</v>
       </c>
       <c r="AP227">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ227">
         <v>1.54</v>
@@ -48413,7 +48431,7 @@
         <v>232</v>
       </c>
       <c r="P229" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q229">
         <v>1.8</v>
@@ -48619,7 +48637,7 @@
         <v>233</v>
       </c>
       <c r="P230" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q230">
         <v>2.63</v>
@@ -48825,7 +48843,7 @@
         <v>234</v>
       </c>
       <c r="P231" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q231">
         <v>3.2</v>
@@ -49031,7 +49049,7 @@
         <v>235</v>
       </c>
       <c r="P232" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q232">
         <v>7</v>
@@ -49112,7 +49130,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ232">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR232">
         <v>1.33</v>
@@ -49600,6 +49618,830 @@
       </c>
       <c r="BP234">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7574777</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45744.71875</v>
+      </c>
+      <c r="F235">
+        <v>24</v>
+      </c>
+      <c r="G235" t="s">
+        <v>80</v>
+      </c>
+      <c r="H235" t="s">
+        <v>83</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>1</v>
+      </c>
+      <c r="K235">
+        <v>1</v>
+      </c>
+      <c r="L235">
+        <v>0</v>
+      </c>
+      <c r="M235">
+        <v>3</v>
+      </c>
+      <c r="N235">
+        <v>3</v>
+      </c>
+      <c r="O235" t="s">
+        <v>90</v>
+      </c>
+      <c r="P235" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q235">
+        <v>7.5</v>
+      </c>
+      <c r="R235">
+        <v>2.38</v>
+      </c>
+      <c r="S235">
+        <v>1.91</v>
+      </c>
+      <c r="T235">
+        <v>1.36</v>
+      </c>
+      <c r="U235">
+        <v>3</v>
+      </c>
+      <c r="V235">
+        <v>2.63</v>
+      </c>
+      <c r="W235">
+        <v>1.44</v>
+      </c>
+      <c r="X235">
+        <v>7</v>
+      </c>
+      <c r="Y235">
+        <v>1.1</v>
+      </c>
+      <c r="Z235">
+        <v>7.5</v>
+      </c>
+      <c r="AA235">
+        <v>4.7</v>
+      </c>
+      <c r="AB235">
+        <v>1.33</v>
+      </c>
+      <c r="AC235">
+        <v>0</v>
+      </c>
+      <c r="AD235">
+        <v>0</v>
+      </c>
+      <c r="AE235">
+        <v>0</v>
+      </c>
+      <c r="AF235">
+        <v>0</v>
+      </c>
+      <c r="AG235">
+        <v>1.75</v>
+      </c>
+      <c r="AH235">
+        <v>2</v>
+      </c>
+      <c r="AI235">
+        <v>2</v>
+      </c>
+      <c r="AJ235">
+        <v>1.75</v>
+      </c>
+      <c r="AK235">
+        <v>0</v>
+      </c>
+      <c r="AL235">
+        <v>0</v>
+      </c>
+      <c r="AM235">
+        <v>0</v>
+      </c>
+      <c r="AN235">
+        <v>1.33</v>
+      </c>
+      <c r="AO235">
+        <v>1.92</v>
+      </c>
+      <c r="AP235">
+        <v>1.23</v>
+      </c>
+      <c r="AQ235">
+        <v>2</v>
+      </c>
+      <c r="AR235">
+        <v>1.26</v>
+      </c>
+      <c r="AS235">
+        <v>1.85</v>
+      </c>
+      <c r="AT235">
+        <v>3.11</v>
+      </c>
+      <c r="AU235">
+        <v>3</v>
+      </c>
+      <c r="AV235">
+        <v>8</v>
+      </c>
+      <c r="AW235">
+        <v>5</v>
+      </c>
+      <c r="AX235">
+        <v>11</v>
+      </c>
+      <c r="AY235">
+        <v>9</v>
+      </c>
+      <c r="AZ235">
+        <v>24</v>
+      </c>
+      <c r="BA235">
+        <v>5</v>
+      </c>
+      <c r="BB235">
+        <v>2</v>
+      </c>
+      <c r="BC235">
+        <v>7</v>
+      </c>
+      <c r="BD235">
+        <v>0</v>
+      </c>
+      <c r="BE235">
+        <v>0</v>
+      </c>
+      <c r="BF235">
+        <v>0</v>
+      </c>
+      <c r="BG235">
+        <v>0</v>
+      </c>
+      <c r="BH235">
+        <v>0</v>
+      </c>
+      <c r="BI235">
+        <v>0</v>
+      </c>
+      <c r="BJ235">
+        <v>0</v>
+      </c>
+      <c r="BK235">
+        <v>0</v>
+      </c>
+      <c r="BL235">
+        <v>0</v>
+      </c>
+      <c r="BM235">
+        <v>0</v>
+      </c>
+      <c r="BN235">
+        <v>0</v>
+      </c>
+      <c r="BO235">
+        <v>0</v>
+      </c>
+      <c r="BP235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7574800</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45745.52083333334</v>
+      </c>
+      <c r="F236">
+        <v>27</v>
+      </c>
+      <c r="G236" t="s">
+        <v>72</v>
+      </c>
+      <c r="H236" t="s">
+        <v>81</v>
+      </c>
+      <c r="I236">
+        <v>1</v>
+      </c>
+      <c r="J236">
+        <v>1</v>
+      </c>
+      <c r="K236">
+        <v>2</v>
+      </c>
+      <c r="L236">
+        <v>2</v>
+      </c>
+      <c r="M236">
+        <v>1</v>
+      </c>
+      <c r="N236">
+        <v>3</v>
+      </c>
+      <c r="O236" t="s">
+        <v>238</v>
+      </c>
+      <c r="P236" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q236">
+        <v>2.88</v>
+      </c>
+      <c r="R236">
+        <v>2.1</v>
+      </c>
+      <c r="S236">
+        <v>4</v>
+      </c>
+      <c r="T236">
+        <v>1.44</v>
+      </c>
+      <c r="U236">
+        <v>2.63</v>
+      </c>
+      <c r="V236">
+        <v>3.25</v>
+      </c>
+      <c r="W236">
+        <v>1.33</v>
+      </c>
+      <c r="X236">
+        <v>9</v>
+      </c>
+      <c r="Y236">
+        <v>1.07</v>
+      </c>
+      <c r="Z236">
+        <v>2.1</v>
+      </c>
+      <c r="AA236">
+        <v>3.2</v>
+      </c>
+      <c r="AB236">
+        <v>3.3</v>
+      </c>
+      <c r="AC236">
+        <v>0</v>
+      </c>
+      <c r="AD236">
+        <v>0</v>
+      </c>
+      <c r="AE236">
+        <v>0</v>
+      </c>
+      <c r="AF236">
+        <v>0</v>
+      </c>
+      <c r="AG236">
+        <v>2.15</v>
+      </c>
+      <c r="AH236">
+        <v>1.65</v>
+      </c>
+      <c r="AI236">
+        <v>1.8</v>
+      </c>
+      <c r="AJ236">
+        <v>1.95</v>
+      </c>
+      <c r="AK236">
+        <v>0</v>
+      </c>
+      <c r="AL236">
+        <v>0</v>
+      </c>
+      <c r="AM236">
+        <v>0</v>
+      </c>
+      <c r="AN236">
+        <v>1.69</v>
+      </c>
+      <c r="AO236">
+        <v>0.62</v>
+      </c>
+      <c r="AP236">
+        <v>1.79</v>
+      </c>
+      <c r="AQ236">
+        <v>0.57</v>
+      </c>
+      <c r="AR236">
+        <v>1.24</v>
+      </c>
+      <c r="AS236">
+        <v>1.02</v>
+      </c>
+      <c r="AT236">
+        <v>2.26</v>
+      </c>
+      <c r="AU236">
+        <v>-1</v>
+      </c>
+      <c r="AV236">
+        <v>-1</v>
+      </c>
+      <c r="AW236">
+        <v>-1</v>
+      </c>
+      <c r="AX236">
+        <v>-1</v>
+      </c>
+      <c r="AY236">
+        <v>-1</v>
+      </c>
+      <c r="AZ236">
+        <v>-1</v>
+      </c>
+      <c r="BA236">
+        <v>-1</v>
+      </c>
+      <c r="BB236">
+        <v>-1</v>
+      </c>
+      <c r="BC236">
+        <v>-1</v>
+      </c>
+      <c r="BD236">
+        <v>0</v>
+      </c>
+      <c r="BE236">
+        <v>0</v>
+      </c>
+      <c r="BF236">
+        <v>0</v>
+      </c>
+      <c r="BG236">
+        <v>0</v>
+      </c>
+      <c r="BH236">
+        <v>0</v>
+      </c>
+      <c r="BI236">
+        <v>0</v>
+      </c>
+      <c r="BJ236">
+        <v>0</v>
+      </c>
+      <c r="BK236">
+        <v>0</v>
+      </c>
+      <c r="BL236">
+        <v>0</v>
+      </c>
+      <c r="BM236">
+        <v>0</v>
+      </c>
+      <c r="BN236">
+        <v>0</v>
+      </c>
+      <c r="BO236">
+        <v>0</v>
+      </c>
+      <c r="BP236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7574798</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45745.625</v>
+      </c>
+      <c r="F237">
+        <v>27</v>
+      </c>
+      <c r="G237" t="s">
+        <v>87</v>
+      </c>
+      <c r="H237" t="s">
+        <v>70</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>0</v>
+      </c>
+      <c r="L237">
+        <v>0</v>
+      </c>
+      <c r="M237">
+        <v>3</v>
+      </c>
+      <c r="N237">
+        <v>3</v>
+      </c>
+      <c r="O237" t="s">
+        <v>90</v>
+      </c>
+      <c r="P237" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q237">
+        <v>8</v>
+      </c>
+      <c r="R237">
+        <v>2.5</v>
+      </c>
+      <c r="S237">
+        <v>1.83</v>
+      </c>
+      <c r="T237">
+        <v>1.33</v>
+      </c>
+      <c r="U237">
+        <v>3.25</v>
+      </c>
+      <c r="V237">
+        <v>2.63</v>
+      </c>
+      <c r="W237">
+        <v>1.44</v>
+      </c>
+      <c r="X237">
+        <v>6.5</v>
+      </c>
+      <c r="Y237">
+        <v>1.11</v>
+      </c>
+      <c r="Z237">
+        <v>8</v>
+      </c>
+      <c r="AA237">
+        <v>4.9</v>
+      </c>
+      <c r="AB237">
+        <v>1.33</v>
+      </c>
+      <c r="AC237">
+        <v>0</v>
+      </c>
+      <c r="AD237">
+        <v>0</v>
+      </c>
+      <c r="AE237">
+        <v>1.78</v>
+      </c>
+      <c r="AF237">
+        <v>2.08</v>
+      </c>
+      <c r="AG237">
+        <v>1.67</v>
+      </c>
+      <c r="AH237">
+        <v>2.1</v>
+      </c>
+      <c r="AI237">
+        <v>2.05</v>
+      </c>
+      <c r="AJ237">
+        <v>1.7</v>
+      </c>
+      <c r="AK237">
+        <v>0</v>
+      </c>
+      <c r="AL237">
+        <v>0</v>
+      </c>
+      <c r="AM237">
+        <v>0</v>
+      </c>
+      <c r="AN237">
+        <v>1.23</v>
+      </c>
+      <c r="AO237">
+        <v>2.15</v>
+      </c>
+      <c r="AP237">
+        <v>1.14</v>
+      </c>
+      <c r="AQ237">
+        <v>2.21</v>
+      </c>
+      <c r="AR237">
+        <v>1.14</v>
+      </c>
+      <c r="AS237">
+        <v>1.91</v>
+      </c>
+      <c r="AT237">
+        <v>3.05</v>
+      </c>
+      <c r="AU237">
+        <v>2</v>
+      </c>
+      <c r="AV237">
+        <v>8</v>
+      </c>
+      <c r="AW237">
+        <v>7</v>
+      </c>
+      <c r="AX237">
+        <v>7</v>
+      </c>
+      <c r="AY237">
+        <v>12</v>
+      </c>
+      <c r="AZ237">
+        <v>16</v>
+      </c>
+      <c r="BA237">
+        <v>3</v>
+      </c>
+      <c r="BB237">
+        <v>2</v>
+      </c>
+      <c r="BC237">
+        <v>5</v>
+      </c>
+      <c r="BD237">
+        <v>0</v>
+      </c>
+      <c r="BE237">
+        <v>0</v>
+      </c>
+      <c r="BF237">
+        <v>0</v>
+      </c>
+      <c r="BG237">
+        <v>0</v>
+      </c>
+      <c r="BH237">
+        <v>0</v>
+      </c>
+      <c r="BI237">
+        <v>0</v>
+      </c>
+      <c r="BJ237">
+        <v>0</v>
+      </c>
+      <c r="BK237">
+        <v>0</v>
+      </c>
+      <c r="BL237">
+        <v>0</v>
+      </c>
+      <c r="BM237">
+        <v>0</v>
+      </c>
+      <c r="BN237">
+        <v>0</v>
+      </c>
+      <c r="BO237">
+        <v>0</v>
+      </c>
+      <c r="BP237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7574802</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45745.72916666666</v>
+      </c>
+      <c r="F238">
+        <v>27</v>
+      </c>
+      <c r="G238" t="s">
+        <v>77</v>
+      </c>
+      <c r="H238" t="s">
+        <v>78</v>
+      </c>
+      <c r="I238">
+        <v>2</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238">
+        <v>2</v>
+      </c>
+      <c r="L238">
+        <v>2</v>
+      </c>
+      <c r="M238">
+        <v>1</v>
+      </c>
+      <c r="N238">
+        <v>3</v>
+      </c>
+      <c r="O238" t="s">
+        <v>239</v>
+      </c>
+      <c r="P238" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q238">
+        <v>2.3</v>
+      </c>
+      <c r="R238">
+        <v>2.25</v>
+      </c>
+      <c r="S238">
+        <v>5</v>
+      </c>
+      <c r="T238">
+        <v>1.36</v>
+      </c>
+      <c r="U238">
+        <v>3</v>
+      </c>
+      <c r="V238">
+        <v>2.75</v>
+      </c>
+      <c r="W238">
+        <v>1.4</v>
+      </c>
+      <c r="X238">
+        <v>7</v>
+      </c>
+      <c r="Y238">
+        <v>1.1</v>
+      </c>
+      <c r="Z238">
+        <v>1.69</v>
+      </c>
+      <c r="AA238">
+        <v>3.6</v>
+      </c>
+      <c r="AB238">
+        <v>4.7</v>
+      </c>
+      <c r="AC238">
+        <v>0</v>
+      </c>
+      <c r="AD238">
+        <v>0</v>
+      </c>
+      <c r="AE238">
+        <v>0</v>
+      </c>
+      <c r="AF238">
+        <v>0</v>
+      </c>
+      <c r="AG238">
+        <v>1.83</v>
+      </c>
+      <c r="AH238">
+        <v>1.91</v>
+      </c>
+      <c r="AI238">
+        <v>1.8</v>
+      </c>
+      <c r="AJ238">
+        <v>1.95</v>
+      </c>
+      <c r="AK238">
+        <v>0</v>
+      </c>
+      <c r="AL238">
+        <v>0</v>
+      </c>
+      <c r="AM238">
+        <v>0</v>
+      </c>
+      <c r="AN238">
+        <v>1.85</v>
+      </c>
+      <c r="AO238">
+        <v>1.15</v>
+      </c>
+      <c r="AP238">
+        <v>1.93</v>
+      </c>
+      <c r="AQ238">
+        <v>1.07</v>
+      </c>
+      <c r="AR238">
+        <v>1.69</v>
+      </c>
+      <c r="AS238">
+        <v>1.36</v>
+      </c>
+      <c r="AT238">
+        <v>3.05</v>
+      </c>
+      <c r="AU238">
+        <v>7</v>
+      </c>
+      <c r="AV238">
+        <v>3</v>
+      </c>
+      <c r="AW238">
+        <v>9</v>
+      </c>
+      <c r="AX238">
+        <v>5</v>
+      </c>
+      <c r="AY238">
+        <v>22</v>
+      </c>
+      <c r="AZ238">
+        <v>10</v>
+      </c>
+      <c r="BA238">
+        <v>7</v>
+      </c>
+      <c r="BB238">
+        <v>1</v>
+      </c>
+      <c r="BC238">
+        <v>8</v>
+      </c>
+      <c r="BD238">
+        <v>0</v>
+      </c>
+      <c r="BE238">
+        <v>0</v>
+      </c>
+      <c r="BF238">
+        <v>0</v>
+      </c>
+      <c r="BG238">
+        <v>0</v>
+      </c>
+      <c r="BH238">
+        <v>0</v>
+      </c>
+      <c r="BI238">
+        <v>0</v>
+      </c>
+      <c r="BJ238">
+        <v>0</v>
+      </c>
+      <c r="BK238">
+        <v>0</v>
+      </c>
+      <c r="BL238">
+        <v>0</v>
+      </c>
+      <c r="BM238">
+        <v>0</v>
+      </c>
+      <c r="BN238">
+        <v>0</v>
+      </c>
+      <c r="BO238">
+        <v>0</v>
+      </c>
+      <c r="BP238">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -49966,31 +49966,31 @@
         <v>2.26</v>
       </c>
       <c r="AU236">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AV236">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AW236">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AX236">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AY236">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AZ236">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="BA236">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BB236">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC236">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD236">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="350">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -736,6 +736,15 @@
     <t>['39', '44']</t>
   </si>
   <si>
+    <t>['3']</t>
+  </si>
+  <si>
+    <t>['52', '63', '77', '90+1']</t>
+  </si>
+  <si>
+    <t>['31', '77']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -752,9 +761,6 @@
   </si>
   <si>
     <t>['16', '41', '51', '57', '66', '76']</t>
-  </si>
-  <si>
-    <t>['3']</t>
   </si>
   <si>
     <t>['40']</t>
@@ -1052,6 +1058,12 @@
   </si>
   <si>
     <t>['68']</t>
+  </si>
+  <si>
+    <t>['45', '64']</t>
+  </si>
+  <si>
+    <t>['37', '51']</t>
   </si>
 </sst>
 </file>
@@ -1413,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP238"/>
+  <dimension ref="A1:BP242"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1875,7 +1887,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -1956,7 +1968,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ3">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2493,7 +2505,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2571,7 +2583,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ6">
         <v>1.54</v>
@@ -2777,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7">
         <v>2</v>
@@ -2905,7 +2917,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -3398,7 +3410,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ10">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3523,7 +3535,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3601,10 +3613,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ11">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3729,7 +3741,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3810,7 +3822,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ12">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4141,7 +4153,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4553,7 +4565,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4631,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ16">
         <v>1.07</v>
@@ -4965,7 +4977,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -5171,7 +5183,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5377,7 +5389,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5583,7 +5595,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -6073,7 +6085,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ23">
         <v>0.6899999999999999</v>
@@ -6488,7 +6500,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ25">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR25">
         <v>0.7</v>
@@ -6691,7 +6703,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ26">
         <v>0.54</v>
@@ -6900,7 +6912,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ27">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR27">
         <v>1.62</v>
@@ -7231,7 +7243,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7309,7 +7321,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ29">
         <v>2</v>
@@ -7437,7 +7449,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7515,10 +7527,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ30">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR30">
         <v>0.55</v>
@@ -7643,7 +7655,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -8136,7 +8148,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ33">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR33">
         <v>2.25</v>
@@ -9085,7 +9097,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9291,7 +9303,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9703,7 +9715,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9781,7 +9793,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ41">
         <v>0.54</v>
@@ -9909,7 +9921,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -10115,7 +10127,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10399,10 +10411,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ44">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR44">
         <v>0.8100000000000001</v>
@@ -10527,7 +10539,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10608,7 +10620,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ45">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR45">
         <v>1.78</v>
@@ -10733,7 +10745,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10939,7 +10951,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -11145,7 +11157,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11429,7 +11441,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ49">
         <v>0.54</v>
@@ -11557,7 +11569,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11638,7 +11650,7 @@
         <v>2</v>
       </c>
       <c r="AQ50">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR50">
         <v>1.4</v>
@@ -11841,7 +11853,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ51">
         <v>1.23</v>
@@ -11969,7 +11981,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -12462,7 +12474,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ54">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR54">
         <v>1.92</v>
@@ -12587,7 +12599,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12793,7 +12805,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -12871,7 +12883,7 @@
         <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ56">
         <v>2.21</v>
@@ -13205,7 +13217,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13286,7 +13298,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ58">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR58">
         <v>1.27</v>
@@ -13411,7 +13423,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -13695,10 +13707,10 @@
         <v>0.33</v>
       </c>
       <c r="AP60">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ60">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR60">
         <v>1.14</v>
@@ -14313,7 +14325,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ63">
         <v>0.6899999999999999</v>
@@ -15137,7 +15149,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ67">
         <v>1.54</v>
@@ -15346,7 +15358,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ68">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR68">
         <v>0.83</v>
@@ -15883,7 +15895,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -16089,7 +16101,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16376,7 +16388,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ73">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR73">
         <v>1.21</v>
@@ -16501,7 +16513,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16579,7 +16591,7 @@
         <v>0.5</v>
       </c>
       <c r="AP74">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ74">
         <v>0.54</v>
@@ -16707,7 +16719,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16785,7 +16797,7 @@
         <v>0.75</v>
       </c>
       <c r="AP75">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ75">
         <v>1.07</v>
@@ -16913,7 +16925,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17119,7 +17131,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17197,7 +17209,7 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ77">
         <v>2.21</v>
@@ -17737,7 +17749,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17818,7 +17830,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ80">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR80">
         <v>1.2</v>
@@ -17943,7 +17955,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -18024,7 +18036,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ81">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR81">
         <v>1.3</v>
@@ -18149,7 +18161,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18355,7 +18367,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18561,7 +18573,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18767,7 +18779,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18973,7 +18985,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19385,7 +19397,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -20003,7 +20015,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -20081,7 +20093,7 @@
         <v>0.4</v>
       </c>
       <c r="AP91">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ91">
         <v>0.54</v>
@@ -20209,7 +20221,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20493,10 +20505,10 @@
         <v>0.25</v>
       </c>
       <c r="AP93">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ93">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR93">
         <v>0.99</v>
@@ -20699,7 +20711,7 @@
         <v>0.6</v>
       </c>
       <c r="AP94">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ94">
         <v>1.07</v>
@@ -20827,7 +20839,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -21114,7 +21126,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ96">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR96">
         <v>1.15</v>
@@ -21317,10 +21329,10 @@
         <v>1.6</v>
       </c>
       <c r="AP97">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ97">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR97">
         <v>1.23</v>
@@ -21445,7 +21457,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21732,7 +21744,7 @@
         <v>2.77</v>
       </c>
       <c r="AQ99">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR99">
         <v>2.36</v>
@@ -22063,7 +22075,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22475,7 +22487,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22759,7 +22771,7 @@
         <v>1.6</v>
       </c>
       <c r="AP104">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ104">
         <v>1.23</v>
@@ -22887,7 +22899,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -23789,7 +23801,7 @@
         <v>3</v>
       </c>
       <c r="AP109">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ109">
         <v>2.21</v>
@@ -23917,7 +23929,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -24204,7 +24216,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ111">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR111">
         <v>1.27</v>
@@ -24410,7 +24422,7 @@
         <v>2.77</v>
       </c>
       <c r="AQ112">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR112">
         <v>2.24</v>
@@ -24613,7 +24625,7 @@
         <v>0.5</v>
       </c>
       <c r="AP113">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ113">
         <v>0.57</v>
@@ -24819,10 +24831,10 @@
         <v>1.8</v>
       </c>
       <c r="AP114">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ114">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR114">
         <v>1.09</v>
@@ -25234,7 +25246,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ116">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR116">
         <v>1.23</v>
@@ -25977,7 +25989,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26595,7 +26607,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26673,7 +26685,7 @@
         <v>0.83</v>
       </c>
       <c r="AP123">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ123">
         <v>1.08</v>
@@ -26801,7 +26813,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -27213,7 +27225,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27294,7 +27306,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ126">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR126">
         <v>1.4</v>
@@ -27419,7 +27431,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27625,7 +27637,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27831,7 +27843,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27909,7 +27921,7 @@
         <v>0.43</v>
       </c>
       <c r="AP129">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ129">
         <v>0.77</v>
@@ -28118,7 +28130,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ130">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR130">
         <v>1.33</v>
@@ -28243,7 +28255,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28321,10 +28333,10 @@
         <v>1.67</v>
       </c>
       <c r="AP131">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ131">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR131">
         <v>1.14</v>
@@ -28449,7 +28461,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28527,7 +28539,7 @@
         <v>2.17</v>
       </c>
       <c r="AP132">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ132">
         <v>2.23</v>
@@ -28861,7 +28873,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -28942,7 +28954,7 @@
         <v>2</v>
       </c>
       <c r="AQ134">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR134">
         <v>1.28</v>
@@ -29685,7 +29697,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29891,7 +29903,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -29969,7 +29981,7 @@
         <v>0.75</v>
       </c>
       <c r="AP139">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ139">
         <v>0.62</v>
@@ -30303,7 +30315,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30384,7 +30396,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ141">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR141">
         <v>1.17</v>
@@ -30509,7 +30521,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30590,7 +30602,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ142">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR142">
         <v>1.33</v>
@@ -30715,7 +30727,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -31127,7 +31139,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31205,7 +31217,7 @@
         <v>1.29</v>
       </c>
       <c r="AP145">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ145">
         <v>1.54</v>
@@ -31333,7 +31345,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31617,10 +31629,10 @@
         <v>0.57</v>
       </c>
       <c r="AP147">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ147">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR147">
         <v>1.11</v>
@@ -31745,7 +31757,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31951,7 +31963,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32235,7 +32247,7 @@
         <v>0.75</v>
       </c>
       <c r="AP150">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ150">
         <v>0.77</v>
@@ -32363,7 +32375,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32569,7 +32581,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32775,7 +32787,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -33062,7 +33074,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ154">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR154">
         <v>1.23</v>
@@ -33393,7 +33405,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33471,7 +33483,7 @@
         <v>0.75</v>
       </c>
       <c r="AP156">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ156">
         <v>1.08</v>
@@ -33599,7 +33611,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33805,7 +33817,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -34011,7 +34023,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34092,7 +34104,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ159">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR159">
         <v>1.19</v>
@@ -34295,7 +34307,7 @@
         <v>0.78</v>
       </c>
       <c r="AP160">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ160">
         <v>0.77</v>
@@ -34423,7 +34435,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34629,7 +34641,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34710,7 +34722,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ162">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR162">
         <v>1.23</v>
@@ -34835,7 +34847,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -35247,7 +35259,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -35531,7 +35543,7 @@
         <v>0.25</v>
       </c>
       <c r="AP166">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ166">
         <v>0.54</v>
@@ -35946,7 +35958,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ168">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR168">
         <v>2.03</v>
@@ -36149,10 +36161,10 @@
         <v>1.11</v>
       </c>
       <c r="AP169">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ169">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR169">
         <v>1.15</v>
@@ -36277,7 +36289,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36895,7 +36907,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -37179,7 +37191,7 @@
         <v>1.56</v>
       </c>
       <c r="AP174">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ174">
         <v>1.08</v>
@@ -37307,7 +37319,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37513,7 +37525,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -37800,7 +37812,7 @@
         <v>2</v>
       </c>
       <c r="AQ177">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR177">
         <v>1.39</v>
@@ -38131,7 +38143,7 @@
         <v>205</v>
       </c>
       <c r="P179" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q179">
         <v>8.5</v>
@@ -38337,7 +38349,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q180">
         <v>4.75</v>
@@ -38415,7 +38427,7 @@
         <v>2.44</v>
       </c>
       <c r="AP180">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ180">
         <v>2.23</v>
@@ -38543,7 +38555,7 @@
         <v>207</v>
       </c>
       <c r="P181" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q181">
         <v>6.5</v>
@@ -38624,7 +38636,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ181">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR181">
         <v>1.3</v>
@@ -38749,7 +38761,7 @@
         <v>167</v>
       </c>
       <c r="P182" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -39161,7 +39173,7 @@
         <v>208</v>
       </c>
       <c r="P184" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q184">
         <v>1.57</v>
@@ -39445,10 +39457,10 @@
         <v>1</v>
       </c>
       <c r="AP185">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ185">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR185">
         <v>1.11</v>
@@ -39573,7 +39585,7 @@
         <v>209</v>
       </c>
       <c r="P186" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q186">
         <v>2.2</v>
@@ -39651,7 +39663,7 @@
         <v>0.9</v>
       </c>
       <c r="AP186">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ186">
         <v>0.6899999999999999</v>
@@ -39860,7 +39872,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ187">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR187">
         <v>1.2</v>
@@ -40397,7 +40409,7 @@
         <v>184</v>
       </c>
       <c r="P190" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q190">
         <v>2.63</v>
@@ -40809,7 +40821,7 @@
         <v>212</v>
       </c>
       <c r="P192" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -40887,7 +40899,7 @@
         <v>1.4</v>
       </c>
       <c r="AP192">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ192">
         <v>1.08</v>
@@ -41015,7 +41027,7 @@
         <v>213</v>
       </c>
       <c r="P193" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q193">
         <v>2.8</v>
@@ -41299,7 +41311,7 @@
         <v>1.7</v>
       </c>
       <c r="AP194">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ194">
         <v>2</v>
@@ -41427,7 +41439,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q195">
         <v>1.67</v>
@@ -41714,7 +41726,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ196">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR196">
         <v>1.29</v>
@@ -41839,7 +41851,7 @@
         <v>90</v>
       </c>
       <c r="P197" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q197">
         <v>7.5</v>
@@ -41920,7 +41932,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ197">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR197">
         <v>1.32</v>
@@ -42251,7 +42263,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42538,7 +42550,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ200">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR200">
         <v>1.68</v>
@@ -43075,7 +43087,7 @@
         <v>218</v>
       </c>
       <c r="P203" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q203">
         <v>2.55</v>
@@ -43153,7 +43165,7 @@
         <v>0.73</v>
       </c>
       <c r="AP203">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ203">
         <v>0.57</v>
@@ -43487,7 +43499,7 @@
         <v>219</v>
       </c>
       <c r="P205" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q205">
         <v>2.45</v>
@@ -43693,7 +43705,7 @@
         <v>220</v>
       </c>
       <c r="P206" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q206">
         <v>7</v>
@@ -43977,7 +43989,7 @@
         <v>0.64</v>
       </c>
       <c r="AP207">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ207">
         <v>0.62</v>
@@ -44105,7 +44117,7 @@
         <v>166</v>
       </c>
       <c r="P208" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44186,7 +44198,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ208">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR208">
         <v>2.01</v>
@@ -44517,7 +44529,7 @@
         <v>90</v>
       </c>
       <c r="P210" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q210">
         <v>5.5</v>
@@ -44598,7 +44610,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ210">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR210">
         <v>1.22</v>
@@ -45007,7 +45019,7 @@
         <v>0.55</v>
       </c>
       <c r="AP212">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ212">
         <v>0.54</v>
@@ -45341,7 +45353,7 @@
         <v>90</v>
       </c>
       <c r="P214" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q214">
         <v>3.1</v>
@@ -45422,7 +45434,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ214">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR214">
         <v>1.29</v>
@@ -45547,7 +45559,7 @@
         <v>224</v>
       </c>
       <c r="P215" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q215">
         <v>4.33</v>
@@ -45959,7 +45971,7 @@
         <v>226</v>
       </c>
       <c r="P217" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q217">
         <v>3.3</v>
@@ -46165,7 +46177,7 @@
         <v>90</v>
       </c>
       <c r="P218" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q218">
         <v>3.4</v>
@@ -46371,7 +46383,7 @@
         <v>227</v>
       </c>
       <c r="P219" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q219">
         <v>2.88</v>
@@ -46449,7 +46461,7 @@
         <v>0.75</v>
       </c>
       <c r="AP219">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ219">
         <v>0.77</v>
@@ -46658,7 +46670,7 @@
         <v>2.77</v>
       </c>
       <c r="AQ220">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR220">
         <v>2.13</v>
@@ -46864,7 +46876,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ221">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR221">
         <v>1.72</v>
@@ -46989,7 +47001,7 @@
         <v>226</v>
       </c>
       <c r="P222" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q222">
         <v>2.7</v>
@@ -47067,7 +47079,7 @@
         <v>0.58</v>
       </c>
       <c r="AP222">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ222">
         <v>0.62</v>
@@ -47195,7 +47207,7 @@
         <v>230</v>
       </c>
       <c r="P223" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q223">
         <v>6</v>
@@ -47401,7 +47413,7 @@
         <v>179</v>
       </c>
       <c r="P224" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q224">
         <v>6.25</v>
@@ -47482,7 +47494,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ224">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR224">
         <v>1.29</v>
@@ -47685,7 +47697,7 @@
         <v>0.67</v>
       </c>
       <c r="AP225">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ225">
         <v>0.57</v>
@@ -47813,7 +47825,7 @@
         <v>90</v>
       </c>
       <c r="P226" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q226">
         <v>5</v>
@@ -48306,7 +48318,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ228">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR228">
         <v>1.98</v>
@@ -48431,7 +48443,7 @@
         <v>232</v>
       </c>
       <c r="P229" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q229">
         <v>1.8</v>
@@ -48637,7 +48649,7 @@
         <v>233</v>
       </c>
       <c r="P230" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q230">
         <v>2.63</v>
@@ -48843,7 +48855,7 @@
         <v>234</v>
       </c>
       <c r="P231" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q231">
         <v>3.2</v>
@@ -49049,7 +49061,7 @@
         <v>235</v>
       </c>
       <c r="P232" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q232">
         <v>7</v>
@@ -49333,7 +49345,7 @@
         <v>0.75</v>
       </c>
       <c r="AP233">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ233">
         <v>0.6899999999999999</v>
@@ -49667,7 +49679,7 @@
         <v>90</v>
       </c>
       <c r="P235" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q235">
         <v>7.5</v>
@@ -49873,7 +49885,7 @@
         <v>238</v>
       </c>
       <c r="P236" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q236">
         <v>2.88</v>
@@ -50079,7 +50091,7 @@
         <v>90</v>
       </c>
       <c r="P237" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q237">
         <v>8</v>
@@ -50285,7 +50297,7 @@
         <v>239</v>
       </c>
       <c r="P238" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q238">
         <v>2.3</v>
@@ -50442,6 +50454,830 @@
       </c>
       <c r="BP238">
         <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7574799</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45746.47916666666</v>
+      </c>
+      <c r="F239">
+        <v>27</v>
+      </c>
+      <c r="G239" t="s">
+        <v>79</v>
+      </c>
+      <c r="H239" t="s">
+        <v>82</v>
+      </c>
+      <c r="I239">
+        <v>1</v>
+      </c>
+      <c r="J239">
+        <v>0</v>
+      </c>
+      <c r="K239">
+        <v>1</v>
+      </c>
+      <c r="L239">
+        <v>1</v>
+      </c>
+      <c r="M239">
+        <v>0</v>
+      </c>
+      <c r="N239">
+        <v>1</v>
+      </c>
+      <c r="O239" t="s">
+        <v>240</v>
+      </c>
+      <c r="P239" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q239">
+        <v>2.63</v>
+      </c>
+      <c r="R239">
+        <v>1.95</v>
+      </c>
+      <c r="S239">
+        <v>5</v>
+      </c>
+      <c r="T239">
+        <v>1.53</v>
+      </c>
+      <c r="U239">
+        <v>2.38</v>
+      </c>
+      <c r="V239">
+        <v>3.75</v>
+      </c>
+      <c r="W239">
+        <v>1.25</v>
+      </c>
+      <c r="X239">
+        <v>11</v>
+      </c>
+      <c r="Y239">
+        <v>1.05</v>
+      </c>
+      <c r="Z239">
+        <v>1.77</v>
+      </c>
+      <c r="AA239">
+        <v>3.2</v>
+      </c>
+      <c r="AB239">
+        <v>4.7</v>
+      </c>
+      <c r="AC239">
+        <v>0</v>
+      </c>
+      <c r="AD239">
+        <v>0</v>
+      </c>
+      <c r="AE239">
+        <v>1.55</v>
+      </c>
+      <c r="AF239">
+        <v>2.3</v>
+      </c>
+      <c r="AG239">
+        <v>2.4</v>
+      </c>
+      <c r="AH239">
+        <v>1.5</v>
+      </c>
+      <c r="AI239">
+        <v>2.2</v>
+      </c>
+      <c r="AJ239">
+        <v>1.62</v>
+      </c>
+      <c r="AK239">
+        <v>0</v>
+      </c>
+      <c r="AL239">
+        <v>0</v>
+      </c>
+      <c r="AM239">
+        <v>0</v>
+      </c>
+      <c r="AN239">
+        <v>1.77</v>
+      </c>
+      <c r="AO239">
+        <v>0.46</v>
+      </c>
+      <c r="AP239">
+        <v>1.86</v>
+      </c>
+      <c r="AQ239">
+        <v>0.43</v>
+      </c>
+      <c r="AR239">
+        <v>1.43</v>
+      </c>
+      <c r="AS239">
+        <v>1.27</v>
+      </c>
+      <c r="AT239">
+        <v>2.7</v>
+      </c>
+      <c r="AU239">
+        <v>6</v>
+      </c>
+      <c r="AV239">
+        <v>5</v>
+      </c>
+      <c r="AW239">
+        <v>8</v>
+      </c>
+      <c r="AX239">
+        <v>5</v>
+      </c>
+      <c r="AY239">
+        <v>14</v>
+      </c>
+      <c r="AZ239">
+        <v>10</v>
+      </c>
+      <c r="BA239">
+        <v>3</v>
+      </c>
+      <c r="BB239">
+        <v>4</v>
+      </c>
+      <c r="BC239">
+        <v>7</v>
+      </c>
+      <c r="BD239">
+        <v>0</v>
+      </c>
+      <c r="BE239">
+        <v>0</v>
+      </c>
+      <c r="BF239">
+        <v>0</v>
+      </c>
+      <c r="BG239">
+        <v>0</v>
+      </c>
+      <c r="BH239">
+        <v>0</v>
+      </c>
+      <c r="BI239">
+        <v>0</v>
+      </c>
+      <c r="BJ239">
+        <v>0</v>
+      </c>
+      <c r="BK239">
+        <v>0</v>
+      </c>
+      <c r="BL239">
+        <v>0</v>
+      </c>
+      <c r="BM239">
+        <v>0</v>
+      </c>
+      <c r="BN239">
+        <v>0</v>
+      </c>
+      <c r="BO239">
+        <v>0</v>
+      </c>
+      <c r="BP239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:68">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>7574803</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" t="s">
+        <v>69</v>
+      </c>
+      <c r="E240" s="2">
+        <v>45746.47916666666</v>
+      </c>
+      <c r="F240">
+        <v>27</v>
+      </c>
+      <c r="G240" t="s">
+        <v>75</v>
+      </c>
+      <c r="H240" t="s">
+        <v>71</v>
+      </c>
+      <c r="I240">
+        <v>0</v>
+      </c>
+      <c r="J240">
+        <v>0</v>
+      </c>
+      <c r="K240">
+        <v>0</v>
+      </c>
+      <c r="L240">
+        <v>4</v>
+      </c>
+      <c r="M240">
+        <v>1</v>
+      </c>
+      <c r="N240">
+        <v>5</v>
+      </c>
+      <c r="O240" t="s">
+        <v>241</v>
+      </c>
+      <c r="P240" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q240">
+        <v>2.5</v>
+      </c>
+      <c r="R240">
+        <v>2.05</v>
+      </c>
+      <c r="S240">
+        <v>5.5</v>
+      </c>
+      <c r="T240">
+        <v>1.5</v>
+      </c>
+      <c r="U240">
+        <v>2.5</v>
+      </c>
+      <c r="V240">
+        <v>3.4</v>
+      </c>
+      <c r="W240">
+        <v>1.3</v>
+      </c>
+      <c r="X240">
+        <v>10</v>
+      </c>
+      <c r="Y240">
+        <v>1.06</v>
+      </c>
+      <c r="Z240">
+        <v>1.71</v>
+      </c>
+      <c r="AA240">
+        <v>3.3</v>
+      </c>
+      <c r="AB240">
+        <v>4.9</v>
+      </c>
+      <c r="AC240">
+        <v>0</v>
+      </c>
+      <c r="AD240">
+        <v>0</v>
+      </c>
+      <c r="AE240">
+        <v>0</v>
+      </c>
+      <c r="AF240">
+        <v>0</v>
+      </c>
+      <c r="AG240">
+        <v>2.25</v>
+      </c>
+      <c r="AH240">
+        <v>1.6</v>
+      </c>
+      <c r="AI240">
+        <v>2.1</v>
+      </c>
+      <c r="AJ240">
+        <v>1.67</v>
+      </c>
+      <c r="AK240">
+        <v>0</v>
+      </c>
+      <c r="AL240">
+        <v>0</v>
+      </c>
+      <c r="AM240">
+        <v>0</v>
+      </c>
+      <c r="AN240">
+        <v>1.38</v>
+      </c>
+      <c r="AO240">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP240">
+        <v>1.5</v>
+      </c>
+      <c r="AQ240">
+        <v>0.64</v>
+      </c>
+      <c r="AR240">
+        <v>1.26</v>
+      </c>
+      <c r="AS240">
+        <v>1.04</v>
+      </c>
+      <c r="AT240">
+        <v>2.3</v>
+      </c>
+      <c r="AU240">
+        <v>5</v>
+      </c>
+      <c r="AV240">
+        <v>2</v>
+      </c>
+      <c r="AW240">
+        <v>10</v>
+      </c>
+      <c r="AX240">
+        <v>4</v>
+      </c>
+      <c r="AY240">
+        <v>15</v>
+      </c>
+      <c r="AZ240">
+        <v>7</v>
+      </c>
+      <c r="BA240">
+        <v>4</v>
+      </c>
+      <c r="BB240">
+        <v>2</v>
+      </c>
+      <c r="BC240">
+        <v>6</v>
+      </c>
+      <c r="BD240">
+        <v>0</v>
+      </c>
+      <c r="BE240">
+        <v>0</v>
+      </c>
+      <c r="BF240">
+        <v>0</v>
+      </c>
+      <c r="BG240">
+        <v>0</v>
+      </c>
+      <c r="BH240">
+        <v>0</v>
+      </c>
+      <c r="BI240">
+        <v>0</v>
+      </c>
+      <c r="BJ240">
+        <v>0</v>
+      </c>
+      <c r="BK240">
+        <v>0</v>
+      </c>
+      <c r="BL240">
+        <v>0</v>
+      </c>
+      <c r="BM240">
+        <v>0</v>
+      </c>
+      <c r="BN240">
+        <v>0</v>
+      </c>
+      <c r="BO240">
+        <v>0</v>
+      </c>
+      <c r="BP240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7574797</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45746.58333333334</v>
+      </c>
+      <c r="F241">
+        <v>27</v>
+      </c>
+      <c r="G241" t="s">
+        <v>74</v>
+      </c>
+      <c r="H241" t="s">
+        <v>73</v>
+      </c>
+      <c r="I241">
+        <v>1</v>
+      </c>
+      <c r="J241">
+        <v>1</v>
+      </c>
+      <c r="K241">
+        <v>2</v>
+      </c>
+      <c r="L241">
+        <v>1</v>
+      </c>
+      <c r="M241">
+        <v>2</v>
+      </c>
+      <c r="N241">
+        <v>3</v>
+      </c>
+      <c r="O241" t="s">
+        <v>141</v>
+      </c>
+      <c r="P241" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q241">
+        <v>6.5</v>
+      </c>
+      <c r="R241">
+        <v>2.2</v>
+      </c>
+      <c r="S241">
+        <v>2.1</v>
+      </c>
+      <c r="T241">
+        <v>1.4</v>
+      </c>
+      <c r="U241">
+        <v>2.75</v>
+      </c>
+      <c r="V241">
+        <v>3</v>
+      </c>
+      <c r="W241">
+        <v>1.36</v>
+      </c>
+      <c r="X241">
+        <v>8</v>
+      </c>
+      <c r="Y241">
+        <v>1.08</v>
+      </c>
+      <c r="Z241">
+        <v>6</v>
+      </c>
+      <c r="AA241">
+        <v>4</v>
+      </c>
+      <c r="AB241">
+        <v>1.48</v>
+      </c>
+      <c r="AC241">
+        <v>0</v>
+      </c>
+      <c r="AD241">
+        <v>0</v>
+      </c>
+      <c r="AE241">
+        <v>0</v>
+      </c>
+      <c r="AF241">
+        <v>0</v>
+      </c>
+      <c r="AG241">
+        <v>1.95</v>
+      </c>
+      <c r="AH241">
+        <v>1.8</v>
+      </c>
+      <c r="AI241">
+        <v>2.05</v>
+      </c>
+      <c r="AJ241">
+        <v>1.7</v>
+      </c>
+      <c r="AK241">
+        <v>0</v>
+      </c>
+      <c r="AL241">
+        <v>0</v>
+      </c>
+      <c r="AM241">
+        <v>0</v>
+      </c>
+      <c r="AN241">
+        <v>1.69</v>
+      </c>
+      <c r="AO241">
+        <v>1.54</v>
+      </c>
+      <c r="AP241">
+        <v>1.57</v>
+      </c>
+      <c r="AQ241">
+        <v>1.64</v>
+      </c>
+      <c r="AR241">
+        <v>1.26</v>
+      </c>
+      <c r="AS241">
+        <v>1.41</v>
+      </c>
+      <c r="AT241">
+        <v>2.67</v>
+      </c>
+      <c r="AU241">
+        <v>3</v>
+      </c>
+      <c r="AV241">
+        <v>9</v>
+      </c>
+      <c r="AW241">
+        <v>1</v>
+      </c>
+      <c r="AX241">
+        <v>9</v>
+      </c>
+      <c r="AY241">
+        <v>4</v>
+      </c>
+      <c r="AZ241">
+        <v>19</v>
+      </c>
+      <c r="BA241">
+        <v>1</v>
+      </c>
+      <c r="BB241">
+        <v>6</v>
+      </c>
+      <c r="BC241">
+        <v>7</v>
+      </c>
+      <c r="BD241">
+        <v>0</v>
+      </c>
+      <c r="BE241">
+        <v>0</v>
+      </c>
+      <c r="BF241">
+        <v>0</v>
+      </c>
+      <c r="BG241">
+        <v>0</v>
+      </c>
+      <c r="BH241">
+        <v>0</v>
+      </c>
+      <c r="BI241">
+        <v>0</v>
+      </c>
+      <c r="BJ241">
+        <v>0</v>
+      </c>
+      <c r="BK241">
+        <v>0</v>
+      </c>
+      <c r="BL241">
+        <v>0</v>
+      </c>
+      <c r="BM241">
+        <v>0</v>
+      </c>
+      <c r="BN241">
+        <v>0</v>
+      </c>
+      <c r="BO241">
+        <v>0</v>
+      </c>
+      <c r="BP241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:68">
+      <c r="A242" s="1">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>7574804</v>
+      </c>
+      <c r="C242" t="s">
+        <v>68</v>
+      </c>
+      <c r="D242" t="s">
+        <v>69</v>
+      </c>
+      <c r="E242" s="2">
+        <v>45746.6875</v>
+      </c>
+      <c r="F242">
+        <v>27</v>
+      </c>
+      <c r="G242" t="s">
+        <v>84</v>
+      </c>
+      <c r="H242" t="s">
+        <v>85</v>
+      </c>
+      <c r="I242">
+        <v>1</v>
+      </c>
+      <c r="J242">
+        <v>1</v>
+      </c>
+      <c r="K242">
+        <v>2</v>
+      </c>
+      <c r="L242">
+        <v>2</v>
+      </c>
+      <c r="M242">
+        <v>2</v>
+      </c>
+      <c r="N242">
+        <v>4</v>
+      </c>
+      <c r="O242" t="s">
+        <v>242</v>
+      </c>
+      <c r="P242" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q242">
+        <v>4.33</v>
+      </c>
+      <c r="R242">
+        <v>1.91</v>
+      </c>
+      <c r="S242">
+        <v>3</v>
+      </c>
+      <c r="T242">
+        <v>1.57</v>
+      </c>
+      <c r="U242">
+        <v>2.25</v>
+      </c>
+      <c r="V242">
+        <v>3.75</v>
+      </c>
+      <c r="W242">
+        <v>1.25</v>
+      </c>
+      <c r="X242">
+        <v>13</v>
+      </c>
+      <c r="Y242">
+        <v>1.04</v>
+      </c>
+      <c r="Z242">
+        <v>3.6</v>
+      </c>
+      <c r="AA242">
+        <v>2.95</v>
+      </c>
+      <c r="AB242">
+        <v>2.05</v>
+      </c>
+      <c r="AC242">
+        <v>1.1</v>
+      </c>
+      <c r="AD242">
+        <v>6.25</v>
+      </c>
+      <c r="AE242">
+        <v>1.5</v>
+      </c>
+      <c r="AF242">
+        <v>2.4</v>
+      </c>
+      <c r="AG242">
+        <v>2.4</v>
+      </c>
+      <c r="AH242">
+        <v>1.53</v>
+      </c>
+      <c r="AI242">
+        <v>2.1</v>
+      </c>
+      <c r="AJ242">
+        <v>1.67</v>
+      </c>
+      <c r="AK242">
+        <v>1.66</v>
+      </c>
+      <c r="AL242">
+        <v>1.35</v>
+      </c>
+      <c r="AM242">
+        <v>1.27</v>
+      </c>
+      <c r="AN242">
+        <v>1.77</v>
+      </c>
+      <c r="AO242">
+        <v>1.15</v>
+      </c>
+      <c r="AP242">
+        <v>1.71</v>
+      </c>
+      <c r="AQ242">
+        <v>1.14</v>
+      </c>
+      <c r="AR242">
+        <v>1.3</v>
+      </c>
+      <c r="AS242">
+        <v>1.54</v>
+      </c>
+      <c r="AT242">
+        <v>2.84</v>
+      </c>
+      <c r="AU242">
+        <v>4</v>
+      </c>
+      <c r="AV242">
+        <v>4</v>
+      </c>
+      <c r="AW242">
+        <v>8</v>
+      </c>
+      <c r="AX242">
+        <v>8</v>
+      </c>
+      <c r="AY242">
+        <v>15</v>
+      </c>
+      <c r="AZ242">
+        <v>15</v>
+      </c>
+      <c r="BA242">
+        <v>2</v>
+      </c>
+      <c r="BB242">
+        <v>3</v>
+      </c>
+      <c r="BC242">
+        <v>5</v>
+      </c>
+      <c r="BD242">
+        <v>2.8</v>
+      </c>
+      <c r="BE242">
+        <v>6.25</v>
+      </c>
+      <c r="BF242">
+        <v>1.61</v>
+      </c>
+      <c r="BG242">
+        <v>1.3</v>
+      </c>
+      <c r="BH242">
+        <v>3.1</v>
+      </c>
+      <c r="BI242">
+        <v>1.55</v>
+      </c>
+      <c r="BJ242">
+        <v>2.2</v>
+      </c>
+      <c r="BK242">
+        <v>1.98</v>
+      </c>
+      <c r="BL242">
+        <v>1.7</v>
+      </c>
+      <c r="BM242">
+        <v>2.65</v>
+      </c>
+      <c r="BN242">
+        <v>1.39</v>
+      </c>
+      <c r="BO242">
+        <v>3.75</v>
+      </c>
+      <c r="BP242">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -50390,22 +50390,22 @@
         <v>3.05</v>
       </c>
       <c r="AU238">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV238">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW238">
+        <v>4</v>
+      </c>
+      <c r="AX238">
+        <v>4</v>
+      </c>
+      <c r="AY238">
+        <v>15</v>
+      </c>
+      <c r="AZ238">
         <v>9</v>
-      </c>
-      <c r="AX238">
-        <v>5</v>
-      </c>
-      <c r="AY238">
-        <v>22</v>
-      </c>
-      <c r="AZ238">
-        <v>10</v>
       </c>
       <c r="BA238">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="351">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -745,6 +745,9 @@
     <t>['31', '77']</t>
   </si>
   <si>
+    <t>['90+6']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -991,9 +994,6 @@
     <t>['19', '85']</t>
   </si>
   <si>
-    <t>['90+6']</t>
-  </si>
-  <si>
     <t>['50', '90+6']</t>
   </si>
   <si>
@@ -1064,6 +1064,9 @@
   </si>
   <si>
     <t>['37', '51']</t>
+  </si>
+  <si>
+    <t>['55', '56', '65']</t>
   </si>
 </sst>
 </file>
@@ -1425,7 +1428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP242"/>
+  <dimension ref="A1:BP243"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1887,7 +1890,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2380,7 +2383,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ5">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2505,7 +2508,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2917,7 +2920,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -3535,7 +3538,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3741,7 +3744,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4153,7 +4156,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4977,7 +4980,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -5055,7 +5058,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AQ18">
         <v>2.23</v>
@@ -5183,7 +5186,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5389,7 +5392,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5595,7 +5598,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -6706,7 +6709,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ26">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR26">
         <v>0.6</v>
@@ -7243,7 +7246,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7449,7 +7452,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7655,7 +7658,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -7939,7 +7942,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AQ32">
         <v>1.08</v>
@@ -9097,7 +9100,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9303,7 +9306,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9715,7 +9718,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9796,7 +9799,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ41">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR41">
         <v>1.05</v>
@@ -9921,7 +9924,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -10127,7 +10130,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10539,7 +10542,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10745,7 +10748,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10951,7 +10954,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -11157,7 +11160,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11569,7 +11572,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11981,7 +11984,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -12599,7 +12602,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12677,7 +12680,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AQ55">
         <v>2</v>
@@ -12805,7 +12808,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -13217,7 +13220,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13423,7 +13426,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -13504,7 +13507,7 @@
         <v>2.77</v>
       </c>
       <c r="AQ59">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR59">
         <v>2.26</v>
@@ -15895,7 +15898,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -16101,7 +16104,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16513,7 +16516,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16594,7 +16597,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ74">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR74">
         <v>1.21</v>
@@ -16719,7 +16722,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16925,7 +16928,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17003,7 +17006,7 @@
         <v>0.75</v>
       </c>
       <c r="AP76">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AQ76">
         <v>0.62</v>
@@ -17131,7 +17134,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17749,7 +17752,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17955,7 +17958,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -18161,7 +18164,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18367,7 +18370,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18573,7 +18576,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18779,7 +18782,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18985,7 +18988,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19397,7 +19400,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -20015,7 +20018,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -20096,7 +20099,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ91">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR91">
         <v>1.03</v>
@@ -20221,7 +20224,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20839,7 +20842,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -20917,7 +20920,7 @@
         <v>0</v>
       </c>
       <c r="AP95">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AQ95">
         <v>0.57</v>
@@ -21457,7 +21460,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -22075,7 +22078,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22487,7 +22490,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22899,7 +22902,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -23392,7 +23395,7 @@
         <v>2</v>
       </c>
       <c r="AQ107">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR107">
         <v>1.2</v>
@@ -23929,7 +23932,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -25037,7 +25040,7 @@
         <v>0.33</v>
       </c>
       <c r="AP115">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AQ115">
         <v>0.77</v>
@@ -25658,7 +25661,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ118">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR118">
         <v>1.14</v>
@@ -25989,7 +25992,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26607,7 +26610,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26813,7 +26816,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -27225,7 +27228,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27431,7 +27434,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27637,7 +27640,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27843,7 +27846,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -28127,7 +28130,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AQ130">
         <v>0.64</v>
@@ -28255,7 +28258,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28461,7 +28464,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28873,7 +28876,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -29572,7 +29575,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ137">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR137">
         <v>1.07</v>
@@ -29697,7 +29700,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29903,7 +29906,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -30315,7 +30318,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30521,7 +30524,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30727,7 +30730,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -31139,7 +31142,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31345,7 +31348,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31757,7 +31760,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31963,7 +31966,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32041,7 +32044,7 @@
         <v>0.5</v>
       </c>
       <c r="AP149">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AQ149">
         <v>1.07</v>
@@ -32375,7 +32378,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32581,7 +32584,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32787,7 +32790,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -33405,7 +33408,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33611,7 +33614,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33817,7 +33820,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -34023,7 +34026,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34435,7 +34438,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34641,7 +34644,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34847,7 +34850,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -34925,7 +34928,7 @@
         <v>1.38</v>
       </c>
       <c r="AP163">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AQ163">
         <v>1.08</v>
@@ -35259,7 +35262,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -36289,7 +36292,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36782,7 +36785,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ172">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR172">
         <v>1.24</v>
@@ -36907,7 +36910,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -36985,7 +36988,7 @@
         <v>1.11</v>
       </c>
       <c r="AP173">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AQ173">
         <v>1.23</v>
@@ -37319,7 +37322,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37525,7 +37528,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -38143,7 +38146,7 @@
         <v>205</v>
       </c>
       <c r="P179" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q179">
         <v>8.5</v>
@@ -38349,7 +38352,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q180">
         <v>4.75</v>
@@ -38555,7 +38558,7 @@
         <v>207</v>
       </c>
       <c r="P181" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q181">
         <v>6.5</v>
@@ -38761,7 +38764,7 @@
         <v>167</v>
       </c>
       <c r="P182" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -39173,7 +39176,7 @@
         <v>208</v>
       </c>
       <c r="P184" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q184">
         <v>1.57</v>
@@ -39585,7 +39588,7 @@
         <v>209</v>
       </c>
       <c r="P186" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q186">
         <v>2.2</v>
@@ -40078,7 +40081,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ188">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR188">
         <v>1.68</v>
@@ -40409,7 +40412,7 @@
         <v>184</v>
       </c>
       <c r="P190" t="s">
-        <v>325</v>
+        <v>243</v>
       </c>
       <c r="Q190">
         <v>2.63</v>
@@ -40693,7 +40696,7 @@
         <v>0.3</v>
       </c>
       <c r="AP191">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AQ191">
         <v>0.54</v>
@@ -41851,7 +41854,7 @@
         <v>90</v>
       </c>
       <c r="P197" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q197">
         <v>7.5</v>
@@ -42756,7 +42759,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ201">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR201">
         <v>1.24</v>
@@ -45225,7 +45228,7 @@
         <v>1.55</v>
       </c>
       <c r="AP213">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AQ213">
         <v>1.54</v>
@@ -45353,7 +45356,7 @@
         <v>90</v>
       </c>
       <c r="P214" t="s">
-        <v>325</v>
+        <v>243</v>
       </c>
       <c r="Q214">
         <v>3.1</v>
@@ -46052,7 +46055,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ217">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR217">
         <v>1.16</v>
@@ -47491,7 +47494,7 @@
         <v>1</v>
       </c>
       <c r="AP224">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AQ224">
         <v>1.14</v>
@@ -48443,7 +48446,7 @@
         <v>232</v>
       </c>
       <c r="P229" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q229">
         <v>1.8</v>
@@ -48855,7 +48858,7 @@
         <v>234</v>
       </c>
       <c r="P231" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q231">
         <v>3.2</v>
@@ -51278,6 +51281,212 @@
       </c>
       <c r="BP242">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="243" spans="1:68">
+      <c r="A243" s="1">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>7574801</v>
+      </c>
+      <c r="C243" t="s">
+        <v>68</v>
+      </c>
+      <c r="D243" t="s">
+        <v>69</v>
+      </c>
+      <c r="E243" s="2">
+        <v>45748.67708333334</v>
+      </c>
+      <c r="F243">
+        <v>27</v>
+      </c>
+      <c r="G243" t="s">
+        <v>86</v>
+      </c>
+      <c r="H243" t="s">
+        <v>80</v>
+      </c>
+      <c r="I243">
+        <v>0</v>
+      </c>
+      <c r="J243">
+        <v>0</v>
+      </c>
+      <c r="K243">
+        <v>0</v>
+      </c>
+      <c r="L243">
+        <v>1</v>
+      </c>
+      <c r="M243">
+        <v>3</v>
+      </c>
+      <c r="N243">
+        <v>4</v>
+      </c>
+      <c r="O243" t="s">
+        <v>243</v>
+      </c>
+      <c r="P243" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q243">
+        <v>4</v>
+      </c>
+      <c r="R243">
+        <v>2</v>
+      </c>
+      <c r="S243">
+        <v>3.1</v>
+      </c>
+      <c r="T243">
+        <v>1.5</v>
+      </c>
+      <c r="U243">
+        <v>2.5</v>
+      </c>
+      <c r="V243">
+        <v>3.4</v>
+      </c>
+      <c r="W243">
+        <v>1.3</v>
+      </c>
+      <c r="X243">
+        <v>10</v>
+      </c>
+      <c r="Y243">
+        <v>1.06</v>
+      </c>
+      <c r="Z243">
+        <v>3.2</v>
+      </c>
+      <c r="AA243">
+        <v>3.1</v>
+      </c>
+      <c r="AB243">
+        <v>2.2</v>
+      </c>
+      <c r="AC243">
+        <v>1.09</v>
+      </c>
+      <c r="AD243">
+        <v>7</v>
+      </c>
+      <c r="AE243">
+        <v>1.5</v>
+      </c>
+      <c r="AF243">
+        <v>2.4</v>
+      </c>
+      <c r="AG243">
+        <v>2.2</v>
+      </c>
+      <c r="AH243">
+        <v>1.6</v>
+      </c>
+      <c r="AI243">
+        <v>1.95</v>
+      </c>
+      <c r="AJ243">
+        <v>1.8</v>
+      </c>
+      <c r="AK243">
+        <v>1.58</v>
+      </c>
+      <c r="AL243">
+        <v>1.34</v>
+      </c>
+      <c r="AM243">
+        <v>1.34</v>
+      </c>
+      <c r="AN243">
+        <v>0.46</v>
+      </c>
+      <c r="AO243">
+        <v>0.54</v>
+      </c>
+      <c r="AP243">
+        <v>0.43</v>
+      </c>
+      <c r="AQ243">
+        <v>0.71</v>
+      </c>
+      <c r="AR243">
+        <v>1.27</v>
+      </c>
+      <c r="AS243">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT243">
+        <v>2.21</v>
+      </c>
+      <c r="AU243">
+        <v>4</v>
+      </c>
+      <c r="AV243">
+        <v>10</v>
+      </c>
+      <c r="AW243">
+        <v>3</v>
+      </c>
+      <c r="AX243">
+        <v>5</v>
+      </c>
+      <c r="AY243">
+        <v>9</v>
+      </c>
+      <c r="AZ243">
+        <v>18</v>
+      </c>
+      <c r="BA243">
+        <v>3</v>
+      </c>
+      <c r="BB243">
+        <v>3</v>
+      </c>
+      <c r="BC243">
+        <v>6</v>
+      </c>
+      <c r="BD243">
+        <v>1.98</v>
+      </c>
+      <c r="BE243">
+        <v>6.25</v>
+      </c>
+      <c r="BF243">
+        <v>2.1</v>
+      </c>
+      <c r="BG243">
+        <v>1.3</v>
+      </c>
+      <c r="BH243">
+        <v>3.1</v>
+      </c>
+      <c r="BI243">
+        <v>1.57</v>
+      </c>
+      <c r="BJ243">
+        <v>2.2</v>
+      </c>
+      <c r="BK243">
+        <v>2</v>
+      </c>
+      <c r="BL243">
+        <v>1.68</v>
+      </c>
+      <c r="BM243">
+        <v>2.7</v>
+      </c>
+      <c r="BN243">
+        <v>1.38</v>
+      </c>
+      <c r="BO243">
+        <v>3.8</v>
+      </c>
+      <c r="BP243">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="353">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -748,6 +748,9 @@
     <t>['90+6']</t>
   </si>
   <si>
+    <t>['7', '23', '54']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -1067,6 +1070,9 @@
   </si>
   <si>
     <t>['55', '56', '65']</t>
+  </si>
+  <si>
+    <t>['43', '63']</t>
   </si>
 </sst>
 </file>
@@ -1428,7 +1434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP243"/>
+  <dimension ref="A1:BP244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1890,7 +1896,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2508,7 +2514,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2920,7 +2926,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -3538,7 +3544,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3744,7 +3750,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4031,7 +4037,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ13">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4156,7 +4162,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4440,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AQ15">
         <v>1.08</v>
@@ -4980,7 +4986,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -5186,7 +5192,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5392,7 +5398,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5598,7 +5604,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -6294,7 +6300,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AQ24">
         <v>0.54</v>
@@ -7246,7 +7252,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7452,7 +7458,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7658,7 +7664,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -8357,7 +8363,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ34">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR34">
         <v>1.18</v>
@@ -9100,7 +9106,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9306,7 +9312,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9718,7 +9724,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9924,7 +9930,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -10002,7 +10008,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AQ42">
         <v>1.54</v>
@@ -10130,7 +10136,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10211,7 +10217,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ43">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR43">
         <v>2.13</v>
@@ -10542,7 +10548,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10748,7 +10754,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10954,7 +10960,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -11160,7 +11166,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11572,7 +11578,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11984,7 +11990,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -12602,7 +12608,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12808,7 +12814,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -13220,7 +13226,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13426,7 +13432,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -13504,7 +13510,7 @@
         <v>0.67</v>
       </c>
       <c r="AP59">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AQ59">
         <v>0.71</v>
@@ -14537,7 +14543,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ64">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR64">
         <v>1.27</v>
@@ -15898,7 +15904,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -16104,7 +16110,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16516,7 +16522,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16722,7 +16728,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16928,7 +16934,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17134,7 +17140,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17421,7 +17427,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ78">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR78">
         <v>1.68</v>
@@ -17624,7 +17630,7 @@
         <v>0</v>
       </c>
       <c r="AP79">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AQ79">
         <v>0.57</v>
@@ -17752,7 +17758,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17958,7 +17964,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -18164,7 +18170,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18370,7 +18376,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18576,7 +18582,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18782,7 +18788,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18988,7 +18994,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19400,7 +19406,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -20018,7 +20024,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -20224,7 +20230,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20305,7 +20311,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ92">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR92">
         <v>1.25</v>
@@ -20842,7 +20848,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -21460,7 +21466,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21744,7 +21750,7 @@
         <v>2.25</v>
       </c>
       <c r="AP99">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AQ99">
         <v>1.64</v>
@@ -22078,7 +22084,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22490,7 +22496,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22902,7 +22908,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -23932,7 +23938,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -24422,7 +24428,7 @@
         <v>1.33</v>
       </c>
       <c r="AP112">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AQ112">
         <v>1.14</v>
@@ -25043,7 +25049,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ115">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR115">
         <v>1.28</v>
@@ -25992,7 +25998,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26610,7 +26616,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26816,7 +26822,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -27228,7 +27234,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27434,7 +27440,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27640,7 +27646,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27846,7 +27852,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27927,7 +27933,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ129">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR129">
         <v>1.02</v>
@@ -28258,7 +28264,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28464,7 +28470,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28876,7 +28882,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -29160,7 +29166,7 @@
         <v>0.5</v>
       </c>
       <c r="AP135">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AQ135">
         <v>1.08</v>
@@ -29700,7 +29706,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29906,7 +29912,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -30318,7 +30324,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30524,7 +30530,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30730,7 +30736,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -31142,7 +31148,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31348,7 +31354,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31760,7 +31766,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31838,7 +31844,7 @@
         <v>2.29</v>
       </c>
       <c r="AP148">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AQ148">
         <v>2.23</v>
@@ -31966,7 +31972,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32253,7 +32259,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ150">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR150">
         <v>1.34</v>
@@ -32378,7 +32384,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32584,7 +32590,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32790,7 +32796,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -33280,7 +33286,7 @@
         <v>1.25</v>
       </c>
       <c r="AP155">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AQ155">
         <v>1.23</v>
@@ -33408,7 +33414,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33614,7 +33620,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33820,7 +33826,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -34026,7 +34032,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34313,7 +34319,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ160">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR160">
         <v>1.14</v>
@@ -34438,7 +34444,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34644,7 +34650,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34850,7 +34856,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -35262,7 +35268,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -36292,7 +36298,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36910,7 +36916,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -37322,7 +37328,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37528,7 +37534,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -38021,7 +38027,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ178">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR178">
         <v>2.03</v>
@@ -38146,7 +38152,7 @@
         <v>205</v>
       </c>
       <c r="P179" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q179">
         <v>8.5</v>
@@ -38352,7 +38358,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q180">
         <v>4.75</v>
@@ -38558,7 +38564,7 @@
         <v>207</v>
       </c>
       <c r="P181" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q181">
         <v>6.5</v>
@@ -38764,7 +38770,7 @@
         <v>167</v>
       </c>
       <c r="P182" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -39176,7 +39182,7 @@
         <v>208</v>
       </c>
       <c r="P184" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q184">
         <v>1.57</v>
@@ -39254,7 +39260,7 @@
         <v>0.7</v>
       </c>
       <c r="AP184">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AQ184">
         <v>0.62</v>
@@ -39588,7 +39594,7 @@
         <v>209</v>
       </c>
       <c r="P186" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q186">
         <v>2.2</v>
@@ -40824,7 +40830,7 @@
         <v>212</v>
       </c>
       <c r="P192" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -41030,7 +41036,7 @@
         <v>213</v>
       </c>
       <c r="P193" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q193">
         <v>2.8</v>
@@ -41442,7 +41448,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q195">
         <v>1.67</v>
@@ -41854,7 +41860,7 @@
         <v>90</v>
       </c>
       <c r="P197" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q197">
         <v>7.5</v>
@@ -42266,7 +42272,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42962,7 +42968,7 @@
         <v>0.82</v>
       </c>
       <c r="AP202">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AQ202">
         <v>0.6899999999999999</v>
@@ -43090,7 +43096,7 @@
         <v>218</v>
       </c>
       <c r="P203" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q203">
         <v>2.55</v>
@@ -43502,7 +43508,7 @@
         <v>219</v>
       </c>
       <c r="P205" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q205">
         <v>2.45</v>
@@ -43583,7 +43589,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ205">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR205">
         <v>1.23</v>
@@ -43708,7 +43714,7 @@
         <v>220</v>
       </c>
       <c r="P206" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q206">
         <v>7</v>
@@ -44120,7 +44126,7 @@
         <v>166</v>
       </c>
       <c r="P208" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44532,7 +44538,7 @@
         <v>90</v>
       </c>
       <c r="P210" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q210">
         <v>5.5</v>
@@ -45562,7 +45568,7 @@
         <v>224</v>
       </c>
       <c r="P215" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q215">
         <v>4.33</v>
@@ -45974,7 +45980,7 @@
         <v>226</v>
       </c>
       <c r="P217" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q217">
         <v>3.3</v>
@@ -46180,7 +46186,7 @@
         <v>90</v>
       </c>
       <c r="P218" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q218">
         <v>3.4</v>
@@ -46386,7 +46392,7 @@
         <v>227</v>
       </c>
       <c r="P219" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q219">
         <v>2.88</v>
@@ -46467,7 +46473,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ219">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR219">
         <v>1.24</v>
@@ -46670,7 +46676,7 @@
         <v>0.5</v>
       </c>
       <c r="AP220">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AQ220">
         <v>0.43</v>
@@ -47004,7 +47010,7 @@
         <v>226</v>
       </c>
       <c r="P222" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q222">
         <v>2.7</v>
@@ -47210,7 +47216,7 @@
         <v>230</v>
       </c>
       <c r="P223" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q223">
         <v>6</v>
@@ -47416,7 +47422,7 @@
         <v>179</v>
       </c>
       <c r="P224" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q224">
         <v>6.25</v>
@@ -47828,7 +47834,7 @@
         <v>90</v>
       </c>
       <c r="P226" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q226">
         <v>5</v>
@@ -48446,7 +48452,7 @@
         <v>232</v>
       </c>
       <c r="P229" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q229">
         <v>1.8</v>
@@ -48652,7 +48658,7 @@
         <v>233</v>
       </c>
       <c r="P230" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q230">
         <v>2.63</v>
@@ -48858,7 +48864,7 @@
         <v>234</v>
       </c>
       <c r="P231" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q231">
         <v>3.2</v>
@@ -49064,7 +49070,7 @@
         <v>235</v>
       </c>
       <c r="P232" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q232">
         <v>7</v>
@@ -49682,7 +49688,7 @@
         <v>90</v>
       </c>
       <c r="P235" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q235">
         <v>7.5</v>
@@ -49888,7 +49894,7 @@
         <v>238</v>
       </c>
       <c r="P236" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q236">
         <v>2.88</v>
@@ -50094,7 +50100,7 @@
         <v>90</v>
       </c>
       <c r="P237" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q237">
         <v>8</v>
@@ -50300,7 +50306,7 @@
         <v>239</v>
       </c>
       <c r="P238" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q238">
         <v>2.3</v>
@@ -50918,7 +50924,7 @@
         <v>141</v>
       </c>
       <c r="P241" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q241">
         <v>6.5</v>
@@ -51124,7 +51130,7 @@
         <v>242</v>
       </c>
       <c r="P242" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q242">
         <v>4.33</v>
@@ -51330,7 +51336,7 @@
         <v>243</v>
       </c>
       <c r="P243" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q243">
         <v>4</v>
@@ -51487,6 +51493,212 @@
       </c>
       <c r="BP243">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="244" spans="1:68">
+      <c r="A244" s="1">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>7574805</v>
+      </c>
+      <c r="C244" t="s">
+        <v>68</v>
+      </c>
+      <c r="D244" t="s">
+        <v>69</v>
+      </c>
+      <c r="E244" s="2">
+        <v>45749.67708333334</v>
+      </c>
+      <c r="F244">
+        <v>27</v>
+      </c>
+      <c r="G244" t="s">
+        <v>83</v>
+      </c>
+      <c r="H244" t="s">
+        <v>76</v>
+      </c>
+      <c r="I244">
+        <v>2</v>
+      </c>
+      <c r="J244">
+        <v>1</v>
+      </c>
+      <c r="K244">
+        <v>3</v>
+      </c>
+      <c r="L244">
+        <v>3</v>
+      </c>
+      <c r="M244">
+        <v>2</v>
+      </c>
+      <c r="N244">
+        <v>5</v>
+      </c>
+      <c r="O244" t="s">
+        <v>244</v>
+      </c>
+      <c r="P244" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q244">
+        <v>1.57</v>
+      </c>
+      <c r="R244">
+        <v>2.75</v>
+      </c>
+      <c r="S244">
+        <v>12</v>
+      </c>
+      <c r="T244">
+        <v>1.29</v>
+      </c>
+      <c r="U244">
+        <v>3.5</v>
+      </c>
+      <c r="V244">
+        <v>2.25</v>
+      </c>
+      <c r="W244">
+        <v>1.57</v>
+      </c>
+      <c r="X244">
+        <v>5.5</v>
+      </c>
+      <c r="Y244">
+        <v>1.14</v>
+      </c>
+      <c r="Z244">
+        <v>1.13</v>
+      </c>
+      <c r="AA244">
+        <v>7</v>
+      </c>
+      <c r="AB244">
+        <v>15</v>
+      </c>
+      <c r="AC244">
+        <v>1.03</v>
+      </c>
+      <c r="AD244">
+        <v>11</v>
+      </c>
+      <c r="AE244">
+        <v>1.18</v>
+      </c>
+      <c r="AF244">
+        <v>4.75</v>
+      </c>
+      <c r="AG244">
+        <v>1.44</v>
+      </c>
+      <c r="AH244">
+        <v>2.67</v>
+      </c>
+      <c r="AI244">
+        <v>2.38</v>
+      </c>
+      <c r="AJ244">
+        <v>1.53</v>
+      </c>
+      <c r="AK244">
+        <v>1.02</v>
+      </c>
+      <c r="AL244">
+        <v>1.09</v>
+      </c>
+      <c r="AM244">
+        <v>5</v>
+      </c>
+      <c r="AN244">
+        <v>2.77</v>
+      </c>
+      <c r="AO244">
+        <v>0.77</v>
+      </c>
+      <c r="AP244">
+        <v>2.79</v>
+      </c>
+      <c r="AQ244">
+        <v>0.71</v>
+      </c>
+      <c r="AR244">
+        <v>2.18</v>
+      </c>
+      <c r="AS244">
+        <v>1.12</v>
+      </c>
+      <c r="AT244">
+        <v>3.3</v>
+      </c>
+      <c r="AU244">
+        <v>8</v>
+      </c>
+      <c r="AV244">
+        <v>7</v>
+      </c>
+      <c r="AW244">
+        <v>7</v>
+      </c>
+      <c r="AX244">
+        <v>5</v>
+      </c>
+      <c r="AY244">
+        <v>15</v>
+      </c>
+      <c r="AZ244">
+        <v>15</v>
+      </c>
+      <c r="BA244">
+        <v>5</v>
+      </c>
+      <c r="BB244">
+        <v>4</v>
+      </c>
+      <c r="BC244">
+        <v>9</v>
+      </c>
+      <c r="BD244">
+        <v>1.03</v>
+      </c>
+      <c r="BE244">
+        <v>21</v>
+      </c>
+      <c r="BF244">
+        <v>12.75</v>
+      </c>
+      <c r="BG244">
+        <v>1.09</v>
+      </c>
+      <c r="BH244">
+        <v>5.4</v>
+      </c>
+      <c r="BI244">
+        <v>1.21</v>
+      </c>
+      <c r="BJ244">
+        <v>3.58</v>
+      </c>
+      <c r="BK244">
+        <v>1.4</v>
+      </c>
+      <c r="BL244">
+        <v>2.64</v>
+      </c>
+      <c r="BM244">
+        <v>1.7</v>
+      </c>
+      <c r="BN244">
+        <v>1.95</v>
+      </c>
+      <c r="BO244">
+        <v>2.05</v>
+      </c>
+      <c r="BP244">
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="356">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -751,6 +751,9 @@
     <t>['7', '23', '54']</t>
   </si>
   <si>
+    <t>['4', '89']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -1073,6 +1076,12 @@
   </si>
   <si>
     <t>['43', '63']</t>
+  </si>
+  <si>
+    <t>['20', '33', '49']</t>
+  </si>
+  <si>
+    <t>['35', '76']</t>
   </si>
 </sst>
 </file>
@@ -1434,7 +1443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP244"/>
+  <dimension ref="A1:BP247"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1896,7 +1905,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -1974,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ3">
         <v>0.43</v>
@@ -2514,7 +2523,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2595,7 +2604,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ6">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2926,7 +2935,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -3416,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ10">
         <v>1.14</v>
@@ -3544,7 +3553,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3750,7 +3759,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4162,7 +4171,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4858,10 +4867,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ17">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4986,7 +4995,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -5192,7 +5201,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5273,7 +5282,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ19">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5398,7 +5407,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5604,7 +5613,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -5685,7 +5694,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ21">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR21">
         <v>1.57</v>
@@ -6506,7 +6515,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ25">
         <v>0.43</v>
@@ -6918,7 +6927,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
         <v>1.14</v>
@@ -7252,7 +7261,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7458,7 +7467,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7664,7 +7673,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -7951,7 +7960,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ32">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR32">
         <v>0.64</v>
@@ -8772,10 +8781,10 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ36">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR36">
         <v>1.59</v>
@@ -9106,7 +9115,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9184,7 +9193,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ38">
         <v>2.21</v>
@@ -9312,7 +9321,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9596,7 +9605,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ40">
         <v>0.57</v>
@@ -9724,7 +9733,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9930,7 +9939,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -10011,7 +10020,7 @@
         <v>2.79</v>
       </c>
       <c r="AQ42">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR42">
         <v>2.4</v>
@@ -10136,7 +10145,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10548,7 +10557,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10754,7 +10763,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10960,7 +10969,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -11166,7 +11175,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11247,7 +11256,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ48">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR48">
         <v>1.23</v>
@@ -11578,7 +11587,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11656,7 +11665,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ50">
         <v>1.64</v>
@@ -11865,7 +11874,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ51">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR51">
         <v>1.08</v>
@@ -11990,7 +11999,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -12608,7 +12617,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12814,7 +12823,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -13226,7 +13235,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13432,7 +13441,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -14540,7 +14549,7 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ64">
         <v>0.71</v>
@@ -14749,7 +14758,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ65">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -15161,7 +15170,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ67">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR67">
         <v>1.08</v>
@@ -15364,7 +15373,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ68">
         <v>0.64</v>
@@ -15779,7 +15788,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ70">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR70">
         <v>1.2</v>
@@ -15904,7 +15913,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -15982,7 +15991,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ71">
         <v>0.6899999999999999</v>
@@ -16110,7 +16119,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16522,7 +16531,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16728,7 +16737,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16934,7 +16943,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17140,7 +17149,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17758,7 +17767,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17964,7 +17973,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -18042,7 +18051,7 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ81">
         <v>1.64</v>
@@ -18170,7 +18179,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18376,7 +18385,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18582,7 +18591,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18788,7 +18797,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18994,7 +19003,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19072,10 +19081,10 @@
         <v>1.25</v>
       </c>
       <c r="AP86">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ86">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR86">
         <v>1.12</v>
@@ -19278,7 +19287,7 @@
         <v>1.2</v>
       </c>
       <c r="AP87">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ87">
         <v>0.62</v>
@@ -19406,7 +19415,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19484,7 +19493,7 @@
         <v>1.75</v>
       </c>
       <c r="AP88">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ88">
         <v>2.23</v>
@@ -19693,7 +19702,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ89">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR89">
         <v>2.03</v>
@@ -19899,7 +19908,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ90">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR90">
         <v>1.22</v>
@@ -20024,7 +20033,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -20230,7 +20239,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20848,7 +20857,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -21466,7 +21475,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -22084,7 +22093,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22496,7 +22505,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22577,7 +22586,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ103">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR103">
         <v>2.02</v>
@@ -22783,7 +22792,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ104">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR104">
         <v>1</v>
@@ -22908,7 +22917,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -22986,7 +22995,7 @@
         <v>1.75</v>
       </c>
       <c r="AP105">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ105">
         <v>2</v>
@@ -23192,7 +23201,7 @@
         <v>2</v>
       </c>
       <c r="AP106">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ106">
         <v>2.23</v>
@@ -23398,7 +23407,7 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ107">
         <v>0.71</v>
@@ -23938,7 +23947,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -24019,7 +24028,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ110">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR110">
         <v>1.54</v>
@@ -25998,7 +26007,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26282,10 +26291,10 @@
         <v>1.5</v>
       </c>
       <c r="AP121">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ121">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR121">
         <v>1.05</v>
@@ -26488,7 +26497,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ122">
         <v>2</v>
@@ -26616,7 +26625,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26822,7 +26831,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -26903,7 +26912,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ124">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR124">
         <v>1.55</v>
@@ -27234,7 +27243,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27440,7 +27449,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27646,7 +27655,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27852,7 +27861,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -28264,7 +28273,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28470,7 +28479,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28882,7 +28891,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -28960,7 +28969,7 @@
         <v>0.29</v>
       </c>
       <c r="AP134">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ134">
         <v>0.43</v>
@@ -29169,7 +29178,7 @@
         <v>2.79</v>
       </c>
       <c r="AQ135">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR135">
         <v>2.03</v>
@@ -29578,7 +29587,7 @@
         <v>0.63</v>
       </c>
       <c r="AP137">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ137">
         <v>0.71</v>
@@ -29706,7 +29715,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29784,7 +29793,7 @@
         <v>0.14</v>
       </c>
       <c r="AP138">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ138">
         <v>0.54</v>
@@ -29912,7 +29921,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -30324,7 +30333,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30530,7 +30539,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30736,7 +30745,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -31148,7 +31157,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31229,7 +31238,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ145">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR145">
         <v>1.04</v>
@@ -31354,7 +31363,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31432,7 +31441,7 @@
         <v>2.38</v>
       </c>
       <c r="AP146">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ146">
         <v>2.21</v>
@@ -31766,7 +31775,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31972,7 +31981,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32384,7 +32393,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32465,7 +32474,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ151">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR151">
         <v>1.25</v>
@@ -32590,7 +32599,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32671,7 +32680,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ152">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR152">
         <v>1.17</v>
@@ -32796,7 +32805,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -33289,7 +33298,7 @@
         <v>2.79</v>
       </c>
       <c r="AQ155">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR155">
         <v>2.01</v>
@@ -33414,7 +33423,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33495,7 +33504,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ156">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR156">
         <v>1.41</v>
@@ -33620,7 +33629,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33826,7 +33835,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33904,7 +33913,7 @@
         <v>0.78</v>
       </c>
       <c r="AP158">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ158">
         <v>1.07</v>
@@ -34032,7 +34041,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34444,7 +34453,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34650,7 +34659,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34856,7 +34865,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -35140,7 +35149,7 @@
         <v>0.78</v>
       </c>
       <c r="AP164">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ164">
         <v>0.62</v>
@@ -35268,7 +35277,7 @@
         <v>195</v>
       </c>
       <c r="P165" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q165">
         <v>3.2</v>
@@ -36298,7 +36307,7 @@
         <v>199</v>
       </c>
       <c r="P170" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q170">
         <v>1.91</v>
@@ -36379,7 +36388,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ170">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR170">
         <v>1.95</v>
@@ -36788,7 +36797,7 @@
         <v>0.67</v>
       </c>
       <c r="AP172">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ172">
         <v>0.71</v>
@@ -36916,7 +36925,7 @@
         <v>90</v>
       </c>
       <c r="P173" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q173">
         <v>4.2</v>
@@ -36997,7 +37006,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ173">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR173">
         <v>1.33</v>
@@ -37328,7 +37337,7 @@
         <v>202</v>
       </c>
       <c r="P175" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q175">
         <v>3.1</v>
@@ -37534,7 +37543,7 @@
         <v>141</v>
       </c>
       <c r="P176" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q176">
         <v>2.88</v>
@@ -37615,7 +37624,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ176">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR176">
         <v>1.21</v>
@@ -37818,7 +37827,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP177">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ177">
         <v>0.64</v>
@@ -38152,7 +38161,7 @@
         <v>205</v>
       </c>
       <c r="P179" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q179">
         <v>8.5</v>
@@ -38358,7 +38367,7 @@
         <v>206</v>
       </c>
       <c r="P180" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q180">
         <v>4.75</v>
@@ -38564,7 +38573,7 @@
         <v>207</v>
       </c>
       <c r="P181" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q181">
         <v>6.5</v>
@@ -38770,7 +38779,7 @@
         <v>167</v>
       </c>
       <c r="P182" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q182">
         <v>3.25</v>
@@ -39054,10 +39063,10 @@
         <v>1.44</v>
       </c>
       <c r="AP183">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ183">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR183">
         <v>1.2</v>
@@ -39182,7 +39191,7 @@
         <v>208</v>
       </c>
       <c r="P184" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q184">
         <v>1.57</v>
@@ -39594,7 +39603,7 @@
         <v>209</v>
       </c>
       <c r="P186" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q186">
         <v>2.2</v>
@@ -40496,7 +40505,7 @@
         <v>0.7</v>
       </c>
       <c r="AP190">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ190">
         <v>0.57</v>
@@ -40830,7 +40839,7 @@
         <v>212</v>
       </c>
       <c r="P192" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -41036,7 +41045,7 @@
         <v>213</v>
       </c>
       <c r="P193" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q193">
         <v>2.8</v>
@@ -41117,7 +41126,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ193">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR193">
         <v>1.34</v>
@@ -41448,7 +41457,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q195">
         <v>1.67</v>
@@ -41860,7 +41869,7 @@
         <v>90</v>
       </c>
       <c r="P197" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q197">
         <v>7.5</v>
@@ -42144,7 +42153,7 @@
         <v>2.5</v>
       </c>
       <c r="AP198">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ198">
         <v>2.23</v>
@@ -42272,7 +42281,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42353,7 +42362,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ199">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR199">
         <v>1.25</v>
@@ -43096,7 +43105,7 @@
         <v>218</v>
       </c>
       <c r="P203" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q203">
         <v>2.55</v>
@@ -43383,7 +43392,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ204">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR204">
         <v>1.15</v>
@@ -43508,7 +43517,7 @@
         <v>219</v>
       </c>
       <c r="P205" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q205">
         <v>2.45</v>
@@ -43586,7 +43595,7 @@
         <v>0.73</v>
       </c>
       <c r="AP205">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ205">
         <v>0.71</v>
@@ -43714,7 +43723,7 @@
         <v>220</v>
       </c>
       <c r="P206" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q206">
         <v>7</v>
@@ -43792,7 +43801,7 @@
         <v>2.18</v>
       </c>
       <c r="AP206">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ206">
         <v>2.21</v>
@@ -44126,7 +44135,7 @@
         <v>166</v>
       </c>
       <c r="P208" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44413,7 +44422,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ209">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR209">
         <v>1.41</v>
@@ -44538,7 +44547,7 @@
         <v>90</v>
       </c>
       <c r="P210" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q210">
         <v>5.5</v>
@@ -44616,7 +44625,7 @@
         <v>1.55</v>
       </c>
       <c r="AP210">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ210">
         <v>1.64</v>
@@ -44822,7 +44831,7 @@
         <v>1.27</v>
       </c>
       <c r="AP211">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ211">
         <v>1.08</v>
@@ -45237,7 +45246,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ213">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR213">
         <v>1.28</v>
@@ -45568,7 +45577,7 @@
         <v>224</v>
       </c>
       <c r="P215" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q215">
         <v>4.33</v>
@@ -45855,7 +45864,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ216">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR216">
         <v>2.12</v>
@@ -45980,7 +45989,7 @@
         <v>226</v>
       </c>
       <c r="P217" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q217">
         <v>3.3</v>
@@ -46186,7 +46195,7 @@
         <v>90</v>
       </c>
       <c r="P218" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q218">
         <v>3.4</v>
@@ -46264,7 +46273,7 @@
         <v>1</v>
       </c>
       <c r="AP218">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ218">
         <v>1.07</v>
@@ -46392,7 +46401,7 @@
         <v>227</v>
       </c>
       <c r="P219" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q219">
         <v>2.88</v>
@@ -47010,7 +47019,7 @@
         <v>226</v>
       </c>
       <c r="P222" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q222">
         <v>2.7</v>
@@ -47216,7 +47225,7 @@
         <v>230</v>
       </c>
       <c r="P223" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q223">
         <v>6</v>
@@ -47422,7 +47431,7 @@
         <v>179</v>
       </c>
       <c r="P224" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q224">
         <v>6.25</v>
@@ -47834,7 +47843,7 @@
         <v>90</v>
       </c>
       <c r="P226" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q226">
         <v>5</v>
@@ -48121,7 +48130,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ227">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR227">
         <v>1.27</v>
@@ -48452,7 +48461,7 @@
         <v>232</v>
       </c>
       <c r="P229" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q229">
         <v>1.8</v>
@@ -48533,7 +48542,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ229">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR229">
         <v>2.09</v>
@@ -48658,7 +48667,7 @@
         <v>233</v>
       </c>
       <c r="P230" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q230">
         <v>2.63</v>
@@ -48736,10 +48745,10 @@
         <v>1.08</v>
       </c>
       <c r="AP230">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ230">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR230">
         <v>1.23</v>
@@ -48864,7 +48873,7 @@
         <v>234</v>
       </c>
       <c r="P231" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q231">
         <v>3.2</v>
@@ -49070,7 +49079,7 @@
         <v>235</v>
       </c>
       <c r="P232" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q232">
         <v>7</v>
@@ -49560,7 +49569,7 @@
         <v>0.58</v>
       </c>
       <c r="AP234">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ234">
         <v>0.54</v>
@@ -49688,7 +49697,7 @@
         <v>90</v>
       </c>
       <c r="P235" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q235">
         <v>7.5</v>
@@ -49894,7 +49903,7 @@
         <v>238</v>
       </c>
       <c r="P236" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q236">
         <v>2.88</v>
@@ -50100,7 +50109,7 @@
         <v>90</v>
       </c>
       <c r="P237" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q237">
         <v>8</v>
@@ -50306,7 +50315,7 @@
         <v>239</v>
       </c>
       <c r="P238" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q238">
         <v>2.3</v>
@@ -50924,7 +50933,7 @@
         <v>141</v>
       </c>
       <c r="P241" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q241">
         <v>6.5</v>
@@ -51130,7 +51139,7 @@
         <v>242</v>
       </c>
       <c r="P242" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q242">
         <v>4.33</v>
@@ -51336,7 +51345,7 @@
         <v>243</v>
       </c>
       <c r="P243" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q243">
         <v>4</v>
@@ -51542,7 +51551,7 @@
         <v>244</v>
       </c>
       <c r="P244" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q244">
         <v>1.57</v>
@@ -51699,6 +51708,624 @@
       </c>
       <c r="BP244">
         <v>1.7</v>
+      </c>
+    </row>
+    <row r="245" spans="1:68">
+      <c r="A245" s="1">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>7574808</v>
+      </c>
+      <c r="C245" t="s">
+        <v>68</v>
+      </c>
+      <c r="D245" t="s">
+        <v>69</v>
+      </c>
+      <c r="E245" s="2">
+        <v>45751.67708333334</v>
+      </c>
+      <c r="F245">
+        <v>28</v>
+      </c>
+      <c r="G245" t="s">
+        <v>71</v>
+      </c>
+      <c r="H245" t="s">
+        <v>74</v>
+      </c>
+      <c r="I245">
+        <v>0</v>
+      </c>
+      <c r="J245">
+        <v>2</v>
+      </c>
+      <c r="K245">
+        <v>2</v>
+      </c>
+      <c r="L245">
+        <v>0</v>
+      </c>
+      <c r="M245">
+        <v>3</v>
+      </c>
+      <c r="N245">
+        <v>3</v>
+      </c>
+      <c r="O245" t="s">
+        <v>90</v>
+      </c>
+      <c r="P245" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q245">
+        <v>3.5</v>
+      </c>
+      <c r="R245">
+        <v>2</v>
+      </c>
+      <c r="S245">
+        <v>3.5</v>
+      </c>
+      <c r="T245">
+        <v>1.5</v>
+      </c>
+      <c r="U245">
+        <v>2.5</v>
+      </c>
+      <c r="V245">
+        <v>3.5</v>
+      </c>
+      <c r="W245">
+        <v>1.29</v>
+      </c>
+      <c r="X245">
+        <v>10</v>
+      </c>
+      <c r="Y245">
+        <v>1.06</v>
+      </c>
+      <c r="Z245">
+        <v>2.7</v>
+      </c>
+      <c r="AA245">
+        <v>3.1</v>
+      </c>
+      <c r="AB245">
+        <v>2.5</v>
+      </c>
+      <c r="AC245">
+        <v>1.08</v>
+      </c>
+      <c r="AD245">
+        <v>7.5</v>
+      </c>
+      <c r="AE245">
+        <v>1.42</v>
+      </c>
+      <c r="AF245">
+        <v>2.8</v>
+      </c>
+      <c r="AG245">
+        <v>2.15</v>
+      </c>
+      <c r="AH245">
+        <v>1.61</v>
+      </c>
+      <c r="AI245">
+        <v>1.95</v>
+      </c>
+      <c r="AJ245">
+        <v>1.8</v>
+      </c>
+      <c r="AK245">
+        <v>1.46</v>
+      </c>
+      <c r="AL245">
+        <v>1.33</v>
+      </c>
+      <c r="AM245">
+        <v>1.44</v>
+      </c>
+      <c r="AN245">
+        <v>1.08</v>
+      </c>
+      <c r="AO245">
+        <v>1.08</v>
+      </c>
+      <c r="AP245">
+        <v>1</v>
+      </c>
+      <c r="AQ245">
+        <v>1.21</v>
+      </c>
+      <c r="AR245">
+        <v>1.2</v>
+      </c>
+      <c r="AS245">
+        <v>1.21</v>
+      </c>
+      <c r="AT245">
+        <v>2.41</v>
+      </c>
+      <c r="AU245">
+        <v>2</v>
+      </c>
+      <c r="AV245">
+        <v>8</v>
+      </c>
+      <c r="AW245">
+        <v>9</v>
+      </c>
+      <c r="AX245">
+        <v>7</v>
+      </c>
+      <c r="AY245">
+        <v>13</v>
+      </c>
+      <c r="AZ245">
+        <v>16</v>
+      </c>
+      <c r="BA245">
+        <v>4</v>
+      </c>
+      <c r="BB245">
+        <v>3</v>
+      </c>
+      <c r="BC245">
+        <v>7</v>
+      </c>
+      <c r="BD245">
+        <v>1.94</v>
+      </c>
+      <c r="BE245">
+        <v>6.4</v>
+      </c>
+      <c r="BF245">
+        <v>2.05</v>
+      </c>
+      <c r="BG245">
+        <v>1.45</v>
+      </c>
+      <c r="BH245">
+        <v>2.48</v>
+      </c>
+      <c r="BI245">
+        <v>1.76</v>
+      </c>
+      <c r="BJ245">
+        <v>1.9</v>
+      </c>
+      <c r="BK245">
+        <v>2.23</v>
+      </c>
+      <c r="BL245">
+        <v>1.56</v>
+      </c>
+      <c r="BM245">
+        <v>2.9</v>
+      </c>
+      <c r="BN245">
+        <v>1.34</v>
+      </c>
+      <c r="BO245">
+        <v>3.9</v>
+      </c>
+      <c r="BP245">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="246" spans="1:68">
+      <c r="A246" s="1">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>7574806</v>
+      </c>
+      <c r="C246" t="s">
+        <v>68</v>
+      </c>
+      <c r="D246" t="s">
+        <v>69</v>
+      </c>
+      <c r="E246" s="2">
+        <v>45752.58333333334</v>
+      </c>
+      <c r="F246">
+        <v>28</v>
+      </c>
+      <c r="G246" t="s">
+        <v>78</v>
+      </c>
+      <c r="H246" t="s">
+        <v>75</v>
+      </c>
+      <c r="I246">
+        <v>0</v>
+      </c>
+      <c r="J246">
+        <v>1</v>
+      </c>
+      <c r="K246">
+        <v>1</v>
+      </c>
+      <c r="L246">
+        <v>1</v>
+      </c>
+      <c r="M246">
+        <v>2</v>
+      </c>
+      <c r="N246">
+        <v>3</v>
+      </c>
+      <c r="O246" t="s">
+        <v>184</v>
+      </c>
+      <c r="P246" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q246">
+        <v>3.2</v>
+      </c>
+      <c r="R246">
+        <v>2.05</v>
+      </c>
+      <c r="S246">
+        <v>3.6</v>
+      </c>
+      <c r="T246">
+        <v>1.44</v>
+      </c>
+      <c r="U246">
+        <v>2.63</v>
+      </c>
+      <c r="V246">
+        <v>3.25</v>
+      </c>
+      <c r="W246">
+        <v>1.33</v>
+      </c>
+      <c r="X246">
+        <v>10</v>
+      </c>
+      <c r="Y246">
+        <v>1.06</v>
+      </c>
+      <c r="Z246">
+        <v>2.3</v>
+      </c>
+      <c r="AA246">
+        <v>3.1</v>
+      </c>
+      <c r="AB246">
+        <v>2.95</v>
+      </c>
+      <c r="AC246">
+        <v>1.1</v>
+      </c>
+      <c r="AD246">
+        <v>7.81</v>
+      </c>
+      <c r="AE246">
+        <v>1.43</v>
+      </c>
+      <c r="AF246">
+        <v>2.93</v>
+      </c>
+      <c r="AG246">
+        <v>2.1</v>
+      </c>
+      <c r="AH246">
+        <v>1.67</v>
+      </c>
+      <c r="AI246">
+        <v>1.91</v>
+      </c>
+      <c r="AJ246">
+        <v>1.91</v>
+      </c>
+      <c r="AK246">
+        <v>1.5</v>
+      </c>
+      <c r="AL246">
+        <v>1.35</v>
+      </c>
+      <c r="AM246">
+        <v>1.44</v>
+      </c>
+      <c r="AN246">
+        <v>1.08</v>
+      </c>
+      <c r="AO246">
+        <v>1.23</v>
+      </c>
+      <c r="AP246">
+        <v>1</v>
+      </c>
+      <c r="AQ246">
+        <v>1.36</v>
+      </c>
+      <c r="AR246">
+        <v>1.19</v>
+      </c>
+      <c r="AS246">
+        <v>1.39</v>
+      </c>
+      <c r="AT246">
+        <v>2.58</v>
+      </c>
+      <c r="AU246">
+        <v>7</v>
+      </c>
+      <c r="AV246">
+        <v>6</v>
+      </c>
+      <c r="AW246">
+        <v>8</v>
+      </c>
+      <c r="AX246">
+        <v>2</v>
+      </c>
+      <c r="AY246">
+        <v>17</v>
+      </c>
+      <c r="AZ246">
+        <v>8</v>
+      </c>
+      <c r="BA246">
+        <v>3</v>
+      </c>
+      <c r="BB246">
+        <v>7</v>
+      </c>
+      <c r="BC246">
+        <v>10</v>
+      </c>
+      <c r="BD246">
+        <v>1.74</v>
+      </c>
+      <c r="BE246">
+        <v>6.7</v>
+      </c>
+      <c r="BF246">
+        <v>2.71</v>
+      </c>
+      <c r="BG246">
+        <v>1.21</v>
+      </c>
+      <c r="BH246">
+        <v>3.58</v>
+      </c>
+      <c r="BI246">
+        <v>1.42</v>
+      </c>
+      <c r="BJ246">
+        <v>2.57</v>
+      </c>
+      <c r="BK246">
+        <v>1.75</v>
+      </c>
+      <c r="BL246">
+        <v>1.96</v>
+      </c>
+      <c r="BM246">
+        <v>2.21</v>
+      </c>
+      <c r="BN246">
+        <v>1.56</v>
+      </c>
+      <c r="BO246">
+        <v>2.92</v>
+      </c>
+      <c r="BP246">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="247" spans="1:68">
+      <c r="A247" s="1">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>7574809</v>
+      </c>
+      <c r="C247" t="s">
+        <v>68</v>
+      </c>
+      <c r="D247" t="s">
+        <v>69</v>
+      </c>
+      <c r="E247" s="2">
+        <v>45752.6875</v>
+      </c>
+      <c r="F247">
+        <v>28</v>
+      </c>
+      <c r="G247" t="s">
+        <v>85</v>
+      </c>
+      <c r="H247" t="s">
+        <v>79</v>
+      </c>
+      <c r="I247">
+        <v>1</v>
+      </c>
+      <c r="J247">
+        <v>0</v>
+      </c>
+      <c r="K247">
+        <v>1</v>
+      </c>
+      <c r="L247">
+        <v>2</v>
+      </c>
+      <c r="M247">
+        <v>0</v>
+      </c>
+      <c r="N247">
+        <v>2</v>
+      </c>
+      <c r="O247" t="s">
+        <v>245</v>
+      </c>
+      <c r="P247" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q247">
+        <v>2.75</v>
+      </c>
+      <c r="R247">
+        <v>1.91</v>
+      </c>
+      <c r="S247">
+        <v>5</v>
+      </c>
+      <c r="T247">
+        <v>1.62</v>
+      </c>
+      <c r="U247">
+        <v>2.2</v>
+      </c>
+      <c r="V247">
+        <v>4</v>
+      </c>
+      <c r="W247">
+        <v>1.22</v>
+      </c>
+      <c r="X247">
+        <v>13</v>
+      </c>
+      <c r="Y247">
+        <v>1.04</v>
+      </c>
+      <c r="Z247">
+        <v>1.77</v>
+      </c>
+      <c r="AA247">
+        <v>3.2</v>
+      </c>
+      <c r="AB247">
+        <v>4.7</v>
+      </c>
+      <c r="AC247">
+        <v>1.13</v>
+      </c>
+      <c r="AD247">
+        <v>6.41</v>
+      </c>
+      <c r="AE247">
+        <v>1.53</v>
+      </c>
+      <c r="AF247">
+        <v>2.38</v>
+      </c>
+      <c r="AG247">
+        <v>2.4</v>
+      </c>
+      <c r="AH247">
+        <v>1.53</v>
+      </c>
+      <c r="AI247">
+        <v>2.25</v>
+      </c>
+      <c r="AJ247">
+        <v>1.57</v>
+      </c>
+      <c r="AK247">
+        <v>1.22</v>
+      </c>
+      <c r="AL247">
+        <v>1.36</v>
+      </c>
+      <c r="AM247">
+        <v>1.83</v>
+      </c>
+      <c r="AN247">
+        <v>2</v>
+      </c>
+      <c r="AO247">
+        <v>1.54</v>
+      </c>
+      <c r="AP247">
+        <v>2.07</v>
+      </c>
+      <c r="AQ247">
+        <v>1.43</v>
+      </c>
+      <c r="AR247">
+        <v>1.56</v>
+      </c>
+      <c r="AS247">
+        <v>0.97</v>
+      </c>
+      <c r="AT247">
+        <v>2.53</v>
+      </c>
+      <c r="AU247">
+        <v>4</v>
+      </c>
+      <c r="AV247">
+        <v>7</v>
+      </c>
+      <c r="AW247">
+        <v>6</v>
+      </c>
+      <c r="AX247">
+        <v>10</v>
+      </c>
+      <c r="AY247">
+        <v>13</v>
+      </c>
+      <c r="AZ247">
+        <v>19</v>
+      </c>
+      <c r="BA247">
+        <v>7</v>
+      </c>
+      <c r="BB247">
+        <v>6</v>
+      </c>
+      <c r="BC247">
+        <v>13</v>
+      </c>
+      <c r="BD247">
+        <v>1.4</v>
+      </c>
+      <c r="BE247">
+        <v>9.1</v>
+      </c>
+      <c r="BF247">
+        <v>3.72</v>
+      </c>
+      <c r="BG247">
+        <v>1.33</v>
+      </c>
+      <c r="BH247">
+        <v>2.83</v>
+      </c>
+      <c r="BI247">
+        <v>1.63</v>
+      </c>
+      <c r="BJ247">
+        <v>2.09</v>
+      </c>
+      <c r="BK247">
+        <v>2.11</v>
+      </c>
+      <c r="BL247">
+        <v>1.65</v>
+      </c>
+      <c r="BM247">
+        <v>2.79</v>
+      </c>
+      <c r="BN247">
+        <v>1.36</v>
+      </c>
+      <c r="BO247">
+        <v>3.84</v>
+      </c>
+      <c r="BP247">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="356">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1443,7 +1443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP247"/>
+  <dimension ref="A1:BP248"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3016,7 +3016,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ8">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3837,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ12">
         <v>0.64</v>
@@ -7136,7 +7136,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ28">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR28">
         <v>1.72</v>
@@ -8987,7 +8987,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ37">
         <v>2.23</v>
@@ -9402,7 +9402,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ39">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR39">
         <v>1.27</v>
@@ -12077,7 +12077,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ52">
         <v>1.08</v>
@@ -13110,7 +13110,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ57">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR57">
         <v>1.33</v>
@@ -14961,7 +14961,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ66">
         <v>0.54</v>
@@ -17024,7 +17024,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ76">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR76">
         <v>1.15</v>
@@ -18875,7 +18875,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ85">
         <v>0.6899999999999999</v>
@@ -19290,7 +19290,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ87">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR87">
         <v>1.16</v>
@@ -22174,7 +22174,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ101">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR101">
         <v>1.42</v>
@@ -24231,7 +24231,7 @@
         <v>0.33</v>
       </c>
       <c r="AP111">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ111">
         <v>0.43</v>
@@ -25882,7 +25882,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ119">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR119">
         <v>1.33</v>
@@ -28763,7 +28763,7 @@
         <v>2.57</v>
       </c>
       <c r="AP133">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ133">
         <v>2.21</v>
@@ -30002,7 +30002,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ139">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR139">
         <v>1.09</v>
@@ -32883,7 +32883,7 @@
         <v>0.38</v>
       </c>
       <c r="AP153">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ153">
         <v>0.57</v>
@@ -34737,7 +34737,7 @@
         <v>1.63</v>
       </c>
       <c r="AP162">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ162">
         <v>1.64</v>
@@ -35152,7 +35152,7 @@
         <v>1</v>
       </c>
       <c r="AQ164">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR164">
         <v>1.09</v>
@@ -37621,7 +37621,7 @@
         <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ176">
         <v>1.21</v>
@@ -39272,7 +39272,7 @@
         <v>2.79</v>
       </c>
       <c r="AQ184">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR184">
         <v>2.05</v>
@@ -42359,7 +42359,7 @@
         <v>1.3</v>
       </c>
       <c r="AP199">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ199">
         <v>1.36</v>
@@ -44010,7 +44010,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ207">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR207">
         <v>1.11</v>
@@ -47100,7 +47100,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ222">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AR222">
         <v>1.43</v>
@@ -48127,7 +48127,7 @@
         <v>1.42</v>
       </c>
       <c r="AP227">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ227">
         <v>1.43</v>
@@ -49775,7 +49775,7 @@
         <v>1.92</v>
       </c>
       <c r="AP235">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ235">
         <v>2</v>
@@ -52326,6 +52326,212 @@
       </c>
       <c r="BP247">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="248" spans="1:68">
+      <c r="A248" s="1">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>7574807</v>
+      </c>
+      <c r="C248" t="s">
+        <v>68</v>
+      </c>
+      <c r="D248" t="s">
+        <v>69</v>
+      </c>
+      <c r="E248" s="2">
+        <v>45753.47916666666</v>
+      </c>
+      <c r="F248">
+        <v>28</v>
+      </c>
+      <c r="G248" t="s">
+        <v>80</v>
+      </c>
+      <c r="H248" t="s">
+        <v>84</v>
+      </c>
+      <c r="I248">
+        <v>0</v>
+      </c>
+      <c r="J248">
+        <v>0</v>
+      </c>
+      <c r="K248">
+        <v>0</v>
+      </c>
+      <c r="L248">
+        <v>0</v>
+      </c>
+      <c r="M248">
+        <v>1</v>
+      </c>
+      <c r="N248">
+        <v>1</v>
+      </c>
+      <c r="O248" t="s">
+        <v>90</v>
+      </c>
+      <c r="P248" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q248">
+        <v>3.4</v>
+      </c>
+      <c r="R248">
+        <v>1.91</v>
+      </c>
+      <c r="S248">
+        <v>3.75</v>
+      </c>
+      <c r="T248">
+        <v>1.57</v>
+      </c>
+      <c r="U248">
+        <v>2.25</v>
+      </c>
+      <c r="V248">
+        <v>3.75</v>
+      </c>
+      <c r="W248">
+        <v>1.25</v>
+      </c>
+      <c r="X248">
+        <v>11</v>
+      </c>
+      <c r="Y248">
+        <v>1.05</v>
+      </c>
+      <c r="Z248">
+        <v>2.5</v>
+      </c>
+      <c r="AA248">
+        <v>3.1</v>
+      </c>
+      <c r="AB248">
+        <v>2.7</v>
+      </c>
+      <c r="AC248">
+        <v>1.08</v>
+      </c>
+      <c r="AD248">
+        <v>7.5</v>
+      </c>
+      <c r="AE248">
+        <v>1.42</v>
+      </c>
+      <c r="AF248">
+        <v>2.8</v>
+      </c>
+      <c r="AG248">
+        <v>2.3</v>
+      </c>
+      <c r="AH248">
+        <v>1.57</v>
+      </c>
+      <c r="AI248">
+        <v>2.05</v>
+      </c>
+      <c r="AJ248">
+        <v>1.7</v>
+      </c>
+      <c r="AK248">
+        <v>1.41</v>
+      </c>
+      <c r="AL248">
+        <v>1.34</v>
+      </c>
+      <c r="AM248">
+        <v>1.49</v>
+      </c>
+      <c r="AN248">
+        <v>1.23</v>
+      </c>
+      <c r="AO248">
+        <v>0.62</v>
+      </c>
+      <c r="AP248">
+        <v>1.14</v>
+      </c>
+      <c r="AQ248">
+        <v>0.79</v>
+      </c>
+      <c r="AR248">
+        <v>1.24</v>
+      </c>
+      <c r="AS248">
+        <v>1.19</v>
+      </c>
+      <c r="AT248">
+        <v>2.43</v>
+      </c>
+      <c r="AU248">
+        <v>5</v>
+      </c>
+      <c r="AV248">
+        <v>3</v>
+      </c>
+      <c r="AW248">
+        <v>7</v>
+      </c>
+      <c r="AX248">
+        <v>7</v>
+      </c>
+      <c r="AY248">
+        <v>13</v>
+      </c>
+      <c r="AZ248">
+        <v>10</v>
+      </c>
+      <c r="BA248">
+        <v>7</v>
+      </c>
+      <c r="BB248">
+        <v>0</v>
+      </c>
+      <c r="BC248">
+        <v>7</v>
+      </c>
+      <c r="BD248">
+        <v>1.68</v>
+      </c>
+      <c r="BE248">
+        <v>6.75</v>
+      </c>
+      <c r="BF248">
+        <v>2.4</v>
+      </c>
+      <c r="BG248">
+        <v>1.3</v>
+      </c>
+      <c r="BH248">
+        <v>3.05</v>
+      </c>
+      <c r="BI248">
+        <v>1.54</v>
+      </c>
+      <c r="BJ248">
+        <v>2.25</v>
+      </c>
+      <c r="BK248">
+        <v>1.88</v>
+      </c>
+      <c r="BL248">
+        <v>1.78</v>
+      </c>
+      <c r="BM248">
+        <v>2.35</v>
+      </c>
+      <c r="BN248">
+        <v>1.5</v>
+      </c>
+      <c r="BO248">
+        <v>3.05</v>
+      </c>
+      <c r="BP248">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="357">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1083,6 +1083,9 @@
   <si>
     <t>['35', '76']</t>
   </si>
+  <si>
+    <t>['1', '42', '69', '90+4']</t>
+  </si>
 </sst>
 </file>
 
@@ -1443,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP248"/>
+  <dimension ref="A1:BP251"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2395,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ5">
         <v>0.71</v>
@@ -2810,7 +2813,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ7">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3013,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ8">
         <v>0.79</v>
@@ -3222,7 +3225,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ9">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -4249,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ14">
         <v>2.21</v>
@@ -4458,7 +4461,7 @@
         <v>2.79</v>
       </c>
       <c r="AQ15">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -5485,7 +5488,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ20">
         <v>2.21</v>
@@ -5897,7 +5900,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ22">
         <v>0.57</v>
@@ -6312,7 +6315,7 @@
         <v>2.79</v>
       </c>
       <c r="AQ24">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR24">
         <v>2.62</v>
@@ -7342,7 +7345,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ29">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR29">
         <v>1.3</v>
@@ -7754,7 +7757,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ31">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR31">
         <v>1</v>
@@ -8369,7 +8372,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ34">
         <v>0.71</v>
@@ -10223,7 +10226,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ43">
         <v>0.71</v>
@@ -11047,7 +11050,7 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ47">
         <v>2.23</v>
@@ -11462,7 +11465,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ49">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR49">
         <v>1.09</v>
@@ -12080,7 +12083,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ52">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR52">
         <v>1.51</v>
@@ -12283,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ53">
         <v>1.07</v>
@@ -12698,7 +12701,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ55">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR55">
         <v>1.28</v>
@@ -13931,7 +13934,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ61">
         <v>1.07</v>
@@ -14964,7 +14967,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ66">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR66">
         <v>1.45</v>
@@ -15582,7 +15585,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ69">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR69">
         <v>2.1</v>
@@ -15785,7 +15788,7 @@
         <v>0.67</v>
       </c>
       <c r="AP70">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ70">
         <v>1.21</v>
@@ -16197,7 +16200,7 @@
         <v>2.33</v>
       </c>
       <c r="AP72">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ72">
         <v>2.23</v>
@@ -18260,7 +18263,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ82">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR82">
         <v>2.06</v>
@@ -18466,7 +18469,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ83">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR83">
         <v>1.47</v>
@@ -18669,10 +18672,10 @@
         <v>1.33</v>
       </c>
       <c r="AP84">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ84">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR84">
         <v>1.17</v>
@@ -19699,7 +19702,7 @@
         <v>0.5</v>
       </c>
       <c r="AP89">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ89">
         <v>1.21</v>
@@ -19905,7 +19908,7 @@
         <v>1.5</v>
       </c>
       <c r="AP90">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ90">
         <v>1.43</v>
@@ -21965,10 +21968,10 @@
         <v>0.2</v>
       </c>
       <c r="AP100">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ100">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR100">
         <v>1.15</v>
@@ -22377,7 +22380,7 @@
         <v>1.33</v>
       </c>
       <c r="AP102">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ102">
         <v>0.6899999999999999</v>
@@ -22998,7 +23001,7 @@
         <v>1</v>
       </c>
       <c r="AQ105">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR105">
         <v>0.97</v>
@@ -23613,10 +23616,10 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ108">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR108">
         <v>2.03</v>
@@ -25673,7 +25676,7 @@
         <v>0.29</v>
       </c>
       <c r="AP118">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ118">
         <v>0.71</v>
@@ -25879,7 +25882,7 @@
         <v>0.86</v>
       </c>
       <c r="AP119">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ119">
         <v>0.79</v>
@@ -26500,7 +26503,7 @@
         <v>1</v>
       </c>
       <c r="AQ122">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR122">
         <v>1.11</v>
@@ -26706,7 +26709,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ123">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR123">
         <v>1.04</v>
@@ -27115,10 +27118,10 @@
         <v>0.17</v>
       </c>
       <c r="AP125">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ125">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR125">
         <v>2.03</v>
@@ -27527,10 +27530,10 @@
         <v>1.83</v>
       </c>
       <c r="AP127">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ127">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR127">
         <v>1.37</v>
@@ -29796,7 +29799,7 @@
         <v>1</v>
       </c>
       <c r="AQ138">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR138">
         <v>1.22</v>
@@ -30205,7 +30208,7 @@
         <v>1.13</v>
       </c>
       <c r="AP140">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ140">
         <v>0.6899999999999999</v>
@@ -30411,7 +30414,7 @@
         <v>1.13</v>
       </c>
       <c r="AP141">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ141">
         <v>1.14</v>
@@ -30826,7 +30829,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ143">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR143">
         <v>1.64</v>
@@ -31032,7 +31035,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ144">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR144">
         <v>2.11</v>
@@ -33089,7 +33092,7 @@
         <v>1.86</v>
       </c>
       <c r="AP154">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ154">
         <v>1.64</v>
@@ -34119,7 +34122,7 @@
         <v>0.63</v>
       </c>
       <c r="AP159">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ159">
         <v>0.64</v>
@@ -34946,7 +34949,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ163">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR163">
         <v>1.32</v>
@@ -35355,7 +35358,7 @@
         <v>0.44</v>
       </c>
       <c r="AP165">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ165">
         <v>0.57</v>
@@ -35564,7 +35567,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ166">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR166">
         <v>1.12</v>
@@ -35770,7 +35773,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ167">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR167">
         <v>1.21</v>
@@ -36385,7 +36388,7 @@
         <v>1.5</v>
       </c>
       <c r="AP170">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ170">
         <v>1.43</v>
@@ -37212,7 +37215,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ174">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR174">
         <v>1.43</v>
@@ -37415,7 +37418,7 @@
         <v>0.8</v>
       </c>
       <c r="AP175">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ175">
         <v>1.07</v>
@@ -38242,7 +38245,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ179">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR179">
         <v>1.18</v>
@@ -38857,7 +38860,7 @@
         <v>2.3</v>
       </c>
       <c r="AP182">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ182">
         <v>2.21</v>
@@ -39887,7 +39890,7 @@
         <v>0.3</v>
       </c>
       <c r="AP187">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ187">
         <v>0.43</v>
@@ -40302,7 +40305,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ189">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR189">
         <v>1.19</v>
@@ -40714,7 +40717,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ191">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR191">
         <v>1.28</v>
@@ -40920,7 +40923,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ192">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR192">
         <v>1.22</v>
@@ -41123,7 +41126,7 @@
         <v>1.2</v>
       </c>
       <c r="AP193">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ193">
         <v>1.21</v>
@@ -41332,7 +41335,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ194">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR194">
         <v>1.46</v>
@@ -41460,73 +41463,73 @@
         <v>330</v>
       </c>
       <c r="Q195">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R195">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S195">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="T195">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="U195">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V195">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="W195">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="X195">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Y195">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z195">
-        <v>999.99</v>
+        <v>0</v>
       </c>
       <c r="AA195">
         <v>0</v>
       </c>
       <c r="AB195">
-        <v>999.99</v>
+        <v>0</v>
       </c>
       <c r="AC195">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AD195">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AE195">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF195">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AG195">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH195">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AI195">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ195">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK195">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AL195">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AM195">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN195">
         <v>2.7</v>
@@ -41577,43 +41580,43 @@
         <v>18</v>
       </c>
       <c r="BD195">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BE195">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BF195">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BG195">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BH195">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BI195">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BJ195">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BK195">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BL195">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BM195">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BN195">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BO195">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="BP195">
-        <v>1.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:68">
@@ -41666,73 +41669,73 @@
         <v>97</v>
       </c>
       <c r="Q196">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R196">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S196">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T196">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U196">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V196">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W196">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X196">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y196">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z196">
-        <v>999.99</v>
+        <v>0</v>
       </c>
       <c r="AA196">
         <v>0</v>
       </c>
       <c r="AB196">
-        <v>999.99</v>
+        <v>0</v>
       </c>
       <c r="AC196">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD196">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AE196">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF196">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AG196">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH196">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI196">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ196">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AK196">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AL196">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AM196">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AN196">
         <v>1.7</v>
@@ -41783,43 +41786,43 @@
         <v>6</v>
       </c>
       <c r="BD196">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BE196">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="BF196">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BG196">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BH196">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI196">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BJ196">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BK196">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BL196">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BM196">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BN196">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BO196">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BP196">
-        <v>1.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:68">
@@ -41947,7 +41950,7 @@
         <v>1.4</v>
       </c>
       <c r="AP197">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ197">
         <v>1.64</v>
@@ -42284,73 +42287,73 @@
         <v>331</v>
       </c>
       <c r="Q199">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R199">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S199">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T199">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="U199">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V199">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="W199">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X199">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y199">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z199">
-        <v>999.99</v>
+        <v>0</v>
       </c>
       <c r="AA199">
         <v>0</v>
       </c>
       <c r="AB199">
-        <v>999.99</v>
+        <v>0</v>
       </c>
       <c r="AC199">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD199">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AE199">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF199">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AG199">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AH199">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI199">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ199">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK199">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL199">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AM199">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AN199">
         <v>1.6</v>
@@ -42401,43 +42404,43 @@
         <v>16</v>
       </c>
       <c r="BD199">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BE199">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BF199">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BG199">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BH199">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BI199">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BJ199">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BK199">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BL199">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BM199">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BN199">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BO199">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BP199">
-        <v>1.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:68">
@@ -44213,7 +44216,7 @@
         <v>1</v>
       </c>
       <c r="AP208">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ208">
         <v>1.14</v>
@@ -44419,7 +44422,7 @@
         <v>1.45</v>
       </c>
       <c r="AP209">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ209">
         <v>1.36</v>
@@ -44834,7 +44837,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ211">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR211">
         <v>1.51</v>
@@ -45040,7 +45043,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ212">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR212">
         <v>1.24</v>
@@ -45449,7 +45452,7 @@
         <v>0.55</v>
       </c>
       <c r="AP214">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ214">
         <v>0.64</v>
@@ -47921,7 +47924,7 @@
         <v>2.17</v>
       </c>
       <c r="AP226">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ226">
         <v>2.23</v>
@@ -48333,7 +48336,7 @@
         <v>0.75</v>
       </c>
       <c r="AP228">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ228">
         <v>0.64</v>
@@ -48951,10 +48954,10 @@
         <v>1.17</v>
       </c>
       <c r="AP231">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ231">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR231">
         <v>1.44</v>
@@ -49160,7 +49163,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ232">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR232">
         <v>1.33</v>
@@ -49572,7 +49575,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ234">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR234">
         <v>1.56</v>
@@ -49778,7 +49781,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ235">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR235">
         <v>1.26</v>
@@ -52531,6 +52534,624 @@
         <v>3.05</v>
       </c>
       <c r="BP248">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="249" spans="1:68">
+      <c r="A249" s="1">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>7574810</v>
+      </c>
+      <c r="C249" t="s">
+        <v>68</v>
+      </c>
+      <c r="D249" t="s">
+        <v>69</v>
+      </c>
+      <c r="E249" s="2">
+        <v>45753.47916666666</v>
+      </c>
+      <c r="F249">
+        <v>28</v>
+      </c>
+      <c r="G249" t="s">
+        <v>82</v>
+      </c>
+      <c r="H249" t="s">
+        <v>87</v>
+      </c>
+      <c r="I249">
+        <v>0</v>
+      </c>
+      <c r="J249">
+        <v>0</v>
+      </c>
+      <c r="K249">
+        <v>0</v>
+      </c>
+      <c r="L249">
+        <v>0</v>
+      </c>
+      <c r="M249">
+        <v>1</v>
+      </c>
+      <c r="N249">
+        <v>1</v>
+      </c>
+      <c r="O249" t="s">
+        <v>90</v>
+      </c>
+      <c r="P249" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q249">
+        <v>2.75</v>
+      </c>
+      <c r="R249">
+        <v>2</v>
+      </c>
+      <c r="S249">
+        <v>4.5</v>
+      </c>
+      <c r="T249">
+        <v>1.5</v>
+      </c>
+      <c r="U249">
+        <v>2.5</v>
+      </c>
+      <c r="V249">
+        <v>3.5</v>
+      </c>
+      <c r="W249">
+        <v>1.29</v>
+      </c>
+      <c r="X249">
+        <v>11</v>
+      </c>
+      <c r="Y249">
+        <v>1.05</v>
+      </c>
+      <c r="Z249">
+        <v>2.05</v>
+      </c>
+      <c r="AA249">
+        <v>3.1</v>
+      </c>
+      <c r="AB249">
+        <v>3.6</v>
+      </c>
+      <c r="AC249">
+        <v>1.09</v>
+      </c>
+      <c r="AD249">
+        <v>7</v>
+      </c>
+      <c r="AE249">
+        <v>1.42</v>
+      </c>
+      <c r="AF249">
+        <v>2.8</v>
+      </c>
+      <c r="AG249">
+        <v>2.3</v>
+      </c>
+      <c r="AH249">
+        <v>1.57</v>
+      </c>
+      <c r="AI249">
+        <v>2</v>
+      </c>
+      <c r="AJ249">
+        <v>1.75</v>
+      </c>
+      <c r="AK249">
+        <v>1.25</v>
+      </c>
+      <c r="AL249">
+        <v>1.3</v>
+      </c>
+      <c r="AM249">
+        <v>1.77</v>
+      </c>
+      <c r="AN249">
+        <v>1.77</v>
+      </c>
+      <c r="AO249">
+        <v>0.54</v>
+      </c>
+      <c r="AP249">
+        <v>1.64</v>
+      </c>
+      <c r="AQ249">
+        <v>0.71</v>
+      </c>
+      <c r="AR249">
+        <v>1.45</v>
+      </c>
+      <c r="AS249">
+        <v>1.06</v>
+      </c>
+      <c r="AT249">
+        <v>2.51</v>
+      </c>
+      <c r="AU249">
+        <v>7</v>
+      </c>
+      <c r="AV249">
+        <v>4</v>
+      </c>
+      <c r="AW249">
+        <v>13</v>
+      </c>
+      <c r="AX249">
+        <v>10</v>
+      </c>
+      <c r="AY249">
+        <v>26</v>
+      </c>
+      <c r="AZ249">
+        <v>14</v>
+      </c>
+      <c r="BA249">
+        <v>7</v>
+      </c>
+      <c r="BB249">
+        <v>5</v>
+      </c>
+      <c r="BC249">
+        <v>12</v>
+      </c>
+      <c r="BD249">
+        <v>1.74</v>
+      </c>
+      <c r="BE249">
+        <v>6.75</v>
+      </c>
+      <c r="BF249">
+        <v>2.32</v>
+      </c>
+      <c r="BG249">
+        <v>1.29</v>
+      </c>
+      <c r="BH249">
+        <v>3.15</v>
+      </c>
+      <c r="BI249">
+        <v>1.5</v>
+      </c>
+      <c r="BJ249">
+        <v>2.35</v>
+      </c>
+      <c r="BK249">
+        <v>1.81</v>
+      </c>
+      <c r="BL249">
+        <v>1.85</v>
+      </c>
+      <c r="BM249">
+        <v>2.28</v>
+      </c>
+      <c r="BN249">
+        <v>1.52</v>
+      </c>
+      <c r="BO249">
+        <v>2.9</v>
+      </c>
+      <c r="BP249">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="250" spans="1:68">
+      <c r="A250" s="1">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>7574811</v>
+      </c>
+      <c r="C250" t="s">
+        <v>68</v>
+      </c>
+      <c r="D250" t="s">
+        <v>69</v>
+      </c>
+      <c r="E250" s="2">
+        <v>45753.6875</v>
+      </c>
+      <c r="F250">
+        <v>28</v>
+      </c>
+      <c r="G250" t="s">
+        <v>73</v>
+      </c>
+      <c r="H250" t="s">
+        <v>83</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250">
+        <v>2</v>
+      </c>
+      <c r="K250">
+        <v>2</v>
+      </c>
+      <c r="L250">
+        <v>1</v>
+      </c>
+      <c r="M250">
+        <v>4</v>
+      </c>
+      <c r="N250">
+        <v>5</v>
+      </c>
+      <c r="O250" t="s">
+        <v>119</v>
+      </c>
+      <c r="P250" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q250">
+        <v>3.4</v>
+      </c>
+      <c r="R250">
+        <v>2.1</v>
+      </c>
+      <c r="S250">
+        <v>3.2</v>
+      </c>
+      <c r="T250">
+        <v>1.4</v>
+      </c>
+      <c r="U250">
+        <v>2.75</v>
+      </c>
+      <c r="V250">
+        <v>3</v>
+      </c>
+      <c r="W250">
+        <v>1.36</v>
+      </c>
+      <c r="X250">
+        <v>8</v>
+      </c>
+      <c r="Y250">
+        <v>1.08</v>
+      </c>
+      <c r="Z250">
+        <v>2.5</v>
+      </c>
+      <c r="AA250">
+        <v>3.2</v>
+      </c>
+      <c r="AB250">
+        <v>2.65</v>
+      </c>
+      <c r="AC250">
+        <v>1.06</v>
+      </c>
+      <c r="AD250">
+        <v>8.5</v>
+      </c>
+      <c r="AE250">
+        <v>1.33</v>
+      </c>
+      <c r="AF250">
+        <v>3.3</v>
+      </c>
+      <c r="AG250">
+        <v>1.93</v>
+      </c>
+      <c r="AH250">
+        <v>1.77</v>
+      </c>
+      <c r="AI250">
+        <v>1.75</v>
+      </c>
+      <c r="AJ250">
+        <v>2</v>
+      </c>
+      <c r="AK250">
+        <v>1.46</v>
+      </c>
+      <c r="AL250">
+        <v>1.31</v>
+      </c>
+      <c r="AM250">
+        <v>1.47</v>
+      </c>
+      <c r="AN250">
+        <v>2.54</v>
+      </c>
+      <c r="AO250">
+        <v>2</v>
+      </c>
+      <c r="AP250">
+        <v>2.36</v>
+      </c>
+      <c r="AQ250">
+        <v>2.07</v>
+      </c>
+      <c r="AR250">
+        <v>2.02</v>
+      </c>
+      <c r="AS250">
+        <v>1.88</v>
+      </c>
+      <c r="AT250">
+        <v>3.9</v>
+      </c>
+      <c r="AU250">
+        <v>4</v>
+      </c>
+      <c r="AV250">
+        <v>9</v>
+      </c>
+      <c r="AW250">
+        <v>10</v>
+      </c>
+      <c r="AX250">
+        <v>9</v>
+      </c>
+      <c r="AY250">
+        <v>18</v>
+      </c>
+      <c r="AZ250">
+        <v>22</v>
+      </c>
+      <c r="BA250">
+        <v>2</v>
+      </c>
+      <c r="BB250">
+        <v>6</v>
+      </c>
+      <c r="BC250">
+        <v>8</v>
+      </c>
+      <c r="BD250">
+        <v>2.13</v>
+      </c>
+      <c r="BE250">
+        <v>6.4</v>
+      </c>
+      <c r="BF250">
+        <v>2.14</v>
+      </c>
+      <c r="BG250">
+        <v>1.27</v>
+      </c>
+      <c r="BH250">
+        <v>3.14</v>
+      </c>
+      <c r="BI250">
+        <v>1.55</v>
+      </c>
+      <c r="BJ250">
+        <v>2.37</v>
+      </c>
+      <c r="BK250">
+        <v>1.92</v>
+      </c>
+      <c r="BL250">
+        <v>1.88</v>
+      </c>
+      <c r="BM250">
+        <v>2.42</v>
+      </c>
+      <c r="BN250">
+        <v>1.53</v>
+      </c>
+      <c r="BO250">
+        <v>3.34</v>
+      </c>
+      <c r="BP250">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="251" spans="1:68">
+      <c r="A251" s="1">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>7574814</v>
+      </c>
+      <c r="C251" t="s">
+        <v>68</v>
+      </c>
+      <c r="D251" t="s">
+        <v>69</v>
+      </c>
+      <c r="E251" s="2">
+        <v>45754.61458333334</v>
+      </c>
+      <c r="F251">
+        <v>28</v>
+      </c>
+      <c r="G251" t="s">
+        <v>76</v>
+      </c>
+      <c r="H251" t="s">
+        <v>72</v>
+      </c>
+      <c r="I251">
+        <v>0</v>
+      </c>
+      <c r="J251">
+        <v>0</v>
+      </c>
+      <c r="K251">
+        <v>0</v>
+      </c>
+      <c r="L251">
+        <v>0</v>
+      </c>
+      <c r="M251">
+        <v>0</v>
+      </c>
+      <c r="N251">
+        <v>0</v>
+      </c>
+      <c r="O251" t="s">
+        <v>90</v>
+      </c>
+      <c r="P251" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q251">
+        <v>3.4</v>
+      </c>
+      <c r="R251">
+        <v>1.95</v>
+      </c>
+      <c r="S251">
+        <v>3.6</v>
+      </c>
+      <c r="T251">
+        <v>1.53</v>
+      </c>
+      <c r="U251">
+        <v>2.38</v>
+      </c>
+      <c r="V251">
+        <v>3.75</v>
+      </c>
+      <c r="W251">
+        <v>1.25</v>
+      </c>
+      <c r="X251">
+        <v>11</v>
+      </c>
+      <c r="Y251">
+        <v>1.05</v>
+      </c>
+      <c r="Z251">
+        <v>2.8</v>
+      </c>
+      <c r="AA251">
+        <v>2.95</v>
+      </c>
+      <c r="AB251">
+        <v>2.5</v>
+      </c>
+      <c r="AC251">
+        <v>1.05</v>
+      </c>
+      <c r="AD251">
+        <v>6.6</v>
+      </c>
+      <c r="AE251">
+        <v>1.43</v>
+      </c>
+      <c r="AF251">
+        <v>2.53</v>
+      </c>
+      <c r="AG251">
+        <v>2.4</v>
+      </c>
+      <c r="AH251">
+        <v>1.53</v>
+      </c>
+      <c r="AI251">
+        <v>2</v>
+      </c>
+      <c r="AJ251">
+        <v>1.75</v>
+      </c>
+      <c r="AK251">
+        <v>1.46</v>
+      </c>
+      <c r="AL251">
+        <v>1.35</v>
+      </c>
+      <c r="AM251">
+        <v>1.44</v>
+      </c>
+      <c r="AN251">
+        <v>0.54</v>
+      </c>
+      <c r="AO251">
+        <v>1.08</v>
+      </c>
+      <c r="AP251">
+        <v>0.57</v>
+      </c>
+      <c r="AQ251">
+        <v>1.07</v>
+      </c>
+      <c r="AR251">
+        <v>1.39</v>
+      </c>
+      <c r="AS251">
+        <v>1.15</v>
+      </c>
+      <c r="AT251">
+        <v>2.54</v>
+      </c>
+      <c r="AU251">
+        <v>7</v>
+      </c>
+      <c r="AV251">
+        <v>0</v>
+      </c>
+      <c r="AW251">
+        <v>7</v>
+      </c>
+      <c r="AX251">
+        <v>3</v>
+      </c>
+      <c r="AY251">
+        <v>15</v>
+      </c>
+      <c r="AZ251">
+        <v>3</v>
+      </c>
+      <c r="BA251">
+        <v>13</v>
+      </c>
+      <c r="BB251">
+        <v>3</v>
+      </c>
+      <c r="BC251">
+        <v>16</v>
+      </c>
+      <c r="BD251">
+        <v>1.82</v>
+      </c>
+      <c r="BE251">
+        <v>6.65</v>
+      </c>
+      <c r="BF251">
+        <v>2.54</v>
+      </c>
+      <c r="BG251">
+        <v>1.21</v>
+      </c>
+      <c r="BH251">
+        <v>3.58</v>
+      </c>
+      <c r="BI251">
+        <v>1.43</v>
+      </c>
+      <c r="BJ251">
+        <v>2.54</v>
+      </c>
+      <c r="BK251">
+        <v>1.77</v>
+      </c>
+      <c r="BL251">
+        <v>1.94</v>
+      </c>
+      <c r="BM251">
+        <v>2.23</v>
+      </c>
+      <c r="BN251">
+        <v>1.55</v>
+      </c>
+      <c r="BO251">
+        <v>2.97</v>
+      </c>
+      <c r="BP251">
         <v>1.3</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="357">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1446,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP251"/>
+  <dimension ref="A1:BP253"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AQ2">
         <v>0.57</v>
@@ -2195,7 +2195,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ4">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -4046,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ13">
         <v>0.71</v>
@@ -5079,7 +5079,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ18">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -6109,7 +6109,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ23">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR23">
         <v>1.27</v>
@@ -8166,7 +8166,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AQ33">
         <v>1.64</v>
@@ -8578,7 +8578,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ35">
         <v>1.07</v>
@@ -8993,7 +8993,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ37">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR37">
         <v>1.77</v>
@@ -10847,7 +10847,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ46">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR46">
         <v>1.1</v>
@@ -11053,7 +11053,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ47">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR47">
         <v>1.27</v>
@@ -11256,7 +11256,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ48">
         <v>1.21</v>
@@ -12492,7 +12492,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AQ54">
         <v>0.64</v>
@@ -14349,7 +14349,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ63">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR63">
         <v>1.11</v>
@@ -14758,7 +14758,7 @@
         <v>1.33</v>
       </c>
       <c r="AP65">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ65">
         <v>1.36</v>
@@ -15582,7 +15582,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AQ69">
         <v>1.07</v>
@@ -15997,7 +15997,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ71">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR71">
         <v>1.19</v>
@@ -16203,7 +16203,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ72">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR72">
         <v>2.36</v>
@@ -18260,7 +18260,7 @@
         <v>0.25</v>
       </c>
       <c r="AP82">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AQ82">
         <v>0.71</v>
@@ -18466,7 +18466,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ83">
         <v>1.07</v>
@@ -18881,7 +18881,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ85">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR85">
         <v>1.21</v>
@@ -19499,7 +19499,7 @@
         <v>1</v>
       </c>
       <c r="AQ88">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR88">
         <v>0.89</v>
@@ -22174,7 +22174,7 @@
         <v>1</v>
       </c>
       <c r="AP101">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ101">
         <v>0.79</v>
@@ -22383,7 +22383,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ102">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR102">
         <v>1.15</v>
@@ -22586,7 +22586,7 @@
         <v>1.2</v>
       </c>
       <c r="AP103">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AQ103">
         <v>1.43</v>
@@ -23207,7 +23207,7 @@
         <v>1</v>
       </c>
       <c r="AQ106">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR106">
         <v>1.19</v>
@@ -26088,10 +26088,10 @@
         <v>1.29</v>
       </c>
       <c r="AP120">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AQ120">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR120">
         <v>2.02</v>
@@ -27324,7 +27324,7 @@
         <v>1.14</v>
       </c>
       <c r="AP126">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ126">
         <v>1.14</v>
@@ -28563,7 +28563,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ132">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR132">
         <v>1.35</v>
@@ -30211,7 +30211,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ140">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR140">
         <v>1.98</v>
@@ -30620,7 +30620,7 @@
         <v>0.38</v>
       </c>
       <c r="AP142">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ142">
         <v>0.43</v>
@@ -31032,7 +31032,7 @@
         <v>2</v>
       </c>
       <c r="AP144">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AQ144">
         <v>2.07</v>
@@ -31859,7 +31859,7 @@
         <v>2.79</v>
       </c>
       <c r="AQ148">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR148">
         <v>2.01</v>
@@ -33710,7 +33710,7 @@
         <v>2.22</v>
       </c>
       <c r="AP157">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ157">
         <v>2.21</v>
@@ -34537,7 +34537,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ161">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR161">
         <v>1.17</v>
@@ -35976,7 +35976,7 @@
         <v>0.33</v>
       </c>
       <c r="AP168">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AQ168">
         <v>0.43</v>
@@ -36597,7 +36597,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ171">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR171">
         <v>1.66</v>
@@ -38036,7 +38036,7 @@
         <v>0.8</v>
       </c>
       <c r="AP178">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AQ178">
         <v>0.71</v>
@@ -38451,7 +38451,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ180">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR180">
         <v>1.19</v>
@@ -38654,7 +38654,7 @@
         <v>1.44</v>
       </c>
       <c r="AP181">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ181">
         <v>1.64</v>
@@ -39687,7 +39687,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ186">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR186">
         <v>1.19</v>
@@ -41538,7 +41538,7 @@
         <v>1</v>
       </c>
       <c r="AP195">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AQ195">
         <v>1.07</v>
@@ -41744,7 +41744,7 @@
         <v>0.5</v>
       </c>
       <c r="AP196">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ196">
         <v>0.64</v>
@@ -42159,7 +42159,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ198">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR198">
         <v>1.47</v>
@@ -42983,7 +42983,7 @@
         <v>2.79</v>
       </c>
       <c r="AQ202">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR202">
         <v>2.01</v>
@@ -45658,10 +45658,10 @@
         <v>2.36</v>
       </c>
       <c r="AP215">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ215">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR215">
         <v>1.31</v>
@@ -45864,7 +45864,7 @@
         <v>1.18</v>
       </c>
       <c r="AP216">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AQ216">
         <v>1.21</v>
@@ -47927,7 +47927,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ226">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR226">
         <v>1.35</v>
@@ -48542,7 +48542,7 @@
         <v>1.33</v>
       </c>
       <c r="AP229">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AQ229">
         <v>1.36</v>
@@ -49160,7 +49160,7 @@
         <v>1.82</v>
       </c>
       <c r="AP232">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ232">
         <v>2.07</v>
@@ -49369,7 +49369,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ233">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR233">
         <v>1.25</v>
@@ -52551,7 +52551,7 @@
         <v>69</v>
       </c>
       <c r="E249" s="2">
-        <v>45753.47916666666</v>
+        <v>45753.58333333334</v>
       </c>
       <c r="F249">
         <v>28</v>
@@ -53153,6 +53153,418 @@
       </c>
       <c r="BP251">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="252" spans="1:68">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>7574812</v>
+      </c>
+      <c r="C252" t="s">
+        <v>68</v>
+      </c>
+      <c r="D252" t="s">
+        <v>69</v>
+      </c>
+      <c r="E252" s="2">
+        <v>45754.67708333334</v>
+      </c>
+      <c r="F252">
+        <v>28</v>
+      </c>
+      <c r="G252" t="s">
+        <v>81</v>
+      </c>
+      <c r="H252" t="s">
+        <v>86</v>
+      </c>
+      <c r="I252">
+        <v>0</v>
+      </c>
+      <c r="J252">
+        <v>1</v>
+      </c>
+      <c r="K252">
+        <v>1</v>
+      </c>
+      <c r="L252">
+        <v>0</v>
+      </c>
+      <c r="M252">
+        <v>2</v>
+      </c>
+      <c r="N252">
+        <v>2</v>
+      </c>
+      <c r="O252" t="s">
+        <v>90</v>
+      </c>
+      <c r="P252" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q252">
+        <v>2.5</v>
+      </c>
+      <c r="R252">
+        <v>2.1</v>
+      </c>
+      <c r="S252">
+        <v>4.75</v>
+      </c>
+      <c r="T252">
+        <v>1.44</v>
+      </c>
+      <c r="U252">
+        <v>2.63</v>
+      </c>
+      <c r="V252">
+        <v>3.25</v>
+      </c>
+      <c r="W252">
+        <v>1.33</v>
+      </c>
+      <c r="X252">
+        <v>9</v>
+      </c>
+      <c r="Y252">
+        <v>1.07</v>
+      </c>
+      <c r="Z252">
+        <v>1.77</v>
+      </c>
+      <c r="AA252">
+        <v>3.4</v>
+      </c>
+      <c r="AB252">
+        <v>4.3</v>
+      </c>
+      <c r="AC252">
+        <v>1.02</v>
+      </c>
+      <c r="AD252">
+        <v>7.8</v>
+      </c>
+      <c r="AE252">
+        <v>1.33</v>
+      </c>
+      <c r="AF252">
+        <v>2.92</v>
+      </c>
+      <c r="AG252">
+        <v>2.05</v>
+      </c>
+      <c r="AH252">
+        <v>1.7</v>
+      </c>
+      <c r="AI252">
+        <v>1.95</v>
+      </c>
+      <c r="AJ252">
+        <v>1.8</v>
+      </c>
+      <c r="AK252">
+        <v>1.21</v>
+      </c>
+      <c r="AL252">
+        <v>1.29</v>
+      </c>
+      <c r="AM252">
+        <v>1.93</v>
+      </c>
+      <c r="AN252">
+        <v>1.62</v>
+      </c>
+      <c r="AO252">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP252">
+        <v>1.5</v>
+      </c>
+      <c r="AQ252">
+        <v>0.86</v>
+      </c>
+      <c r="AR252">
+        <v>1.3</v>
+      </c>
+      <c r="AS252">
+        <v>0.96</v>
+      </c>
+      <c r="AT252">
+        <v>2.26</v>
+      </c>
+      <c r="AU252">
+        <v>4</v>
+      </c>
+      <c r="AV252">
+        <v>5</v>
+      </c>
+      <c r="AW252">
+        <v>15</v>
+      </c>
+      <c r="AX252">
+        <v>2</v>
+      </c>
+      <c r="AY252">
+        <v>20</v>
+      </c>
+      <c r="AZ252">
+        <v>8</v>
+      </c>
+      <c r="BA252">
+        <v>9</v>
+      </c>
+      <c r="BB252">
+        <v>2</v>
+      </c>
+      <c r="BC252">
+        <v>11</v>
+      </c>
+      <c r="BD252">
+        <v>1.59</v>
+      </c>
+      <c r="BE252">
+        <v>6.85</v>
+      </c>
+      <c r="BF252">
+        <v>3.14</v>
+      </c>
+      <c r="BG252">
+        <v>1.24</v>
+      </c>
+      <c r="BH252">
+        <v>3.34</v>
+      </c>
+      <c r="BI252">
+        <v>1.48</v>
+      </c>
+      <c r="BJ252">
+        <v>2.4</v>
+      </c>
+      <c r="BK252">
+        <v>1.85</v>
+      </c>
+      <c r="BL252">
+        <v>1.85</v>
+      </c>
+      <c r="BM252">
+        <v>2.38</v>
+      </c>
+      <c r="BN252">
+        <v>1.49</v>
+      </c>
+      <c r="BO252">
+        <v>3.14</v>
+      </c>
+      <c r="BP252">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="253" spans="1:68">
+      <c r="A253" s="1">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>7574813</v>
+      </c>
+      <c r="C253" t="s">
+        <v>68</v>
+      </c>
+      <c r="D253" t="s">
+        <v>69</v>
+      </c>
+      <c r="E253" s="2">
+        <v>45754.69791666666</v>
+      </c>
+      <c r="F253">
+        <v>28</v>
+      </c>
+      <c r="G253" t="s">
+        <v>70</v>
+      </c>
+      <c r="H253" t="s">
+        <v>77</v>
+      </c>
+      <c r="I253">
+        <v>1</v>
+      </c>
+      <c r="J253">
+        <v>0</v>
+      </c>
+      <c r="K253">
+        <v>1</v>
+      </c>
+      <c r="L253">
+        <v>1</v>
+      </c>
+      <c r="M253">
+        <v>1</v>
+      </c>
+      <c r="N253">
+        <v>2</v>
+      </c>
+      <c r="O253" t="s">
+        <v>141</v>
+      </c>
+      <c r="P253" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q253">
+        <v>2.1</v>
+      </c>
+      <c r="R253">
+        <v>2.38</v>
+      </c>
+      <c r="S253">
+        <v>5.5</v>
+      </c>
+      <c r="T253">
+        <v>1.33</v>
+      </c>
+      <c r="U253">
+        <v>3.25</v>
+      </c>
+      <c r="V253">
+        <v>2.63</v>
+      </c>
+      <c r="W253">
+        <v>1.44</v>
+      </c>
+      <c r="X253">
+        <v>6.5</v>
+      </c>
+      <c r="Y253">
+        <v>1.11</v>
+      </c>
+      <c r="Z253">
+        <v>1.51</v>
+      </c>
+      <c r="AA253">
+        <v>4</v>
+      </c>
+      <c r="AB253">
+        <v>5.5</v>
+      </c>
+      <c r="AC253">
+        <v>0</v>
+      </c>
+      <c r="AD253">
+        <v>0</v>
+      </c>
+      <c r="AE253">
+        <v>0</v>
+      </c>
+      <c r="AF253">
+        <v>0</v>
+      </c>
+      <c r="AG253">
+        <v>1.73</v>
+      </c>
+      <c r="AH253">
+        <v>2</v>
+      </c>
+      <c r="AI253">
+        <v>1.8</v>
+      </c>
+      <c r="AJ253">
+        <v>1.95</v>
+      </c>
+      <c r="AK253">
+        <v>0</v>
+      </c>
+      <c r="AL253">
+        <v>0</v>
+      </c>
+      <c r="AM253">
+        <v>0</v>
+      </c>
+      <c r="AN253">
+        <v>2.62</v>
+      </c>
+      <c r="AO253">
+        <v>2.23</v>
+      </c>
+      <c r="AP253">
+        <v>2.5</v>
+      </c>
+      <c r="AQ253">
+        <v>2.14</v>
+      </c>
+      <c r="AR253">
+        <v>2.13</v>
+      </c>
+      <c r="AS253">
+        <v>1.47</v>
+      </c>
+      <c r="AT253">
+        <v>3.6</v>
+      </c>
+      <c r="AU253">
+        <v>9</v>
+      </c>
+      <c r="AV253">
+        <v>4</v>
+      </c>
+      <c r="AW253">
+        <v>8</v>
+      </c>
+      <c r="AX253">
+        <v>5</v>
+      </c>
+      <c r="AY253">
+        <v>17</v>
+      </c>
+      <c r="AZ253">
+        <v>11</v>
+      </c>
+      <c r="BA253">
+        <v>4</v>
+      </c>
+      <c r="BB253">
+        <v>0</v>
+      </c>
+      <c r="BC253">
+        <v>4</v>
+      </c>
+      <c r="BD253">
+        <v>0</v>
+      </c>
+      <c r="BE253">
+        <v>0</v>
+      </c>
+      <c r="BF253">
+        <v>0</v>
+      </c>
+      <c r="BG253">
+        <v>0</v>
+      </c>
+      <c r="BH253">
+        <v>0</v>
+      </c>
+      <c r="BI253">
+        <v>0</v>
+      </c>
+      <c r="BJ253">
+        <v>0</v>
+      </c>
+      <c r="BK253">
+        <v>0</v>
+      </c>
+      <c r="BL253">
+        <v>0</v>
+      </c>
+      <c r="BM253">
+        <v>0</v>
+      </c>
+      <c r="BN253">
+        <v>0</v>
+      </c>
+      <c r="BO253">
+        <v>0</v>
+      </c>
+      <c r="BP253">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal Liga NOS_20242025.xlsx
@@ -1948,7 +1948,7 @@
         <v>3</v>
       </c>
       <c r="AY2">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AZ2">
         <v>5</v>
@@ -2154,7 +2154,7 @@
         <v>5</v>
       </c>
       <c r="AY3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ3">
         <v>8</v>
@@ -2360,10 +2360,10 @@
         <v>4</v>
       </c>
       <c r="AY4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA4">
         <v>3</v>
@@ -2566,7 +2566,7 @@
         <v>1</v>
       </c>
       <c r="AY5">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AZ5">
         <v>3</v>
@@ -2772,10 +2772,10 @@
         <v>2</v>
       </c>
       <c r="AY6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ6">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA6">
         <v>1</v>
@@ -2981,7 +2981,7 @@
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA7">
         <v>0</v>
@@ -3184,10 +3184,10 @@
         <v>4</v>
       </c>
       <c r="AY8">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ8">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA8">
         <v>5</v>
@@ -3390,7 +3390,7 @@
         <v>2</v>
       </c>
       <c r="AY9">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ9">
         <v>7</v>
@@ -3596,10 +3596,10 @@
         <v>4</v>
       </c>
       <c r="AY10">
+        <v>5</v>
+      </c>
+      <c r="AZ10">
         <v>9</v>
-      </c>
-      <c r="AZ10">
-        <v>12</v>
       </c>
       <c r="BA10">
         <v>6</v>
@@ -3802,10 +3802,10 @@
         <v>3</v>
       </c>
       <c r="AY11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA11">
         <v>2</v>
@@ -4008,10 +4008,10 @@
         <v>2</v>
       </c>
       <c r="AY12">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ12">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA12">
         <v>2</v>
@@ -4214,10 +4214,10 @@
         <v>7</v>
       </c>
       <c r="AY13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ13">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="BA13">
         <v>7</v>
@@ -4420,10 +4420,10 @@
         <v>5</v>
       </c>
       <c r="AY14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ14">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BA14">
         <v>4</v>
@@ -4626,10 +4626,10 @@
         <v>3</v>
       </c>
       <c r="AY15">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AZ15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA15">
         <v>12</v>
@@ -4832,10 +4832,10 @@
         <v>6</v>
       </c>
       <c r="AY16">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ16">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA16">
         <v>6</v>
@@ -5038,10 +5038,10 @@
         <v>2</v>
       </c>
       <c r="AY17">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AZ17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA17">
         <v>9</v>
@@ -5244,10 +5244,10 @@
         <v>6</v>
       </c>
       <c r="AY18">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ18">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA18">
         <v>3</v>
@@ -5450,10 +5450,10 @@
         <v>5</v>
       </c>
       <c r="AY19">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ19">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA19">
         <v>2</v>
@@ -5656,10 +5656,10 @@
         <v>9</v>
       </c>
       <c r="AY20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AZ20">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="BA20">
         <v>1</v>
@@ -5862,10 +5862,10 @@
         <v>2</v>
       </c>
       <c r="AY21">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA21">
         <v>7</v>
@@ -6068,7 +6068,7 @@
         <v>0</v>
       </c>
       <c r="AY22">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ22">
         <v>0</v>
@@ -6274,10 +6274,10 @@
         <v>2</v>
       </c>
       <c r="AY23">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AZ23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA23">
         <v>7</v>
@@ -6480,10 +6480,10 @@
         <v>5</v>
       </c>
       <c r="AY24">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA24">
         <v>12</v>
@@ -6686,10 +6686,10 @@
         <v>10</v>
       </c>
       <c r="AY25">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ25">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA25">
         <v>9</v>
@@ -6892,10 +6892,10 @@
         <v>6</v>
       </c>
       <c r="AY26">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ26">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA26">
         <v>8</v>
@@ -7098,10 +7098,10 @@
         <v>7</v>
       </c>
       <c r="AY27">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ27">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA27">
         <v>3</v>
@@ -7304,10 +7304,10 @@
         <v>4</v>
       </c>
       <c r="AY28">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ28">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA28">
         <v>6</v>
@@ -7510,10 +7510,10 @@
         <v>7</v>
       </c>
       <c r="AY29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ29">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA29">
         <v>0</v>
@@ -7716,10 +7716,10 @@
         <v>6</v>
       </c>
       <c r="AY30">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA30">
         <v>3</v>
@@ -7922,10 +7922,10 @@
         <v>5</v>
       </c>
       <c r="AY31">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ31">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA31">
         <v>2</v>
@@ -8128,10 +8128,10 @@
         <v>6</v>
       </c>
       <c r="AY32">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA32">
         <v>8</v>
@@ -8334,10 +8334,10 @@
         <v>3</v>
       </c>
       <c r="AY33">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA33">
         <v>2</v>
@@ -8540,10 +8540,10 @@
         <v>7</v>
       </c>
       <c r="AY34">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ34">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BA34">
         <v>4</v>
@@ -8746,10 +8746,10 @@
         <v>8</v>
       </c>
       <c r="AY35">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ35">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA35">
         <v>8</v>
@@ -8952,10 +8952,10 @@
         <v>3</v>
       </c>
       <c r="AY36">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA36">
         <v>5</v>
@@ -9158,10 +9158,10 @@
         <v>5</v>
       </c>
       <c r="AY37">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA37">
         <v>4</v>
@@ -9364,10 +9364,10 @@
         <v>7</v>
       </c>
       <c r="AY38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ38">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="BA38">
         <v>2</v>
@@ -9570,10 +9570,10 @@
         <v>7</v>
       </c>
       <c r="AY39">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AZ39">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA39">
         <v>4</v>
@@ -9776,10 +9776,10 @@
         <v>6</v>
       </c>
       <c r="AY40">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ40">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="BA40">
         <v>4</v>
@@ -9982,10 +9982,10 @@
         <v>5</v>
       </c>
       <c r="AY41">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA41">
         <v>8</v>
@@ -10188,10 +10188,10 @@
         <v>3</v>
       </c>
       <c r="AY42">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ42">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA42">
         <v>5</v>
@@ -10394,19 +10394,19 @@
         <v>6</v>
       </c>
       <c r="AY43">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AZ43">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA43">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB43">
         <v>0</v>
       </c>
       <c r="BC43">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD43">
         <v>1.07</v>
@@ -10600,10 +10600,10 @@
         <v>11</v>
       </c>
       <c r="AY44">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ44">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA44">
         <v>3</v>
@@ -10806,10 +10806,10 @@
         <v>6</v>
       </c>
       <c r="AY45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ45">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA45">
         <v>6</v>
@@ -11012,10 +11012,10 @@
         <v>6</v>
       </c>
       <c r="AY46">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ46">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA46">
         <v>9</v>
@@ -11218,10 +11218,10 @@
         <v>7</v>
       </c>
       <c r="AY47">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ47">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA47">
         <v>6</v>
@@ -11424,10 +11424,10 @@
         <v>3</v>
       </c>
       <c r="AY48">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ48">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA48">
         <v>7</v>
@@ -11633,7 +11633,7 @@
         <v>9</v>
       </c>
       <c r="AZ49">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA49">
         <v>3</v>
@@ -11836,10 +11836,10 @@
         <v>4</v>
       </c>
       <c r="AY50">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ50">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA50">
         <v>5</v>
@@ -12042,10 +12042,10 @@
         <v>2</v>
       </c>
       <c r="AY51">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ51">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BA51">
         <v>4</v>
@@ -12248,10 +12248,10 @@
         <v>3</v>
       </c>
       <c r="AY52">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ52">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA52">
         <v>9</v>
@@ -12454,10 +12454,10 @@
         <v>3</v>
       </c>
       <c r="AY53">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ53">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BA53">
         <v>10</v>
@@ -12660,10 +12660,10 @@
         <v>3</v>
       </c>
       <c r="AY54">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AZ54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA54">
         <v>9</v>
@@ -12866,10 +12866,10 @@
         <v>3</v>
       </c>
       <c r="AY55">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ55">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA55">
         <v>4</v>
@@ -13075,7 +13075,7 @@
         <v>6</v>
       </c>
       <c r="AZ56">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="BA56">
         <v>1</v>
@@ -13278,10 +13278,10 @@
         <v>9</v>
       </c>
       <c r="AY57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ57">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA57">
         <v>2</v>
@@ -13484,10 +13484,10 @@
         <v>7</v>
       </c>
       <c r="AY58">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ58">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="BA58">
         <v>7</v>
@@ -13690,10 +13690,10 @@
         <v>5</v>
       </c>
       <c r="AY59">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ59">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA59">
         <v>11</v>
@@ -13896,10 +13896,10 @@
         <v>5</v>
       </c>
       <c r="AY60">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AZ60">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA60">
         <v>8</v>
@@ -14102,10 +14102,10 @@
         <v>4</v>
       </c>
       <c r="AY61">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AZ61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA61">
         <v>8</v>
@@ -14308,10 +14308,10 @@
         <v>6</v>
       </c>
       <c r="AY62">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ62">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA62">
         <v>4</v>
@@ -14514,10 +14514,10 @@
         <v>2</v>
       </c>
       <c r="AY63">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA63">
         <v>3</v>
@@ -14720,10 +14720,10 @@
         <v>6</v>
       </c>
       <c r="AY64">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ64">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA64">
         <v>6</v>
@@ -14926,10 +14926,10 @@
         <v>2</v>
       </c>
       <c r="AY65">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ65">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA65">
         <v>11</v>
@@ -16574,7 +16574,7 @@
         <v>13</v>
       </c>
       <c r="AY73">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ73">
         <v>20</v>
@@ -16780,10 +16780,10 @@
         <v>5</v>
       </c>
       <c r="AY74">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ74">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA74">
         <v>6</v>
@@ -16986,10 +16986,10 @@
         <v>7</v>
       </c>
       <c r="AY75">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ75">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA75">
         <v>6</v>
@@ -17192,10 +17192,10 @@
         <v>7</v>
       </c>
       <c r="AY76">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ76">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA76">
         <v>4</v>
@@ -17398,10 +17398,10 @@
         <v>9</v>
       </c>
       <c r="AY77">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ77">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="BA77">
         <v>4</v>
@@ -17604,10 +17604,10 @@
         <v>1</v>
       </c>
       <c r="AY78">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA78">
         <v>10</v>
@@ -17810,10 +17810,10 @@
         <v>4</v>
       </c>
       <c r="AY79">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AZ79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA79">
         <v>8</v>
@@ -18019,7 +18019,7 @@
         <v>8</v>
       </c>
       <c r="AZ80">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA80">
         <v>3</v>
@@ -18428,10 +18428,10 @@
         <v>3</v>
       </c>
       <c r="AY82">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AZ82">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA82">
         <v>12</v>
@@ -18634,10 +18634,10 @@
         <v>5</v>
       </c>
       <c r="AY83">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ83">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA83">
         <v>3</v>
@@ -18840,10 +18840,10 @@
         <v>6</v>
       </c>
       <c r="AY84">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ84">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA84">
         <v>3</v>
@@ -19046,10 +19046,10 @@
         <v>7</v>
       </c>
       <c r="AY85">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ85">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA85">
         <v>7</v>
@@ -19252,10 +19252,10 @@
         <v>10</v>
       </c>
       <c r="AY86">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ86">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA86">
         <v>4</v>
@@ -19458,10 +19458,10 @@
         <v>3</v>
       </c>
       <c r="AY87">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ87">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA87">
         <v>9</v>
@@ -19664,10 +19664,10 @@
         <v>8</v>
       </c>
       <c r="AY88">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ88">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA88">
         <v>12</v>
@@ -19870,10 +19870,10 @@
         <v>4</v>
       </c>
       <c r="AY89">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ89">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA89">
         <v>9</v>
@@ -20076,10 +20076,10 @@
         <v>5</v>
       </c>
       <c r="AY90">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ90">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="BA90">
         <v>2</v>
@@ -20285,7 +20285,7 @@
         <v>13</v>
       </c>
       <c r="AZ91">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA91">
         <v>3</v>
@@ -20488,10 +20488,10 @@
         <v>2</v>
       </c>
       <c r="AY92">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ92">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA92">
         <v>4</v>
@@ -20900,10 +20900,10 @@
         <v>4</v>
       </c>
       <c r="AY94">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AZ94">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA94">
         <v>4</v>
@@ -21106,10 +21106,10 @@
         <v>2</v>
       </c>
       <c r="AY95">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AZ95">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA95">
         <v>7</v>
@@ -21312,10 +21312,10 @@
         <v>8</v>
       </c>
       <c r="AY96">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ96">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA96">
         <v>10</v>
@@ -21518,10 +21518,10 @@
         <v>1</v>
       </c>
       <c r="AY97">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ97">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA97">
         <v>9</v>
@@ -21724,10 +21724,10 @@
         <v>5</v>
       </c>
       <c r="AY98">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ98">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA98">
         <v>0</v>
@@ -21930,10 +21930,10 @@
         <v>4</v>
       </c>
       <c r="AY99">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ99">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA99">
         <v>2</v>
@@ -22136,10 +22136,10 @@
         <v>7</v>
       </c>
       <c r="AY100">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ100">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA100">
         <v>3</v>
@@ -22342,10 +22342,10 @@
         <v>7</v>
       </c>
       <c r="AY101">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ101">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA101">
         <v>2</v>
@@ -22548,10 +22548,10 @@
         <v>4</v>
       </c>
       <c r="AY102">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AZ102">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA102">
         <v>4</v>
@@ -22754,7 +22754,7 @@
         <v>1</v>
       </c>
       <c r="AY103">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AZ103">
         <v>5</v>
@@ -23166,10 +23166,10 @@
         <v>2</v>
       </c>
       <c r="AY105">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ105">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA105">
         <v>5</v>
@@ -23372,10 +23372,10 @@
         <v>4</v>
       </c>
       <c r="AY106">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ106">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BA106">
         <v>2</v>
@@ -23578,7 +23578,7 @@
         <v>4</v>
       </c>
       <c r="AY107">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AZ107">
         <v>4</v>
@@ -23784,10 +23784,10 @@
         <v>3</v>
       </c>
       <c r="AY108">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ108">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA108">
         <v>8</v>
@@ -23990,10 +23990,10 @@
         <v>8</v>
       </c>
       <c r="AY109">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ109">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BA109">
         <v>4</v>
@@ -24196,10 +24196,10 @@
         <v>6</v>
       </c>
       <c r="AY110">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ110">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA110">
         <v>3</v>
@@ -24402,10 +24402,10 @@
         <v>4</v>
       </c>
       <c r="AY111">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ111">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BA111">
         <v>6</v>
@@ -24608,10 +24608,10 @@
         <v>6</v>
       </c>
       <c r="AY112">
+        <v>5</v>
+      </c>
+      <c r="AZ112">
         <v>9</v>
-      </c>
-      <c r="AZ112">
-        <v>11</v>
       </c>
       <c r="BA112">
         <v>6</v>
@@ -24814,7 +24814,7 @@
         <v>2</v>
       </c>
       <c r="AY113">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ113">
         <v>5</v>
@@ -25020,10 +25020,10 @@
         <v>5</v>
       </c>
       <c r="AY114">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ114">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="BA114">
         <v>3</v>
@@ -25432,10 +25432,10 @@
         <v>3</v>
       </c>
       <c r="AY116">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ116">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA116">
         <v>6</v>
@@ -25638,10 +25638,10 @@
         <v>4</v>
       </c>
       <c r="AY117">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ117">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA117">
         <v>2</v>
@@ -25844,10 +25844,10 @@
         <v>3</v>
       </c>
       <c r="AY118">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ118">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA118">
         <v>7</v>
@@ -26462,10 +26462,10 @@
         <v>2</v>
       </c>
       <c r="AY121">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ121">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA121">
         <v>7</v>
@@ -26668,10 +26668,10 @@
         <v>6</v>
       </c>
       <c r="AY122">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ122">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA122">
         <v>0</v>
@@ -26874,10 +26874,10 @@
         <v>5</v>
       </c>
       <c r="AY123">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ123">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA123">
         <v>5</v>
@@ -27080,7 +27080,7 @@
         <v>2</v>
       </c>
       <c r="AY124">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ124">
         <v>11</v>
@@ -27495,7 +27495,7 @@
         <v>6</v>
       </c>
       <c r="AZ126">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA126">
         <v>0</v>
@@ -27698,10 +27698,10 @@
         <v>5</v>
       </c>
       <c r="AY127">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AZ127">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA127">
         <v>4</v>
@@ -27904,10 +27904,10 @@
         <v>2</v>
       </c>
       <c r="AY128">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ128">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA128">
         <v>3</v>
@@ -28110,10 +28110,10 @@
         <v>1</v>
       </c>
       <c r="AY129">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ129">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA129">
         <v>7</v>
@@ -28316,10 +28316,10 @@
         <v>4</v>
       </c>
       <c r="AY130">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ130">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA130">
         <v>5</v>
@@ -28522,10 +28522,10 @@
         <v>3</v>
       </c>
       <c r="AY131">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ131">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA131">
         <v>2</v>
@@ -28728,10 +28728,10 @@
         <v>5</v>
       </c>
       <c r="AY132">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ132">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA132">
         <v>2</v>
@@ -28937,7 +28937,7 @@
         <v>4</v>
       </c>
       <c r="AZ133">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA133">
         <v>3</v>
@@ -29140,10 +29140,10 @@
         <v>5</v>
       </c>
       <c r="AY134">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AZ134">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA134">
         <v>7</v>
@@ -29346,10 +29346,10 @@
         <v>8</v>
       </c>
       <c r="AY135">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ135">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA135">
         <v>4</v>
@@ -29552,10 +29552,10 @@
         <v>3</v>
       </c>
       <c r="AY136">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ136">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BA136">
         <v>5</v>
@@ -29758,10 +29758,10 @@
         <v>2</v>
       </c>
       <c r="AY137">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ137">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA137">
         <v>5</v>
@@ -29964,10 +29964,10 @@
         <v>9</v>
       </c>
       <c r="AY138">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ138">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA138">
         <v>7</v>
@@ -30170,10 +30170,10 @@
         <v>1</v>
       </c>
       <c r="AY139">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ139">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA139">
         <v>6</v>
@@ -30376,10 +30376,10 @@
         <v>1</v>
       </c>
       <c r="AY140">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ140">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA140">
         <v>4</v>
@@ -30582,10 +30582,10 @@
         <v>11</v>
       </c>
       <c r="AY141">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ141">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BA141">
         <v>6</v>
@@ -30788,10 +30788,10 @@
         <v>11</v>
       </c>
       <c r="AY142">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AZ142">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA142">
         <v>11</v>
@@ -30994,10 +30994,10 @@
         <v>3</v>
       </c>
       <c r="AY143">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ143">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA143">
         <v>10</v>
@@ -31200,10 +31200,10 @@
         <v>9</v>
       </c>
       <c r="AY144">
+        <v>10</v>
+      </c>
+      <c r="AZ144">
         <v>13</v>
-      </c>
-      <c r="AZ144">
-        <v>16</v>
       </c>
       <c r="BA144">
         <v>4</v>
@@ -31406,10 +31406,10 @@
         <v>4</v>
       </c>
       <c r="AY145">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ145">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA145">
         <v>5</v>
@@ -31612,10 +31612,10 @@
         <v>3</v>
       </c>
       <c r="AY146">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ146">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA146">
         <v>6</v>
@@ -31818,10 +31818,10 @@
         <v>8</v>
       </c>
       <c r="AY147">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ147">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BA147">
         <v>3</v>
@@ -32024,10 +32024,10 @@
         <v>2</v>
       </c>
       <c r="AY148">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ148">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA148">
         <v>8</v>
@@ -32230,10 +32230,10 @@
         <v>7</v>
       </c>
       <c r="AY149">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ149">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA149">
         <v>3</v>
@@ -32436,10 +32436,10 @@
         <v>0</v>
       </c>
       <c r="AY150">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ150">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA150">
         <v>13</v>
@@ -32642,10 +32642,10 @@
         <v>3</v>
       </c>
       <c r="AY151">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ151">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA151">
         <v>5</v>
@@ -32848,10 +32848,10 @@
         <v>5</v>
       </c>
       <c r="AY152">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ152">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA152">
         <v>3</v>
@@ -33054,10 +33054,10 @@
         <v>5</v>
       </c>
       <c r="AY153">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ153">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA153">
         <v>4</v>
@@ -33260,10 +33260,10 @@
         <v>7</v>
       </c>
       <c r="AY154">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ154">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA154">
         <v>1</v>
@@ -33466,7 +33466,7 @@
         <v>2</v>
       </c>
       <c r="AY155">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ155">
         <v>2</v>
@@ -33672,10 +33672,10 @@
         <v>7</v>
       </c>
       <c r="AY156">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ156">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA156">
         <v>7</v>
@@ -33878,10 +33878,10 @@
         <v>17</v>
       </c>
       <c r="AY157">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ157">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BA157">
         <v>0</v>
@@ -34084,10 +34084,10 @@
         <v>14</v>
       </c>
       <c r="AY158">
+        <v>16</v>
+      </c>
+      <c r="AZ158">
         <v>20</v>
-      </c>
-      <c r="AZ158">
-        <v>22</v>
       </c>
       <c r="BA158">
         <v>9</v>
@@ -34702,10 +34702,10 @@
         <v>10</v>
       </c>
       <c r="AY161">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ161">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA161">
         <v>1</v>
@@ -34908,10 +34908,10 @@
         <v>11</v>
       </c>
       <c r="AY162">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ162">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA162">
         <v>4</v>
@@ -35114,7 +35114,7 @@
         <v>3</v>
       </c>
       <c r="AY163">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ163">
         <v>11</v>
@@ -35320,7 +35320,7 @@
         <v>6</v>
       </c>
       <c r="AY164">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ164">
         <v>9</v>
@@ -35526,7 +35526,7 @@
         <v>7</v>
       </c>
       <c r="AY165">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ165">
         <v>10</v>
@@ -35732,10 +35732,10 @@
         <v>4</v>
       </c>
       <c r="AY166">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ166">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA166">
         <v>5</v>
@@ -35938,10 +35938,10 @@
         <v>10</v>
       </c>
       <c r="AY167">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ167">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA167">
         <v>2</v>
@@ -36144,10 +36144,10 @@
         <v>3</v>
       </c>
       <c r="AY168">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ168">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA168">
         <v>6</v>
@@ -36556,7 +36556,7 @@
         <v>2</v>
       </c>
       <c r="AY170">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AZ170">
         <v>2</v>
@@ -36762,7 +36762,7 @@
         <v>6</v>
       </c>
       <c r="AY171">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ171">
         <v>9</v>
@@ -36968,10 +36968,10 @@
         <v>10</v>
       </c>
       <c r="AY172">
+        <v>9</v>
+      </c>
+      <c r="AZ172">
         <v>10</v>
-      </c>
-      <c r="AZ172">
-        <v>12</v>
       </c>
       <c r="BA172">
         <v>1</v>
@@ -37174,10 +37174,10 @@
         <v>15</v>
       </c>
       <c r="AY173">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ173">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BA173">
         <v>2</v>
@@ -37380,10 +37380,10 @@
         <v>4</v>
       </c>
       <c r="AY174">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ174">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA174">
         <v>5</v>
@@ -37586,10 +37586,10 @@
         <v>4</v>
       </c>
       <c r="AY175">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ175">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA175">
         <v>3</v>
@@ -37792,10 +37792,10 @@
         <v>13</v>
       </c>
       <c r="AY176">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ176">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BA176">
         <v>3</v>
@@ -37998,10 +37998,10 @@
         <v>3</v>
       </c>
       <c r="AY177">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ177">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA177">
         <v>8</v>
@@ -38204,10 +38204,10 @@
         <v>5</v>
       </c>
       <c r="AY178">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AZ178">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA178">
         <v>9</v>
@@ -38413,7 +38413,7 @@
         <v>8</v>
       </c>
       <c r="AZ179">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA179">
         <v>0</v>
@@ -38616,10 +38616,10 @@
         <v>7</v>
       </c>
       <c r="AY180">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ180">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA180">
         <v>1</v>
@@ -38822,10 +38822,10 @@
         <v>14</v>
       </c>
       <c r="AY181">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ181">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BA181">
         <v>3</v>
@@ -39028,10 +39028,10 @@
         <v>9</v>
       </c>
       <c r="AY182">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AZ182">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA182">
         <v>6</v>
@@ -39234,10 +39234,10 @@
         <v>3</v>
       </c>
       <c r="AY183">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ183">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA183">
         <v>2</v>
@@ -39440,7 +39440,7 @@
         <v>4</v>
       </c>
       <c r="AY184">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ184">
         <v>9</v>
@@ -39646,10 +39646,10 @@
         <v>6</v>
       </c>
       <c r="AY185">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ185">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA185">
         <v>4</v>
@@ -39852,10 +39852,10 @@
         <v>6</v>
       </c>
       <c r="AY186">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ186">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA186">
         <v>5</v>
@@ -40058,10 +40058,10 @@
         <v>6</v>
       </c>
       <c r="AY187">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AZ187">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA187">
         <v>12</v>
@@ -40264,10 +40264,10 @@
         <v>3</v>
       </c>
       <c r="AY188">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ188">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA188">
         <v>4</v>
@@ -40470,10 +40470,10 @@
         <v>8</v>
       </c>
       <c r="AY189">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ189">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA189">
         <v>5</v>
@@ -40676,10 +40676,10 @@
         <v>7</v>
       </c>
       <c r="AY190">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ190">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA190">
         <v>6</v>
@@ -40882,7 +40882,7 @@
         <v>3</v>
       </c>
       <c r="AY191">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ191">
         <v>9</v>
@@ -41088,10 +41088,10 @@
         <v>11</v>
       </c>
       <c r="AY192">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ192">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BA192">
         <v>4</v>
@@ -41294,10 +41294,10 @@
         <v>3</v>
       </c>
       <c r="AY193">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AZ193">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA193">
         <v>7</v>
@@ -41500,10 +41500,10 @@
         <v>11</v>
       </c>
       <c r="AY194">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ194">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA194">
         <v>2</v>
@@ -41706,10 +41706,10 @@
         <v>10</v>
       </c>
       <c r="AY195">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AZ195">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BA195">
         <v>9</v>
@@ -41912,10 +41912,10 @@
         <v>10</v>
       </c>
       <c r="AY196">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ196">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA196">
         <v>2</v>
@@ -42121,7 +42121,7 @@
         <v>10</v>
       </c>
       <c r="AZ197">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA197">
         <v>2</v>
@@ -42324,7 +42324,7 @@
         <v>2</v>
       </c>
       <c r="AY198">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ198">
         <v>6</v>
@@ -42530,10 +42530,10 @@
         <v>16</v>
       </c>
       <c r="AY199">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ199">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BA199">
         <v>5</v>
@@ -42736,10 +42736,10 @@
         <v>5</v>
       </c>
       <c r="AY200">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ200">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA200">
         <v>7</v>
@@ -42942,10 +42942,10 @@
         <v>4</v>
       </c>
       <c r="AY201">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ201">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA201">
         <v>2</v>
@@ -43148,10 +43148,10 @@
         <v>3</v>
       </c>
       <c r="AY202">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="AZ202">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA202">
         <v>13</v>
@@ -43354,10 +43354,10 @@
         <v>8</v>
       </c>
       <c r="AY203">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ203">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA203">
         <v>0</v>
@@ -43560,10 +43560,10 @@
         <v>4</v>
       </c>
       <c r="AY204">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ204">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA204">
         <v>5</v>
@@ -43766,10 +43766,10 @@
         <v>10</v>
       </c>
       <c r="AY205">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ205">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA205">
         <v>4</v>
@@ -43972,10 +43972,10 @@
         <v>6</v>
       </c>
       <c r="AY206">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ206">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA206">
         <v>4</v>
@@ -44178,7 +44178,7 @@
         <v>2</v>
       </c>
       <c r="AY207">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AZ207">
         <v>9</v>
@@ -44384,10 +44384,10 @@
         <v>7</v>
       </c>
       <c r="AY208">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ208">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA208">
         <v>6</v>
@@ -44590,10 +44590,10 @@
         <v>13</v>
       </c>
       <c r="AY209">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ209">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA209">
         <v>1</v>
@@ -44796,10 +44796,10 @@
         <v>7</v>
       </c>
       <c r="AY210">
+        <v>9</v>
+      </c>
+      <c r="AZ210">
         <v>10</v>
-      </c>
-      <c r="AZ210">
-        <v>13</v>
       </c>
       <c r="BA210">
         <v>4</v>
@@ -45002,10 +45002,10 @@
         <v>7</v>
       </c>
       <c r="AY211">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ211">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA211">
         <v>7</v>
@@ -45208,10 +45208,10 @@
         <v>6</v>
       </c>
       <c r="AY212">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ212">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA212">
         <v>4</v>
@@ -45414,10 +45414,10 @@
         <v>10</v>
       </c>
       <c r="AY213">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ213">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BA213">
         <v>9</v>
@@ -45620,7 +45620,7 @@
         <v>3</v>
       </c>
       <c r="AY214">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ214">
         <v>7</v>
@@ -45829,7 +45829,7 @@
         <v>15</v>
       </c>
       <c r="AZ215">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA215">
         <v>2</v>
@@ -46032,10 +46032,10 @@
         <v>7</v>
       </c>
       <c r="AY216">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ216">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA216">
         <v>6</v>
@@ -46238,10 +46238,10 @@
         <v>8</v>
       </c>
       <c r="AY217">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ217">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA217">
         <v>7</v>
@@ -46444,10 +46444,10 @@
         <v>14</v>
       </c>
       <c r="AY218">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ218">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA218">
         <v>1</v>
@@ -46650,10 +46650,10 @@
         <v>10</v>
       </c>
       <c r="AY219">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ219">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA219">
         <v>4</v>
@@ -46856,10 +46856,10 @@
         <v>8</v>
       </c>
       <c r="AY220">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ220">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA220">
         <v>5</v>
@@ -47065,7 +47065,7 @@
         <v>9</v>
       </c>
       <c r="AZ221">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA221">
         <v>7</v>
@@ -47268,10 +47268,10 @@
         <v>6</v>
       </c>
       <c r="AY222">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ222">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA222">
         <v>4</v>
@@ -47680,10 +47680,10 @@
         <v>11</v>
       </c>
       <c r="AY224">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ224">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA224">
         <v>2</v>
@@ -47886,10 +47886,10 @@
         <v>10</v>
       </c>
       <c r="AY225">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ225">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA225">
         <v>5</v>
@@ -48092,10 +48092,10 @@
         <v>5</v>
       </c>
       <c r="AY226">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ226">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA226">
         <v>12</v>
@@ -48298,7 +48298,7 @@
         <v>1</v>
       </c>
       <c r="AY227">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ227">
         <v>5</v>
@@ -48504,10 +48504,10 @@
         <v>5</v>
       </c>
       <c r="AY228">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ228">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA228">
         <v>4</v>
@@ -48710,10 +48710,10 @@
         <v>5</v>
       </c>
       <c r="AY229">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AZ229">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA229">
         <v>11</v>
@@ -48916,10 +48916,10 @@
         <v>7</v>
       </c>
       <c r="AY230">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ230">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA230">
         <v>3</v>
@@ -49122,10 +49122,10 @@
         <v>8</v>
       </c>
       <c r="AY231">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ231">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA231">
         <v>2</v>
@@ -49328,10 +49328,10 @@
         <v>13</v>
       </c>
       <c r="AY232">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ232">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA232">
         <v>3</v>
@@ -49534,10 +49534,10 @@
         <v>4</v>
       </c>
       <c r="AY233">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AZ233">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA233">
         <v>6</v>
@@ -49740,7 +49740,7 @@
         <v>6</v>
       </c>
       <c r="AY234">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ234">
         <v>8</v>
@@ -49946,10 +49946,10 @@
         <v>11</v>
       </c>
       <c r="AY235">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ235">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BA235">
         <v>5</v>
@@ -50152,10 +50152,10 @@
         <v>7</v>
       </c>
       <c r="AY236">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ236">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA236">
         <v>7</v>
@@ -50358,10 +50358,10 @@
         <v>7</v>
       </c>
       <c r="AY237">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ237">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA237">
         <v>3</v>
@@ -50564,10 +50564,10 @@
         <v>4</v>
       </c>
       <c r="AY238">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ238">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA238">
         <v>7</v>
@@ -50979,7 +50979,7 @@
         <v>15</v>
       </c>
       <c r="AZ240">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA240">
         <v>4</v>
@@ -51185,7 +51185,7 @@
         <v>4</v>
       </c>
       <c r="AZ241">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA241">
         <v>1</v>
@@ -51388,10 +51388,10 @@
         <v>8</v>
       </c>
       <c r="AY242">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ242">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA242">
         <v>2</v>
@@ -51594,10 +51594,10 @@
         <v>5</v>
       </c>
       <c r="AY243">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ243">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA243">
         <v>3</v>
@@ -51803,7 +51803,7 @@
         <v>15</v>
       </c>
       <c r="AZ244">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA244">
         <v>5</v>
@@ -52006,10 +52006,10 @@
         <v>7</v>
       </c>
       <c r="AY245">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ245">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA245">
         <v>4</v>
@@ -52212,7 +52212,7 @@
         <v>2</v>
       </c>
       <c r="AY246">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ246">
         <v>8</v>
@@ -52418,10 +52418,10 @@
         <v>10</v>
       </c>
       <c r="AY247">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ247">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA247">
         <v>7</v>
@@ -52624,7 +52624,7 @@
         <v>7</v>
       </c>
       <c r="AY248">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ248">
         <v>10</v>
@@ -52830,7 +52830,7 @@
         <v>10</v>
       </c>
       <c r="AY249">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AZ249">
         <v>14</v>
@@ -53036,10 +53036,10 @@
         <v>9</v>
       </c>
       <c r="AY250">
+        <v>14</v>
+      </c>
+      <c r="AZ250">
         <v>18</v>
-      </c>
-      <c r="AZ250">
-        <v>22</v>
       </c>
       <c r="BA250">
         <v>2</v>
@@ -53242,7 +53242,7 @@
         <v>3</v>
       </c>
       <c r="AY251">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ251">
         <v>3</v>
@@ -53448,10 +53448,10 @@
         <v>2</v>
       </c>
       <c r="AY252">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ252">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA252">
         <v>9</v>
@@ -53657,7 +53657,7 @@
         <v>17</v>
       </c>
       <c r="AZ253">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA253">
         <v>4</v>
@@ -53860,19 +53860,19 @@
         <v>4</v>
       </c>
       <c r="AY254">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ254">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA254">
         <v>1</v>
       </c>
       <c r="BB254">
+        <v>5</v>
+      </c>
+      <c r="BC254">
         <v>6</v>
-      </c>
-      <c r="BC254">
-        <v>7</v>
       </c>
       <c r="BD254">
         <v>2.43</v>
@@ -54066,10 +54066,10 @@
         <v>10</v>
       </c>
       <c r="AY255">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AZ255">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA255">
         <v>7</v>
@@ -54272,10 +54272,10 @@
         <v>4</v>
       </c>
       <c r="AY256">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ256">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA256">
         <v>3</v>
@@ -54478,10 +54478,10 @@
         <v>3</v>
       </c>
       <c r="AY257">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ257">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA257">
         <v>3</v>
@@ -54687,7 +54687,7 @@
         <v>6</v>
       </c>
       <c r="AZ258">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA258">
         <v>4</v>
@@ -54890,10 +54890,10 @@
         <v>4</v>
       </c>
       <c r="AY259">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ259">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA259">
         <v>7</v>
@@ -55096,7 +55096,7 @@
         <v>1</v>
       </c>
       <c r="AY260">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ260">
         <v>5</v>
@@ -55302,10 +55302,10 @@
         <v>4</v>
       </c>
       <c r="AY261">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="AZ261">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA261">
         <v>11</v>
@@ -55508,10 +55508,10 @@
         <v>6</v>
       </c>
       <c r="AY262">
+        <v>7</v>
+      </c>
+      <c r="AZ262">
         <v>10</v>
-      </c>
-      <c r="AZ262">
-        <v>13</v>
       </c>
       <c r="BA262">
         <v>2</v>
@@ -55714,7 +55714,7 @@
         <v>2</v>
       </c>
       <c r="AY263">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ263">
         <v>6</v>
@@ -55923,7 +55923,7 @@
         <v>10</v>
       </c>
       <c r="AZ264">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA264">
         <v>6</v>
@@ -56129,7 +56129,7 @@
         <v>9</v>
       </c>
       <c r="AZ265">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA265">
         <v>4</v>
@@ -56332,10 +56332,10 @@
         <v>4</v>
       </c>
       <c r="AY266">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ266">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA266">
         <v>4</v>
@@ -56538,10 +56538,10 @@
         <v>4</v>
       </c>
       <c r="AY267">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ267">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA267">
         <v>3</v>
@@ -56744,10 +56744,10 @@
         <v>3</v>
       </c>
       <c r="AY268">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AZ268">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA268">
         <v>9</v>
@@ -56950,10 +56950,10 @@
         <v>2</v>
       </c>
       <c r="AY269">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ269">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA269">
         <v>1</v>
@@ -57156,7 +57156,7 @@
         <v>5</v>
       </c>
       <c r="AY270">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AZ270">
         <v>9</v>
@@ -57362,10 +57362,10 @@
         <v>1</v>
       </c>
       <c r="AY271">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AZ271">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA271">
         <v>7</v>
@@ -57568,10 +57568,10 @@
         <v>13</v>
       </c>
       <c r="AY272">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ272">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BA272">
         <v>6</v>
@@ -57774,10 +57774,10 @@
         <v>11</v>
       </c>
       <c r="AY273">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ273">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA273">
         <v>3</v>
@@ -57980,7 +57980,7 @@
         <v>7</v>
       </c>
       <c r="AY274">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ274">
         <v>10</v>
@@ -58186,10 +58186,10 @@
         <v>6</v>
       </c>
       <c r="AY275">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ275">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA275">
         <v>5</v>
@@ -58392,10 +58392,10 @@
         <v>15</v>
       </c>
       <c r="AY276">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ276">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BA276">
         <v>2</v>
@@ -58598,10 +58598,10 @@
         <v>4</v>
       </c>
       <c r="AY277">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AZ277">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA277">
         <v>10</v>
@@ -58804,10 +58804,10 @@
         <v>8</v>
       </c>
       <c r="AY278">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AZ278">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA278">
         <v>9</v>
@@ -59010,10 +59010,10 @@
         <v>13</v>
       </c>
       <c r="AY279">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ279">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BA279">
         <v>3</v>
@@ -59216,10 +59216,10 @@
         <v>7</v>
       </c>
       <c r="AY280">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ280">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA280">
         <v>4</v>
@@ -59422,7 +59422,7 @@
         <v>1</v>
       </c>
       <c r="AY281">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ281">
         <v>6</v>
@@ -59628,10 +59628,10 @@
         <v>6</v>
       </c>
       <c r="AY282">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ282">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA282">
         <v>4</v>
@@ -59834,10 +59834,10 @@
         <v>8</v>
       </c>
       <c r="AY283">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ283">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA283">
         <v>6</v>
@@ -60040,10 +60040,10 @@
         <v>4</v>
       </c>
       <c r="AY284">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ284">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA284">
         <v>8</v>
@@ -60246,10 +60246,10 @@
         <v>7</v>
       </c>
       <c r="AY285">
+        <v>10</v>
+      </c>
+      <c r="AZ285">
         <v>11</v>
-      </c>
-      <c r="AZ285">
-        <v>12</v>
       </c>
       <c r="BA285">
         <v>2</v>
@@ -60452,7 +60452,7 @@
         <v>3</v>
       </c>
       <c r="AY286">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ286">
         <v>5</v>
@@ -60658,7 +60658,7 @@
         <v>1</v>
       </c>
       <c r="AY287">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ287">
         <v>3</v>
@@ -60864,10 +60864,10 @@
         <v>6</v>
       </c>
       <c r="AY288">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AZ288">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA288">
         <v>5</v>
@@ -61073,7 +61073,7 @@
         <v>15</v>
       </c>
       <c r="AZ289">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA289">
         <v>4</v>
@@ -61276,10 +61276,10 @@
         <v>5</v>
       </c>
       <c r="AY290">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ290">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA290">
         <v>4</v>
@@ -61482,10 +61482,10 @@
         <v>9</v>
       </c>
       <c r="AY291">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ291">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA291">
         <v>3</v>
@@ -61688,10 +61688,10 @@
         <v>3</v>
       </c>
       <c r="AY292">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AZ292">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA292">
         <v>6</v>
@@ -61894,10 +61894,10 @@
         <v>5</v>
       </c>
       <c r="AY293">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ293">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA293">
         <v>4</v>
@@ -62100,10 +62100,10 @@
         <v>14</v>
       </c>
       <c r="AY294">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ294">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BA294">
         <v>2</v>
@@ -62306,10 +62306,10 @@
         <v>14</v>
       </c>
       <c r="AY295">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ295">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BA295">
         <v>1</v>
@@ -62515,7 +62515,7 @@
         <v>11</v>
       </c>
       <c r="AZ296">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA296">
         <v>2</v>
@@ -62718,7 +62718,7 @@
         <v>4</v>
       </c>
       <c r="AY297">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ297">
         <v>8</v>
@@ -62924,10 +62924,10 @@
         <v>9</v>
       </c>
       <c r="AY298">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ298">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA298">
         <v>0</v>
@@ -63130,7 +63130,7 @@
         <v>2</v>
       </c>
       <c r="AY299">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ299">
         <v>4</v>
@@ -63336,10 +63336,10 @@
         <v>8</v>
       </c>
       <c r="AY300">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ300">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA300">
         <v>6</v>
@@ -63542,19 +63542,19 @@
         <v>8</v>
       </c>
       <c r="AY301">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ301">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA301">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB301">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC301">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD301">
         <v>1.54</v>
@@ -63748,7 +63748,7 @@
         <v>8</v>
       </c>
       <c r="AY302">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ302">
         <v>13</v>
@@ -63954,10 +63954,10 @@
         <v>10</v>
       </c>
       <c r="AY303">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ303">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA303">
         <v>3</v>
@@ -64160,10 +64160,10 @@
         <v>12</v>
       </c>
       <c r="AY304">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ304">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BA304">
         <v>6</v>
@@ -64366,7 +64366,7 @@
         <v>4</v>
       </c>
       <c r="AY305">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ305">
         <v>4</v>
@@ -64572,10 +64572,10 @@
         <v>18</v>
       </c>
       <c r="AY306">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ306">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BA306">
         <v>2</v>
@@ -64781,7 +64781,7 @@
         <v>12</v>
       </c>
       <c r="AZ307">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA307">
         <v>4</v>
